--- a/agents/compassus-capacity-pm/rfp/Compassus-Vendor-Questionnaire-MASTER.xlsx
+++ b/agents/compassus-capacity-pm/rfp/Compassus-Vendor-Questionnaire-MASTER.xlsx
@@ -9,15 +9,17 @@
   <sheets>
     <sheet name="Instructions" sheetId="1" state="visible" r:id="rId1"/>
     <sheet name="Questionnaire" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="Lists" sheetId="3" state="hidden" r:id="rId3"/>
-    <sheet name="Coverage — Expanded" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet name="Additional Questions" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet name="Vetting — For Leaders" sheetId="6" state="visible" r:id="rId6"/>
-    <sheet name="Meta" sheetId="7" state="hidden" r:id="rId7"/>
+    <sheet name="Overview" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="Lists" sheetId="4" state="hidden" r:id="rId4"/>
+    <sheet name="Coverage — Expanded" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet name="Additional Questions" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet name="Vetting — For Leaders" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet name="Meta" sheetId="8" state="hidden" r:id="rId8"/>
   </sheets>
   <definedNames>
     <definedName name="StatusList">Lists!$A$1:$A$4</definedName>
-    <definedName name="_xlnm.Print_Titles" localSheetId="1">'Questionnaire'!$1:$4</definedName>
+    <definedName name="_xlnm.Print_Titles" localSheetId="1">'Questionnaire'!$1:$6</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="2">'Overview'!$A$1:$R$228</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -26,7 +28,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="10">
+  <fonts count="24">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -87,8 +89,87 @@
       <color rgb="FF1F3B57"/>
       <sz val="10.5"/>
     </font>
+    <font>
+      <name val="Arial"/>
+      <b val="1"/>
+      <color rgb="FF7C8781"/>
+      <sz val="10.1"/>
+    </font>
+    <font>
+      <name val="Georgia"/>
+      <b val="1"/>
+      <color rgb="FF171E1A"/>
+      <sz val="27"/>
+    </font>
+    <font>
+      <name val="Arial"/>
+      <color rgb="FF4E5A54"/>
+      <sz val="12.2"/>
+    </font>
+    <font>
+      <name val="Arial"/>
+      <b val="1"/>
+      <color rgb="FF2C6A55"/>
+      <sz val="10.1"/>
+    </font>
+    <font>
+      <name val="Georgia"/>
+      <b val="1"/>
+      <color rgb="FF171E1A"/>
+      <sz val="19.8"/>
+    </font>
+    <font>
+      <name val="Arial"/>
+      <color rgb="FF4E5A54"/>
+      <sz val="11.5"/>
+    </font>
+    <font>
+      <name val="Arial"/>
+      <b val="1"/>
+      <color rgb="FF171E1A"/>
+      <sz val="12.9"/>
+    </font>
+    <font>
+      <name val="Arial"/>
+      <i val="1"/>
+      <color rgb="FF7C8781"/>
+      <sz val="10.8"/>
+    </font>
+    <font>
+      <name val="Arial"/>
+      <color rgb="FF2C6A55"/>
+      <sz val="11.5"/>
+    </font>
+    <font>
+      <name val="Arial"/>
+      <b val="1"/>
+      <color rgb="FF3A5C86"/>
+      <sz val="10.1"/>
+    </font>
+    <font>
+      <name val="Arial"/>
+      <color rgb="FF3A5C86"/>
+      <sz val="11.5"/>
+    </font>
+    <font>
+      <name val="Arial"/>
+      <b val="1"/>
+      <color rgb="FF8C5A2E"/>
+      <sz val="10.1"/>
+    </font>
+    <font>
+      <name val="Arial"/>
+      <color rgb="FF8C5A2E"/>
+      <sz val="11.5"/>
+    </font>
+    <font>
+      <name val="Arial"/>
+      <i val="1"/>
+      <color rgb="FF4E5A54"/>
+      <sz val="12.2"/>
+    </font>
   </fonts>
-  <fills count="5">
+  <fills count="10">
     <fill>
       <patternFill/>
     </fill>
@@ -110,8 +191,33 @@
         <fgColor rgb="FFEEF2F6"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFBFBF8"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE8E6DB"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF2C6A55"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF3A5C86"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF8C5A2E"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="3">
+  <borders count="19">
     <border>
       <left/>
       <right/>
@@ -138,11 +244,155 @@
         <color rgb="FFD8DEE6"/>
       </bottom>
     </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="thin">
+        <color rgb="FFD8DAD2"/>
+      </bottom>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="dashed">
+        <color rgb="FFC9C6B6"/>
+      </top>
+      <bottom/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="dashed">
+        <color rgb="FFC9C6B6"/>
+      </bottom>
+    </border>
+    <border>
+      <left style="dashed">
+        <color rgb="FFC9C6B6"/>
+      </left>
+      <right/>
+      <top style="dashed">
+        <color rgb="FFC9C6B6"/>
+      </top>
+      <bottom/>
+    </border>
+    <border>
+      <left/>
+      <right style="dashed">
+        <color rgb="FFC9C6B6"/>
+      </right>
+      <top style="dashed">
+        <color rgb="FFC9C6B6"/>
+      </top>
+      <bottom/>
+    </border>
+    <border>
+      <left style="dashed">
+        <color rgb="FFC9C6B6"/>
+      </left>
+      <right/>
+      <top/>
+      <bottom/>
+    </border>
+    <border>
+      <left/>
+      <right style="dashed">
+        <color rgb="FFC9C6B6"/>
+      </right>
+      <top/>
+      <bottom/>
+    </border>
+    <border>
+      <left style="dashed">
+        <color rgb="FFC9C6B6"/>
+      </left>
+      <right/>
+      <top/>
+      <bottom style="dashed">
+        <color rgb="FFC9C6B6"/>
+      </bottom>
+    </border>
+    <border>
+      <left/>
+      <right style="dashed">
+        <color rgb="FFC9C6B6"/>
+      </right>
+      <top/>
+      <bottom style="dashed">
+        <color rgb="FFC9C6B6"/>
+      </bottom>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color rgb="FFD8DAD2"/>
+      </top>
+      <bottom/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FFD8DAD2"/>
+      </left>
+      <right/>
+      <top style="thin">
+        <color rgb="FFD8DAD2"/>
+      </top>
+      <bottom/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color rgb="FFD8DAD2"/>
+      </right>
+      <top style="thin">
+        <color rgb="FFD8DAD2"/>
+      </top>
+      <bottom/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FFD8DAD2"/>
+      </left>
+      <right/>
+      <top/>
+      <bottom/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color rgb="FFD8DAD2"/>
+      </right>
+      <top/>
+      <bottom/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FFD8DAD2"/>
+      </left>
+      <right/>
+      <top/>
+      <bottom style="thin">
+        <color rgb="FFD8DAD2"/>
+      </bottom>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color rgb="FFD8DAD2"/>
+      </right>
+      <top/>
+      <bottom style="thin">
+        <color rgb="FFD8DAD2"/>
+      </bottom>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="20">
+  <cellXfs count="57">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -152,32 +402,97 @@
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="1" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1" indent="1"/>
       <protection locked="0" hidden="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="right"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="2" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="1" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="top" wrapText="1" indent="1"/>
-      <protection locked="0" hidden="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="9" fillId="4" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="10" fillId="5" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="5" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="5" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="3" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="6" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="10" fillId="6" borderId="4" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="4" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="7" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="8" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="9" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="13" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="12" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="14" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="8" borderId="13" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="8" borderId="12" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="8" borderId="14" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="9" borderId="13" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="9" borderId="12" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="9" borderId="14" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="15" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="16" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="13" fillId="5" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="5" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="5" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="5" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="5" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="5" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="5" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="5" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="5" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="5" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="17" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="18" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="10" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="5" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="11" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="23" fillId="5" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="1" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1" indent="1"/>
       <protection locked="0" hidden="0"/>
@@ -678,7 +993,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="B1:D66"/>
+  <dimension ref="B1:D68"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="2.5" customWidth="1" min="1" max="1"/>
@@ -688,574 +1003,849 @@
     <col width="2.5" customWidth="1" min="5" max="5"/>
   </cols>
   <sheetData>
-    <row r="1">
+    <row r="1" ht="15" customHeight="1">
       <c r="B1" s="1" t="inlineStr">
         <is>
           <t>Compassus Home Health  ·  Capacity &amp; Scheduling Platform</t>
         </is>
       </c>
     </row>
-    <row r="2" ht="22" customHeight="1">
+    <row r="2" ht="24" customHeight="1">
       <c r="B2" s="2" t="inlineStr">
         <is>
           <t>Vendor Questionnaire</t>
         </is>
       </c>
     </row>
-    <row r="3" ht="18" customHeight="1">
-      <c r="B3" s="7" t="inlineStr">
+    <row r="3" ht="8" customHeight="1"/>
+    <row r="4" ht="20" customHeight="1">
+      <c r="C4" s="7" t="inlineStr">
         <is>
           <t>Vendor</t>
         </is>
       </c>
-      <c r="C3" s="8" t="n"/>
-      <c r="D3" s="9" t="inlineStr">
+      <c r="D4" s="8" t="n"/>
+    </row>
+    <row r="5" ht="20" customHeight="1">
+      <c r="C5" s="7" t="inlineStr">
         <is>
           <t>Completed by / date</t>
         </is>
       </c>
-    </row>
-    <row r="4" ht="6" customHeight="1"/>
-    <row r="5" ht="22" customHeight="1">
-      <c r="B5" s="10" t="inlineStr">
+      <c r="D5" s="8" t="n"/>
+    </row>
+    <row r="6" ht="8" customHeight="1"/>
+    <row r="7" ht="22" customHeight="1">
+      <c r="B7" s="9" t="inlineStr">
         <is>
           <t>A.   COMPANY AND PRODUCT</t>
         </is>
       </c>
-      <c r="C5" s="11" t="n"/>
-      <c r="D5" s="11" t="n"/>
-    </row>
-    <row r="6" ht="15" customHeight="1">
-      <c r="B6" s="12" t="inlineStr">
+    </row>
+    <row r="8" ht="15" customHeight="1">
+      <c r="B8" s="10" t="inlineStr">
         <is>
           <t>#</t>
         </is>
       </c>
-      <c r="C6" s="12" t="inlineStr">
+      <c r="C8" s="10" t="inlineStr">
         <is>
           <t>QUESTION</t>
         </is>
       </c>
-      <c r="D6" s="12" t="inlineStr">
+      <c r="D8" s="10" t="inlineStr">
         <is>
           <t>YOUR ANSWER</t>
         </is>
       </c>
     </row>
-    <row r="7" ht="253" customHeight="1">
-      <c r="B7" s="13" t="inlineStr">
+    <row r="9" ht="253" customHeight="1">
+      <c r="B9" s="11" t="inlineStr">
         <is>
           <t>A1</t>
         </is>
       </c>
-      <c r="C7" s="4" t="inlineStr">
-        <is>
-          <t>Home Care Home Base integration
-Have you built an integration with Home Care Home Base (HCHB)? Please cover: whether it is live in production with customers today and since when; what it reads from HCHB and what it writes back; how it is implemented (published API, HL7/FHIR, flat file, database, screen automation, other); and how you handle sync latency when data changes on both sides. If you have not built it, tell us your path, what it would need from us, and your timeline.</t>
-        </is>
-      </c>
-      <c r="D7" s="14" t="n"/>
-    </row>
-    <row r="8" ht="5" customHeight="1"/>
-    <row r="9" ht="195" customHeight="1">
-      <c r="B9" s="13" t="inlineStr">
+      <c r="C9" s="12" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <b val="1"/>
+              <color rgb="001F2A37"/>
+              <sz val="11"/>
+            </rPr>
+            <t xml:space="preserve">Home Care Home Base integration
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <color rgb="001F2A37"/>
+              <sz val="11"/>
+            </rPr>
+            <t>Have you built an integration with Home Care Home Base (HCHB)? Please cover: whether it is live in production with customers today and since when; what it reads from HCHB and what it writes back; how it is implemented (published API, HL7/FHIR, flat file, database, screen automation, other); and how you handle sync latency when data changes on both sides. If you have not built it, tell us your path, what it would need from us, and your timeline.</t>
+          </r>
+        </is>
+      </c>
+      <c r="D9" s="8" t="n"/>
+    </row>
+    <row r="10" ht="5" customHeight="1"/>
+    <row r="11" ht="195" customHeight="1">
+      <c r="B11" s="11" t="inlineStr">
         <is>
           <t>A2</t>
         </is>
       </c>
-      <c r="C9" s="4" t="inlineStr">
-        <is>
-          <t>Where your product is today
-Give us a picture of maturity. What is in production with customers today, what is in active development and when it lands, and what is on the roadmap but not yet started?</t>
-        </is>
-      </c>
-      <c r="D9" s="14" t="n"/>
-    </row>
-    <row r="10" ht="5" customHeight="1"/>
-    <row r="11" ht="151" customHeight="1">
-      <c r="B11" s="13" t="inlineStr">
+      <c r="C11" s="12" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <b val="1"/>
+              <color rgb="001F2A37"/>
+              <sz val="11"/>
+            </rPr>
+            <t xml:space="preserve">Where your product is today
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <color rgb="001F2A37"/>
+              <sz val="11"/>
+            </rPr>
+            <t>Give us a picture of maturity. What is in production with customers today, what is in active development and when it lands, and what is on the roadmap but not yet started?</t>
+          </r>
+        </is>
+      </c>
+      <c r="D11" s="8" t="n"/>
+    </row>
+    <row r="12" ht="5" customHeight="1"/>
+    <row r="13" ht="151" customHeight="1">
+      <c r="B13" s="11" t="inlineStr">
         <is>
           <t>A3</t>
         </is>
       </c>
-      <c r="C11" s="4" t="inlineStr">
-        <is>
-          <t>Customers and references
-How many organizations run your product in production today, and how many of those are Medicare-certified home health? Describe your largest deployment by census, branches and clinicians. Please provide two or three references we may contact.</t>
-        </is>
-      </c>
-      <c r="D11" s="14" t="n"/>
-    </row>
-    <row r="12" ht="5" customHeight="1"/>
-    <row r="13" ht="122" customHeight="1">
-      <c r="B13" s="13" t="inlineStr">
+      <c r="C13" s="12" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <b val="1"/>
+              <color rgb="001F2A37"/>
+              <sz val="11"/>
+            </rPr>
+            <t xml:space="preserve">Customers and references
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <color rgb="001F2A37"/>
+              <sz val="11"/>
+            </rPr>
+            <t>How many organizations run your product in production today, and how many of those are Medicare-certified home health? Describe your largest deployment by census, branches and clinicians. Please provide two or three references we may contact.</t>
+          </r>
+        </is>
+      </c>
+      <c r="D13" s="8" t="n"/>
+    </row>
+    <row r="14" ht="5" customHeight="1"/>
+    <row r="15" ht="122" customHeight="1">
+      <c r="B15" s="11" t="inlineStr">
         <is>
           <t>A4</t>
         </is>
       </c>
-      <c r="C13" s="4" t="inlineStr">
-        <is>
-          <t>Market focus
-What share of your business is Medicare-certified home health, versus hospice, private duty or home care, or other verticals? How does PDGM shape your product, if at all?</t>
-        </is>
-      </c>
-      <c r="D13" s="14" t="n"/>
-    </row>
-    <row r="14" ht="5" customHeight="1"/>
-    <row r="16" ht="22" customHeight="1">
-      <c r="B16" s="10" t="inlineStr">
+      <c r="C15" s="12" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <b val="1"/>
+              <color rgb="001F2A37"/>
+              <sz val="11"/>
+            </rPr>
+            <t xml:space="preserve">Market focus
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <color rgb="001F2A37"/>
+              <sz val="11"/>
+            </rPr>
+            <t>What share of your business is Medicare-certified home health, versus hospice, private duty or home care, or other verticals? How does PDGM shape your product, if at all?</t>
+          </r>
+        </is>
+      </c>
+      <c r="D15" s="8" t="n"/>
+    </row>
+    <row r="16" ht="5" customHeight="1"/>
+    <row r="18" ht="22" customHeight="1">
+      <c r="B18" s="9" t="inlineStr">
         <is>
           <t>B.   COVERAGE SELF-ASSESSMENT</t>
         </is>
       </c>
-      <c r="C16" s="11" t="n"/>
-      <c r="D16" s="11" t="n"/>
-    </row>
-    <row r="17" ht="28" customHeight="1">
-      <c r="B17" s="15" t="inlineStr">
+    </row>
+    <row r="19" ht="28" customHeight="1">
+      <c r="B19" s="13" t="inlineStr">
         <is>
           <t>Mark where you stand on each area, then add anything you want us to understand in the notes column.</t>
         </is>
       </c>
     </row>
-    <row r="18">
-      <c r="B18" s="12" t="inlineStr">
+    <row r="20">
+      <c r="B20" s="10" t="inlineStr">
         <is>
           <t>#</t>
         </is>
       </c>
-      <c r="C18" s="12" t="inlineStr">
+      <c r="C20" s="10" t="inlineStr">
         <is>
           <t>AREA</t>
         </is>
       </c>
-      <c r="D18" s="12" t="inlineStr">
+      <c r="D20" s="10" t="inlineStr">
         <is>
           <t>STATUS  →  then notes</t>
         </is>
       </c>
     </row>
-    <row r="19" ht="18" customHeight="1">
-      <c r="B19" s="16" t="inlineStr">
+    <row r="21" ht="18" customHeight="1">
+      <c r="B21" s="14" t="inlineStr">
         <is>
           <t>Capacity Management</t>
         </is>
       </c>
-      <c r="C19" s="17" t="n"/>
-      <c r="D19" s="17" t="n"/>
-    </row>
-    <row r="20" ht="30" customHeight="1">
-      <c r="B20" s="13" t="n">
+      <c r="C21" s="15" t="n"/>
+      <c r="D21" s="15" t="n"/>
+    </row>
+    <row r="22" ht="30" customHeight="1">
+      <c r="B22" s="11" t="n">
         <v>1</v>
       </c>
-      <c r="C20" s="4" t="inlineStr">
+      <c r="C22" s="4" t="inlineStr">
         <is>
           <t>Workforce supply — Roster, disciplines, roles, competencies, ramp, float pool</t>
         </is>
       </c>
-      <c r="D20" s="14" t="n"/>
-    </row>
-    <row r="21" ht="30" customHeight="1">
-      <c r="B21" s="13" t="n">
+      <c r="D22" s="8" t="n"/>
+    </row>
+    <row r="23" ht="30" customHeight="1">
+      <c r="B23" s="11" t="n">
         <v>2</v>
       </c>
-      <c r="C21" s="4" t="inlineStr">
+      <c r="C23" s="4" t="inlineStr">
         <is>
           <t>Availability &amp; reach — Availability and time off, territory, drive-time reachability</t>
         </is>
       </c>
-      <c r="D21" s="14" t="n"/>
-    </row>
-    <row r="22" ht="30" customHeight="1">
-      <c r="B22" s="13" t="n">
+      <c r="D23" s="8" t="n"/>
+    </row>
+    <row r="24" ht="30" customHeight="1">
+      <c r="B24" s="11" t="n">
         <v>3</v>
       </c>
-      <c r="C22" s="4" t="inlineStr">
+      <c r="C24" s="4" t="inlineStr">
         <is>
           <t>The capacity math — Visit weighting, targets and ceilings, committed load vs. open room</t>
         </is>
       </c>
-      <c r="D22" s="14" t="n"/>
-    </row>
-    <row r="23" ht="18" customHeight="1">
-      <c r="B23" s="16" t="inlineStr">
+      <c r="D24" s="8" t="n"/>
+    </row>
+    <row r="25" ht="18" customHeight="1">
+      <c r="B25" s="14" t="inlineStr">
         <is>
           <t>Scheduling Engine</t>
         </is>
       </c>
-      <c r="C23" s="17" t="n"/>
-      <c r="D23" s="17" t="n"/>
-    </row>
-    <row r="24" ht="30" customHeight="1">
-      <c r="B24" s="13" t="n">
+      <c r="C25" s="15" t="n"/>
+      <c r="D25" s="15" t="n"/>
+    </row>
+    <row r="26" ht="30" customHeight="1">
+      <c r="B26" s="11" t="n">
         <v>4</v>
       </c>
-      <c r="C24" s="4" t="inlineStr">
+      <c r="C26" s="4" t="inlineStr">
         <is>
           <t>Demand — Ingesting ordered visits, authorization, readiness, compliance windows</t>
         </is>
       </c>
-      <c r="D24" s="14" t="n"/>
-    </row>
-    <row r="25" ht="30" customHeight="1">
-      <c r="B25" s="13" t="n">
+      <c r="D26" s="8" t="n"/>
+    </row>
+    <row r="27" ht="30" customHeight="1">
+      <c r="B27" s="11" t="n">
         <v>5</v>
       </c>
-      <c r="C25" s="4" t="inlineStr">
+      <c r="C27" s="4" t="inlineStr">
         <is>
           <t>Matching — Discipline and competency fit, clinician and patient needs, clinical timing, continuity</t>
         </is>
       </c>
-      <c r="D25" s="14" t="n"/>
-    </row>
-    <row r="26" ht="30" customHeight="1">
-      <c r="B26" s="13" t="n">
+      <c r="D27" s="8" t="n"/>
+    </row>
+    <row r="28" ht="30" customHeight="1">
+      <c r="B28" s="11" t="n">
         <v>6</v>
       </c>
-      <c r="C26" s="4" t="inlineStr">
+      <c r="C28" s="4" t="inlineStr">
         <is>
           <t>Routing &amp; the week — Routing, sequencing, front-loading, week balancing</t>
         </is>
       </c>
-      <c r="D26" s="14" t="n"/>
-    </row>
-    <row r="27" ht="30" customHeight="1">
-      <c r="B27" s="13" t="n">
+      <c r="D28" s="8" t="n"/>
+    </row>
+    <row r="29" ht="30" customHeight="1">
+      <c r="B29" s="11" t="n">
         <v>7</v>
       </c>
-      <c r="C27" s="4" t="inlineStr">
+      <c r="C29" s="4" t="inlineStr">
         <is>
           <t>Exceptions — Missed visits, reassignment, coverage, rebooking</t>
         </is>
       </c>
-      <c r="D27" s="14" t="n"/>
-    </row>
-    <row r="28" ht="18" customHeight="1">
-      <c r="B28" s="16" t="inlineStr">
+      <c r="D29" s="8" t="n"/>
+    </row>
+    <row r="30" ht="18" customHeight="1">
+      <c r="B30" s="14" t="inlineStr">
         <is>
           <t>Engagement</t>
         </is>
       </c>
-      <c r="C28" s="17" t="n"/>
-      <c r="D28" s="17" t="n"/>
-    </row>
-    <row r="29" ht="30" customHeight="1">
-      <c r="B29" s="13" t="n">
+      <c r="C30" s="15" t="n"/>
+      <c r="D30" s="15" t="n"/>
+    </row>
+    <row r="31" ht="30" customHeight="1">
+      <c r="B31" s="11" t="n">
         <v>8</v>
       </c>
-      <c r="C29" s="4" t="inlineStr">
+      <c r="C31" s="4" t="inlineStr">
         <is>
           <t>Before the visit — Welcome call, availability capture, reminders, confirmation, en-route</t>
         </is>
       </c>
-      <c r="D29" s="14" t="n"/>
-    </row>
-    <row r="30" ht="30" customHeight="1">
-      <c r="B30" s="13" t="n">
+      <c r="D31" s="8" t="n"/>
+    </row>
+    <row r="32" ht="30" customHeight="1">
+      <c r="B32" s="11" t="n">
         <v>9</v>
       </c>
-      <c r="C30" s="4" t="inlineStr">
+      <c r="C32" s="4" t="inlineStr">
         <is>
           <t>When plans change — Reschedule, coverage coordination and clinician outreach, urgent same-day needs</t>
         </is>
       </c>
-      <c r="D30" s="14" t="n"/>
-    </row>
-    <row r="31" ht="30" customHeight="1">
-      <c r="B31" s="13" t="n">
+      <c r="D32" s="8" t="n"/>
+    </row>
+    <row r="33" ht="30" customHeight="1">
+      <c r="B33" s="11" t="n">
         <v>10</v>
       </c>
-      <c r="C31" s="4" t="inlineStr">
+      <c r="C33" s="4" t="inlineStr">
         <is>
           <t>Across the care team — Multi-discipline coordination, clinician and office updates</t>
         </is>
       </c>
-      <c r="D31" s="14" t="n"/>
-    </row>
-    <row r="33" ht="22" customHeight="1">
-      <c r="B33" s="10" t="inlineStr">
+      <c r="D33" s="8" t="n"/>
+    </row>
+    <row r="35" ht="22" customHeight="1">
+      <c r="B35" s="9" t="inlineStr">
         <is>
           <t>C.   HOW YOUR PRODUCT WORKS</t>
         </is>
       </c>
-      <c r="C33" s="11" t="n"/>
-      <c r="D33" s="11" t="n"/>
-    </row>
-    <row r="34" ht="15" customHeight="1">
-      <c r="B34" s="12" t="inlineStr">
+    </row>
+    <row r="36" ht="15" customHeight="1">
+      <c r="B36" s="10" t="inlineStr">
         <is>
           <t>#</t>
         </is>
       </c>
-      <c r="C34" s="12" t="inlineStr">
+      <c r="C36" s="10" t="inlineStr">
         <is>
           <t>QUESTION</t>
         </is>
       </c>
-      <c r="D34" s="12" t="inlineStr">
+      <c r="D36" s="10" t="inlineStr">
         <is>
           <t>YOUR ANSWER</t>
         </is>
       </c>
     </row>
-    <row r="35" ht="195" customHeight="1">
-      <c r="B35" s="13" t="inlineStr">
+    <row r="37" ht="195" customHeight="1">
+      <c r="B37" s="11" t="inlineStr">
         <is>
           <t>C1</t>
         </is>
       </c>
-      <c r="C35" s="4" t="inlineStr">
-        <is>
-          <t>Capacity
-How does your product determine how much capacity a branch has and how much is left? Cover the unit you measure in and where the inputs come from. Add anything else you think we should understand about how you approach this.</t>
-        </is>
-      </c>
-      <c r="D35" s="14" t="n"/>
-    </row>
-    <row r="36" ht="5" customHeight="1"/>
-    <row r="37" ht="137" customHeight="1">
-      <c r="B37" s="13" t="inlineStr">
+      <c r="C37" s="12" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <b val="1"/>
+              <color rgb="001F2A37"/>
+              <sz val="11"/>
+            </rPr>
+            <t xml:space="preserve">Capacity
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <color rgb="001F2A37"/>
+              <sz val="11"/>
+            </rPr>
+            <t>How does your product determine how much capacity a branch has and how much is left? Cover the unit you measure in and where the inputs come from. Add anything else you think we should understand about how you approach this.</t>
+          </r>
+        </is>
+      </c>
+      <c r="D37" s="8" t="n"/>
+    </row>
+    <row r="38" ht="5" customHeight="1"/>
+    <row r="39" ht="137" customHeight="1">
+      <c r="B39" s="11" t="inlineStr">
         <is>
           <t>C2</t>
         </is>
       </c>
-      <c r="C37" s="4" t="inlineStr">
-        <is>
-          <t>Capacity in use
-A branch leader is deciding whether to accept a referral today. What can your product tell them?</t>
-        </is>
-      </c>
-      <c r="D37" s="14" t="n"/>
-    </row>
-    <row r="38" ht="5" customHeight="1"/>
-    <row r="39" ht="195" customHeight="1">
-      <c r="B39" s="13" t="inlineStr">
+      <c r="C39" s="12" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <b val="1"/>
+              <color rgb="001F2A37"/>
+              <sz val="11"/>
+            </rPr>
+            <t xml:space="preserve">Capacity in use
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <color rgb="001F2A37"/>
+              <sz val="11"/>
+            </rPr>
+            <t>A branch leader is deciding whether to accept a referral today. What can your product tell them?</t>
+          </r>
+        </is>
+      </c>
+      <c r="D39" s="8" t="n"/>
+    </row>
+    <row r="40" ht="5" customHeight="1"/>
+    <row r="41" ht="195" customHeight="1">
+      <c r="B41" s="11" t="inlineStr">
         <is>
           <t>C3</t>
         </is>
       </c>
-      <c r="C39" s="4" t="inlineStr">
-        <is>
-          <t>Assignment
-Walk us through how your product decides which clinician should take a given visit — what it considers, how it weighs those factors, and what a customer can configure.</t>
-        </is>
-      </c>
-      <c r="D39" s="14" t="n"/>
-    </row>
-    <row r="40" ht="5" customHeight="1"/>
-    <row r="41" ht="180" customHeight="1">
-      <c r="B41" s="13" t="inlineStr">
-        <is>
-          <t>C4</t>
-        </is>
-      </c>
-      <c r="C41" s="4" t="inlineStr">
-        <is>
-          <t>Readiness
-What does your product do with a visit that has been ordered but is not yet schedulable — for example because authorization is still pending, consent from a power of attorney is outstanding, or the clinician it will be assigned to has not yet been determined?</t>
-        </is>
-      </c>
-      <c r="D41" s="14" t="n"/>
+      <c r="C41" s="12" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <b val="1"/>
+              <color rgb="001F2A37"/>
+              <sz val="11"/>
+            </rPr>
+            <t xml:space="preserve">Assignment
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <color rgb="001F2A37"/>
+              <sz val="11"/>
+            </rPr>
+            <t>Walk us through how your product decides which clinician should take a given visit — what it considers, how it weighs those factors, and what a customer can configure.</t>
+          </r>
+        </is>
+      </c>
+      <c r="D41" s="8" t="n"/>
     </row>
     <row r="42" ht="5" customHeight="1"/>
     <row r="43" ht="180" customHeight="1">
-      <c r="B43" s="13" t="inlineStr">
-        <is>
-          <t>C5</t>
-        </is>
-      </c>
-      <c r="C43" s="4" t="inlineStr">
-        <is>
-          <t>The week
-How does your product plan across a week or an episode rather than a single day — and what does it do when that plan breaks mid-week?</t>
-        </is>
-      </c>
-      <c r="D43" s="14" t="n"/>
+      <c r="B43" s="11" t="inlineStr">
+        <is>
+          <t>C4</t>
+        </is>
+      </c>
+      <c r="C43" s="12" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <b val="1"/>
+              <color rgb="001F2A37"/>
+              <sz val="11"/>
+            </rPr>
+            <t xml:space="preserve">Readiness
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <color rgb="001F2A37"/>
+              <sz val="11"/>
+            </rPr>
+            <t>What does your product do with a visit that has been ordered but is not yet schedulable — for example because authorization is still pending, consent from a power of attorney is outstanding, or the clinician it will be assigned to has not yet been determined?</t>
+          </r>
+        </is>
+      </c>
+      <c r="D43" s="8" t="n"/>
     </row>
     <row r="44" ht="5" customHeight="1"/>
     <row r="45" ht="180" customHeight="1">
-      <c r="B45" s="13" t="inlineStr">
+      <c r="B45" s="11" t="inlineStr">
+        <is>
+          <t>C5</t>
+        </is>
+      </c>
+      <c r="C45" s="12" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <b val="1"/>
+              <color rgb="001F2A37"/>
+              <sz val="11"/>
+            </rPr>
+            <t xml:space="preserve">The week
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <color rgb="001F2A37"/>
+              <sz val="11"/>
+            </rPr>
+            <t>How does your product plan across a week or an episode rather than a single day — and what does it do when that plan breaks mid-week?</t>
+          </r>
+        </is>
+      </c>
+      <c r="D45" s="8" t="n"/>
+    </row>
+    <row r="46" ht="5" customHeight="1"/>
+    <row r="47" ht="180" customHeight="1">
+      <c r="B47" s="11" t="inlineStr">
         <is>
           <t>C6</t>
         </is>
       </c>
-      <c r="C45" s="4" t="inlineStr">
-        <is>
-          <t>Communication
-Describe how your product communicates with patients, with clinicians, and with the office. Which of those are automated today, and which still need a person?</t>
-        </is>
-      </c>
-      <c r="D45" s="14" t="n"/>
-    </row>
-    <row r="46" ht="5" customHeight="1"/>
-    <row r="48" ht="22" customHeight="1">
-      <c r="B48" s="10" t="inlineStr">
+      <c r="C47" s="12" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <b val="1"/>
+              <color rgb="001F2A37"/>
+              <sz val="11"/>
+            </rPr>
+            <t xml:space="preserve">Communication
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <color rgb="001F2A37"/>
+              <sz val="11"/>
+            </rPr>
+            <t>Describe how your product communicates with patients, with clinicians, and with the office. Which of those are automated today, and which still need a person?</t>
+          </r>
+        </is>
+      </c>
+      <c r="D47" s="8" t="n"/>
+    </row>
+    <row r="48" ht="5" customHeight="1"/>
+    <row r="50" ht="22" customHeight="1">
+      <c r="B50" s="9" t="inlineStr">
         <is>
           <t>D.   THE CLINICIAN'S PLACE IN THE MODEL</t>
         </is>
       </c>
-      <c r="C48" s="11" t="n"/>
-      <c r="D48" s="11" t="n"/>
-    </row>
-    <row r="49" ht="64" customHeight="1">
-      <c r="B49" s="15" t="inlineStr">
+    </row>
+    <row r="51" ht="64" customHeight="1">
+      <c r="B51" s="13" t="inlineStr">
         <is>
           <t>Scheduling in home health is operationally critical and personally consequential. Many clinicians come to home health for the control it gives them over their own day and week, and any change to how visits get assigned lands on people who feel strongly about it. In our experience adoption, more than algorithm quality, decides whether tools like this succeed. These questions are about how your product treats the clinician.</t>
         </is>
       </c>
     </row>
-    <row r="50" ht="15" customHeight="1">
-      <c r="B50" s="12" t="inlineStr">
+    <row r="52" ht="15" customHeight="1">
+      <c r="B52" s="10" t="inlineStr">
         <is>
           <t>#</t>
         </is>
       </c>
-      <c r="C50" s="12" t="inlineStr">
+      <c r="C52" s="10" t="inlineStr">
         <is>
           <t>QUESTION</t>
         </is>
       </c>
-      <c r="D50" s="12" t="inlineStr">
+      <c r="D52" s="10" t="inlineStr">
         <is>
           <t>YOUR ANSWER</t>
         </is>
       </c>
     </row>
-    <row r="51" ht="195" customHeight="1">
-      <c r="B51" s="13" t="inlineStr">
+    <row r="53" ht="195" customHeight="1">
+      <c r="B53" s="11" t="inlineStr">
         <is>
           <t>D1</t>
         </is>
       </c>
-      <c r="C51" s="4" t="inlineStr">
-        <is>
-          <t>What the clinician decides
-Which scheduling decisions does the clinician make in your product, and which are made for them? Be specific about what they can change, what requires approval, and what they cannot change at all.</t>
-        </is>
-      </c>
-      <c r="D51" s="14" t="n"/>
-    </row>
-    <row r="52" ht="5" customHeight="1"/>
-    <row r="53" ht="151" customHeight="1">
-      <c r="B53" s="13" t="inlineStr">
+      <c r="C53" s="12" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <b val="1"/>
+              <color rgb="001F2A37"/>
+              <sz val="11"/>
+            </rPr>
+            <t xml:space="preserve">What the clinician decides
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <color rgb="001F2A37"/>
+              <sz val="11"/>
+            </rPr>
+            <t>Which scheduling decisions does the clinician make in your product, and which are made for them? Be specific about what they can change, what requires approval, and what they cannot change at all.</t>
+          </r>
+        </is>
+      </c>
+      <c r="D53" s="8" t="n"/>
+    </row>
+    <row r="54" ht="5" customHeight="1"/>
+    <row r="55" ht="151" customHeight="1">
+      <c r="B55" s="11" t="inlineStr">
         <is>
           <t>D2</t>
         </is>
       </c>
-      <c r="C53" s="4" t="inlineStr">
-        <is>
-          <t>Disagreement
-When your product proposes an assignment and the clinician disagrees, what happens? Does anything change as a result — for that clinician, or in the model?</t>
-        </is>
-      </c>
-      <c r="D53" s="14" t="n"/>
-    </row>
-    <row r="54" ht="5" customHeight="1"/>
-    <row r="55" ht="195" customHeight="1">
-      <c r="B55" s="13" t="inlineStr">
+      <c r="C55" s="12" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <b val="1"/>
+              <color rgb="001F2A37"/>
+              <sz val="11"/>
+            </rPr>
+            <t xml:space="preserve">Disagreement
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <color rgb="001F2A37"/>
+              <sz val="11"/>
+            </rPr>
+            <t>When your product proposes an assignment and the clinician disagrees, what happens? Does anything change as a result — for that clinician, or in the model?</t>
+          </r>
+        </is>
+      </c>
+      <c r="D55" s="8" t="n"/>
+    </row>
+    <row r="56" ht="5" customHeight="1"/>
+    <row r="57" ht="195" customHeight="1">
+      <c r="B57" s="11" t="inlineStr">
         <is>
           <t>D3</t>
         </is>
       </c>
-      <c r="C55" s="4" t="inlineStr">
-        <is>
-          <t>Resistance
-Describe a deployment where clinicians resisted your product. What did you learn, and what did you change — in the product, or in how you rolled it out?</t>
-        </is>
-      </c>
-      <c r="D55" s="14" t="n"/>
-    </row>
-    <row r="56" ht="5" customHeight="1"/>
-    <row r="57" ht="151" customHeight="1">
-      <c r="B57" s="13" t="inlineStr">
+      <c r="C57" s="12" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <b val="1"/>
+              <color rgb="001F2A37"/>
+              <sz val="11"/>
+            </rPr>
+            <t xml:space="preserve">Resistance
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <color rgb="001F2A37"/>
+              <sz val="11"/>
+            </rPr>
+            <t>Describe a deployment where clinicians resisted your product. What did you learn, and what did you change — in the product, or in how you rolled it out?</t>
+          </r>
+        </is>
+      </c>
+      <c r="D57" s="8" t="n"/>
+    </row>
+    <row r="58" ht="5" customHeight="1"/>
+    <row r="59" ht="151" customHeight="1">
+      <c r="B59" s="11" t="inlineStr">
         <is>
           <t>D4</t>
         </is>
       </c>
-      <c r="C57" s="4" t="inlineStr">
-        <is>
-          <t>Decide or advise
-Some organizations want the system to decide; others want it to advise. Where was your product designed to sit on that spectrum, and how much of that can a customer change?</t>
-        </is>
-      </c>
-      <c r="D57" s="14" t="n"/>
-    </row>
-    <row r="58" ht="5" customHeight="1"/>
-    <row r="60" ht="22" customHeight="1">
-      <c r="B60" s="10" t="inlineStr">
+      <c r="C59" s="12" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <b val="1"/>
+              <color rgb="001F2A37"/>
+              <sz val="11"/>
+            </rPr>
+            <t xml:space="preserve">Decide or advise
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <color rgb="001F2A37"/>
+              <sz val="11"/>
+            </rPr>
+            <t>Some organizations want the system to decide; others want it to advise. Where was your product designed to sit on that spectrum, and how much of that can a customer change?</t>
+          </r>
+        </is>
+      </c>
+      <c r="D59" s="8" t="n"/>
+    </row>
+    <row r="60" ht="5" customHeight="1"/>
+    <row r="62" ht="22" customHeight="1">
+      <c r="B62" s="9" t="inlineStr">
         <is>
           <t>E.   FIT AND PERSPECTIVE</t>
         </is>
       </c>
-      <c r="C60" s="11" t="n"/>
-      <c r="D60" s="11" t="n"/>
-    </row>
-    <row r="61" ht="15" customHeight="1">
-      <c r="B61" s="12" t="inlineStr">
+    </row>
+    <row r="63" ht="15" customHeight="1">
+      <c r="B63" s="10" t="inlineStr">
         <is>
           <t>#</t>
         </is>
       </c>
-      <c r="C61" s="12" t="inlineStr">
+      <c r="C63" s="10" t="inlineStr">
         <is>
           <t>QUESTION</t>
         </is>
       </c>
-      <c r="D61" s="12" t="inlineStr">
+      <c r="D63" s="10" t="inlineStr">
         <is>
           <t>YOUR ANSWER</t>
         </is>
       </c>
     </row>
-    <row r="62" ht="180" customHeight="1">
-      <c r="B62" s="13" t="inlineStr">
+    <row r="64" ht="180" customHeight="1">
+      <c r="B64" s="11" t="inlineStr">
         <is>
           <t>E1</t>
         </is>
       </c>
-      <c r="C62" s="4" t="inlineStr">
-        <is>
-          <t>What we did not ask
-What do you do that we have not asked about, and that you believe would matter to an organization like ours?</t>
-        </is>
-      </c>
-      <c r="D62" s="14" t="n"/>
-    </row>
-    <row r="63" ht="5" customHeight="1"/>
-    <row r="64" ht="180" customHeight="1">
-      <c r="B64" s="13" t="inlineStr">
+      <c r="C64" s="12" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <b val="1"/>
+              <color rgb="001F2A37"/>
+              <sz val="11"/>
+            </rPr>
+            <t xml:space="preserve">What we did not ask
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <color rgb="001F2A37"/>
+              <sz val="11"/>
+            </rPr>
+            <t>What do you do that we have not asked about, and that you believe would matter to an organization like ours?</t>
+          </r>
+        </is>
+      </c>
+      <c r="D64" s="8" t="n"/>
+    </row>
+    <row r="65" ht="5" customHeight="1"/>
+    <row r="66" ht="180" customHeight="1">
+      <c r="B66" s="11" t="inlineStr">
         <is>
           <t>E2</t>
         </is>
       </c>
-      <c r="C64" s="4" t="inlineStr">
-        <is>
-          <t>Where a design partner helps
-We are open to partnering with a product that is strong today and still building. Which parts of what we have described are you actively building, and where would a committed design partner be genuinely useful to you?</t>
-        </is>
-      </c>
-      <c r="D64" s="14" t="n"/>
-    </row>
-    <row r="65" ht="5" customHeight="1"/>
-    <row r="66" ht="137" customHeight="1">
-      <c r="B66" s="13" t="inlineStr">
+      <c r="C66" s="12" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <b val="1"/>
+              <color rgb="001F2A37"/>
+              <sz val="11"/>
+            </rPr>
+            <t xml:space="preserve">Where a design partner helps
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <color rgb="001F2A37"/>
+              <sz val="11"/>
+            </rPr>
+            <t>We are open to partnering with a product that is strong today and still building. Which parts of what we have described are you actively building, and where would a committed design partner be genuinely useful to you?</t>
+          </r>
+        </is>
+      </c>
+      <c r="D66" s="8" t="n"/>
+    </row>
+    <row r="67" ht="5" customHeight="1"/>
+    <row r="68" ht="137" customHeight="1">
+      <c r="B68" s="11" t="inlineStr">
         <is>
           <t>E3</t>
         </is>
       </c>
-      <c r="C66" s="4" t="inlineStr">
-        <is>
-          <t>What you chose not to build
-What have you deliberately chosen not to build, and why?</t>
-        </is>
-      </c>
-      <c r="D66" s="14" t="n"/>
-    </row>
-    <row r="67" ht="5" customHeight="1"/>
+      <c r="C68" s="12" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <b val="1"/>
+              <color rgb="001F2A37"/>
+              <sz val="11"/>
+            </rPr>
+            <t xml:space="preserve">What you chose not to build
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <color rgb="001F2A37"/>
+              <sz val="11"/>
+            </rPr>
+            <t>What have you deliberately chosen not to build, and why?</t>
+          </r>
+        </is>
+      </c>
+      <c r="D68" s="8" t="n"/>
+    </row>
+    <row r="69" ht="5" customHeight="1"/>
   </sheetData>
   <sheetProtection selectLockedCells="0" selectUnlockedCells="0" sheet="1" objects="1" insertRows="1" insertHyperlinks="1" autoFilter="1" scenarios="1" formatColumns="1" deleteColumns="1" insertColumns="1" pivotTables="1" deleteRows="1" formatCells="0" formatRows="0" sort="1" password="DB7D"/>
+  <mergeCells count="7">
+    <mergeCell ref="B1:D1"/>
+    <mergeCell ref="B35:D35"/>
+    <mergeCell ref="B50:D50"/>
+    <mergeCell ref="B18:D18"/>
+    <mergeCell ref="B62:D62"/>
+    <mergeCell ref="B7:D7"/>
+    <mergeCell ref="B2:D2"/>
+  </mergeCells>
   <dataValidations count="1">
-    <dataValidation sqref="D20 D21 D22 D24 D25 D26 D27 D29 D30 D31" showDropDown="0" showInputMessage="1" showErrorMessage="0" allowBlank="1" promptTitle="Select status" prompt="Production · In development · Roadmap · Not offered. Add a note after your choice." type="list">
+    <dataValidation sqref="D22 D23 D24 D26 D27 D28 D29 D31 D32 D33" showDropDown="0" showInputMessage="1" showErrorMessage="0" allowBlank="1" promptTitle="Select status" prompt="Production · In development · Roadmap · Not offered. Add a note after your choice." type="list">
       <formula1>StatusList</formula1>
     </dataValidation>
   </dataValidations>
@@ -1276,6 +1866,5011 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
+    <tabColor rgb="FF2C6A55"/>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr fitToPage="1"/>
+  </sheetPr>
+  <dimension ref="A1:R226"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="1.4" customWidth="1" min="1" max="1"/>
+    <col width="1.5" customWidth="1" min="2" max="2"/>
+    <col width="2" customWidth="1" min="3" max="3"/>
+    <col width="58" customWidth="1" min="4" max="4"/>
+    <col width="1.5" customWidth="1" min="5" max="5"/>
+    <col width="2.6" customWidth="1" min="6" max="6"/>
+    <col width="1.8" customWidth="1" min="7" max="7"/>
+    <col width="1.5" customWidth="1" min="8" max="8"/>
+    <col width="2" customWidth="1" min="9" max="9"/>
+    <col width="58" customWidth="1" min="10" max="10"/>
+    <col width="1.5" customWidth="1" min="11" max="11"/>
+    <col width="2.6" customWidth="1" min="12" max="12"/>
+    <col width="1.5" customWidth="1" min="13" max="13"/>
+    <col width="2" customWidth="1" min="14" max="14"/>
+    <col width="58" customWidth="1" min="15" max="15"/>
+    <col width="1.5" customWidth="1" min="16" max="16"/>
+    <col width="1.8" customWidth="1" min="17" max="17"/>
+    <col width="1.4" customWidth="1" min="18" max="18"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="3.8525" customHeight="1">
+      <c r="A1" s="16" t="n"/>
+      <c r="B1" s="16" t="n"/>
+      <c r="C1" s="16" t="n"/>
+      <c r="D1" s="16" t="n"/>
+      <c r="E1" s="16" t="n"/>
+      <c r="F1" s="16" t="n"/>
+      <c r="G1" s="16" t="n"/>
+      <c r="H1" s="16" t="n"/>
+      <c r="I1" s="16" t="n"/>
+      <c r="J1" s="16" t="n"/>
+      <c r="K1" s="16" t="n"/>
+      <c r="L1" s="16" t="n"/>
+      <c r="M1" s="16" t="n"/>
+      <c r="N1" s="16" t="n"/>
+      <c r="O1" s="16" t="n"/>
+      <c r="P1" s="16" t="n"/>
+      <c r="Q1" s="16" t="n"/>
+      <c r="R1" s="16" t="n"/>
+    </row>
+    <row r="2" ht="3.8525" customHeight="1">
+      <c r="A2" s="16" t="n"/>
+      <c r="B2" s="17" t="inlineStr">
+        <is>
+          <t>COMPASSUS  ·  HOME HEALTH</t>
+        </is>
+      </c>
+      <c r="C2" s="16" t="n"/>
+      <c r="D2" s="16" t="n"/>
+      <c r="E2" s="16" t="n"/>
+      <c r="F2" s="16" t="n"/>
+      <c r="G2" s="16" t="n"/>
+      <c r="H2" s="16" t="n"/>
+      <c r="I2" s="16" t="n"/>
+      <c r="J2" s="16" t="n"/>
+      <c r="K2" s="16" t="n"/>
+      <c r="L2" s="16" t="n"/>
+      <c r="M2" s="16" t="n"/>
+      <c r="N2" s="16" t="n"/>
+      <c r="O2" s="16" t="n"/>
+      <c r="P2" s="16" t="n"/>
+      <c r="Q2" s="16" t="n"/>
+      <c r="R2" s="16" t="n"/>
+    </row>
+    <row r="3" ht="3.8525" customHeight="1">
+      <c r="A3" s="16" t="n"/>
+      <c r="B3" s="16" t="n"/>
+      <c r="C3" s="16" t="n"/>
+      <c r="D3" s="16" t="n"/>
+      <c r="E3" s="16" t="n"/>
+      <c r="F3" s="16" t="n"/>
+      <c r="G3" s="16" t="n"/>
+      <c r="H3" s="16" t="n"/>
+      <c r="I3" s="16" t="n"/>
+      <c r="J3" s="16" t="n"/>
+      <c r="K3" s="16" t="n"/>
+      <c r="L3" s="16" t="n"/>
+      <c r="M3" s="16" t="n"/>
+      <c r="N3" s="16" t="n"/>
+      <c r="O3" s="16" t="n"/>
+      <c r="P3" s="16" t="n"/>
+      <c r="Q3" s="16" t="n"/>
+      <c r="R3" s="16" t="n"/>
+    </row>
+    <row r="4" ht="3.8525" customHeight="1">
+      <c r="A4" s="16" t="n"/>
+      <c r="B4" s="16" t="n"/>
+      <c r="C4" s="16" t="n"/>
+      <c r="D4" s="16" t="n"/>
+      <c r="E4" s="16" t="n"/>
+      <c r="F4" s="16" t="n"/>
+      <c r="G4" s="16" t="n"/>
+      <c r="H4" s="16" t="n"/>
+      <c r="I4" s="16" t="n"/>
+      <c r="J4" s="16" t="n"/>
+      <c r="K4" s="16" t="n"/>
+      <c r="L4" s="16" t="n"/>
+      <c r="M4" s="16" t="n"/>
+      <c r="N4" s="16" t="n"/>
+      <c r="O4" s="16" t="n"/>
+      <c r="P4" s="16" t="n"/>
+      <c r="Q4" s="16" t="n"/>
+      <c r="R4" s="16" t="n"/>
+    </row>
+    <row r="5" ht="3.8525" customHeight="1">
+      <c r="A5" s="16" t="n"/>
+      <c r="B5" s="16" t="n"/>
+      <c r="C5" s="16" t="n"/>
+      <c r="D5" s="16" t="n"/>
+      <c r="E5" s="16" t="n"/>
+      <c r="F5" s="16" t="n"/>
+      <c r="G5" s="16" t="n"/>
+      <c r="H5" s="16" t="n"/>
+      <c r="I5" s="16" t="n"/>
+      <c r="J5" s="16" t="n"/>
+      <c r="K5" s="16" t="n"/>
+      <c r="L5" s="16" t="n"/>
+      <c r="M5" s="16" t="n"/>
+      <c r="N5" s="16" t="n"/>
+      <c r="O5" s="16" t="n"/>
+      <c r="P5" s="16" t="n"/>
+      <c r="Q5" s="16" t="n"/>
+      <c r="R5" s="16" t="n"/>
+    </row>
+    <row r="6" ht="3.8525" customHeight="1">
+      <c r="A6" s="16" t="n"/>
+      <c r="B6" s="16" t="n"/>
+      <c r="C6" s="16" t="n"/>
+      <c r="D6" s="16" t="n"/>
+      <c r="E6" s="16" t="n"/>
+      <c r="F6" s="16" t="n"/>
+      <c r="G6" s="16" t="n"/>
+      <c r="H6" s="16" t="n"/>
+      <c r="I6" s="16" t="n"/>
+      <c r="J6" s="16" t="n"/>
+      <c r="K6" s="16" t="n"/>
+      <c r="L6" s="16" t="n"/>
+      <c r="M6" s="16" t="n"/>
+      <c r="N6" s="16" t="n"/>
+      <c r="O6" s="16" t="n"/>
+      <c r="P6" s="16" t="n"/>
+      <c r="Q6" s="16" t="n"/>
+      <c r="R6" s="16" t="n"/>
+    </row>
+    <row r="7" ht="3.8525" customHeight="1">
+      <c r="A7" s="16" t="n"/>
+      <c r="B7" s="18" t="inlineStr">
+        <is>
+          <t>Capacity &amp; Scheduling</t>
+        </is>
+      </c>
+      <c r="C7" s="16" t="n"/>
+      <c r="D7" s="16" t="n"/>
+      <c r="E7" s="16" t="n"/>
+      <c r="F7" s="16" t="n"/>
+      <c r="G7" s="16" t="n"/>
+      <c r="H7" s="16" t="n"/>
+      <c r="I7" s="19" t="inlineStr">
+        <is>
+          <t>What we are looking to build. Three connected capabilities decide whether a referral becomes a delivered visit — and a platform has to serve all three.</t>
+        </is>
+      </c>
+      <c r="J7" s="16" t="n"/>
+      <c r="K7" s="16" t="n"/>
+      <c r="L7" s="16" t="n"/>
+      <c r="M7" s="16" t="n"/>
+      <c r="N7" s="16" t="n"/>
+      <c r="O7" s="16" t="n"/>
+      <c r="P7" s="16" t="n"/>
+      <c r="Q7" s="16" t="n"/>
+      <c r="R7" s="16" t="n"/>
+    </row>
+    <row r="8" ht="3.8525" customHeight="1">
+      <c r="A8" s="16" t="n"/>
+      <c r="B8" s="16" t="n"/>
+      <c r="C8" s="16" t="n"/>
+      <c r="D8" s="16" t="n"/>
+      <c r="E8" s="16" t="n"/>
+      <c r="F8" s="16" t="n"/>
+      <c r="G8" s="16" t="n"/>
+      <c r="H8" s="16" t="n"/>
+      <c r="I8" s="16" t="n"/>
+      <c r="J8" s="16" t="n"/>
+      <c r="K8" s="16" t="n"/>
+      <c r="L8" s="16" t="n"/>
+      <c r="M8" s="16" t="n"/>
+      <c r="N8" s="16" t="n"/>
+      <c r="O8" s="16" t="n"/>
+      <c r="P8" s="16" t="n"/>
+      <c r="Q8" s="16" t="n"/>
+      <c r="R8" s="16" t="n"/>
+    </row>
+    <row r="9" ht="3.8525" customHeight="1">
+      <c r="A9" s="16" t="n"/>
+      <c r="B9" s="16" t="n"/>
+      <c r="C9" s="16" t="n"/>
+      <c r="D9" s="16" t="n"/>
+      <c r="E9" s="16" t="n"/>
+      <c r="F9" s="16" t="n"/>
+      <c r="G9" s="16" t="n"/>
+      <c r="H9" s="16" t="n"/>
+      <c r="I9" s="16" t="n"/>
+      <c r="J9" s="16" t="n"/>
+      <c r="K9" s="16" t="n"/>
+      <c r="L9" s="16" t="n"/>
+      <c r="M9" s="16" t="n"/>
+      <c r="N9" s="16" t="n"/>
+      <c r="O9" s="16" t="n"/>
+      <c r="P9" s="16" t="n"/>
+      <c r="Q9" s="16" t="n"/>
+      <c r="R9" s="16" t="n"/>
+    </row>
+    <row r="10" ht="3.8525" customHeight="1">
+      <c r="A10" s="16" t="n"/>
+      <c r="B10" s="16" t="n"/>
+      <c r="C10" s="16" t="n"/>
+      <c r="D10" s="16" t="n"/>
+      <c r="E10" s="16" t="n"/>
+      <c r="F10" s="16" t="n"/>
+      <c r="G10" s="16" t="n"/>
+      <c r="H10" s="16" t="n"/>
+      <c r="I10" s="16" t="n"/>
+      <c r="J10" s="16" t="n"/>
+      <c r="K10" s="16" t="n"/>
+      <c r="L10" s="16" t="n"/>
+      <c r="M10" s="16" t="n"/>
+      <c r="N10" s="16" t="n"/>
+      <c r="O10" s="16" t="n"/>
+      <c r="P10" s="16" t="n"/>
+      <c r="Q10" s="16" t="n"/>
+      <c r="R10" s="16" t="n"/>
+    </row>
+    <row r="11" ht="3.8525" customHeight="1">
+      <c r="A11" s="16" t="n"/>
+      <c r="B11" s="16" t="n"/>
+      <c r="C11" s="16" t="n"/>
+      <c r="D11" s="16" t="n"/>
+      <c r="E11" s="16" t="n"/>
+      <c r="F11" s="16" t="n"/>
+      <c r="G11" s="16" t="n"/>
+      <c r="H11" s="16" t="n"/>
+      <c r="I11" s="16" t="n"/>
+      <c r="J11" s="16" t="n"/>
+      <c r="K11" s="16" t="n"/>
+      <c r="L11" s="16" t="n"/>
+      <c r="M11" s="16" t="n"/>
+      <c r="N11" s="16" t="n"/>
+      <c r="O11" s="16" t="n"/>
+      <c r="P11" s="16" t="n"/>
+      <c r="Q11" s="16" t="n"/>
+      <c r="R11" s="16" t="n"/>
+    </row>
+    <row r="12" ht="3.8525" customHeight="1">
+      <c r="A12" s="16" t="n"/>
+      <c r="B12" s="16" t="n"/>
+      <c r="C12" s="16" t="n"/>
+      <c r="D12" s="16" t="n"/>
+      <c r="E12" s="16" t="n"/>
+      <c r="F12" s="16" t="n"/>
+      <c r="G12" s="16" t="n"/>
+      <c r="H12" s="16" t="n"/>
+      <c r="I12" s="16" t="n"/>
+      <c r="J12" s="16" t="n"/>
+      <c r="K12" s="16" t="n"/>
+      <c r="L12" s="16" t="n"/>
+      <c r="M12" s="16" t="n"/>
+      <c r="N12" s="16" t="n"/>
+      <c r="O12" s="16" t="n"/>
+      <c r="P12" s="16" t="n"/>
+      <c r="Q12" s="16" t="n"/>
+      <c r="R12" s="16" t="n"/>
+    </row>
+    <row r="13" ht="3.8525" customHeight="1">
+      <c r="A13" s="16" t="n"/>
+      <c r="B13" s="16" t="n"/>
+      <c r="C13" s="16" t="n"/>
+      <c r="D13" s="16" t="n"/>
+      <c r="E13" s="16" t="n"/>
+      <c r="F13" s="16" t="n"/>
+      <c r="G13" s="16" t="n"/>
+      <c r="H13" s="16" t="n"/>
+      <c r="I13" s="16" t="n"/>
+      <c r="J13" s="16" t="n"/>
+      <c r="K13" s="16" t="n"/>
+      <c r="L13" s="16" t="n"/>
+      <c r="M13" s="16" t="n"/>
+      <c r="N13" s="16" t="n"/>
+      <c r="O13" s="16" t="n"/>
+      <c r="P13" s="16" t="n"/>
+      <c r="Q13" s="16" t="n"/>
+      <c r="R13" s="16" t="n"/>
+    </row>
+    <row r="14" ht="3.8525" customHeight="1">
+      <c r="A14" s="16" t="n"/>
+      <c r="B14" s="16" t="n"/>
+      <c r="C14" s="16" t="n"/>
+      <c r="D14" s="16" t="n"/>
+      <c r="E14" s="16" t="n"/>
+      <c r="F14" s="16" t="n"/>
+      <c r="G14" s="16" t="n"/>
+      <c r="H14" s="16" t="n"/>
+      <c r="I14" s="16" t="n"/>
+      <c r="J14" s="16" t="n"/>
+      <c r="K14" s="16" t="n"/>
+      <c r="L14" s="16" t="n"/>
+      <c r="M14" s="16" t="n"/>
+      <c r="N14" s="16" t="n"/>
+      <c r="O14" s="16" t="n"/>
+      <c r="P14" s="16" t="n"/>
+      <c r="Q14" s="16" t="n"/>
+      <c r="R14" s="16" t="n"/>
+    </row>
+    <row r="15" ht="3.8525" customHeight="1">
+      <c r="A15" s="16" t="n"/>
+      <c r="B15" s="16" t="n"/>
+      <c r="C15" s="16" t="n"/>
+      <c r="D15" s="16" t="n"/>
+      <c r="E15" s="16" t="n"/>
+      <c r="F15" s="16" t="n"/>
+      <c r="G15" s="16" t="n"/>
+      <c r="H15" s="16" t="n"/>
+      <c r="I15" s="16" t="n"/>
+      <c r="J15" s="16" t="n"/>
+      <c r="K15" s="16" t="n"/>
+      <c r="L15" s="16" t="n"/>
+      <c r="M15" s="16" t="n"/>
+      <c r="N15" s="16" t="n"/>
+      <c r="O15" s="16" t="n"/>
+      <c r="P15" s="16" t="n"/>
+      <c r="Q15" s="16" t="n"/>
+      <c r="R15" s="16" t="n"/>
+    </row>
+    <row r="16" ht="3.8525" customHeight="1">
+      <c r="A16" s="16" t="n"/>
+      <c r="B16" s="16" t="n"/>
+      <c r="C16" s="16" t="n"/>
+      <c r="D16" s="16" t="n"/>
+      <c r="E16" s="16" t="n"/>
+      <c r="F16" s="16" t="n"/>
+      <c r="G16" s="16" t="n"/>
+      <c r="H16" s="16" t="n"/>
+      <c r="I16" s="16" t="n"/>
+      <c r="J16" s="16" t="n"/>
+      <c r="K16" s="16" t="n"/>
+      <c r="L16" s="16" t="n"/>
+      <c r="M16" s="16" t="n"/>
+      <c r="N16" s="16" t="n"/>
+      <c r="O16" s="16" t="n"/>
+      <c r="P16" s="16" t="n"/>
+      <c r="Q16" s="16" t="n"/>
+      <c r="R16" s="16" t="n"/>
+    </row>
+    <row r="17" ht="3.8525" customHeight="1">
+      <c r="A17" s="16" t="n"/>
+      <c r="B17" s="16" t="n"/>
+      <c r="C17" s="16" t="n"/>
+      <c r="D17" s="16" t="n"/>
+      <c r="E17" s="16" t="n"/>
+      <c r="F17" s="16" t="n"/>
+      <c r="G17" s="16" t="n"/>
+      <c r="H17" s="16" t="n"/>
+      <c r="I17" s="16" t="n"/>
+      <c r="J17" s="16" t="n"/>
+      <c r="K17" s="16" t="n"/>
+      <c r="L17" s="16" t="n"/>
+      <c r="M17" s="16" t="n"/>
+      <c r="N17" s="16" t="n"/>
+      <c r="O17" s="16" t="n"/>
+      <c r="P17" s="16" t="n"/>
+      <c r="Q17" s="16" t="n"/>
+      <c r="R17" s="16" t="n"/>
+    </row>
+    <row r="18" ht="3.8525" customHeight="1">
+      <c r="A18" s="16" t="n"/>
+      <c r="B18" s="16" t="n"/>
+      <c r="C18" s="16" t="n"/>
+      <c r="D18" s="16" t="n"/>
+      <c r="E18" s="16" t="n"/>
+      <c r="F18" s="16" t="n"/>
+      <c r="G18" s="16" t="n"/>
+      <c r="H18" s="16" t="n"/>
+      <c r="I18" s="16" t="n"/>
+      <c r="J18" s="16" t="n"/>
+      <c r="K18" s="16" t="n"/>
+      <c r="L18" s="16" t="n"/>
+      <c r="M18" s="16" t="n"/>
+      <c r="N18" s="16" t="n"/>
+      <c r="O18" s="16" t="n"/>
+      <c r="P18" s="16" t="n"/>
+      <c r="Q18" s="16" t="n"/>
+      <c r="R18" s="16" t="n"/>
+    </row>
+    <row r="19" ht="3.8525" customHeight="1">
+      <c r="A19" s="16" t="n"/>
+      <c r="B19" s="16" t="n"/>
+      <c r="C19" s="16" t="n"/>
+      <c r="D19" s="16" t="n"/>
+      <c r="E19" s="16" t="n"/>
+      <c r="F19" s="16" t="n"/>
+      <c r="G19" s="16" t="n"/>
+      <c r="H19" s="16" t="n"/>
+      <c r="I19" s="16" t="n"/>
+      <c r="J19" s="16" t="n"/>
+      <c r="K19" s="16" t="n"/>
+      <c r="L19" s="16" t="n"/>
+      <c r="M19" s="16" t="n"/>
+      <c r="N19" s="16" t="n"/>
+      <c r="O19" s="16" t="n"/>
+      <c r="P19" s="16" t="n"/>
+      <c r="Q19" s="16" t="n"/>
+      <c r="R19" s="16" t="n"/>
+    </row>
+    <row r="20" ht="3.8525" customHeight="1">
+      <c r="A20" s="16" t="n"/>
+      <c r="B20" s="16" t="n"/>
+      <c r="C20" s="16" t="n"/>
+      <c r="D20" s="16" t="n"/>
+      <c r="E20" s="16" t="n"/>
+      <c r="F20" s="16" t="n"/>
+      <c r="G20" s="16" t="n"/>
+      <c r="H20" s="16" t="n"/>
+      <c r="I20" s="16" t="n"/>
+      <c r="J20" s="16" t="n"/>
+      <c r="K20" s="16" t="n"/>
+      <c r="L20" s="16" t="n"/>
+      <c r="M20" s="16" t="n"/>
+      <c r="N20" s="16" t="n"/>
+      <c r="O20" s="16" t="n"/>
+      <c r="P20" s="16" t="n"/>
+      <c r="Q20" s="16" t="n"/>
+      <c r="R20" s="16" t="n"/>
+    </row>
+    <row r="21" ht="3.8525" customHeight="1">
+      <c r="A21" s="16" t="n"/>
+      <c r="B21" s="20" t="n"/>
+      <c r="C21" s="20" t="n"/>
+      <c r="D21" s="20" t="n"/>
+      <c r="E21" s="20" t="n"/>
+      <c r="F21" s="20" t="n"/>
+      <c r="G21" s="20" t="n"/>
+      <c r="H21" s="20" t="n"/>
+      <c r="I21" s="20" t="n"/>
+      <c r="J21" s="20" t="n"/>
+      <c r="K21" s="20" t="n"/>
+      <c r="L21" s="20" t="n"/>
+      <c r="M21" s="20" t="n"/>
+      <c r="N21" s="20" t="n"/>
+      <c r="O21" s="20" t="n"/>
+      <c r="P21" s="20" t="n"/>
+      <c r="Q21" s="20" t="n"/>
+      <c r="R21" s="16" t="n"/>
+    </row>
+    <row r="22" ht="3.8525" customHeight="1">
+      <c r="A22" s="16" t="n"/>
+      <c r="B22" s="16" t="n"/>
+      <c r="C22" s="16" t="n"/>
+      <c r="D22" s="16" t="n"/>
+      <c r="E22" s="16" t="n"/>
+      <c r="F22" s="16" t="n"/>
+      <c r="G22" s="16" t="n"/>
+      <c r="H22" s="16" t="n"/>
+      <c r="I22" s="16" t="n"/>
+      <c r="J22" s="16" t="n"/>
+      <c r="K22" s="16" t="n"/>
+      <c r="L22" s="16" t="n"/>
+      <c r="M22" s="16" t="n"/>
+      <c r="N22" s="16" t="n"/>
+      <c r="O22" s="16" t="n"/>
+      <c r="P22" s="16" t="n"/>
+      <c r="Q22" s="16" t="n"/>
+      <c r="R22" s="16" t="n"/>
+    </row>
+    <row r="23" ht="3.8525" customHeight="1">
+      <c r="A23" s="16" t="n"/>
+      <c r="B23" s="16" t="n"/>
+      <c r="C23" s="16" t="n"/>
+      <c r="D23" s="16" t="n"/>
+      <c r="E23" s="16" t="n"/>
+      <c r="F23" s="16" t="n"/>
+      <c r="G23" s="16" t="n"/>
+      <c r="H23" s="16" t="n"/>
+      <c r="I23" s="16" t="n"/>
+      <c r="J23" s="16" t="n"/>
+      <c r="K23" s="16" t="n"/>
+      <c r="L23" s="16" t="n"/>
+      <c r="M23" s="16" t="n"/>
+      <c r="N23" s="16" t="n"/>
+      <c r="O23" s="16" t="n"/>
+      <c r="P23" s="16" t="n"/>
+      <c r="Q23" s="16" t="n"/>
+      <c r="R23" s="16" t="n"/>
+    </row>
+    <row r="24" ht="3.8525" customHeight="1">
+      <c r="A24" s="16" t="n"/>
+      <c r="B24" s="16" t="n"/>
+      <c r="C24" s="16" t="n"/>
+      <c r="D24" s="16" t="n"/>
+      <c r="E24" s="16" t="n"/>
+      <c r="F24" s="16" t="n"/>
+      <c r="G24" s="21" t="n"/>
+      <c r="H24" s="22" t="inlineStr">
+        <is>
+          <t>COORDINATION</t>
+        </is>
+      </c>
+      <c r="I24" s="23" t="n"/>
+      <c r="J24" s="23" t="n"/>
+      <c r="K24" s="23" t="n"/>
+      <c r="L24" s="23" t="n"/>
+      <c r="M24" s="23" t="n"/>
+      <c r="N24" s="23" t="n"/>
+      <c r="O24" s="23" t="n"/>
+      <c r="P24" s="23" t="n"/>
+      <c r="Q24" s="24" t="n"/>
+      <c r="R24" s="16" t="n"/>
+    </row>
+    <row r="25" ht="3.8525" customHeight="1">
+      <c r="A25" s="16" t="n"/>
+      <c r="B25" s="16" t="n"/>
+      <c r="C25" s="16" t="n"/>
+      <c r="D25" s="16" t="n"/>
+      <c r="E25" s="16" t="n"/>
+      <c r="F25" s="16" t="n"/>
+      <c r="G25" s="25" t="n"/>
+      <c r="H25" s="26" t="n"/>
+      <c r="I25" s="26" t="n"/>
+      <c r="J25" s="26" t="n"/>
+      <c r="K25" s="26" t="n"/>
+      <c r="L25" s="26" t="n"/>
+      <c r="M25" s="26" t="n"/>
+      <c r="N25" s="26" t="n"/>
+      <c r="O25" s="26" t="n"/>
+      <c r="P25" s="26" t="n"/>
+      <c r="Q25" s="27" t="n"/>
+      <c r="R25" s="16" t="n"/>
+    </row>
+    <row r="26" ht="3.8525" customHeight="1">
+      <c r="A26" s="16" t="n"/>
+      <c r="B26" s="16" t="n"/>
+      <c r="C26" s="16" t="n"/>
+      <c r="D26" s="16" t="n"/>
+      <c r="E26" s="16" t="n"/>
+      <c r="F26" s="16" t="n"/>
+      <c r="G26" s="25" t="n"/>
+      <c r="H26" s="26" t="n"/>
+      <c r="I26" s="26" t="n"/>
+      <c r="J26" s="26" t="n"/>
+      <c r="K26" s="26" t="n"/>
+      <c r="L26" s="26" t="n"/>
+      <c r="M26" s="26" t="n"/>
+      <c r="N26" s="26" t="n"/>
+      <c r="O26" s="26" t="n"/>
+      <c r="P26" s="26" t="n"/>
+      <c r="Q26" s="27" t="n"/>
+      <c r="R26" s="16" t="n"/>
+    </row>
+    <row r="27" ht="3.8525" customHeight="1">
+      <c r="A27" s="16" t="n"/>
+      <c r="B27" s="16" t="n"/>
+      <c r="C27" s="16" t="n"/>
+      <c r="D27" s="16" t="n"/>
+      <c r="E27" s="16" t="n"/>
+      <c r="F27" s="16" t="n"/>
+      <c r="G27" s="25" t="n"/>
+      <c r="H27" s="26" t="n"/>
+      <c r="I27" s="26" t="n"/>
+      <c r="J27" s="26" t="n"/>
+      <c r="K27" s="26" t="n"/>
+      <c r="L27" s="26" t="n"/>
+      <c r="M27" s="26" t="n"/>
+      <c r="N27" s="26" t="n"/>
+      <c r="O27" s="26" t="n"/>
+      <c r="P27" s="26" t="n"/>
+      <c r="Q27" s="27" t="n"/>
+      <c r="R27" s="16" t="n"/>
+    </row>
+    <row r="28" ht="3.8525" customHeight="1">
+      <c r="A28" s="16" t="n"/>
+      <c r="B28" s="16" t="n"/>
+      <c r="C28" s="16" t="n"/>
+      <c r="D28" s="16" t="n"/>
+      <c r="E28" s="16" t="n"/>
+      <c r="F28" s="16" t="n"/>
+      <c r="G28" s="25" t="n"/>
+      <c r="H28" s="26" t="n"/>
+      <c r="I28" s="26" t="n"/>
+      <c r="J28" s="26" t="n"/>
+      <c r="K28" s="26" t="n"/>
+      <c r="L28" s="26" t="n"/>
+      <c r="M28" s="26" t="n"/>
+      <c r="N28" s="26" t="n"/>
+      <c r="O28" s="26" t="n"/>
+      <c r="P28" s="26" t="n"/>
+      <c r="Q28" s="27" t="n"/>
+      <c r="R28" s="16" t="n"/>
+    </row>
+    <row r="29" ht="3.8525" customHeight="1">
+      <c r="A29" s="16" t="n"/>
+      <c r="B29" s="16" t="n"/>
+      <c r="C29" s="16" t="n"/>
+      <c r="D29" s="16" t="n"/>
+      <c r="E29" s="16" t="n"/>
+      <c r="F29" s="16" t="n"/>
+      <c r="G29" s="25" t="n"/>
+      <c r="H29" s="26" t="n"/>
+      <c r="I29" s="26" t="n"/>
+      <c r="J29" s="26" t="n"/>
+      <c r="K29" s="26" t="n"/>
+      <c r="L29" s="26" t="n"/>
+      <c r="M29" s="26" t="n"/>
+      <c r="N29" s="26" t="n"/>
+      <c r="O29" s="26" t="n"/>
+      <c r="P29" s="26" t="n"/>
+      <c r="Q29" s="27" t="n"/>
+      <c r="R29" s="16" t="n"/>
+    </row>
+    <row r="30" ht="3" customHeight="1">
+      <c r="A30" s="16" t="n"/>
+      <c r="B30" s="28" t="n"/>
+      <c r="C30" s="29" t="n"/>
+      <c r="D30" s="29" t="n"/>
+      <c r="E30" s="30" t="n"/>
+      <c r="F30" s="16" t="n"/>
+      <c r="G30" s="25" t="n"/>
+      <c r="H30" s="31" t="n"/>
+      <c r="I30" s="32" t="n"/>
+      <c r="J30" s="32" t="n"/>
+      <c r="K30" s="33" t="n"/>
+      <c r="L30" s="26" t="n"/>
+      <c r="M30" s="34" t="n"/>
+      <c r="N30" s="35" t="n"/>
+      <c r="O30" s="35" t="n"/>
+      <c r="P30" s="36" t="n"/>
+      <c r="Q30" s="27" t="n"/>
+      <c r="R30" s="16" t="n"/>
+    </row>
+    <row r="31" ht="3.8525" customHeight="1">
+      <c r="A31" s="16" t="n"/>
+      <c r="B31" s="37" t="n"/>
+      <c r="C31" s="16" t="n"/>
+      <c r="D31" s="16" t="n"/>
+      <c r="E31" s="38" t="n"/>
+      <c r="F31" s="16" t="n"/>
+      <c r="G31" s="25" t="n"/>
+      <c r="H31" s="37" t="n"/>
+      <c r="I31" s="16" t="n"/>
+      <c r="J31" s="16" t="n"/>
+      <c r="K31" s="38" t="n"/>
+      <c r="L31" s="26" t="n"/>
+      <c r="M31" s="37" t="n"/>
+      <c r="N31" s="16" t="n"/>
+      <c r="O31" s="16" t="n"/>
+      <c r="P31" s="38" t="n"/>
+      <c r="Q31" s="27" t="n"/>
+      <c r="R31" s="16" t="n"/>
+    </row>
+    <row r="32" ht="3.8525" customHeight="1">
+      <c r="A32" s="16" t="n"/>
+      <c r="B32" s="37" t="n"/>
+      <c r="C32" s="39" t="inlineStr">
+        <is>
+          <t>THE ENVELOPE</t>
+        </is>
+      </c>
+      <c r="D32" s="16" t="n"/>
+      <c r="E32" s="38" t="n"/>
+      <c r="F32" s="16" t="n"/>
+      <c r="G32" s="25" t="n"/>
+      <c r="H32" s="37" t="n"/>
+      <c r="I32" s="40" t="inlineStr">
+        <is>
+          <t>FILLING THE ENVELOPE</t>
+        </is>
+      </c>
+      <c r="J32" s="16" t="n"/>
+      <c r="K32" s="38" t="n"/>
+      <c r="L32" s="26" t="n"/>
+      <c r="M32" s="37" t="n"/>
+      <c r="N32" s="41" t="inlineStr">
+        <is>
+          <t>MAKING IT HAPPEN</t>
+        </is>
+      </c>
+      <c r="O32" s="16" t="n"/>
+      <c r="P32" s="38" t="n"/>
+      <c r="Q32" s="27" t="n"/>
+      <c r="R32" s="16" t="n"/>
+    </row>
+    <row r="33" ht="3.8525" customHeight="1">
+      <c r="A33" s="16" t="n"/>
+      <c r="B33" s="37" t="n"/>
+      <c r="C33" s="16" t="n"/>
+      <c r="D33" s="16" t="n"/>
+      <c r="E33" s="38" t="n"/>
+      <c r="F33" s="16" t="n"/>
+      <c r="G33" s="25" t="n"/>
+      <c r="H33" s="37" t="n"/>
+      <c r="I33" s="16" t="n"/>
+      <c r="J33" s="16" t="n"/>
+      <c r="K33" s="38" t="n"/>
+      <c r="L33" s="26" t="n"/>
+      <c r="M33" s="37" t="n"/>
+      <c r="N33" s="16" t="n"/>
+      <c r="O33" s="16" t="n"/>
+      <c r="P33" s="38" t="n"/>
+      <c r="Q33" s="27" t="n"/>
+      <c r="R33" s="16" t="n"/>
+    </row>
+    <row r="34" ht="3.8525" customHeight="1">
+      <c r="A34" s="16" t="n"/>
+      <c r="B34" s="37" t="n"/>
+      <c r="C34" s="16" t="n"/>
+      <c r="D34" s="16" t="n"/>
+      <c r="E34" s="38" t="n"/>
+      <c r="F34" s="16" t="n"/>
+      <c r="G34" s="25" t="n"/>
+      <c r="H34" s="37" t="n"/>
+      <c r="I34" s="16" t="n"/>
+      <c r="J34" s="16" t="n"/>
+      <c r="K34" s="38" t="n"/>
+      <c r="L34" s="26" t="n"/>
+      <c r="M34" s="37" t="n"/>
+      <c r="N34" s="16" t="n"/>
+      <c r="O34" s="16" t="n"/>
+      <c r="P34" s="38" t="n"/>
+      <c r="Q34" s="27" t="n"/>
+      <c r="R34" s="16" t="n"/>
+    </row>
+    <row r="35" ht="3.8525" customHeight="1">
+      <c r="A35" s="16" t="n"/>
+      <c r="B35" s="37" t="n"/>
+      <c r="C35" s="16" t="n"/>
+      <c r="D35" s="16" t="n"/>
+      <c r="E35" s="38" t="n"/>
+      <c r="F35" s="16" t="n"/>
+      <c r="G35" s="25" t="n"/>
+      <c r="H35" s="37" t="n"/>
+      <c r="I35" s="16" t="n"/>
+      <c r="J35" s="16" t="n"/>
+      <c r="K35" s="38" t="n"/>
+      <c r="L35" s="26" t="n"/>
+      <c r="M35" s="37" t="n"/>
+      <c r="N35" s="16" t="n"/>
+      <c r="O35" s="16" t="n"/>
+      <c r="P35" s="38" t="n"/>
+      <c r="Q35" s="27" t="n"/>
+      <c r="R35" s="16" t="n"/>
+    </row>
+    <row r="36" ht="3.8525" customHeight="1">
+      <c r="A36" s="16" t="n"/>
+      <c r="B36" s="37" t="n"/>
+      <c r="C36" s="16" t="n"/>
+      <c r="D36" s="16" t="n"/>
+      <c r="E36" s="38" t="n"/>
+      <c r="F36" s="16" t="n"/>
+      <c r="G36" s="25" t="n"/>
+      <c r="H36" s="37" t="n"/>
+      <c r="I36" s="16" t="n"/>
+      <c r="J36" s="16" t="n"/>
+      <c r="K36" s="38" t="n"/>
+      <c r="L36" s="26" t="n"/>
+      <c r="M36" s="37" t="n"/>
+      <c r="N36" s="16" t="n"/>
+      <c r="O36" s="16" t="n"/>
+      <c r="P36" s="38" t="n"/>
+      <c r="Q36" s="27" t="n"/>
+      <c r="R36" s="16" t="n"/>
+    </row>
+    <row r="37" ht="3.8525" customHeight="1">
+      <c r="A37" s="16" t="n"/>
+      <c r="B37" s="37" t="n"/>
+      <c r="C37" s="42" t="inlineStr">
+        <is>
+          <t>Capacity Management</t>
+        </is>
+      </c>
+      <c r="D37" s="16" t="n"/>
+      <c r="E37" s="38" t="n"/>
+      <c r="F37" s="16" t="n"/>
+      <c r="G37" s="25" t="n"/>
+      <c r="H37" s="37" t="n"/>
+      <c r="I37" s="42" t="inlineStr">
+        <is>
+          <t>Scheduling Engine</t>
+        </is>
+      </c>
+      <c r="J37" s="16" t="n"/>
+      <c r="K37" s="38" t="n"/>
+      <c r="L37" s="26" t="n"/>
+      <c r="M37" s="37" t="n"/>
+      <c r="N37" s="42" t="inlineStr">
+        <is>
+          <t>Engagement</t>
+        </is>
+      </c>
+      <c r="O37" s="16" t="n"/>
+      <c r="P37" s="38" t="n"/>
+      <c r="Q37" s="27" t="n"/>
+      <c r="R37" s="16" t="n"/>
+    </row>
+    <row r="38" ht="3.8525" customHeight="1">
+      <c r="A38" s="16" t="n"/>
+      <c r="B38" s="37" t="n"/>
+      <c r="C38" s="16" t="n"/>
+      <c r="D38" s="16" t="n"/>
+      <c r="E38" s="38" t="n"/>
+      <c r="F38" s="16" t="n"/>
+      <c r="G38" s="25" t="n"/>
+      <c r="H38" s="37" t="n"/>
+      <c r="I38" s="16" t="n"/>
+      <c r="J38" s="16" t="n"/>
+      <c r="K38" s="38" t="n"/>
+      <c r="L38" s="26" t="n"/>
+      <c r="M38" s="37" t="n"/>
+      <c r="N38" s="16" t="n"/>
+      <c r="O38" s="16" t="n"/>
+      <c r="P38" s="38" t="n"/>
+      <c r="Q38" s="27" t="n"/>
+      <c r="R38" s="16" t="n"/>
+    </row>
+    <row r="39" ht="3.8525" customHeight="1">
+      <c r="A39" s="16" t="n"/>
+      <c r="B39" s="37" t="n"/>
+      <c r="C39" s="16" t="n"/>
+      <c r="D39" s="16" t="n"/>
+      <c r="E39" s="38" t="n"/>
+      <c r="F39" s="16" t="n"/>
+      <c r="G39" s="25" t="n"/>
+      <c r="H39" s="37" t="n"/>
+      <c r="I39" s="16" t="n"/>
+      <c r="J39" s="16" t="n"/>
+      <c r="K39" s="38" t="n"/>
+      <c r="L39" s="26" t="n"/>
+      <c r="M39" s="37" t="n"/>
+      <c r="N39" s="16" t="n"/>
+      <c r="O39" s="16" t="n"/>
+      <c r="P39" s="38" t="n"/>
+      <c r="Q39" s="27" t="n"/>
+      <c r="R39" s="16" t="n"/>
+    </row>
+    <row r="40" ht="3.8525" customHeight="1">
+      <c r="A40" s="16" t="n"/>
+      <c r="B40" s="37" t="n"/>
+      <c r="C40" s="16" t="n"/>
+      <c r="D40" s="16" t="n"/>
+      <c r="E40" s="38" t="n"/>
+      <c r="F40" s="16" t="n"/>
+      <c r="G40" s="25" t="n"/>
+      <c r="H40" s="37" t="n"/>
+      <c r="I40" s="16" t="n"/>
+      <c r="J40" s="16" t="n"/>
+      <c r="K40" s="38" t="n"/>
+      <c r="L40" s="26" t="n"/>
+      <c r="M40" s="37" t="n"/>
+      <c r="N40" s="16" t="n"/>
+      <c r="O40" s="16" t="n"/>
+      <c r="P40" s="38" t="n"/>
+      <c r="Q40" s="27" t="n"/>
+      <c r="R40" s="16" t="n"/>
+    </row>
+    <row r="41" ht="3.8525" customHeight="1">
+      <c r="A41" s="16" t="n"/>
+      <c r="B41" s="37" t="n"/>
+      <c r="C41" s="16" t="n"/>
+      <c r="D41" s="16" t="n"/>
+      <c r="E41" s="38" t="n"/>
+      <c r="F41" s="16" t="n"/>
+      <c r="G41" s="25" t="n"/>
+      <c r="H41" s="37" t="n"/>
+      <c r="I41" s="16" t="n"/>
+      <c r="J41" s="16" t="n"/>
+      <c r="K41" s="38" t="n"/>
+      <c r="L41" s="26" t="n"/>
+      <c r="M41" s="37" t="n"/>
+      <c r="N41" s="16" t="n"/>
+      <c r="O41" s="16" t="n"/>
+      <c r="P41" s="38" t="n"/>
+      <c r="Q41" s="27" t="n"/>
+      <c r="R41" s="16" t="n"/>
+    </row>
+    <row r="42" ht="3.8525" customHeight="1">
+      <c r="A42" s="16" t="n"/>
+      <c r="B42" s="37" t="n"/>
+      <c r="C42" s="16" t="n"/>
+      <c r="D42" s="16" t="n"/>
+      <c r="E42" s="38" t="n"/>
+      <c r="F42" s="16" t="n"/>
+      <c r="G42" s="25" t="n"/>
+      <c r="H42" s="37" t="n"/>
+      <c r="I42" s="16" t="n"/>
+      <c r="J42" s="16" t="n"/>
+      <c r="K42" s="38" t="n"/>
+      <c r="L42" s="26" t="n"/>
+      <c r="M42" s="37" t="n"/>
+      <c r="N42" s="16" t="n"/>
+      <c r="O42" s="16" t="n"/>
+      <c r="P42" s="38" t="n"/>
+      <c r="Q42" s="27" t="n"/>
+      <c r="R42" s="16" t="n"/>
+    </row>
+    <row r="43" ht="3.8525" customHeight="1">
+      <c r="A43" s="16" t="n"/>
+      <c r="B43" s="37" t="n"/>
+      <c r="C43" s="16" t="n"/>
+      <c r="D43" s="16" t="n"/>
+      <c r="E43" s="38" t="n"/>
+      <c r="F43" s="16" t="n"/>
+      <c r="G43" s="25" t="n"/>
+      <c r="H43" s="37" t="n"/>
+      <c r="I43" s="16" t="n"/>
+      <c r="J43" s="16" t="n"/>
+      <c r="K43" s="38" t="n"/>
+      <c r="L43" s="26" t="n"/>
+      <c r="M43" s="37" t="n"/>
+      <c r="N43" s="16" t="n"/>
+      <c r="O43" s="16" t="n"/>
+      <c r="P43" s="38" t="n"/>
+      <c r="Q43" s="27" t="n"/>
+      <c r="R43" s="16" t="n"/>
+    </row>
+    <row r="44" ht="3.8525" customHeight="1">
+      <c r="A44" s="16" t="n"/>
+      <c r="B44" s="37" t="n"/>
+      <c r="C44" s="16" t="n"/>
+      <c r="D44" s="16" t="n"/>
+      <c r="E44" s="38" t="n"/>
+      <c r="F44" s="16" t="n"/>
+      <c r="G44" s="25" t="n"/>
+      <c r="H44" s="37" t="n"/>
+      <c r="I44" s="16" t="n"/>
+      <c r="J44" s="16" t="n"/>
+      <c r="K44" s="38" t="n"/>
+      <c r="L44" s="26" t="n"/>
+      <c r="M44" s="37" t="n"/>
+      <c r="N44" s="16" t="n"/>
+      <c r="O44" s="16" t="n"/>
+      <c r="P44" s="38" t="n"/>
+      <c r="Q44" s="27" t="n"/>
+      <c r="R44" s="16" t="n"/>
+    </row>
+    <row r="45" ht="3.8525" customHeight="1">
+      <c r="A45" s="16" t="n"/>
+      <c r="B45" s="37" t="n"/>
+      <c r="C45" s="43" t="inlineStr">
+        <is>
+          <t>How much work a branch can deliver, and how much room is left.</t>
+        </is>
+      </c>
+      <c r="D45" s="16" t="n"/>
+      <c r="E45" s="38" t="n"/>
+      <c r="F45" s="16" t="n"/>
+      <c r="G45" s="25" t="n"/>
+      <c r="H45" s="37" t="n"/>
+      <c r="I45" s="43" t="inlineStr">
+        <is>
+          <t>Which clinician, which day, which route.</t>
+        </is>
+      </c>
+      <c r="J45" s="16" t="n"/>
+      <c r="K45" s="38" t="n"/>
+      <c r="L45" s="26" t="n"/>
+      <c r="M45" s="37" t="n"/>
+      <c r="N45" s="43" t="inlineStr">
+        <is>
+          <t>Turning a schedule into delivered visits — with patients, clinicians and the office.</t>
+        </is>
+      </c>
+      <c r="O45" s="16" t="n"/>
+      <c r="P45" s="38" t="n"/>
+      <c r="Q45" s="27" t="n"/>
+      <c r="R45" s="16" t="n"/>
+    </row>
+    <row r="46" ht="3.8525" customHeight="1">
+      <c r="A46" s="16" t="n"/>
+      <c r="B46" s="37" t="n"/>
+      <c r="C46" s="16" t="n"/>
+      <c r="D46" s="16" t="n"/>
+      <c r="E46" s="38" t="n"/>
+      <c r="F46" s="16" t="n"/>
+      <c r="G46" s="25" t="n"/>
+      <c r="H46" s="37" t="n"/>
+      <c r="I46" s="16" t="n"/>
+      <c r="J46" s="16" t="n"/>
+      <c r="K46" s="38" t="n"/>
+      <c r="L46" s="26" t="n"/>
+      <c r="M46" s="37" t="n"/>
+      <c r="N46" s="16" t="n"/>
+      <c r="O46" s="16" t="n"/>
+      <c r="P46" s="38" t="n"/>
+      <c r="Q46" s="27" t="n"/>
+      <c r="R46" s="16" t="n"/>
+    </row>
+    <row r="47" ht="3.8525" customHeight="1">
+      <c r="A47" s="16" t="n"/>
+      <c r="B47" s="37" t="n"/>
+      <c r="C47" s="16" t="n"/>
+      <c r="D47" s="16" t="n"/>
+      <c r="E47" s="38" t="n"/>
+      <c r="F47" s="16" t="n"/>
+      <c r="G47" s="25" t="n"/>
+      <c r="H47" s="37" t="n"/>
+      <c r="I47" s="16" t="n"/>
+      <c r="J47" s="16" t="n"/>
+      <c r="K47" s="38" t="n"/>
+      <c r="L47" s="26" t="n"/>
+      <c r="M47" s="37" t="n"/>
+      <c r="N47" s="16" t="n"/>
+      <c r="O47" s="16" t="n"/>
+      <c r="P47" s="38" t="n"/>
+      <c r="Q47" s="27" t="n"/>
+      <c r="R47" s="16" t="n"/>
+    </row>
+    <row r="48" ht="3.8525" customHeight="1">
+      <c r="A48" s="16" t="n"/>
+      <c r="B48" s="37" t="n"/>
+      <c r="C48" s="16" t="n"/>
+      <c r="D48" s="16" t="n"/>
+      <c r="E48" s="38" t="n"/>
+      <c r="F48" s="16" t="n"/>
+      <c r="G48" s="25" t="n"/>
+      <c r="H48" s="37" t="n"/>
+      <c r="I48" s="16" t="n"/>
+      <c r="J48" s="16" t="n"/>
+      <c r="K48" s="38" t="n"/>
+      <c r="L48" s="26" t="n"/>
+      <c r="M48" s="37" t="n"/>
+      <c r="N48" s="16" t="n"/>
+      <c r="O48" s="16" t="n"/>
+      <c r="P48" s="38" t="n"/>
+      <c r="Q48" s="27" t="n"/>
+      <c r="R48" s="16" t="n"/>
+    </row>
+    <row r="49" ht="3.8525" customHeight="1">
+      <c r="A49" s="16" t="n"/>
+      <c r="B49" s="37" t="n"/>
+      <c r="C49" s="16" t="n"/>
+      <c r="D49" s="16" t="n"/>
+      <c r="E49" s="38" t="n"/>
+      <c r="F49" s="16" t="n"/>
+      <c r="G49" s="25" t="n"/>
+      <c r="H49" s="37" t="n"/>
+      <c r="I49" s="16" t="n"/>
+      <c r="J49" s="16" t="n"/>
+      <c r="K49" s="38" t="n"/>
+      <c r="L49" s="26" t="n"/>
+      <c r="M49" s="37" t="n"/>
+      <c r="N49" s="16" t="n"/>
+      <c r="O49" s="16" t="n"/>
+      <c r="P49" s="38" t="n"/>
+      <c r="Q49" s="27" t="n"/>
+      <c r="R49" s="16" t="n"/>
+    </row>
+    <row r="50" ht="3.8525" customHeight="1">
+      <c r="A50" s="16" t="n"/>
+      <c r="B50" s="37" t="n"/>
+      <c r="C50" s="16" t="n"/>
+      <c r="D50" s="16" t="n"/>
+      <c r="E50" s="38" t="n"/>
+      <c r="F50" s="16" t="n"/>
+      <c r="G50" s="25" t="n"/>
+      <c r="H50" s="37" t="n"/>
+      <c r="I50" s="20" t="n"/>
+      <c r="J50" s="20" t="n"/>
+      <c r="K50" s="38" t="n"/>
+      <c r="L50" s="26" t="n"/>
+      <c r="M50" s="37" t="n"/>
+      <c r="N50" s="16" t="n"/>
+      <c r="O50" s="16" t="n"/>
+      <c r="P50" s="38" t="n"/>
+      <c r="Q50" s="27" t="n"/>
+      <c r="R50" s="16" t="n"/>
+    </row>
+    <row r="51" ht="3.8525" customHeight="1">
+      <c r="A51" s="16" t="n"/>
+      <c r="B51" s="37" t="n"/>
+      <c r="C51" s="16" t="n"/>
+      <c r="D51" s="16" t="n"/>
+      <c r="E51" s="38" t="n"/>
+      <c r="F51" s="16" t="n"/>
+      <c r="G51" s="25" t="n"/>
+      <c r="H51" s="37" t="n"/>
+      <c r="I51" s="16" t="n"/>
+      <c r="J51" s="16" t="n"/>
+      <c r="K51" s="38" t="n"/>
+      <c r="L51" s="26" t="n"/>
+      <c r="M51" s="37" t="n"/>
+      <c r="N51" s="16" t="n"/>
+      <c r="O51" s="16" t="n"/>
+      <c r="P51" s="38" t="n"/>
+      <c r="Q51" s="27" t="n"/>
+      <c r="R51" s="16" t="n"/>
+    </row>
+    <row r="52" ht="3.8525" customHeight="1">
+      <c r="A52" s="16" t="n"/>
+      <c r="B52" s="37" t="n"/>
+      <c r="C52" s="16" t="n"/>
+      <c r="D52" s="16" t="n"/>
+      <c r="E52" s="38" t="n"/>
+      <c r="F52" s="16" t="n"/>
+      <c r="G52" s="25" t="n"/>
+      <c r="H52" s="37" t="n"/>
+      <c r="I52" s="16" t="n"/>
+      <c r="J52" s="16" t="n"/>
+      <c r="K52" s="38" t="n"/>
+      <c r="L52" s="26" t="n"/>
+      <c r="M52" s="37" t="n"/>
+      <c r="N52" s="16" t="n"/>
+      <c r="O52" s="16" t="n"/>
+      <c r="P52" s="38" t="n"/>
+      <c r="Q52" s="27" t="n"/>
+      <c r="R52" s="16" t="n"/>
+    </row>
+    <row r="53" ht="3.8525" customHeight="1">
+      <c r="A53" s="16" t="n"/>
+      <c r="B53" s="37" t="n"/>
+      <c r="C53" s="16" t="n"/>
+      <c r="D53" s="16" t="n"/>
+      <c r="E53" s="38" t="n"/>
+      <c r="F53" s="16" t="n"/>
+      <c r="G53" s="25" t="n"/>
+      <c r="H53" s="37" t="n"/>
+      <c r="I53" s="44" t="inlineStr">
+        <is>
+          <t>Demand</t>
+        </is>
+      </c>
+      <c r="J53" s="16" t="n"/>
+      <c r="K53" s="38" t="n"/>
+      <c r="L53" s="26" t="n"/>
+      <c r="M53" s="37" t="n"/>
+      <c r="N53" s="16" t="n"/>
+      <c r="O53" s="16" t="n"/>
+      <c r="P53" s="38" t="n"/>
+      <c r="Q53" s="27" t="n"/>
+      <c r="R53" s="16" t="n"/>
+    </row>
+    <row r="54" ht="3.8525" customHeight="1">
+      <c r="A54" s="16" t="n"/>
+      <c r="B54" s="37" t="n"/>
+      <c r="C54" s="20" t="n"/>
+      <c r="D54" s="20" t="n"/>
+      <c r="E54" s="38" t="n"/>
+      <c r="F54" s="16" t="n"/>
+      <c r="G54" s="25" t="n"/>
+      <c r="H54" s="37" t="n"/>
+      <c r="I54" s="16" t="n"/>
+      <c r="J54" s="16" t="n"/>
+      <c r="K54" s="38" t="n"/>
+      <c r="L54" s="26" t="n"/>
+      <c r="M54" s="37" t="n"/>
+      <c r="N54" s="20" t="n"/>
+      <c r="O54" s="20" t="n"/>
+      <c r="P54" s="38" t="n"/>
+      <c r="Q54" s="27" t="n"/>
+      <c r="R54" s="16" t="n"/>
+    </row>
+    <row r="55" ht="3.8525" customHeight="1">
+      <c r="A55" s="16" t="n"/>
+      <c r="B55" s="37" t="n"/>
+      <c r="C55" s="16" t="n"/>
+      <c r="D55" s="16" t="n"/>
+      <c r="E55" s="38" t="n"/>
+      <c r="F55" s="16" t="n"/>
+      <c r="G55" s="25" t="n"/>
+      <c r="H55" s="37" t="n"/>
+      <c r="I55" s="16" t="n"/>
+      <c r="J55" s="16" t="n"/>
+      <c r="K55" s="38" t="n"/>
+      <c r="L55" s="26" t="n"/>
+      <c r="M55" s="37" t="n"/>
+      <c r="N55" s="16" t="n"/>
+      <c r="O55" s="16" t="n"/>
+      <c r="P55" s="38" t="n"/>
+      <c r="Q55" s="27" t="n"/>
+      <c r="R55" s="16" t="n"/>
+    </row>
+    <row r="56" ht="3.8525" customHeight="1">
+      <c r="A56" s="16" t="n"/>
+      <c r="B56" s="37" t="n"/>
+      <c r="C56" s="16" t="n"/>
+      <c r="D56" s="16" t="n"/>
+      <c r="E56" s="38" t="n"/>
+      <c r="F56" s="16" t="n"/>
+      <c r="G56" s="25" t="n"/>
+      <c r="H56" s="37" t="n"/>
+      <c r="I56" s="16" t="n"/>
+      <c r="J56" s="16" t="n"/>
+      <c r="K56" s="38" t="n"/>
+      <c r="L56" s="26" t="n"/>
+      <c r="M56" s="37" t="n"/>
+      <c r="N56" s="16" t="n"/>
+      <c r="O56" s="16" t="n"/>
+      <c r="P56" s="38" t="n"/>
+      <c r="Q56" s="27" t="n"/>
+      <c r="R56" s="16" t="n"/>
+    </row>
+    <row r="57" ht="3.8525" customHeight="1">
+      <c r="A57" s="16" t="n"/>
+      <c r="B57" s="37" t="n"/>
+      <c r="C57" s="44" t="inlineStr">
+        <is>
+          <t>Workforce supply</t>
+        </is>
+      </c>
+      <c r="D57" s="16" t="n"/>
+      <c r="E57" s="38" t="n"/>
+      <c r="F57" s="16" t="n"/>
+      <c r="G57" s="25" t="n"/>
+      <c r="H57" s="37" t="n"/>
+      <c r="I57" s="16" t="n"/>
+      <c r="J57" s="16" t="n"/>
+      <c r="K57" s="38" t="n"/>
+      <c r="L57" s="26" t="n"/>
+      <c r="M57" s="37" t="n"/>
+      <c r="N57" s="44" t="inlineStr">
+        <is>
+          <t>Before the visit</t>
+        </is>
+      </c>
+      <c r="O57" s="16" t="n"/>
+      <c r="P57" s="38" t="n"/>
+      <c r="Q57" s="27" t="n"/>
+      <c r="R57" s="16" t="n"/>
+    </row>
+    <row r="58" ht="3.8525" customHeight="1">
+      <c r="A58" s="16" t="n"/>
+      <c r="B58" s="37" t="n"/>
+      <c r="C58" s="16" t="n"/>
+      <c r="D58" s="16" t="n"/>
+      <c r="E58" s="38" t="n"/>
+      <c r="F58" s="16" t="n"/>
+      <c r="G58" s="25" t="n"/>
+      <c r="H58" s="37" t="n"/>
+      <c r="I58" s="16" t="n"/>
+      <c r="J58" s="16" t="n"/>
+      <c r="K58" s="38" t="n"/>
+      <c r="L58" s="26" t="n"/>
+      <c r="M58" s="37" t="n"/>
+      <c r="N58" s="16" t="n"/>
+      <c r="O58" s="16" t="n"/>
+      <c r="P58" s="38" t="n"/>
+      <c r="Q58" s="27" t="n"/>
+      <c r="R58" s="16" t="n"/>
+    </row>
+    <row r="59" ht="3.8525" customHeight="1">
+      <c r="A59" s="16" t="n"/>
+      <c r="B59" s="37" t="n"/>
+      <c r="C59" s="16" t="n"/>
+      <c r="D59" s="16" t="n"/>
+      <c r="E59" s="38" t="n"/>
+      <c r="F59" s="16" t="n"/>
+      <c r="G59" s="25" t="n"/>
+      <c r="H59" s="37" t="n"/>
+      <c r="I59" s="45" t="inlineStr">
+        <is>
+          <t>Everything the engine must know about what has been ordered.</t>
+        </is>
+      </c>
+      <c r="J59" s="16" t="n"/>
+      <c r="K59" s="38" t="n"/>
+      <c r="L59" s="26" t="n"/>
+      <c r="M59" s="37" t="n"/>
+      <c r="N59" s="16" t="n"/>
+      <c r="O59" s="16" t="n"/>
+      <c r="P59" s="38" t="n"/>
+      <c r="Q59" s="27" t="n"/>
+      <c r="R59" s="16" t="n"/>
+    </row>
+    <row r="60" ht="3.8525" customHeight="1">
+      <c r="A60" s="16" t="n"/>
+      <c r="B60" s="37" t="n"/>
+      <c r="C60" s="16" t="n"/>
+      <c r="D60" s="16" t="n"/>
+      <c r="E60" s="38" t="n"/>
+      <c r="F60" s="16" t="n"/>
+      <c r="G60" s="25" t="n"/>
+      <c r="H60" s="37" t="n"/>
+      <c r="I60" s="16" t="n"/>
+      <c r="J60" s="16" t="n"/>
+      <c r="K60" s="38" t="n"/>
+      <c r="L60" s="26" t="n"/>
+      <c r="M60" s="37" t="n"/>
+      <c r="N60" s="16" t="n"/>
+      <c r="O60" s="16" t="n"/>
+      <c r="P60" s="38" t="n"/>
+      <c r="Q60" s="27" t="n"/>
+      <c r="R60" s="16" t="n"/>
+    </row>
+    <row r="61" ht="3.8525" customHeight="1">
+      <c r="A61" s="16" t="n"/>
+      <c r="B61" s="37" t="n"/>
+      <c r="C61" s="16" t="n"/>
+      <c r="D61" s="16" t="n"/>
+      <c r="E61" s="38" t="n"/>
+      <c r="F61" s="16" t="n"/>
+      <c r="G61" s="25" t="n"/>
+      <c r="H61" s="37" t="n"/>
+      <c r="I61" s="16" t="n"/>
+      <c r="J61" s="16" t="n"/>
+      <c r="K61" s="38" t="n"/>
+      <c r="L61" s="26" t="n"/>
+      <c r="M61" s="37" t="n"/>
+      <c r="N61" s="16" t="n"/>
+      <c r="O61" s="16" t="n"/>
+      <c r="P61" s="38" t="n"/>
+      <c r="Q61" s="27" t="n"/>
+      <c r="R61" s="16" t="n"/>
+    </row>
+    <row r="62" ht="3.8525" customHeight="1">
+      <c r="A62" s="16" t="n"/>
+      <c r="B62" s="37" t="n"/>
+      <c r="C62" s="16" t="n"/>
+      <c r="D62" s="16" t="n"/>
+      <c r="E62" s="38" t="n"/>
+      <c r="F62" s="16" t="n"/>
+      <c r="G62" s="25" t="n"/>
+      <c r="H62" s="37" t="n"/>
+      <c r="I62" s="16" t="n"/>
+      <c r="J62" s="16" t="n"/>
+      <c r="K62" s="38" t="n"/>
+      <c r="L62" s="26" t="n"/>
+      <c r="M62" s="37" t="n"/>
+      <c r="N62" s="16" t="n"/>
+      <c r="O62" s="16" t="n"/>
+      <c r="P62" s="38" t="n"/>
+      <c r="Q62" s="27" t="n"/>
+      <c r="R62" s="16" t="n"/>
+    </row>
+    <row r="63" ht="3.8525" customHeight="1">
+      <c r="A63" s="16" t="n"/>
+      <c r="B63" s="37" t="n"/>
+      <c r="C63" s="45" t="inlineStr">
+        <is>
+          <t>Who we have, and what each of them is qualified to do.</t>
+        </is>
+      </c>
+      <c r="D63" s="16" t="n"/>
+      <c r="E63" s="38" t="n"/>
+      <c r="F63" s="16" t="n"/>
+      <c r="G63" s="25" t="n"/>
+      <c r="H63" s="37" t="n"/>
+      <c r="I63" s="16" t="n"/>
+      <c r="J63" s="16" t="n"/>
+      <c r="K63" s="38" t="n"/>
+      <c r="L63" s="26" t="n"/>
+      <c r="M63" s="37" t="n"/>
+      <c r="N63" s="45" t="inlineStr">
+        <is>
+          <t>Securing the visit before the clinician drives.</t>
+        </is>
+      </c>
+      <c r="O63" s="16" t="n"/>
+      <c r="P63" s="38" t="n"/>
+      <c r="Q63" s="27" t="n"/>
+      <c r="R63" s="16" t="n"/>
+    </row>
+    <row r="64" ht="3.8525" customHeight="1">
+      <c r="A64" s="16" t="n"/>
+      <c r="B64" s="37" t="n"/>
+      <c r="C64" s="16" t="n"/>
+      <c r="D64" s="16" t="n"/>
+      <c r="E64" s="38" t="n"/>
+      <c r="F64" s="16" t="n"/>
+      <c r="G64" s="25" t="n"/>
+      <c r="H64" s="37" t="n"/>
+      <c r="I64" s="16" t="n"/>
+      <c r="J64" s="16" t="n"/>
+      <c r="K64" s="38" t="n"/>
+      <c r="L64" s="26" t="n"/>
+      <c r="M64" s="37" t="n"/>
+      <c r="N64" s="16" t="n"/>
+      <c r="O64" s="16" t="n"/>
+      <c r="P64" s="38" t="n"/>
+      <c r="Q64" s="27" t="n"/>
+      <c r="R64" s="16" t="n"/>
+    </row>
+    <row r="65" ht="3.8525" customHeight="1">
+      <c r="A65" s="16" t="n"/>
+      <c r="B65" s="37" t="n"/>
+      <c r="C65" s="16" t="n"/>
+      <c r="D65" s="16" t="n"/>
+      <c r="E65" s="38" t="n"/>
+      <c r="F65" s="16" t="n"/>
+      <c r="G65" s="25" t="n"/>
+      <c r="H65" s="37" t="n"/>
+      <c r="I65" s="46" t="inlineStr">
+        <is>
+          <t>•</t>
+        </is>
+      </c>
+      <c r="J65" s="43" t="inlineStr">
+        <is>
+          <t>Plan-of-care orders, ordered frequency and visit types, from the EMR (Home Care Home Base) and the intake platform</t>
+        </is>
+      </c>
+      <c r="K65" s="38" t="n"/>
+      <c r="L65" s="26" t="n"/>
+      <c r="M65" s="37" t="n"/>
+      <c r="N65" s="16" t="n"/>
+      <c r="O65" s="16" t="n"/>
+      <c r="P65" s="38" t="n"/>
+      <c r="Q65" s="27" t="n"/>
+      <c r="R65" s="16" t="n"/>
+    </row>
+    <row r="66" ht="3.8525" customHeight="1">
+      <c r="A66" s="16" t="n"/>
+      <c r="B66" s="37" t="n"/>
+      <c r="C66" s="16" t="n"/>
+      <c r="D66" s="16" t="n"/>
+      <c r="E66" s="38" t="n"/>
+      <c r="F66" s="16" t="n"/>
+      <c r="G66" s="25" t="n"/>
+      <c r="H66" s="37" t="n"/>
+      <c r="I66" s="16" t="n"/>
+      <c r="J66" s="16" t="n"/>
+      <c r="K66" s="38" t="n"/>
+      <c r="L66" s="26" t="n"/>
+      <c r="M66" s="37" t="n"/>
+      <c r="N66" s="16" t="n"/>
+      <c r="O66" s="16" t="n"/>
+      <c r="P66" s="38" t="n"/>
+      <c r="Q66" s="27" t="n"/>
+      <c r="R66" s="16" t="n"/>
+    </row>
+    <row r="67" ht="3.8525" customHeight="1">
+      <c r="A67" s="16" t="n"/>
+      <c r="B67" s="37" t="n"/>
+      <c r="C67" s="16" t="n"/>
+      <c r="D67" s="16" t="n"/>
+      <c r="E67" s="38" t="n"/>
+      <c r="F67" s="16" t="n"/>
+      <c r="G67" s="25" t="n"/>
+      <c r="H67" s="37" t="n"/>
+      <c r="I67" s="16" t="n"/>
+      <c r="J67" s="16" t="n"/>
+      <c r="K67" s="38" t="n"/>
+      <c r="L67" s="26" t="n"/>
+      <c r="M67" s="37" t="n"/>
+      <c r="N67" s="16" t="n"/>
+      <c r="O67" s="16" t="n"/>
+      <c r="P67" s="38" t="n"/>
+      <c r="Q67" s="27" t="n"/>
+      <c r="R67" s="16" t="n"/>
+    </row>
+    <row r="68" ht="3.8525" customHeight="1">
+      <c r="A68" s="16" t="n"/>
+      <c r="B68" s="37" t="n"/>
+      <c r="C68" s="16" t="n"/>
+      <c r="D68" s="16" t="n"/>
+      <c r="E68" s="38" t="n"/>
+      <c r="F68" s="16" t="n"/>
+      <c r="G68" s="25" t="n"/>
+      <c r="H68" s="37" t="n"/>
+      <c r="I68" s="16" t="n"/>
+      <c r="J68" s="16" t="n"/>
+      <c r="K68" s="38" t="n"/>
+      <c r="L68" s="26" t="n"/>
+      <c r="M68" s="37" t="n"/>
+      <c r="N68" s="16" t="n"/>
+      <c r="O68" s="16" t="n"/>
+      <c r="P68" s="38" t="n"/>
+      <c r="Q68" s="27" t="n"/>
+      <c r="R68" s="16" t="n"/>
+    </row>
+    <row r="69" ht="3.8525" customHeight="1">
+      <c r="A69" s="16" t="n"/>
+      <c r="B69" s="37" t="n"/>
+      <c r="C69" s="47" t="inlineStr">
+        <is>
+          <t>•</t>
+        </is>
+      </c>
+      <c r="D69" s="43" t="inlineStr">
+        <is>
+          <t>Roster by discipline, role (assessing vs. assistant), FTE and employment type</t>
+        </is>
+      </c>
+      <c r="E69" s="38" t="n"/>
+      <c r="F69" s="16" t="n"/>
+      <c r="G69" s="25" t="n"/>
+      <c r="H69" s="37" t="n"/>
+      <c r="I69" s="16" t="n"/>
+      <c r="J69" s="16" t="n"/>
+      <c r="K69" s="38" t="n"/>
+      <c r="L69" s="26" t="n"/>
+      <c r="M69" s="37" t="n"/>
+      <c r="N69" s="48" t="inlineStr">
+        <is>
+          <t>•</t>
+        </is>
+      </c>
+      <c r="O69" s="43" t="inlineStr">
+        <is>
+          <t>New-patient welcome call</t>
+        </is>
+      </c>
+      <c r="P69" s="38" t="n"/>
+      <c r="Q69" s="27" t="n"/>
+      <c r="R69" s="16" t="n"/>
+    </row>
+    <row r="70" ht="3.8525" customHeight="1">
+      <c r="A70" s="16" t="n"/>
+      <c r="B70" s="37" t="n"/>
+      <c r="C70" s="16" t="n"/>
+      <c r="D70" s="16" t="n"/>
+      <c r="E70" s="38" t="n"/>
+      <c r="F70" s="16" t="n"/>
+      <c r="G70" s="25" t="n"/>
+      <c r="H70" s="37" t="n"/>
+      <c r="I70" s="16" t="n"/>
+      <c r="J70" s="16" t="n"/>
+      <c r="K70" s="38" t="n"/>
+      <c r="L70" s="26" t="n"/>
+      <c r="M70" s="37" t="n"/>
+      <c r="N70" s="16" t="n"/>
+      <c r="O70" s="16" t="n"/>
+      <c r="P70" s="38" t="n"/>
+      <c r="Q70" s="27" t="n"/>
+      <c r="R70" s="16" t="n"/>
+    </row>
+    <row r="71" ht="3.8525" customHeight="1">
+      <c r="A71" s="16" t="n"/>
+      <c r="B71" s="37" t="n"/>
+      <c r="C71" s="16" t="n"/>
+      <c r="D71" s="16" t="n"/>
+      <c r="E71" s="38" t="n"/>
+      <c r="F71" s="16" t="n"/>
+      <c r="G71" s="25" t="n"/>
+      <c r="H71" s="37" t="n"/>
+      <c r="I71" s="16" t="n"/>
+      <c r="J71" s="16" t="n"/>
+      <c r="K71" s="38" t="n"/>
+      <c r="L71" s="26" t="n"/>
+      <c r="M71" s="37" t="n"/>
+      <c r="N71" s="16" t="n"/>
+      <c r="O71" s="16" t="n"/>
+      <c r="P71" s="38" t="n"/>
+      <c r="Q71" s="27" t="n"/>
+      <c r="R71" s="16" t="n"/>
+    </row>
+    <row r="72" ht="3.8525" customHeight="1">
+      <c r="A72" s="16" t="n"/>
+      <c r="B72" s="37" t="n"/>
+      <c r="C72" s="16" t="n"/>
+      <c r="D72" s="16" t="n"/>
+      <c r="E72" s="38" t="n"/>
+      <c r="F72" s="16" t="n"/>
+      <c r="G72" s="25" t="n"/>
+      <c r="H72" s="37" t="n"/>
+      <c r="I72" s="16" t="n"/>
+      <c r="J72" s="16" t="n"/>
+      <c r="K72" s="38" t="n"/>
+      <c r="L72" s="26" t="n"/>
+      <c r="M72" s="37" t="n"/>
+      <c r="N72" s="16" t="n"/>
+      <c r="O72" s="16" t="n"/>
+      <c r="P72" s="38" t="n"/>
+      <c r="Q72" s="27" t="n"/>
+      <c r="R72" s="16" t="n"/>
+    </row>
+    <row r="73" ht="3.8525" customHeight="1">
+      <c r="A73" s="16" t="n"/>
+      <c r="B73" s="37" t="n"/>
+      <c r="C73" s="16" t="n"/>
+      <c r="D73" s="16" t="n"/>
+      <c r="E73" s="38" t="n"/>
+      <c r="F73" s="16" t="n"/>
+      <c r="G73" s="25" t="n"/>
+      <c r="H73" s="37" t="n"/>
+      <c r="I73" s="16" t="n"/>
+      <c r="J73" s="16" t="n"/>
+      <c r="K73" s="38" t="n"/>
+      <c r="L73" s="26" t="n"/>
+      <c r="M73" s="37" t="n"/>
+      <c r="N73" s="16" t="n"/>
+      <c r="O73" s="16" t="n"/>
+      <c r="P73" s="38" t="n"/>
+      <c r="Q73" s="27" t="n"/>
+      <c r="R73" s="16" t="n"/>
+    </row>
+    <row r="74" ht="3.8525" customHeight="1">
+      <c r="A74" s="16" t="n"/>
+      <c r="B74" s="37" t="n"/>
+      <c r="C74" s="16" t="n"/>
+      <c r="D74" s="16" t="n"/>
+      <c r="E74" s="38" t="n"/>
+      <c r="F74" s="16" t="n"/>
+      <c r="G74" s="25" t="n"/>
+      <c r="H74" s="37" t="n"/>
+      <c r="I74" s="16" t="n"/>
+      <c r="J74" s="16" t="n"/>
+      <c r="K74" s="38" t="n"/>
+      <c r="L74" s="26" t="n"/>
+      <c r="M74" s="37" t="n"/>
+      <c r="N74" s="48" t="inlineStr">
+        <is>
+          <t>•</t>
+        </is>
+      </c>
+      <c r="O74" s="43" t="inlineStr">
+        <is>
+          <t>Patient availability captured before the visit is booked</t>
+        </is>
+      </c>
+      <c r="P74" s="38" t="n"/>
+      <c r="Q74" s="27" t="n"/>
+      <c r="R74" s="16" t="n"/>
+    </row>
+    <row r="75" ht="3.8525" customHeight="1">
+      <c r="A75" s="16" t="n"/>
+      <c r="B75" s="37" t="n"/>
+      <c r="C75" s="16" t="n"/>
+      <c r="D75" s="16" t="n"/>
+      <c r="E75" s="38" t="n"/>
+      <c r="F75" s="16" t="n"/>
+      <c r="G75" s="25" t="n"/>
+      <c r="H75" s="37" t="n"/>
+      <c r="I75" s="16" t="n"/>
+      <c r="J75" s="16" t="n"/>
+      <c r="K75" s="38" t="n"/>
+      <c r="L75" s="26" t="n"/>
+      <c r="M75" s="37" t="n"/>
+      <c r="N75" s="16" t="n"/>
+      <c r="O75" s="16" t="n"/>
+      <c r="P75" s="38" t="n"/>
+      <c r="Q75" s="27" t="n"/>
+      <c r="R75" s="16" t="n"/>
+    </row>
+    <row r="76" ht="3.8525" customHeight="1">
+      <c r="A76" s="16" t="n"/>
+      <c r="B76" s="37" t="n"/>
+      <c r="C76" s="16" t="n"/>
+      <c r="D76" s="16" t="n"/>
+      <c r="E76" s="38" t="n"/>
+      <c r="F76" s="16" t="n"/>
+      <c r="G76" s="25" t="n"/>
+      <c r="H76" s="37" t="n"/>
+      <c r="I76" s="16" t="n"/>
+      <c r="J76" s="16" t="n"/>
+      <c r="K76" s="38" t="n"/>
+      <c r="L76" s="26" t="n"/>
+      <c r="M76" s="37" t="n"/>
+      <c r="N76" s="16" t="n"/>
+      <c r="O76" s="16" t="n"/>
+      <c r="P76" s="38" t="n"/>
+      <c r="Q76" s="27" t="n"/>
+      <c r="R76" s="16" t="n"/>
+    </row>
+    <row r="77" ht="3.8525" customHeight="1">
+      <c r="A77" s="16" t="n"/>
+      <c r="B77" s="37" t="n"/>
+      <c r="C77" s="16" t="n"/>
+      <c r="D77" s="16" t="n"/>
+      <c r="E77" s="38" t="n"/>
+      <c r="F77" s="16" t="n"/>
+      <c r="G77" s="25" t="n"/>
+      <c r="H77" s="37" t="n"/>
+      <c r="I77" s="16" t="n"/>
+      <c r="J77" s="16" t="n"/>
+      <c r="K77" s="38" t="n"/>
+      <c r="L77" s="26" t="n"/>
+      <c r="M77" s="37" t="n"/>
+      <c r="N77" s="16" t="n"/>
+      <c r="O77" s="16" t="n"/>
+      <c r="P77" s="38" t="n"/>
+      <c r="Q77" s="27" t="n"/>
+      <c r="R77" s="16" t="n"/>
+    </row>
+    <row r="78" ht="3.8525" customHeight="1">
+      <c r="A78" s="16" t="n"/>
+      <c r="B78" s="37" t="n"/>
+      <c r="C78" s="47" t="inlineStr">
+        <is>
+          <t>•</t>
+        </is>
+      </c>
+      <c r="D78" s="43" t="inlineStr">
+        <is>
+          <t>Start-of-care capable clinicians, measured as their own distinct capacity</t>
+        </is>
+      </c>
+      <c r="E78" s="38" t="n"/>
+      <c r="F78" s="16" t="n"/>
+      <c r="G78" s="25" t="n"/>
+      <c r="H78" s="37" t="n"/>
+      <c r="I78" s="46" t="inlineStr">
+        <is>
+          <t>•</t>
+        </is>
+      </c>
+      <c r="J78" s="43" t="inlineStr">
+        <is>
+          <t>Authorization status and payer rules attached to each visit</t>
+        </is>
+      </c>
+      <c r="K78" s="38" t="n"/>
+      <c r="L78" s="26" t="n"/>
+      <c r="M78" s="37" t="n"/>
+      <c r="N78" s="16" t="n"/>
+      <c r="O78" s="16" t="n"/>
+      <c r="P78" s="38" t="n"/>
+      <c r="Q78" s="27" t="n"/>
+      <c r="R78" s="16" t="n"/>
+    </row>
+    <row r="79" ht="3.8525" customHeight="1">
+      <c r="A79" s="16" t="n"/>
+      <c r="B79" s="37" t="n"/>
+      <c r="C79" s="16" t="n"/>
+      <c r="D79" s="16" t="n"/>
+      <c r="E79" s="38" t="n"/>
+      <c r="F79" s="16" t="n"/>
+      <c r="G79" s="25" t="n"/>
+      <c r="H79" s="37" t="n"/>
+      <c r="I79" s="16" t="n"/>
+      <c r="J79" s="16" t="n"/>
+      <c r="K79" s="38" t="n"/>
+      <c r="L79" s="26" t="n"/>
+      <c r="M79" s="37" t="n"/>
+      <c r="N79" s="48" t="inlineStr">
+        <is>
+          <t>•</t>
+        </is>
+      </c>
+      <c r="O79" s="43" t="inlineStr">
+        <is>
+          <t>Automated reminders, day-before confirmation, en-route notification</t>
+        </is>
+      </c>
+      <c r="P79" s="38" t="n"/>
+      <c r="Q79" s="27" t="n"/>
+      <c r="R79" s="16" t="n"/>
+    </row>
+    <row r="80" ht="3.8525" customHeight="1">
+      <c r="A80" s="16" t="n"/>
+      <c r="B80" s="37" t="n"/>
+      <c r="C80" s="16" t="n"/>
+      <c r="D80" s="16" t="n"/>
+      <c r="E80" s="38" t="n"/>
+      <c r="F80" s="16" t="n"/>
+      <c r="G80" s="25" t="n"/>
+      <c r="H80" s="37" t="n"/>
+      <c r="I80" s="16" t="n"/>
+      <c r="J80" s="16" t="n"/>
+      <c r="K80" s="38" t="n"/>
+      <c r="L80" s="26" t="n"/>
+      <c r="M80" s="37" t="n"/>
+      <c r="N80" s="16" t="n"/>
+      <c r="O80" s="16" t="n"/>
+      <c r="P80" s="38" t="n"/>
+      <c r="Q80" s="27" t="n"/>
+      <c r="R80" s="16" t="n"/>
+    </row>
+    <row r="81" ht="3.8525" customHeight="1">
+      <c r="A81" s="16" t="n"/>
+      <c r="B81" s="37" t="n"/>
+      <c r="C81" s="16" t="n"/>
+      <c r="D81" s="16" t="n"/>
+      <c r="E81" s="38" t="n"/>
+      <c r="F81" s="16" t="n"/>
+      <c r="G81" s="25" t="n"/>
+      <c r="H81" s="37" t="n"/>
+      <c r="I81" s="16" t="n"/>
+      <c r="J81" s="16" t="n"/>
+      <c r="K81" s="38" t="n"/>
+      <c r="L81" s="26" t="n"/>
+      <c r="M81" s="37" t="n"/>
+      <c r="N81" s="16" t="n"/>
+      <c r="O81" s="16" t="n"/>
+      <c r="P81" s="38" t="n"/>
+      <c r="Q81" s="27" t="n"/>
+      <c r="R81" s="16" t="n"/>
+    </row>
+    <row r="82" ht="3.8525" customHeight="1">
+      <c r="A82" s="16" t="n"/>
+      <c r="B82" s="37" t="n"/>
+      <c r="C82" s="16" t="n"/>
+      <c r="D82" s="16" t="n"/>
+      <c r="E82" s="38" t="n"/>
+      <c r="F82" s="16" t="n"/>
+      <c r="G82" s="25" t="n"/>
+      <c r="H82" s="37" t="n"/>
+      <c r="I82" s="16" t="n"/>
+      <c r="J82" s="16" t="n"/>
+      <c r="K82" s="38" t="n"/>
+      <c r="L82" s="26" t="n"/>
+      <c r="M82" s="37" t="n"/>
+      <c r="N82" s="16" t="n"/>
+      <c r="O82" s="16" t="n"/>
+      <c r="P82" s="38" t="n"/>
+      <c r="Q82" s="27" t="n"/>
+      <c r="R82" s="16" t="n"/>
+    </row>
+    <row r="83" ht="3.8525" customHeight="1">
+      <c r="A83" s="16" t="n"/>
+      <c r="B83" s="37" t="n"/>
+      <c r="C83" s="16" t="n"/>
+      <c r="D83" s="16" t="n"/>
+      <c r="E83" s="38" t="n"/>
+      <c r="F83" s="16" t="n"/>
+      <c r="G83" s="25" t="n"/>
+      <c r="H83" s="37" t="n"/>
+      <c r="I83" s="46" t="inlineStr">
+        <is>
+          <t>•</t>
+        </is>
+      </c>
+      <c r="J83" s="43" t="inlineStr">
+        <is>
+          <t>Order, consent and readiness state — what is schedulable, not merely ordered</t>
+        </is>
+      </c>
+      <c r="K83" s="38" t="n"/>
+      <c r="L83" s="26" t="n"/>
+      <c r="M83" s="37" t="n"/>
+      <c r="N83" s="16" t="n"/>
+      <c r="O83" s="16" t="n"/>
+      <c r="P83" s="38" t="n"/>
+      <c r="Q83" s="27" t="n"/>
+      <c r="R83" s="16" t="n"/>
+    </row>
+    <row r="84" ht="3.8525" customHeight="1">
+      <c r="A84" s="16" t="n"/>
+      <c r="B84" s="37" t="n"/>
+      <c r="C84" s="16" t="n"/>
+      <c r="D84" s="16" t="n"/>
+      <c r="E84" s="38" t="n"/>
+      <c r="F84" s="16" t="n"/>
+      <c r="G84" s="25" t="n"/>
+      <c r="H84" s="37" t="n"/>
+      <c r="I84" s="16" t="n"/>
+      <c r="J84" s="16" t="n"/>
+      <c r="K84" s="38" t="n"/>
+      <c r="L84" s="26" t="n"/>
+      <c r="M84" s="37" t="n"/>
+      <c r="N84" s="16" t="n"/>
+      <c r="O84" s="16" t="n"/>
+      <c r="P84" s="38" t="n"/>
+      <c r="Q84" s="27" t="n"/>
+      <c r="R84" s="16" t="n"/>
+    </row>
+    <row r="85" ht="3.8525" customHeight="1">
+      <c r="A85" s="16" t="n"/>
+      <c r="B85" s="37" t="n"/>
+      <c r="C85" s="16" t="n"/>
+      <c r="D85" s="16" t="n"/>
+      <c r="E85" s="38" t="n"/>
+      <c r="F85" s="16" t="n"/>
+      <c r="G85" s="25" t="n"/>
+      <c r="H85" s="37" t="n"/>
+      <c r="I85" s="16" t="n"/>
+      <c r="J85" s="16" t="n"/>
+      <c r="K85" s="38" t="n"/>
+      <c r="L85" s="26" t="n"/>
+      <c r="M85" s="37" t="n"/>
+      <c r="N85" s="16" t="n"/>
+      <c r="O85" s="16" t="n"/>
+      <c r="P85" s="38" t="n"/>
+      <c r="Q85" s="27" t="n"/>
+      <c r="R85" s="16" t="n"/>
+    </row>
+    <row r="86" ht="3.8525" customHeight="1">
+      <c r="A86" s="16" t="n"/>
+      <c r="B86" s="37" t="n"/>
+      <c r="C86" s="16" t="n"/>
+      <c r="D86" s="16" t="n"/>
+      <c r="E86" s="38" t="n"/>
+      <c r="F86" s="16" t="n"/>
+      <c r="G86" s="25" t="n"/>
+      <c r="H86" s="37" t="n"/>
+      <c r="I86" s="16" t="n"/>
+      <c r="J86" s="16" t="n"/>
+      <c r="K86" s="38" t="n"/>
+      <c r="L86" s="26" t="n"/>
+      <c r="M86" s="37" t="n"/>
+      <c r="N86" s="16" t="n"/>
+      <c r="O86" s="16" t="n"/>
+      <c r="P86" s="38" t="n"/>
+      <c r="Q86" s="27" t="n"/>
+      <c r="R86" s="16" t="n"/>
+    </row>
+    <row r="87" ht="3.8525" customHeight="1">
+      <c r="A87" s="16" t="n"/>
+      <c r="B87" s="37" t="n"/>
+      <c r="C87" s="47" t="inlineStr">
+        <is>
+          <t>•</t>
+        </is>
+      </c>
+      <c r="D87" s="43" t="inlineStr">
+        <is>
+          <t>Specialty competencies, plus orientation and ramp status</t>
+        </is>
+      </c>
+      <c r="E87" s="38" t="n"/>
+      <c r="F87" s="16" t="n"/>
+      <c r="G87" s="25" t="n"/>
+      <c r="H87" s="37" t="n"/>
+      <c r="I87" s="16" t="n"/>
+      <c r="J87" s="16" t="n"/>
+      <c r="K87" s="38" t="n"/>
+      <c r="L87" s="26" t="n"/>
+      <c r="M87" s="37" t="n"/>
+      <c r="N87" s="16" t="n"/>
+      <c r="O87" s="16" t="n"/>
+      <c r="P87" s="38" t="n"/>
+      <c r="Q87" s="27" t="n"/>
+      <c r="R87" s="16" t="n"/>
+    </row>
+    <row r="88" ht="3.8525" customHeight="1">
+      <c r="A88" s="16" t="n"/>
+      <c r="B88" s="37" t="n"/>
+      <c r="C88" s="16" t="n"/>
+      <c r="D88" s="16" t="n"/>
+      <c r="E88" s="38" t="n"/>
+      <c r="F88" s="16" t="n"/>
+      <c r="G88" s="25" t="n"/>
+      <c r="H88" s="37" t="n"/>
+      <c r="I88" s="16" t="n"/>
+      <c r="J88" s="16" t="n"/>
+      <c r="K88" s="38" t="n"/>
+      <c r="L88" s="26" t="n"/>
+      <c r="M88" s="37" t="n"/>
+      <c r="N88" s="48" t="inlineStr">
+        <is>
+          <t>•</t>
+        </is>
+      </c>
+      <c r="O88" s="43" t="inlineStr">
+        <is>
+          <t>Automating the day-before outreach clinicians perform manually today, for every patient, every day</t>
+        </is>
+      </c>
+      <c r="P88" s="38" t="n"/>
+      <c r="Q88" s="27" t="n"/>
+      <c r="R88" s="16" t="n"/>
+    </row>
+    <row r="89" ht="3.8525" customHeight="1">
+      <c r="A89" s="16" t="n"/>
+      <c r="B89" s="37" t="n"/>
+      <c r="C89" s="16" t="n"/>
+      <c r="D89" s="16" t="n"/>
+      <c r="E89" s="38" t="n"/>
+      <c r="F89" s="16" t="n"/>
+      <c r="G89" s="25" t="n"/>
+      <c r="H89" s="37" t="n"/>
+      <c r="I89" s="16" t="n"/>
+      <c r="J89" s="16" t="n"/>
+      <c r="K89" s="38" t="n"/>
+      <c r="L89" s="26" t="n"/>
+      <c r="M89" s="37" t="n"/>
+      <c r="N89" s="16" t="n"/>
+      <c r="O89" s="16" t="n"/>
+      <c r="P89" s="38" t="n"/>
+      <c r="Q89" s="27" t="n"/>
+      <c r="R89" s="16" t="n"/>
+    </row>
+    <row r="90" ht="3.8525" customHeight="1">
+      <c r="A90" s="16" t="n"/>
+      <c r="B90" s="37" t="n"/>
+      <c r="C90" s="16" t="n"/>
+      <c r="D90" s="16" t="n"/>
+      <c r="E90" s="38" t="n"/>
+      <c r="F90" s="16" t="n"/>
+      <c r="G90" s="25" t="n"/>
+      <c r="H90" s="37" t="n"/>
+      <c r="I90" s="16" t="n"/>
+      <c r="J90" s="16" t="n"/>
+      <c r="K90" s="38" t="n"/>
+      <c r="L90" s="26" t="n"/>
+      <c r="M90" s="37" t="n"/>
+      <c r="N90" s="16" t="n"/>
+      <c r="O90" s="16" t="n"/>
+      <c r="P90" s="38" t="n"/>
+      <c r="Q90" s="27" t="n"/>
+      <c r="R90" s="16" t="n"/>
+    </row>
+    <row r="91" ht="3.8525" customHeight="1">
+      <c r="A91" s="16" t="n"/>
+      <c r="B91" s="37" t="n"/>
+      <c r="C91" s="16" t="n"/>
+      <c r="D91" s="16" t="n"/>
+      <c r="E91" s="38" t="n"/>
+      <c r="F91" s="16" t="n"/>
+      <c r="G91" s="25" t="n"/>
+      <c r="H91" s="37" t="n"/>
+      <c r="I91" s="16" t="n"/>
+      <c r="J91" s="16" t="n"/>
+      <c r="K91" s="38" t="n"/>
+      <c r="L91" s="26" t="n"/>
+      <c r="M91" s="37" t="n"/>
+      <c r="N91" s="16" t="n"/>
+      <c r="O91" s="16" t="n"/>
+      <c r="P91" s="38" t="n"/>
+      <c r="Q91" s="27" t="n"/>
+      <c r="R91" s="16" t="n"/>
+    </row>
+    <row r="92" ht="3.8525" customHeight="1">
+      <c r="A92" s="16" t="n"/>
+      <c r="B92" s="37" t="n"/>
+      <c r="C92" s="47" t="inlineStr">
+        <is>
+          <t>•</t>
+        </is>
+      </c>
+      <c r="D92" s="43" t="inlineStr">
+        <is>
+          <t>Per-diem and float pool</t>
+        </is>
+      </c>
+      <c r="E92" s="38" t="n"/>
+      <c r="F92" s="16" t="n"/>
+      <c r="G92" s="25" t="n"/>
+      <c r="H92" s="37" t="n"/>
+      <c r="I92" s="46" t="inlineStr">
+        <is>
+          <t>•</t>
+        </is>
+      </c>
+      <c r="J92" s="43" t="inlineStr">
+        <is>
+          <t>The compliance window each visit has to fall inside</t>
+        </is>
+      </c>
+      <c r="K92" s="38" t="n"/>
+      <c r="L92" s="26" t="n"/>
+      <c r="M92" s="37" t="n"/>
+      <c r="N92" s="16" t="n"/>
+      <c r="O92" s="16" t="n"/>
+      <c r="P92" s="38" t="n"/>
+      <c r="Q92" s="27" t="n"/>
+      <c r="R92" s="16" t="n"/>
+    </row>
+    <row r="93" ht="3.8525" customHeight="1">
+      <c r="A93" s="16" t="n"/>
+      <c r="B93" s="37" t="n"/>
+      <c r="C93" s="16" t="n"/>
+      <c r="D93" s="16" t="n"/>
+      <c r="E93" s="38" t="n"/>
+      <c r="F93" s="16" t="n"/>
+      <c r="G93" s="25" t="n"/>
+      <c r="H93" s="37" t="n"/>
+      <c r="I93" s="16" t="n"/>
+      <c r="J93" s="16" t="n"/>
+      <c r="K93" s="38" t="n"/>
+      <c r="L93" s="26" t="n"/>
+      <c r="M93" s="37" t="n"/>
+      <c r="N93" s="16" t="n"/>
+      <c r="O93" s="16" t="n"/>
+      <c r="P93" s="38" t="n"/>
+      <c r="Q93" s="27" t="n"/>
+      <c r="R93" s="16" t="n"/>
+    </row>
+    <row r="94" ht="3.8525" customHeight="1">
+      <c r="A94" s="16" t="n"/>
+      <c r="B94" s="37" t="n"/>
+      <c r="C94" s="16" t="n"/>
+      <c r="D94" s="16" t="n"/>
+      <c r="E94" s="38" t="n"/>
+      <c r="F94" s="16" t="n"/>
+      <c r="G94" s="25" t="n"/>
+      <c r="H94" s="37" t="n"/>
+      <c r="I94" s="16" t="n"/>
+      <c r="J94" s="16" t="n"/>
+      <c r="K94" s="38" t="n"/>
+      <c r="L94" s="26" t="n"/>
+      <c r="M94" s="37" t="n"/>
+      <c r="N94" s="16" t="n"/>
+      <c r="O94" s="16" t="n"/>
+      <c r="P94" s="38" t="n"/>
+      <c r="Q94" s="27" t="n"/>
+      <c r="R94" s="16" t="n"/>
+    </row>
+    <row r="95" ht="3.8525" customHeight="1">
+      <c r="A95" s="16" t="n"/>
+      <c r="B95" s="37" t="n"/>
+      <c r="C95" s="16" t="n"/>
+      <c r="D95" s="16" t="n"/>
+      <c r="E95" s="38" t="n"/>
+      <c r="F95" s="16" t="n"/>
+      <c r="G95" s="25" t="n"/>
+      <c r="H95" s="37" t="n"/>
+      <c r="I95" s="16" t="n"/>
+      <c r="J95" s="16" t="n"/>
+      <c r="K95" s="38" t="n"/>
+      <c r="L95" s="26" t="n"/>
+      <c r="M95" s="37" t="n"/>
+      <c r="N95" s="16" t="n"/>
+      <c r="O95" s="16" t="n"/>
+      <c r="P95" s="38" t="n"/>
+      <c r="Q95" s="27" t="n"/>
+      <c r="R95" s="16" t="n"/>
+    </row>
+    <row r="96" ht="3.8525" customHeight="1">
+      <c r="A96" s="16" t="n"/>
+      <c r="B96" s="37" t="n"/>
+      <c r="C96" s="16" t="n"/>
+      <c r="D96" s="16" t="n"/>
+      <c r="E96" s="38" t="n"/>
+      <c r="F96" s="16" t="n"/>
+      <c r="G96" s="25" t="n"/>
+      <c r="H96" s="37" t="n"/>
+      <c r="I96" s="16" t="n"/>
+      <c r="J96" s="16" t="n"/>
+      <c r="K96" s="38" t="n"/>
+      <c r="L96" s="26" t="n"/>
+      <c r="M96" s="37" t="n"/>
+      <c r="N96" s="16" t="n"/>
+      <c r="O96" s="16" t="n"/>
+      <c r="P96" s="38" t="n"/>
+      <c r="Q96" s="27" t="n"/>
+      <c r="R96" s="16" t="n"/>
+    </row>
+    <row r="97" ht="3.8525" customHeight="1">
+      <c r="A97" s="16" t="n"/>
+      <c r="B97" s="37" t="n"/>
+      <c r="C97" s="47" t="inlineStr">
+        <is>
+          <t>•</t>
+        </is>
+      </c>
+      <c r="D97" s="43" t="inlineStr">
+        <is>
+          <t>On-call and weekend rotation load</t>
+        </is>
+      </c>
+      <c r="E97" s="38" t="n"/>
+      <c r="F97" s="16" t="n"/>
+      <c r="G97" s="25" t="n"/>
+      <c r="H97" s="37" t="n"/>
+      <c r="I97" s="16" t="n"/>
+      <c r="J97" s="16" t="n"/>
+      <c r="K97" s="38" t="n"/>
+      <c r="L97" s="26" t="n"/>
+      <c r="M97" s="37" t="n"/>
+      <c r="N97" s="48" t="inlineStr">
+        <is>
+          <t>•</t>
+        </is>
+      </c>
+      <c r="O97" s="43" t="inlineStr">
+        <is>
+          <t>Channel and communication-preference management</t>
+        </is>
+      </c>
+      <c r="P97" s="38" t="n"/>
+      <c r="Q97" s="27" t="n"/>
+      <c r="R97" s="16" t="n"/>
+    </row>
+    <row r="98" ht="3.8525" customHeight="1">
+      <c r="A98" s="16" t="n"/>
+      <c r="B98" s="37" t="n"/>
+      <c r="C98" s="16" t="n"/>
+      <c r="D98" s="16" t="n"/>
+      <c r="E98" s="38" t="n"/>
+      <c r="F98" s="16" t="n"/>
+      <c r="G98" s="25" t="n"/>
+      <c r="H98" s="37" t="n"/>
+      <c r="I98" s="16" t="n"/>
+      <c r="J98" s="16" t="n"/>
+      <c r="K98" s="38" t="n"/>
+      <c r="L98" s="26" t="n"/>
+      <c r="M98" s="37" t="n"/>
+      <c r="N98" s="16" t="n"/>
+      <c r="O98" s="16" t="n"/>
+      <c r="P98" s="38" t="n"/>
+      <c r="Q98" s="27" t="n"/>
+      <c r="R98" s="16" t="n"/>
+    </row>
+    <row r="99" ht="3.8525" customHeight="1">
+      <c r="A99" s="16" t="n"/>
+      <c r="B99" s="37" t="n"/>
+      <c r="C99" s="16" t="n"/>
+      <c r="D99" s="16" t="n"/>
+      <c r="E99" s="38" t="n"/>
+      <c r="F99" s="16" t="n"/>
+      <c r="G99" s="25" t="n"/>
+      <c r="H99" s="37" t="n"/>
+      <c r="I99" s="44" t="inlineStr">
+        <is>
+          <t>Matching</t>
+        </is>
+      </c>
+      <c r="J99" s="16" t="n"/>
+      <c r="K99" s="38" t="n"/>
+      <c r="L99" s="26" t="n"/>
+      <c r="M99" s="37" t="n"/>
+      <c r="N99" s="16" t="n"/>
+      <c r="O99" s="16" t="n"/>
+      <c r="P99" s="38" t="n"/>
+      <c r="Q99" s="27" t="n"/>
+      <c r="R99" s="16" t="n"/>
+    </row>
+    <row r="100" ht="3.8525" customHeight="1">
+      <c r="A100" s="16" t="n"/>
+      <c r="B100" s="37" t="n"/>
+      <c r="C100" s="16" t="n"/>
+      <c r="D100" s="16" t="n"/>
+      <c r="E100" s="38" t="n"/>
+      <c r="F100" s="16" t="n"/>
+      <c r="G100" s="25" t="n"/>
+      <c r="H100" s="37" t="n"/>
+      <c r="I100" s="16" t="n"/>
+      <c r="J100" s="16" t="n"/>
+      <c r="K100" s="38" t="n"/>
+      <c r="L100" s="26" t="n"/>
+      <c r="M100" s="37" t="n"/>
+      <c r="N100" s="16" t="n"/>
+      <c r="O100" s="16" t="n"/>
+      <c r="P100" s="38" t="n"/>
+      <c r="Q100" s="27" t="n"/>
+      <c r="R100" s="16" t="n"/>
+    </row>
+    <row r="101" ht="3.8525" customHeight="1">
+      <c r="A101" s="16" t="n"/>
+      <c r="B101" s="37" t="n"/>
+      <c r="C101" s="16" t="n"/>
+      <c r="D101" s="16" t="n"/>
+      <c r="E101" s="38" t="n"/>
+      <c r="F101" s="16" t="n"/>
+      <c r="G101" s="25" t="n"/>
+      <c r="H101" s="37" t="n"/>
+      <c r="I101" s="16" t="n"/>
+      <c r="J101" s="16" t="n"/>
+      <c r="K101" s="38" t="n"/>
+      <c r="L101" s="26" t="n"/>
+      <c r="M101" s="37" t="n"/>
+      <c r="N101" s="16" t="n"/>
+      <c r="O101" s="16" t="n"/>
+      <c r="P101" s="38" t="n"/>
+      <c r="Q101" s="27" t="n"/>
+      <c r="R101" s="16" t="n"/>
+    </row>
+    <row r="102" ht="3.8525" customHeight="1">
+      <c r="A102" s="16" t="n"/>
+      <c r="B102" s="37" t="n"/>
+      <c r="C102" s="16" t="n"/>
+      <c r="D102" s="16" t="n"/>
+      <c r="E102" s="38" t="n"/>
+      <c r="F102" s="16" t="n"/>
+      <c r="G102" s="25" t="n"/>
+      <c r="H102" s="37" t="n"/>
+      <c r="I102" s="16" t="n"/>
+      <c r="J102" s="16" t="n"/>
+      <c r="K102" s="38" t="n"/>
+      <c r="L102" s="26" t="n"/>
+      <c r="M102" s="37" t="n"/>
+      <c r="N102" s="16" t="n"/>
+      <c r="O102" s="16" t="n"/>
+      <c r="P102" s="38" t="n"/>
+      <c r="Q102" s="27" t="n"/>
+      <c r="R102" s="16" t="n"/>
+    </row>
+    <row r="103" ht="3.8525" customHeight="1">
+      <c r="A103" s="16" t="n"/>
+      <c r="B103" s="37" t="n"/>
+      <c r="C103" s="16" t="n"/>
+      <c r="D103" s="16" t="n"/>
+      <c r="E103" s="38" t="n"/>
+      <c r="F103" s="16" t="n"/>
+      <c r="G103" s="25" t="n"/>
+      <c r="H103" s="37" t="n"/>
+      <c r="I103" s="16" t="n"/>
+      <c r="J103" s="16" t="n"/>
+      <c r="K103" s="38" t="n"/>
+      <c r="L103" s="26" t="n"/>
+      <c r="M103" s="37" t="n"/>
+      <c r="N103" s="16" t="n"/>
+      <c r="O103" s="16" t="n"/>
+      <c r="P103" s="38" t="n"/>
+      <c r="Q103" s="27" t="n"/>
+      <c r="R103" s="16" t="n"/>
+    </row>
+    <row r="104" ht="3.8525" customHeight="1">
+      <c r="A104" s="16" t="n"/>
+      <c r="B104" s="37" t="n"/>
+      <c r="C104" s="44" t="inlineStr">
+        <is>
+          <t>Availability &amp; reach</t>
+        </is>
+      </c>
+      <c r="D104" s="16" t="n"/>
+      <c r="E104" s="38" t="n"/>
+      <c r="F104" s="16" t="n"/>
+      <c r="G104" s="25" t="n"/>
+      <c r="H104" s="37" t="n"/>
+      <c r="I104" s="16" t="n"/>
+      <c r="J104" s="16" t="n"/>
+      <c r="K104" s="38" t="n"/>
+      <c r="L104" s="26" t="n"/>
+      <c r="M104" s="37" t="n"/>
+      <c r="N104" s="44" t="inlineStr">
+        <is>
+          <t>When plans change</t>
+        </is>
+      </c>
+      <c r="O104" s="16" t="n"/>
+      <c r="P104" s="38" t="n"/>
+      <c r="Q104" s="27" t="n"/>
+      <c r="R104" s="16" t="n"/>
+    </row>
+    <row r="105" ht="3.8525" customHeight="1">
+      <c r="A105" s="16" t="n"/>
+      <c r="B105" s="37" t="n"/>
+      <c r="C105" s="16" t="n"/>
+      <c r="D105" s="16" t="n"/>
+      <c r="E105" s="38" t="n"/>
+      <c r="F105" s="16" t="n"/>
+      <c r="G105" s="25" t="n"/>
+      <c r="H105" s="37" t="n"/>
+      <c r="I105" s="45" t="inlineStr">
+        <is>
+          <t>Putting the right clinician with the right patient.</t>
+        </is>
+      </c>
+      <c r="J105" s="16" t="n"/>
+      <c r="K105" s="38" t="n"/>
+      <c r="L105" s="26" t="n"/>
+      <c r="M105" s="37" t="n"/>
+      <c r="N105" s="16" t="n"/>
+      <c r="O105" s="16" t="n"/>
+      <c r="P105" s="38" t="n"/>
+      <c r="Q105" s="27" t="n"/>
+      <c r="R105" s="16" t="n"/>
+    </row>
+    <row r="106" ht="3.8525" customHeight="1">
+      <c r="A106" s="16" t="n"/>
+      <c r="B106" s="37" t="n"/>
+      <c r="C106" s="16" t="n"/>
+      <c r="D106" s="16" t="n"/>
+      <c r="E106" s="38" t="n"/>
+      <c r="F106" s="16" t="n"/>
+      <c r="G106" s="25" t="n"/>
+      <c r="H106" s="37" t="n"/>
+      <c r="I106" s="16" t="n"/>
+      <c r="J106" s="16" t="n"/>
+      <c r="K106" s="38" t="n"/>
+      <c r="L106" s="26" t="n"/>
+      <c r="M106" s="37" t="n"/>
+      <c r="N106" s="16" t="n"/>
+      <c r="O106" s="16" t="n"/>
+      <c r="P106" s="38" t="n"/>
+      <c r="Q106" s="27" t="n"/>
+      <c r="R106" s="16" t="n"/>
+    </row>
+    <row r="107" ht="3.8525" customHeight="1">
+      <c r="A107" s="16" t="n"/>
+      <c r="B107" s="37" t="n"/>
+      <c r="C107" s="16" t="n"/>
+      <c r="D107" s="16" t="n"/>
+      <c r="E107" s="38" t="n"/>
+      <c r="F107" s="16" t="n"/>
+      <c r="G107" s="25" t="n"/>
+      <c r="H107" s="37" t="n"/>
+      <c r="I107" s="16" t="n"/>
+      <c r="J107" s="16" t="n"/>
+      <c r="K107" s="38" t="n"/>
+      <c r="L107" s="26" t="n"/>
+      <c r="M107" s="37" t="n"/>
+      <c r="N107" s="16" t="n"/>
+      <c r="O107" s="16" t="n"/>
+      <c r="P107" s="38" t="n"/>
+      <c r="Q107" s="27" t="n"/>
+      <c r="R107" s="16" t="n"/>
+    </row>
+    <row r="108" ht="3.8525" customHeight="1">
+      <c r="A108" s="16" t="n"/>
+      <c r="B108" s="37" t="n"/>
+      <c r="C108" s="16" t="n"/>
+      <c r="D108" s="16" t="n"/>
+      <c r="E108" s="38" t="n"/>
+      <c r="F108" s="16" t="n"/>
+      <c r="G108" s="25" t="n"/>
+      <c r="H108" s="37" t="n"/>
+      <c r="I108" s="16" t="n"/>
+      <c r="J108" s="16" t="n"/>
+      <c r="K108" s="38" t="n"/>
+      <c r="L108" s="26" t="n"/>
+      <c r="M108" s="37" t="n"/>
+      <c r="N108" s="16" t="n"/>
+      <c r="O108" s="16" t="n"/>
+      <c r="P108" s="38" t="n"/>
+      <c r="Q108" s="27" t="n"/>
+      <c r="R108" s="16" t="n"/>
+    </row>
+    <row r="109" ht="3.8525" customHeight="1">
+      <c r="A109" s="16" t="n"/>
+      <c r="B109" s="37" t="n"/>
+      <c r="C109" s="16" t="n"/>
+      <c r="D109" s="16" t="n"/>
+      <c r="E109" s="38" t="n"/>
+      <c r="F109" s="16" t="n"/>
+      <c r="G109" s="25" t="n"/>
+      <c r="H109" s="37" t="n"/>
+      <c r="I109" s="16" t="n"/>
+      <c r="J109" s="16" t="n"/>
+      <c r="K109" s="38" t="n"/>
+      <c r="L109" s="26" t="n"/>
+      <c r="M109" s="37" t="n"/>
+      <c r="N109" s="16" t="n"/>
+      <c r="O109" s="16" t="n"/>
+      <c r="P109" s="38" t="n"/>
+      <c r="Q109" s="27" t="n"/>
+      <c r="R109" s="16" t="n"/>
+    </row>
+    <row r="110" ht="3.8525" customHeight="1">
+      <c r="A110" s="16" t="n"/>
+      <c r="B110" s="37" t="n"/>
+      <c r="C110" s="45" t="inlineStr">
+        <is>
+          <t>When each clinician works, and where they can actually get to.</t>
+        </is>
+      </c>
+      <c r="D110" s="16" t="n"/>
+      <c r="E110" s="38" t="n"/>
+      <c r="F110" s="16" t="n"/>
+      <c r="G110" s="25" t="n"/>
+      <c r="H110" s="37" t="n"/>
+      <c r="I110" s="16" t="n"/>
+      <c r="J110" s="16" t="n"/>
+      <c r="K110" s="38" t="n"/>
+      <c r="L110" s="26" t="n"/>
+      <c r="M110" s="37" t="n"/>
+      <c r="N110" s="45" t="inlineStr">
+        <is>
+          <t>Recovering a visit rather than losing it — with the patient and the clinician.</t>
+        </is>
+      </c>
+      <c r="O110" s="16" t="n"/>
+      <c r="P110" s="38" t="n"/>
+      <c r="Q110" s="27" t="n"/>
+      <c r="R110" s="16" t="n"/>
+    </row>
+    <row r="111" ht="3.8525" customHeight="1">
+      <c r="A111" s="16" t="n"/>
+      <c r="B111" s="37" t="n"/>
+      <c r="C111" s="16" t="n"/>
+      <c r="D111" s="16" t="n"/>
+      <c r="E111" s="38" t="n"/>
+      <c r="F111" s="16" t="n"/>
+      <c r="G111" s="25" t="n"/>
+      <c r="H111" s="37" t="n"/>
+      <c r="I111" s="46" t="inlineStr">
+        <is>
+          <t>•</t>
+        </is>
+      </c>
+      <c r="J111" s="43" t="inlineStr">
+        <is>
+          <t>Discipline and role match, specialty competency, acuity to skill level</t>
+        </is>
+      </c>
+      <c r="K111" s="38" t="n"/>
+      <c r="L111" s="26" t="n"/>
+      <c r="M111" s="37" t="n"/>
+      <c r="N111" s="16" t="n"/>
+      <c r="O111" s="16" t="n"/>
+      <c r="P111" s="38" t="n"/>
+      <c r="Q111" s="27" t="n"/>
+      <c r="R111" s="16" t="n"/>
+    </row>
+    <row r="112" ht="3.8525" customHeight="1">
+      <c r="A112" s="16" t="n"/>
+      <c r="B112" s="37" t="n"/>
+      <c r="C112" s="16" t="n"/>
+      <c r="D112" s="16" t="n"/>
+      <c r="E112" s="38" t="n"/>
+      <c r="F112" s="16" t="n"/>
+      <c r="G112" s="25" t="n"/>
+      <c r="H112" s="37" t="n"/>
+      <c r="I112" s="16" t="n"/>
+      <c r="J112" s="16" t="n"/>
+      <c r="K112" s="38" t="n"/>
+      <c r="L112" s="26" t="n"/>
+      <c r="M112" s="37" t="n"/>
+      <c r="N112" s="16" t="n"/>
+      <c r="O112" s="16" t="n"/>
+      <c r="P112" s="38" t="n"/>
+      <c r="Q112" s="27" t="n"/>
+      <c r="R112" s="16" t="n"/>
+    </row>
+    <row r="113" ht="3.8525" customHeight="1">
+      <c r="A113" s="16" t="n"/>
+      <c r="B113" s="37" t="n"/>
+      <c r="C113" s="16" t="n"/>
+      <c r="D113" s="16" t="n"/>
+      <c r="E113" s="38" t="n"/>
+      <c r="F113" s="16" t="n"/>
+      <c r="G113" s="25" t="n"/>
+      <c r="H113" s="37" t="n"/>
+      <c r="I113" s="16" t="n"/>
+      <c r="J113" s="16" t="n"/>
+      <c r="K113" s="38" t="n"/>
+      <c r="L113" s="26" t="n"/>
+      <c r="M113" s="37" t="n"/>
+      <c r="N113" s="16" t="n"/>
+      <c r="O113" s="16" t="n"/>
+      <c r="P113" s="38" t="n"/>
+      <c r="Q113" s="27" t="n"/>
+      <c r="R113" s="16" t="n"/>
+    </row>
+    <row r="114" ht="3.8525" customHeight="1">
+      <c r="A114" s="16" t="n"/>
+      <c r="B114" s="37" t="n"/>
+      <c r="C114" s="16" t="n"/>
+      <c r="D114" s="16" t="n"/>
+      <c r="E114" s="38" t="n"/>
+      <c r="F114" s="16" t="n"/>
+      <c r="G114" s="25" t="n"/>
+      <c r="H114" s="37" t="n"/>
+      <c r="I114" s="16" t="n"/>
+      <c r="J114" s="16" t="n"/>
+      <c r="K114" s="38" t="n"/>
+      <c r="L114" s="26" t="n"/>
+      <c r="M114" s="37" t="n"/>
+      <c r="N114" s="16" t="n"/>
+      <c r="O114" s="16" t="n"/>
+      <c r="P114" s="38" t="n"/>
+      <c r="Q114" s="27" t="n"/>
+      <c r="R114" s="16" t="n"/>
+    </row>
+    <row r="115" ht="3.8525" customHeight="1">
+      <c r="A115" s="16" t="n"/>
+      <c r="B115" s="37" t="n"/>
+      <c r="C115" s="16" t="n"/>
+      <c r="D115" s="16" t="n"/>
+      <c r="E115" s="38" t="n"/>
+      <c r="F115" s="16" t="n"/>
+      <c r="G115" s="25" t="n"/>
+      <c r="H115" s="37" t="n"/>
+      <c r="I115" s="16" t="n"/>
+      <c r="J115" s="16" t="n"/>
+      <c r="K115" s="38" t="n"/>
+      <c r="L115" s="26" t="n"/>
+      <c r="M115" s="37" t="n"/>
+      <c r="N115" s="16" t="n"/>
+      <c r="O115" s="16" t="n"/>
+      <c r="P115" s="38" t="n"/>
+      <c r="Q115" s="27" t="n"/>
+      <c r="R115" s="16" t="n"/>
+    </row>
+    <row r="116" ht="3.8525" customHeight="1">
+      <c r="A116" s="16" t="n"/>
+      <c r="B116" s="37" t="n"/>
+      <c r="C116" s="47" t="inlineStr">
+        <is>
+          <t>•</t>
+        </is>
+      </c>
+      <c r="D116" s="43" t="inlineStr">
+        <is>
+          <t>Approved time off and working availability</t>
+        </is>
+      </c>
+      <c r="E116" s="38" t="n"/>
+      <c r="F116" s="16" t="n"/>
+      <c r="G116" s="25" t="n"/>
+      <c r="H116" s="37" t="n"/>
+      <c r="I116" s="16" t="n"/>
+      <c r="J116" s="16" t="n"/>
+      <c r="K116" s="38" t="n"/>
+      <c r="L116" s="26" t="n"/>
+      <c r="M116" s="37" t="n"/>
+      <c r="N116" s="16" t="n"/>
+      <c r="O116" s="16" t="n"/>
+      <c r="P116" s="38" t="n"/>
+      <c r="Q116" s="27" t="n"/>
+      <c r="R116" s="16" t="n"/>
+    </row>
+    <row r="117" ht="3.8525" customHeight="1">
+      <c r="A117" s="16" t="n"/>
+      <c r="B117" s="37" t="n"/>
+      <c r="C117" s="16" t="n"/>
+      <c r="D117" s="16" t="n"/>
+      <c r="E117" s="38" t="n"/>
+      <c r="F117" s="16" t="n"/>
+      <c r="G117" s="25" t="n"/>
+      <c r="H117" s="37" t="n"/>
+      <c r="I117" s="16" t="n"/>
+      <c r="J117" s="16" t="n"/>
+      <c r="K117" s="38" t="n"/>
+      <c r="L117" s="26" t="n"/>
+      <c r="M117" s="37" t="n"/>
+      <c r="N117" s="16" t="n"/>
+      <c r="O117" s="16" t="n"/>
+      <c r="P117" s="38" t="n"/>
+      <c r="Q117" s="27" t="n"/>
+      <c r="R117" s="16" t="n"/>
+    </row>
+    <row r="118" ht="3.8525" customHeight="1">
+      <c r="A118" s="16" t="n"/>
+      <c r="B118" s="37" t="n"/>
+      <c r="C118" s="16" t="n"/>
+      <c r="D118" s="16" t="n"/>
+      <c r="E118" s="38" t="n"/>
+      <c r="F118" s="16" t="n"/>
+      <c r="G118" s="25" t="n"/>
+      <c r="H118" s="37" t="n"/>
+      <c r="I118" s="16" t="n"/>
+      <c r="J118" s="16" t="n"/>
+      <c r="K118" s="38" t="n"/>
+      <c r="L118" s="26" t="n"/>
+      <c r="M118" s="37" t="n"/>
+      <c r="N118" s="16" t="n"/>
+      <c r="O118" s="16" t="n"/>
+      <c r="P118" s="38" t="n"/>
+      <c r="Q118" s="27" t="n"/>
+      <c r="R118" s="16" t="n"/>
+    </row>
+    <row r="119" ht="3.8525" customHeight="1">
+      <c r="A119" s="16" t="n"/>
+      <c r="B119" s="37" t="n"/>
+      <c r="C119" s="16" t="n"/>
+      <c r="D119" s="16" t="n"/>
+      <c r="E119" s="38" t="n"/>
+      <c r="F119" s="16" t="n"/>
+      <c r="G119" s="25" t="n"/>
+      <c r="H119" s="37" t="n"/>
+      <c r="I119" s="16" t="n"/>
+      <c r="J119" s="16" t="n"/>
+      <c r="K119" s="38" t="n"/>
+      <c r="L119" s="26" t="n"/>
+      <c r="M119" s="37" t="n"/>
+      <c r="N119" s="16" t="n"/>
+      <c r="O119" s="16" t="n"/>
+      <c r="P119" s="38" t="n"/>
+      <c r="Q119" s="27" t="n"/>
+      <c r="R119" s="16" t="n"/>
+    </row>
+    <row r="120" ht="3.8525" customHeight="1">
+      <c r="A120" s="16" t="n"/>
+      <c r="B120" s="37" t="n"/>
+      <c r="C120" s="16" t="n"/>
+      <c r="D120" s="16" t="n"/>
+      <c r="E120" s="38" t="n"/>
+      <c r="F120" s="16" t="n"/>
+      <c r="G120" s="25" t="n"/>
+      <c r="H120" s="37" t="n"/>
+      <c r="I120" s="46" t="inlineStr">
+        <is>
+          <t>•</t>
+        </is>
+      </c>
+      <c r="J120" s="43" t="inlineStr">
+        <is>
+          <t>Clinician working pattern, needs and restrictions</t>
+        </is>
+      </c>
+      <c r="K120" s="38" t="n"/>
+      <c r="L120" s="26" t="n"/>
+      <c r="M120" s="37" t="n"/>
+      <c r="N120" s="48" t="inlineStr">
+        <is>
+          <t>•</t>
+        </is>
+      </c>
+      <c r="O120" s="43" t="inlineStr">
+        <is>
+          <t>Reschedule coordination with the patient</t>
+        </is>
+      </c>
+      <c r="P120" s="38" t="n"/>
+      <c r="Q120" s="27" t="n"/>
+      <c r="R120" s="16" t="n"/>
+    </row>
+    <row r="121" ht="3.8525" customHeight="1">
+      <c r="A121" s="16" t="n"/>
+      <c r="B121" s="37" t="n"/>
+      <c r="C121" s="47" t="inlineStr">
+        <is>
+          <t>•</t>
+        </is>
+      </c>
+      <c r="D121" s="43" t="inlineStr">
+        <is>
+          <t>Clinician territory assignment by zip, against branch coverage area</t>
+        </is>
+      </c>
+      <c r="E121" s="38" t="n"/>
+      <c r="F121" s="16" t="n"/>
+      <c r="G121" s="25" t="n"/>
+      <c r="H121" s="37" t="n"/>
+      <c r="I121" s="16" t="n"/>
+      <c r="J121" s="16" t="n"/>
+      <c r="K121" s="38" t="n"/>
+      <c r="L121" s="26" t="n"/>
+      <c r="M121" s="37" t="n"/>
+      <c r="N121" s="16" t="n"/>
+      <c r="O121" s="16" t="n"/>
+      <c r="P121" s="38" t="n"/>
+      <c r="Q121" s="27" t="n"/>
+      <c r="R121" s="16" t="n"/>
+    </row>
+    <row r="122" ht="3.8525" customHeight="1">
+      <c r="A122" s="16" t="n"/>
+      <c r="B122" s="37" t="n"/>
+      <c r="C122" s="16" t="n"/>
+      <c r="D122" s="16" t="n"/>
+      <c r="E122" s="38" t="n"/>
+      <c r="F122" s="16" t="n"/>
+      <c r="G122" s="25" t="n"/>
+      <c r="H122" s="37" t="n"/>
+      <c r="I122" s="16" t="n"/>
+      <c r="J122" s="16" t="n"/>
+      <c r="K122" s="38" t="n"/>
+      <c r="L122" s="26" t="n"/>
+      <c r="M122" s="37" t="n"/>
+      <c r="N122" s="16" t="n"/>
+      <c r="O122" s="16" t="n"/>
+      <c r="P122" s="38" t="n"/>
+      <c r="Q122" s="27" t="n"/>
+      <c r="R122" s="16" t="n"/>
+    </row>
+    <row r="123" ht="3.8525" customHeight="1">
+      <c r="A123" s="16" t="n"/>
+      <c r="B123" s="37" t="n"/>
+      <c r="C123" s="16" t="n"/>
+      <c r="D123" s="16" t="n"/>
+      <c r="E123" s="38" t="n"/>
+      <c r="F123" s="16" t="n"/>
+      <c r="G123" s="25" t="n"/>
+      <c r="H123" s="37" t="n"/>
+      <c r="I123" s="16" t="n"/>
+      <c r="J123" s="16" t="n"/>
+      <c r="K123" s="38" t="n"/>
+      <c r="L123" s="26" t="n"/>
+      <c r="M123" s="37" t="n"/>
+      <c r="N123" s="16" t="n"/>
+      <c r="O123" s="16" t="n"/>
+      <c r="P123" s="38" t="n"/>
+      <c r="Q123" s="27" t="n"/>
+      <c r="R123" s="16" t="n"/>
+    </row>
+    <row r="124" ht="3.8525" customHeight="1">
+      <c r="A124" s="16" t="n"/>
+      <c r="B124" s="37" t="n"/>
+      <c r="C124" s="16" t="n"/>
+      <c r="D124" s="16" t="n"/>
+      <c r="E124" s="38" t="n"/>
+      <c r="F124" s="16" t="n"/>
+      <c r="G124" s="25" t="n"/>
+      <c r="H124" s="37" t="n"/>
+      <c r="I124" s="16" t="n"/>
+      <c r="J124" s="16" t="n"/>
+      <c r="K124" s="38" t="n"/>
+      <c r="L124" s="26" t="n"/>
+      <c r="M124" s="37" t="n"/>
+      <c r="N124" s="16" t="n"/>
+      <c r="O124" s="16" t="n"/>
+      <c r="P124" s="38" t="n"/>
+      <c r="Q124" s="27" t="n"/>
+      <c r="R124" s="16" t="n"/>
+    </row>
+    <row r="125" ht="3.8525" customHeight="1">
+      <c r="A125" s="16" t="n"/>
+      <c r="B125" s="37" t="n"/>
+      <c r="C125" s="16" t="n"/>
+      <c r="D125" s="16" t="n"/>
+      <c r="E125" s="38" t="n"/>
+      <c r="F125" s="16" t="n"/>
+      <c r="G125" s="25" t="n"/>
+      <c r="H125" s="37" t="n"/>
+      <c r="I125" s="46" t="inlineStr">
+        <is>
+          <t>•</t>
+        </is>
+      </c>
+      <c r="J125" s="43" t="inlineStr">
+        <is>
+          <t>Patient and caregiver needs, restrictions and availability, sourced from the patient</t>
+        </is>
+      </c>
+      <c r="K125" s="38" t="n"/>
+      <c r="L125" s="26" t="n"/>
+      <c r="M125" s="37" t="n"/>
+      <c r="N125" s="48" t="inlineStr">
+        <is>
+          <t>•</t>
+        </is>
+      </c>
+      <c r="O125" s="43" t="inlineStr">
+        <is>
+          <t>Coverage coordination — matching potential clinicians to an open need, and reaching them directly</t>
+        </is>
+      </c>
+      <c r="P125" s="38" t="n"/>
+      <c r="Q125" s="27" t="n"/>
+      <c r="R125" s="16" t="n"/>
+    </row>
+    <row r="126" ht="3.8525" customHeight="1">
+      <c r="A126" s="16" t="n"/>
+      <c r="B126" s="37" t="n"/>
+      <c r="C126" s="16" t="n"/>
+      <c r="D126" s="16" t="n"/>
+      <c r="E126" s="38" t="n"/>
+      <c r="F126" s="16" t="n"/>
+      <c r="G126" s="25" t="n"/>
+      <c r="H126" s="37" t="n"/>
+      <c r="I126" s="16" t="n"/>
+      <c r="J126" s="16" t="n"/>
+      <c r="K126" s="38" t="n"/>
+      <c r="L126" s="26" t="n"/>
+      <c r="M126" s="37" t="n"/>
+      <c r="N126" s="16" t="n"/>
+      <c r="O126" s="16" t="n"/>
+      <c r="P126" s="38" t="n"/>
+      <c r="Q126" s="27" t="n"/>
+      <c r="R126" s="16" t="n"/>
+    </row>
+    <row r="127" ht="3.8525" customHeight="1">
+      <c r="A127" s="16" t="n"/>
+      <c r="B127" s="37" t="n"/>
+      <c r="C127" s="16" t="n"/>
+      <c r="D127" s="16" t="n"/>
+      <c r="E127" s="38" t="n"/>
+      <c r="F127" s="16" t="n"/>
+      <c r="G127" s="25" t="n"/>
+      <c r="H127" s="37" t="n"/>
+      <c r="I127" s="16" t="n"/>
+      <c r="J127" s="16" t="n"/>
+      <c r="K127" s="38" t="n"/>
+      <c r="L127" s="26" t="n"/>
+      <c r="M127" s="37" t="n"/>
+      <c r="N127" s="16" t="n"/>
+      <c r="O127" s="16" t="n"/>
+      <c r="P127" s="38" t="n"/>
+      <c r="Q127" s="27" t="n"/>
+      <c r="R127" s="16" t="n"/>
+    </row>
+    <row r="128" ht="3.8525" customHeight="1">
+      <c r="A128" s="16" t="n"/>
+      <c r="B128" s="37" t="n"/>
+      <c r="C128" s="16" t="n"/>
+      <c r="D128" s="16" t="n"/>
+      <c r="E128" s="38" t="n"/>
+      <c r="F128" s="16" t="n"/>
+      <c r="G128" s="25" t="n"/>
+      <c r="H128" s="37" t="n"/>
+      <c r="I128" s="16" t="n"/>
+      <c r="J128" s="16" t="n"/>
+      <c r="K128" s="38" t="n"/>
+      <c r="L128" s="26" t="n"/>
+      <c r="M128" s="37" t="n"/>
+      <c r="N128" s="16" t="n"/>
+      <c r="O128" s="16" t="n"/>
+      <c r="P128" s="38" t="n"/>
+      <c r="Q128" s="27" t="n"/>
+      <c r="R128" s="16" t="n"/>
+    </row>
+    <row r="129" ht="3.8525" customHeight="1">
+      <c r="A129" s="16" t="n"/>
+      <c r="B129" s="37" t="n"/>
+      <c r="C129" s="16" t="n"/>
+      <c r="D129" s="16" t="n"/>
+      <c r="E129" s="38" t="n"/>
+      <c r="F129" s="16" t="n"/>
+      <c r="G129" s="25" t="n"/>
+      <c r="H129" s="37" t="n"/>
+      <c r="I129" s="16" t="n"/>
+      <c r="J129" s="16" t="n"/>
+      <c r="K129" s="38" t="n"/>
+      <c r="L129" s="26" t="n"/>
+      <c r="M129" s="37" t="n"/>
+      <c r="N129" s="16" t="n"/>
+      <c r="O129" s="16" t="n"/>
+      <c r="P129" s="38" t="n"/>
+      <c r="Q129" s="27" t="n"/>
+      <c r="R129" s="16" t="n"/>
+    </row>
+    <row r="130" ht="3.8525" customHeight="1">
+      <c r="A130" s="16" t="n"/>
+      <c r="B130" s="37" t="n"/>
+      <c r="C130" s="47" t="inlineStr">
+        <is>
+          <t>•</t>
+        </is>
+      </c>
+      <c r="D130" s="43" t="inlineStr">
+        <is>
+          <t>Reachability from the clinician's home base, measured by drive time</t>
+        </is>
+      </c>
+      <c r="E130" s="38" t="n"/>
+      <c r="F130" s="16" t="n"/>
+      <c r="G130" s="25" t="n"/>
+      <c r="H130" s="37" t="n"/>
+      <c r="I130" s="16" t="n"/>
+      <c r="J130" s="16" t="n"/>
+      <c r="K130" s="38" t="n"/>
+      <c r="L130" s="26" t="n"/>
+      <c r="M130" s="37" t="n"/>
+      <c r="N130" s="16" t="n"/>
+      <c r="O130" s="16" t="n"/>
+      <c r="P130" s="38" t="n"/>
+      <c r="Q130" s="27" t="n"/>
+      <c r="R130" s="16" t="n"/>
+    </row>
+    <row r="131" ht="3.8525" customHeight="1">
+      <c r="A131" s="16" t="n"/>
+      <c r="B131" s="37" t="n"/>
+      <c r="C131" s="16" t="n"/>
+      <c r="D131" s="16" t="n"/>
+      <c r="E131" s="38" t="n"/>
+      <c r="F131" s="16" t="n"/>
+      <c r="G131" s="25" t="n"/>
+      <c r="H131" s="37" t="n"/>
+      <c r="I131" s="16" t="n"/>
+      <c r="J131" s="16" t="n"/>
+      <c r="K131" s="38" t="n"/>
+      <c r="L131" s="26" t="n"/>
+      <c r="M131" s="37" t="n"/>
+      <c r="N131" s="16" t="n"/>
+      <c r="O131" s="16" t="n"/>
+      <c r="P131" s="38" t="n"/>
+      <c r="Q131" s="27" t="n"/>
+      <c r="R131" s="16" t="n"/>
+    </row>
+    <row r="132" ht="3.8525" customHeight="1">
+      <c r="A132" s="16" t="n"/>
+      <c r="B132" s="37" t="n"/>
+      <c r="C132" s="16" t="n"/>
+      <c r="D132" s="16" t="n"/>
+      <c r="E132" s="38" t="n"/>
+      <c r="F132" s="16" t="n"/>
+      <c r="G132" s="25" t="n"/>
+      <c r="H132" s="37" t="n"/>
+      <c r="I132" s="16" t="n"/>
+      <c r="J132" s="16" t="n"/>
+      <c r="K132" s="38" t="n"/>
+      <c r="L132" s="26" t="n"/>
+      <c r="M132" s="37" t="n"/>
+      <c r="N132" s="16" t="n"/>
+      <c r="O132" s="16" t="n"/>
+      <c r="P132" s="38" t="n"/>
+      <c r="Q132" s="27" t="n"/>
+      <c r="R132" s="16" t="n"/>
+    </row>
+    <row r="133" ht="3.8525" customHeight="1">
+      <c r="A133" s="16" t="n"/>
+      <c r="B133" s="37" t="n"/>
+      <c r="C133" s="16" t="n"/>
+      <c r="D133" s="16" t="n"/>
+      <c r="E133" s="38" t="n"/>
+      <c r="F133" s="16" t="n"/>
+      <c r="G133" s="25" t="n"/>
+      <c r="H133" s="37" t="n"/>
+      <c r="I133" s="16" t="n"/>
+      <c r="J133" s="16" t="n"/>
+      <c r="K133" s="38" t="n"/>
+      <c r="L133" s="26" t="n"/>
+      <c r="M133" s="37" t="n"/>
+      <c r="N133" s="16" t="n"/>
+      <c r="O133" s="16" t="n"/>
+      <c r="P133" s="38" t="n"/>
+      <c r="Q133" s="27" t="n"/>
+      <c r="R133" s="16" t="n"/>
+    </row>
+    <row r="134" ht="3.8525" customHeight="1">
+      <c r="A134" s="16" t="n"/>
+      <c r="B134" s="37" t="n"/>
+      <c r="C134" s="16" t="n"/>
+      <c r="D134" s="16" t="n"/>
+      <c r="E134" s="38" t="n"/>
+      <c r="F134" s="16" t="n"/>
+      <c r="G134" s="25" t="n"/>
+      <c r="H134" s="37" t="n"/>
+      <c r="I134" s="46" t="inlineStr">
+        <is>
+          <t>•</t>
+        </is>
+      </c>
+      <c r="J134" s="43" t="inlineStr">
+        <is>
+          <t>Clinical timing — diagnosis-driven cadence, competing appointments, infection-control sequencing</t>
+        </is>
+      </c>
+      <c r="K134" s="38" t="n"/>
+      <c r="L134" s="26" t="n"/>
+      <c r="M134" s="37" t="n"/>
+      <c r="N134" s="48" t="inlineStr">
+        <is>
+          <t>•</t>
+        </is>
+      </c>
+      <c r="O134" s="43" t="inlineStr">
+        <is>
+          <t>Call-out coverage, and the urgent or prioritized needs that surface during the day</t>
+        </is>
+      </c>
+      <c r="P134" s="38" t="n"/>
+      <c r="Q134" s="27" t="n"/>
+      <c r="R134" s="16" t="n"/>
+    </row>
+    <row r="135" ht="3.8525" customHeight="1">
+      <c r="A135" s="16" t="n"/>
+      <c r="B135" s="37" t="n"/>
+      <c r="C135" s="16" t="n"/>
+      <c r="D135" s="16" t="n"/>
+      <c r="E135" s="38" t="n"/>
+      <c r="F135" s="16" t="n"/>
+      <c r="G135" s="25" t="n"/>
+      <c r="H135" s="37" t="n"/>
+      <c r="I135" s="16" t="n"/>
+      <c r="J135" s="16" t="n"/>
+      <c r="K135" s="38" t="n"/>
+      <c r="L135" s="26" t="n"/>
+      <c r="M135" s="37" t="n"/>
+      <c r="N135" s="16" t="n"/>
+      <c r="O135" s="16" t="n"/>
+      <c r="P135" s="38" t="n"/>
+      <c r="Q135" s="27" t="n"/>
+      <c r="R135" s="16" t="n"/>
+    </row>
+    <row r="136" ht="3.8525" customHeight="1">
+      <c r="A136" s="16" t="n"/>
+      <c r="B136" s="37" t="n"/>
+      <c r="C136" s="16" t="n"/>
+      <c r="D136" s="16" t="n"/>
+      <c r="E136" s="38" t="n"/>
+      <c r="F136" s="16" t="n"/>
+      <c r="G136" s="25" t="n"/>
+      <c r="H136" s="37" t="n"/>
+      <c r="I136" s="16" t="n"/>
+      <c r="J136" s="16" t="n"/>
+      <c r="K136" s="38" t="n"/>
+      <c r="L136" s="26" t="n"/>
+      <c r="M136" s="37" t="n"/>
+      <c r="N136" s="16" t="n"/>
+      <c r="O136" s="16" t="n"/>
+      <c r="P136" s="38" t="n"/>
+      <c r="Q136" s="27" t="n"/>
+      <c r="R136" s="16" t="n"/>
+    </row>
+    <row r="137" ht="3.8525" customHeight="1">
+      <c r="A137" s="16" t="n"/>
+      <c r="B137" s="37" t="n"/>
+      <c r="C137" s="16" t="n"/>
+      <c r="D137" s="16" t="n"/>
+      <c r="E137" s="38" t="n"/>
+      <c r="F137" s="16" t="n"/>
+      <c r="G137" s="25" t="n"/>
+      <c r="H137" s="37" t="n"/>
+      <c r="I137" s="16" t="n"/>
+      <c r="J137" s="16" t="n"/>
+      <c r="K137" s="38" t="n"/>
+      <c r="L137" s="26" t="n"/>
+      <c r="M137" s="37" t="n"/>
+      <c r="N137" s="16" t="n"/>
+      <c r="O137" s="16" t="n"/>
+      <c r="P137" s="38" t="n"/>
+      <c r="Q137" s="27" t="n"/>
+      <c r="R137" s="16" t="n"/>
+    </row>
+    <row r="138" ht="3.8525" customHeight="1">
+      <c r="A138" s="16" t="n"/>
+      <c r="B138" s="37" t="n"/>
+      <c r="C138" s="16" t="n"/>
+      <c r="D138" s="16" t="n"/>
+      <c r="E138" s="38" t="n"/>
+      <c r="F138" s="16" t="n"/>
+      <c r="G138" s="25" t="n"/>
+      <c r="H138" s="37" t="n"/>
+      <c r="I138" s="16" t="n"/>
+      <c r="J138" s="16" t="n"/>
+      <c r="K138" s="38" t="n"/>
+      <c r="L138" s="26" t="n"/>
+      <c r="M138" s="37" t="n"/>
+      <c r="N138" s="16" t="n"/>
+      <c r="O138" s="16" t="n"/>
+      <c r="P138" s="38" t="n"/>
+      <c r="Q138" s="27" t="n"/>
+      <c r="R138" s="16" t="n"/>
+    </row>
+    <row r="139" ht="3.8525" customHeight="1">
+      <c r="A139" s="16" t="n"/>
+      <c r="B139" s="37" t="n"/>
+      <c r="C139" s="16" t="n"/>
+      <c r="D139" s="16" t="n"/>
+      <c r="E139" s="38" t="n"/>
+      <c r="F139" s="16" t="n"/>
+      <c r="G139" s="25" t="n"/>
+      <c r="H139" s="37" t="n"/>
+      <c r="I139" s="16" t="n"/>
+      <c r="J139" s="16" t="n"/>
+      <c r="K139" s="38" t="n"/>
+      <c r="L139" s="26" t="n"/>
+      <c r="M139" s="37" t="n"/>
+      <c r="N139" s="16" t="n"/>
+      <c r="O139" s="16" t="n"/>
+      <c r="P139" s="38" t="n"/>
+      <c r="Q139" s="27" t="n"/>
+      <c r="R139" s="16" t="n"/>
+    </row>
+    <row r="140" ht="3.8525" customHeight="1">
+      <c r="A140" s="16" t="n"/>
+      <c r="B140" s="37" t="n"/>
+      <c r="C140" s="16" t="n"/>
+      <c r="D140" s="16" t="n"/>
+      <c r="E140" s="38" t="n"/>
+      <c r="F140" s="16" t="n"/>
+      <c r="G140" s="25" t="n"/>
+      <c r="H140" s="37" t="n"/>
+      <c r="I140" s="16" t="n"/>
+      <c r="J140" s="16" t="n"/>
+      <c r="K140" s="38" t="n"/>
+      <c r="L140" s="26" t="n"/>
+      <c r="M140" s="37" t="n"/>
+      <c r="N140" s="16" t="n"/>
+      <c r="O140" s="16" t="n"/>
+      <c r="P140" s="38" t="n"/>
+      <c r="Q140" s="27" t="n"/>
+      <c r="R140" s="16" t="n"/>
+    </row>
+    <row r="141" ht="3.8525" customHeight="1">
+      <c r="A141" s="16" t="n"/>
+      <c r="B141" s="37" t="n"/>
+      <c r="C141" s="44" t="inlineStr">
+        <is>
+          <t>The capacity math</t>
+        </is>
+      </c>
+      <c r="D141" s="16" t="n"/>
+      <c r="E141" s="38" t="n"/>
+      <c r="F141" s="16" t="n"/>
+      <c r="G141" s="25" t="n"/>
+      <c r="H141" s="37" t="n"/>
+      <c r="I141" s="16" t="n"/>
+      <c r="J141" s="16" t="n"/>
+      <c r="K141" s="38" t="n"/>
+      <c r="L141" s="26" t="n"/>
+      <c r="M141" s="37" t="n"/>
+      <c r="N141" s="16" t="n"/>
+      <c r="O141" s="16" t="n"/>
+      <c r="P141" s="38" t="n"/>
+      <c r="Q141" s="27" t="n"/>
+      <c r="R141" s="16" t="n"/>
+    </row>
+    <row r="142" ht="3.8525" customHeight="1">
+      <c r="A142" s="16" t="n"/>
+      <c r="B142" s="37" t="n"/>
+      <c r="C142" s="16" t="n"/>
+      <c r="D142" s="16" t="n"/>
+      <c r="E142" s="38" t="n"/>
+      <c r="F142" s="16" t="n"/>
+      <c r="G142" s="25" t="n"/>
+      <c r="H142" s="37" t="n"/>
+      <c r="I142" s="16" t="n"/>
+      <c r="J142" s="16" t="n"/>
+      <c r="K142" s="38" t="n"/>
+      <c r="L142" s="26" t="n"/>
+      <c r="M142" s="37" t="n"/>
+      <c r="N142" s="16" t="n"/>
+      <c r="O142" s="16" t="n"/>
+      <c r="P142" s="38" t="n"/>
+      <c r="Q142" s="27" t="n"/>
+      <c r="R142" s="16" t="n"/>
+    </row>
+    <row r="143" ht="3.8525" customHeight="1">
+      <c r="A143" s="16" t="n"/>
+      <c r="B143" s="37" t="n"/>
+      <c r="C143" s="16" t="n"/>
+      <c r="D143" s="16" t="n"/>
+      <c r="E143" s="38" t="n"/>
+      <c r="F143" s="16" t="n"/>
+      <c r="G143" s="25" t="n"/>
+      <c r="H143" s="37" t="n"/>
+      <c r="I143" s="46" t="inlineStr">
+        <is>
+          <t>•</t>
+        </is>
+      </c>
+      <c r="J143" s="43" t="inlineStr">
+        <is>
+          <t>Continuity of care, and supervisory visit dependencies</t>
+        </is>
+      </c>
+      <c r="K143" s="38" t="n"/>
+      <c r="L143" s="26" t="n"/>
+      <c r="M143" s="37" t="n"/>
+      <c r="N143" s="48" t="inlineStr">
+        <is>
+          <t>•</t>
+        </is>
+      </c>
+      <c r="O143" s="43" t="inlineStr">
+        <is>
+          <t>Failed-visit and no-show follow-up and rebooking</t>
+        </is>
+      </c>
+      <c r="P143" s="38" t="n"/>
+      <c r="Q143" s="27" t="n"/>
+      <c r="R143" s="16" t="n"/>
+    </row>
+    <row r="144" ht="3.8525" customHeight="1">
+      <c r="A144" s="16" t="n"/>
+      <c r="B144" s="37" t="n"/>
+      <c r="C144" s="16" t="n"/>
+      <c r="D144" s="16" t="n"/>
+      <c r="E144" s="38" t="n"/>
+      <c r="F144" s="16" t="n"/>
+      <c r="G144" s="25" t="n"/>
+      <c r="H144" s="37" t="n"/>
+      <c r="I144" s="16" t="n"/>
+      <c r="J144" s="16" t="n"/>
+      <c r="K144" s="38" t="n"/>
+      <c r="L144" s="26" t="n"/>
+      <c r="M144" s="37" t="n"/>
+      <c r="N144" s="16" t="n"/>
+      <c r="O144" s="16" t="n"/>
+      <c r="P144" s="38" t="n"/>
+      <c r="Q144" s="27" t="n"/>
+      <c r="R144" s="16" t="n"/>
+    </row>
+    <row r="145" ht="3.8525" customHeight="1">
+      <c r="A145" s="16" t="n"/>
+      <c r="B145" s="37" t="n"/>
+      <c r="C145" s="16" t="n"/>
+      <c r="D145" s="16" t="n"/>
+      <c r="E145" s="38" t="n"/>
+      <c r="F145" s="16" t="n"/>
+      <c r="G145" s="25" t="n"/>
+      <c r="H145" s="37" t="n"/>
+      <c r="I145" s="16" t="n"/>
+      <c r="J145" s="16" t="n"/>
+      <c r="K145" s="38" t="n"/>
+      <c r="L145" s="26" t="n"/>
+      <c r="M145" s="37" t="n"/>
+      <c r="N145" s="16" t="n"/>
+      <c r="O145" s="16" t="n"/>
+      <c r="P145" s="38" t="n"/>
+      <c r="Q145" s="27" t="n"/>
+      <c r="R145" s="16" t="n"/>
+    </row>
+    <row r="146" ht="3.8525" customHeight="1">
+      <c r="A146" s="16" t="n"/>
+      <c r="B146" s="37" t="n"/>
+      <c r="C146" s="16" t="n"/>
+      <c r="D146" s="16" t="n"/>
+      <c r="E146" s="38" t="n"/>
+      <c r="F146" s="16" t="n"/>
+      <c r="G146" s="25" t="n"/>
+      <c r="H146" s="37" t="n"/>
+      <c r="I146" s="16" t="n"/>
+      <c r="J146" s="16" t="n"/>
+      <c r="K146" s="38" t="n"/>
+      <c r="L146" s="26" t="n"/>
+      <c r="M146" s="37" t="n"/>
+      <c r="N146" s="16" t="n"/>
+      <c r="O146" s="16" t="n"/>
+      <c r="P146" s="38" t="n"/>
+      <c r="Q146" s="27" t="n"/>
+      <c r="R146" s="16" t="n"/>
+    </row>
+    <row r="147" ht="3.8525" customHeight="1">
+      <c r="A147" s="16" t="n"/>
+      <c r="B147" s="37" t="n"/>
+      <c r="C147" s="45" t="inlineStr">
+        <is>
+          <t>What is committed, what is open, and what is arriving.</t>
+        </is>
+      </c>
+      <c r="D147" s="16" t="n"/>
+      <c r="E147" s="38" t="n"/>
+      <c r="F147" s="16" t="n"/>
+      <c r="G147" s="25" t="n"/>
+      <c r="H147" s="37" t="n"/>
+      <c r="I147" s="16" t="n"/>
+      <c r="J147" s="16" t="n"/>
+      <c r="K147" s="38" t="n"/>
+      <c r="L147" s="26" t="n"/>
+      <c r="M147" s="37" t="n"/>
+      <c r="N147" s="16" t="n"/>
+      <c r="O147" s="16" t="n"/>
+      <c r="P147" s="38" t="n"/>
+      <c r="Q147" s="27" t="n"/>
+      <c r="R147" s="16" t="n"/>
+    </row>
+    <row r="148" ht="3.8525" customHeight="1">
+      <c r="A148" s="16" t="n"/>
+      <c r="B148" s="37" t="n"/>
+      <c r="C148" s="16" t="n"/>
+      <c r="D148" s="16" t="n"/>
+      <c r="E148" s="38" t="n"/>
+      <c r="F148" s="16" t="n"/>
+      <c r="G148" s="25" t="n"/>
+      <c r="H148" s="37" t="n"/>
+      <c r="I148" s="16" t="n"/>
+      <c r="J148" s="16" t="n"/>
+      <c r="K148" s="38" t="n"/>
+      <c r="L148" s="26" t="n"/>
+      <c r="M148" s="37" t="n"/>
+      <c r="N148" s="16" t="n"/>
+      <c r="O148" s="16" t="n"/>
+      <c r="P148" s="38" t="n"/>
+      <c r="Q148" s="27" t="n"/>
+      <c r="R148" s="16" t="n"/>
+    </row>
+    <row r="149" ht="3.8525" customHeight="1">
+      <c r="A149" s="16" t="n"/>
+      <c r="B149" s="37" t="n"/>
+      <c r="C149" s="16" t="n"/>
+      <c r="D149" s="16" t="n"/>
+      <c r="E149" s="38" t="n"/>
+      <c r="F149" s="16" t="n"/>
+      <c r="G149" s="25" t="n"/>
+      <c r="H149" s="37" t="n"/>
+      <c r="I149" s="16" t="n"/>
+      <c r="J149" s="16" t="n"/>
+      <c r="K149" s="38" t="n"/>
+      <c r="L149" s="26" t="n"/>
+      <c r="M149" s="37" t="n"/>
+      <c r="N149" s="16" t="n"/>
+      <c r="O149" s="16" t="n"/>
+      <c r="P149" s="38" t="n"/>
+      <c r="Q149" s="27" t="n"/>
+      <c r="R149" s="16" t="n"/>
+    </row>
+    <row r="150" ht="3.8525" customHeight="1">
+      <c r="A150" s="16" t="n"/>
+      <c r="B150" s="37" t="n"/>
+      <c r="C150" s="16" t="n"/>
+      <c r="D150" s="16" t="n"/>
+      <c r="E150" s="38" t="n"/>
+      <c r="F150" s="16" t="n"/>
+      <c r="G150" s="25" t="n"/>
+      <c r="H150" s="37" t="n"/>
+      <c r="I150" s="44" t="inlineStr">
+        <is>
+          <t>Routing &amp; the week</t>
+        </is>
+      </c>
+      <c r="J150" s="16" t="n"/>
+      <c r="K150" s="38" t="n"/>
+      <c r="L150" s="26" t="n"/>
+      <c r="M150" s="37" t="n"/>
+      <c r="N150" s="44" t="inlineStr">
+        <is>
+          <t>Across the care team</t>
+        </is>
+      </c>
+      <c r="O150" s="16" t="n"/>
+      <c r="P150" s="38" t="n"/>
+      <c r="Q150" s="27" t="n"/>
+      <c r="R150" s="16" t="n"/>
+    </row>
+    <row r="151" ht="3.8525" customHeight="1">
+      <c r="A151" s="16" t="n"/>
+      <c r="B151" s="37" t="n"/>
+      <c r="C151" s="16" t="n"/>
+      <c r="D151" s="16" t="n"/>
+      <c r="E151" s="38" t="n"/>
+      <c r="F151" s="16" t="n"/>
+      <c r="G151" s="25" t="n"/>
+      <c r="H151" s="37" t="n"/>
+      <c r="I151" s="16" t="n"/>
+      <c r="J151" s="16" t="n"/>
+      <c r="K151" s="38" t="n"/>
+      <c r="L151" s="26" t="n"/>
+      <c r="M151" s="37" t="n"/>
+      <c r="N151" s="16" t="n"/>
+      <c r="O151" s="16" t="n"/>
+      <c r="P151" s="38" t="n"/>
+      <c r="Q151" s="27" t="n"/>
+      <c r="R151" s="16" t="n"/>
+    </row>
+    <row r="152" ht="3.8525" customHeight="1">
+      <c r="A152" s="16" t="n"/>
+      <c r="B152" s="37" t="n"/>
+      <c r="C152" s="16" t="n"/>
+      <c r="D152" s="16" t="n"/>
+      <c r="E152" s="38" t="n"/>
+      <c r="F152" s="16" t="n"/>
+      <c r="G152" s="25" t="n"/>
+      <c r="H152" s="37" t="n"/>
+      <c r="I152" s="16" t="n"/>
+      <c r="J152" s="16" t="n"/>
+      <c r="K152" s="38" t="n"/>
+      <c r="L152" s="26" t="n"/>
+      <c r="M152" s="37" t="n"/>
+      <c r="N152" s="16" t="n"/>
+      <c r="O152" s="16" t="n"/>
+      <c r="P152" s="38" t="n"/>
+      <c r="Q152" s="27" t="n"/>
+      <c r="R152" s="16" t="n"/>
+    </row>
+    <row r="153" ht="3.8525" customHeight="1">
+      <c r="A153" s="16" t="n"/>
+      <c r="B153" s="37" t="n"/>
+      <c r="C153" s="47" t="inlineStr">
+        <is>
+          <t>•</t>
+        </is>
+      </c>
+      <c r="D153" s="43" t="inlineStr">
+        <is>
+          <t>Visit weighting — the point value per visit type, and the productivity target and ceiling it is measured against</t>
+        </is>
+      </c>
+      <c r="E153" s="38" t="n"/>
+      <c r="F153" s="16" t="n"/>
+      <c r="G153" s="25" t="n"/>
+      <c r="H153" s="37" t="n"/>
+      <c r="I153" s="16" t="n"/>
+      <c r="J153" s="16" t="n"/>
+      <c r="K153" s="38" t="n"/>
+      <c r="L153" s="26" t="n"/>
+      <c r="M153" s="37" t="n"/>
+      <c r="N153" s="16" t="n"/>
+      <c r="O153" s="16" t="n"/>
+      <c r="P153" s="38" t="n"/>
+      <c r="Q153" s="27" t="n"/>
+      <c r="R153" s="16" t="n"/>
+    </row>
+    <row r="154" ht="3.8525" customHeight="1">
+      <c r="A154" s="16" t="n"/>
+      <c r="B154" s="37" t="n"/>
+      <c r="C154" s="16" t="n"/>
+      <c r="D154" s="16" t="n"/>
+      <c r="E154" s="38" t="n"/>
+      <c r="F154" s="16" t="n"/>
+      <c r="G154" s="25" t="n"/>
+      <c r="H154" s="37" t="n"/>
+      <c r="I154" s="16" t="n"/>
+      <c r="J154" s="16" t="n"/>
+      <c r="K154" s="38" t="n"/>
+      <c r="L154" s="26" t="n"/>
+      <c r="M154" s="37" t="n"/>
+      <c r="N154" s="16" t="n"/>
+      <c r="O154" s="16" t="n"/>
+      <c r="P154" s="38" t="n"/>
+      <c r="Q154" s="27" t="n"/>
+      <c r="R154" s="16" t="n"/>
+    </row>
+    <row r="155" ht="3.8525" customHeight="1">
+      <c r="A155" s="16" t="n"/>
+      <c r="B155" s="37" t="n"/>
+      <c r="C155" s="16" t="n"/>
+      <c r="D155" s="16" t="n"/>
+      <c r="E155" s="38" t="n"/>
+      <c r="F155" s="16" t="n"/>
+      <c r="G155" s="25" t="n"/>
+      <c r="H155" s="37" t="n"/>
+      <c r="I155" s="16" t="n"/>
+      <c r="J155" s="16" t="n"/>
+      <c r="K155" s="38" t="n"/>
+      <c r="L155" s="26" t="n"/>
+      <c r="M155" s="37" t="n"/>
+      <c r="N155" s="16" t="n"/>
+      <c r="O155" s="16" t="n"/>
+      <c r="P155" s="38" t="n"/>
+      <c r="Q155" s="27" t="n"/>
+      <c r="R155" s="16" t="n"/>
+    </row>
+    <row r="156" ht="3.8525" customHeight="1">
+      <c r="A156" s="16" t="n"/>
+      <c r="B156" s="37" t="n"/>
+      <c r="C156" s="16" t="n"/>
+      <c r="D156" s="16" t="n"/>
+      <c r="E156" s="38" t="n"/>
+      <c r="F156" s="16" t="n"/>
+      <c r="G156" s="25" t="n"/>
+      <c r="H156" s="37" t="n"/>
+      <c r="I156" s="45" t="inlineStr">
+        <is>
+          <t>A day that works, inside a week that holds.</t>
+        </is>
+      </c>
+      <c r="J156" s="16" t="n"/>
+      <c r="K156" s="38" t="n"/>
+      <c r="L156" s="26" t="n"/>
+      <c r="M156" s="37" t="n"/>
+      <c r="N156" s="45" t="inlineStr">
+        <is>
+          <t>Keeping clinicians and the office on the same schedule.</t>
+        </is>
+      </c>
+      <c r="O156" s="16" t="n"/>
+      <c r="P156" s="38" t="n"/>
+      <c r="Q156" s="27" t="n"/>
+      <c r="R156" s="16" t="n"/>
+    </row>
+    <row r="157" ht="3.8525" customHeight="1">
+      <c r="A157" s="16" t="n"/>
+      <c r="B157" s="37" t="n"/>
+      <c r="C157" s="16" t="n"/>
+      <c r="D157" s="16" t="n"/>
+      <c r="E157" s="38" t="n"/>
+      <c r="F157" s="16" t="n"/>
+      <c r="G157" s="25" t="n"/>
+      <c r="H157" s="37" t="n"/>
+      <c r="I157" s="16" t="n"/>
+      <c r="J157" s="16" t="n"/>
+      <c r="K157" s="38" t="n"/>
+      <c r="L157" s="26" t="n"/>
+      <c r="M157" s="37" t="n"/>
+      <c r="N157" s="16" t="n"/>
+      <c r="O157" s="16" t="n"/>
+      <c r="P157" s="38" t="n"/>
+      <c r="Q157" s="27" t="n"/>
+      <c r="R157" s="16" t="n"/>
+    </row>
+    <row r="158" ht="3.8525" customHeight="1">
+      <c r="A158" s="16" t="n"/>
+      <c r="B158" s="37" t="n"/>
+      <c r="C158" s="16" t="n"/>
+      <c r="D158" s="16" t="n"/>
+      <c r="E158" s="38" t="n"/>
+      <c r="F158" s="16" t="n"/>
+      <c r="G158" s="25" t="n"/>
+      <c r="H158" s="37" t="n"/>
+      <c r="I158" s="16" t="n"/>
+      <c r="J158" s="16" t="n"/>
+      <c r="K158" s="38" t="n"/>
+      <c r="L158" s="26" t="n"/>
+      <c r="M158" s="37" t="n"/>
+      <c r="N158" s="16" t="n"/>
+      <c r="O158" s="16" t="n"/>
+      <c r="P158" s="38" t="n"/>
+      <c r="Q158" s="27" t="n"/>
+      <c r="R158" s="16" t="n"/>
+    </row>
+    <row r="159" ht="3.8525" customHeight="1">
+      <c r="A159" s="16" t="n"/>
+      <c r="B159" s="37" t="n"/>
+      <c r="C159" s="16" t="n"/>
+      <c r="D159" s="16" t="n"/>
+      <c r="E159" s="38" t="n"/>
+      <c r="F159" s="16" t="n"/>
+      <c r="G159" s="25" t="n"/>
+      <c r="H159" s="37" t="n"/>
+      <c r="I159" s="16" t="n"/>
+      <c r="J159" s="16" t="n"/>
+      <c r="K159" s="38" t="n"/>
+      <c r="L159" s="26" t="n"/>
+      <c r="M159" s="37" t="n"/>
+      <c r="N159" s="16" t="n"/>
+      <c r="O159" s="16" t="n"/>
+      <c r="P159" s="38" t="n"/>
+      <c r="Q159" s="27" t="n"/>
+      <c r="R159" s="16" t="n"/>
+    </row>
+    <row r="160" ht="3.8525" customHeight="1">
+      <c r="A160" s="16" t="n"/>
+      <c r="B160" s="37" t="n"/>
+      <c r="C160" s="16" t="n"/>
+      <c r="D160" s="16" t="n"/>
+      <c r="E160" s="38" t="n"/>
+      <c r="F160" s="16" t="n"/>
+      <c r="G160" s="25" t="n"/>
+      <c r="H160" s="37" t="n"/>
+      <c r="I160" s="16" t="n"/>
+      <c r="J160" s="16" t="n"/>
+      <c r="K160" s="38" t="n"/>
+      <c r="L160" s="26" t="n"/>
+      <c r="M160" s="37" t="n"/>
+      <c r="N160" s="16" t="n"/>
+      <c r="O160" s="16" t="n"/>
+      <c r="P160" s="38" t="n"/>
+      <c r="Q160" s="27" t="n"/>
+      <c r="R160" s="16" t="n"/>
+    </row>
+    <row r="161" ht="3.8525" customHeight="1">
+      <c r="A161" s="16" t="n"/>
+      <c r="B161" s="37" t="n"/>
+      <c r="C161" s="16" t="n"/>
+      <c r="D161" s="16" t="n"/>
+      <c r="E161" s="38" t="n"/>
+      <c r="F161" s="16" t="n"/>
+      <c r="G161" s="25" t="n"/>
+      <c r="H161" s="37" t="n"/>
+      <c r="I161" s="16" t="n"/>
+      <c r="J161" s="16" t="n"/>
+      <c r="K161" s="38" t="n"/>
+      <c r="L161" s="26" t="n"/>
+      <c r="M161" s="37" t="n"/>
+      <c r="N161" s="16" t="n"/>
+      <c r="O161" s="16" t="n"/>
+      <c r="P161" s="38" t="n"/>
+      <c r="Q161" s="27" t="n"/>
+      <c r="R161" s="16" t="n"/>
+    </row>
+    <row r="162" ht="3.8525" customHeight="1">
+      <c r="A162" s="16" t="n"/>
+      <c r="B162" s="37" t="n"/>
+      <c r="C162" s="47" t="inlineStr">
+        <is>
+          <t>•</t>
+        </is>
+      </c>
+      <c r="D162" s="43" t="inlineStr">
+        <is>
+          <t>Committed load vs. open room, by day, week, discipline and territory</t>
+        </is>
+      </c>
+      <c r="E162" s="38" t="n"/>
+      <c r="F162" s="16" t="n"/>
+      <c r="G162" s="25" t="n"/>
+      <c r="H162" s="37" t="n"/>
+      <c r="I162" s="46" t="inlineStr">
+        <is>
+          <t>•</t>
+        </is>
+      </c>
+      <c r="J162" s="43" t="inlineStr">
+        <is>
+          <t>Home base start and end, route proximity, mileage</t>
+        </is>
+      </c>
+      <c r="K162" s="38" t="n"/>
+      <c r="L162" s="26" t="n"/>
+      <c r="M162" s="37" t="n"/>
+      <c r="N162" s="48" t="inlineStr">
+        <is>
+          <t>•</t>
+        </is>
+      </c>
+      <c r="O162" s="43" t="inlineStr">
+        <is>
+          <t>Multi-discipline visit coordination</t>
+        </is>
+      </c>
+      <c r="P162" s="38" t="n"/>
+      <c r="Q162" s="27" t="n"/>
+      <c r="R162" s="16" t="n"/>
+    </row>
+    <row r="163" ht="3.8525" customHeight="1">
+      <c r="A163" s="16" t="n"/>
+      <c r="B163" s="37" t="n"/>
+      <c r="C163" s="16" t="n"/>
+      <c r="D163" s="16" t="n"/>
+      <c r="E163" s="38" t="n"/>
+      <c r="F163" s="16" t="n"/>
+      <c r="G163" s="25" t="n"/>
+      <c r="H163" s="37" t="n"/>
+      <c r="I163" s="16" t="n"/>
+      <c r="J163" s="16" t="n"/>
+      <c r="K163" s="38" t="n"/>
+      <c r="L163" s="26" t="n"/>
+      <c r="M163" s="37" t="n"/>
+      <c r="N163" s="16" t="n"/>
+      <c r="O163" s="16" t="n"/>
+      <c r="P163" s="38" t="n"/>
+      <c r="Q163" s="27" t="n"/>
+      <c r="R163" s="16" t="n"/>
+    </row>
+    <row r="164" ht="3.8525" customHeight="1">
+      <c r="A164" s="16" t="n"/>
+      <c r="B164" s="37" t="n"/>
+      <c r="C164" s="16" t="n"/>
+      <c r="D164" s="16" t="n"/>
+      <c r="E164" s="38" t="n"/>
+      <c r="F164" s="16" t="n"/>
+      <c r="G164" s="25" t="n"/>
+      <c r="H164" s="37" t="n"/>
+      <c r="I164" s="16" t="n"/>
+      <c r="J164" s="16" t="n"/>
+      <c r="K164" s="38" t="n"/>
+      <c r="L164" s="26" t="n"/>
+      <c r="M164" s="37" t="n"/>
+      <c r="N164" s="16" t="n"/>
+      <c r="O164" s="16" t="n"/>
+      <c r="P164" s="38" t="n"/>
+      <c r="Q164" s="27" t="n"/>
+      <c r="R164" s="16" t="n"/>
+    </row>
+    <row r="165" ht="3.8525" customHeight="1">
+      <c r="A165" s="16" t="n"/>
+      <c r="B165" s="37" t="n"/>
+      <c r="C165" s="16" t="n"/>
+      <c r="D165" s="16" t="n"/>
+      <c r="E165" s="38" t="n"/>
+      <c r="F165" s="16" t="n"/>
+      <c r="G165" s="25" t="n"/>
+      <c r="H165" s="37" t="n"/>
+      <c r="I165" s="16" t="n"/>
+      <c r="J165" s="16" t="n"/>
+      <c r="K165" s="38" t="n"/>
+      <c r="L165" s="26" t="n"/>
+      <c r="M165" s="37" t="n"/>
+      <c r="N165" s="16" t="n"/>
+      <c r="O165" s="16" t="n"/>
+      <c r="P165" s="38" t="n"/>
+      <c r="Q165" s="27" t="n"/>
+      <c r="R165" s="16" t="n"/>
+    </row>
+    <row r="166" ht="3.8525" customHeight="1">
+      <c r="A166" s="16" t="n"/>
+      <c r="B166" s="37" t="n"/>
+      <c r="C166" s="16" t="n"/>
+      <c r="D166" s="16" t="n"/>
+      <c r="E166" s="38" t="n"/>
+      <c r="F166" s="16" t="n"/>
+      <c r="G166" s="25" t="n"/>
+      <c r="H166" s="37" t="n"/>
+      <c r="I166" s="16" t="n"/>
+      <c r="J166" s="16" t="n"/>
+      <c r="K166" s="38" t="n"/>
+      <c r="L166" s="26" t="n"/>
+      <c r="M166" s="37" t="n"/>
+      <c r="N166" s="16" t="n"/>
+      <c r="O166" s="16" t="n"/>
+      <c r="P166" s="38" t="n"/>
+      <c r="Q166" s="27" t="n"/>
+      <c r="R166" s="16" t="n"/>
+    </row>
+    <row r="167" ht="3.8525" customHeight="1">
+      <c r="A167" s="16" t="n"/>
+      <c r="B167" s="37" t="n"/>
+      <c r="C167" s="16" t="n"/>
+      <c r="D167" s="16" t="n"/>
+      <c r="E167" s="38" t="n"/>
+      <c r="F167" s="16" t="n"/>
+      <c r="G167" s="25" t="n"/>
+      <c r="H167" s="37" t="n"/>
+      <c r="I167" s="46" t="inlineStr">
+        <is>
+          <t>•</t>
+        </is>
+      </c>
+      <c r="J167" s="43" t="inlineStr">
+        <is>
+          <t>Appointment time windows and intra-day sequencing</t>
+        </is>
+      </c>
+      <c r="K167" s="38" t="n"/>
+      <c r="L167" s="26" t="n"/>
+      <c r="M167" s="37" t="n"/>
+      <c r="N167" s="48" t="inlineStr">
+        <is>
+          <t>•</t>
+        </is>
+      </c>
+      <c r="O167" s="43" t="inlineStr">
+        <is>
+          <t>Care-team and office coordination updates</t>
+        </is>
+      </c>
+      <c r="P167" s="38" t="n"/>
+      <c r="Q167" s="27" t="n"/>
+      <c r="R167" s="16" t="n"/>
+    </row>
+    <row r="168" ht="3.8525" customHeight="1">
+      <c r="A168" s="16" t="n"/>
+      <c r="B168" s="37" t="n"/>
+      <c r="C168" s="16" t="n"/>
+      <c r="D168" s="16" t="n"/>
+      <c r="E168" s="38" t="n"/>
+      <c r="F168" s="16" t="n"/>
+      <c r="G168" s="25" t="n"/>
+      <c r="H168" s="37" t="n"/>
+      <c r="I168" s="16" t="n"/>
+      <c r="J168" s="16" t="n"/>
+      <c r="K168" s="38" t="n"/>
+      <c r="L168" s="26" t="n"/>
+      <c r="M168" s="37" t="n"/>
+      <c r="N168" s="16" t="n"/>
+      <c r="O168" s="16" t="n"/>
+      <c r="P168" s="38" t="n"/>
+      <c r="Q168" s="27" t="n"/>
+      <c r="R168" s="16" t="n"/>
+    </row>
+    <row r="169" ht="3.8525" customHeight="1">
+      <c r="A169" s="16" t="n"/>
+      <c r="B169" s="37" t="n"/>
+      <c r="C169" s="16" t="n"/>
+      <c r="D169" s="16" t="n"/>
+      <c r="E169" s="38" t="n"/>
+      <c r="F169" s="16" t="n"/>
+      <c r="G169" s="25" t="n"/>
+      <c r="H169" s="37" t="n"/>
+      <c r="I169" s="16" t="n"/>
+      <c r="J169" s="16" t="n"/>
+      <c r="K169" s="38" t="n"/>
+      <c r="L169" s="26" t="n"/>
+      <c r="M169" s="37" t="n"/>
+      <c r="N169" s="16" t="n"/>
+      <c r="O169" s="16" t="n"/>
+      <c r="P169" s="38" t="n"/>
+      <c r="Q169" s="27" t="n"/>
+      <c r="R169" s="16" t="n"/>
+    </row>
+    <row r="170" ht="3.8525" customHeight="1">
+      <c r="A170" s="16" t="n"/>
+      <c r="B170" s="37" t="n"/>
+      <c r="C170" s="16" t="n"/>
+      <c r="D170" s="16" t="n"/>
+      <c r="E170" s="38" t="n"/>
+      <c r="F170" s="16" t="n"/>
+      <c r="G170" s="25" t="n"/>
+      <c r="H170" s="37" t="n"/>
+      <c r="I170" s="16" t="n"/>
+      <c r="J170" s="16" t="n"/>
+      <c r="K170" s="38" t="n"/>
+      <c r="L170" s="26" t="n"/>
+      <c r="M170" s="37" t="n"/>
+      <c r="N170" s="16" t="n"/>
+      <c r="O170" s="16" t="n"/>
+      <c r="P170" s="38" t="n"/>
+      <c r="Q170" s="27" t="n"/>
+      <c r="R170" s="16" t="n"/>
+    </row>
+    <row r="171" ht="3.8525" customHeight="1">
+      <c r="A171" s="16" t="n"/>
+      <c r="B171" s="37" t="n"/>
+      <c r="C171" s="47" t="inlineStr">
+        <is>
+          <t>•</t>
+        </is>
+      </c>
+      <c r="D171" s="43" t="inlineStr">
+        <is>
+          <t>Referral inflow and discharge outflow against the envelope</t>
+        </is>
+      </c>
+      <c r="E171" s="38" t="n"/>
+      <c r="F171" s="16" t="n"/>
+      <c r="G171" s="25" t="n"/>
+      <c r="H171" s="37" t="n"/>
+      <c r="I171" s="16" t="n"/>
+      <c r="J171" s="16" t="n"/>
+      <c r="K171" s="38" t="n"/>
+      <c r="L171" s="26" t="n"/>
+      <c r="M171" s="37" t="n"/>
+      <c r="N171" s="16" t="n"/>
+      <c r="O171" s="16" t="n"/>
+      <c r="P171" s="38" t="n"/>
+      <c r="Q171" s="27" t="n"/>
+      <c r="R171" s="16" t="n"/>
+    </row>
+    <row r="172" ht="3.8525" customHeight="1">
+      <c r="A172" s="16" t="n"/>
+      <c r="B172" s="37" t="n"/>
+      <c r="C172" s="16" t="n"/>
+      <c r="D172" s="16" t="n"/>
+      <c r="E172" s="38" t="n"/>
+      <c r="F172" s="16" t="n"/>
+      <c r="G172" s="25" t="n"/>
+      <c r="H172" s="37" t="n"/>
+      <c r="I172" s="46" t="inlineStr">
+        <is>
+          <t>•</t>
+        </is>
+      </c>
+      <c r="J172" s="43" t="inlineStr">
+        <is>
+          <t>Front-loading, pace against the plan of care, day-by-day balancing</t>
+        </is>
+      </c>
+      <c r="K172" s="38" t="n"/>
+      <c r="L172" s="26" t="n"/>
+      <c r="M172" s="37" t="n"/>
+      <c r="N172" s="48" t="inlineStr">
+        <is>
+          <t>•</t>
+        </is>
+      </c>
+      <c r="O172" s="43" t="inlineStr">
+        <is>
+          <t>The staff time coordination consumes today</t>
+        </is>
+      </c>
+      <c r="P172" s="38" t="n"/>
+      <c r="Q172" s="27" t="n"/>
+      <c r="R172" s="16" t="n"/>
+    </row>
+    <row r="173" ht="3.8525" customHeight="1">
+      <c r="A173" s="16" t="n"/>
+      <c r="B173" s="37" t="n"/>
+      <c r="C173" s="16" t="n"/>
+      <c r="D173" s="16" t="n"/>
+      <c r="E173" s="38" t="n"/>
+      <c r="F173" s="16" t="n"/>
+      <c r="G173" s="25" t="n"/>
+      <c r="H173" s="37" t="n"/>
+      <c r="I173" s="16" t="n"/>
+      <c r="J173" s="16" t="n"/>
+      <c r="K173" s="38" t="n"/>
+      <c r="L173" s="26" t="n"/>
+      <c r="M173" s="37" t="n"/>
+      <c r="N173" s="16" t="n"/>
+      <c r="O173" s="16" t="n"/>
+      <c r="P173" s="38" t="n"/>
+      <c r="Q173" s="27" t="n"/>
+      <c r="R173" s="16" t="n"/>
+    </row>
+    <row r="174" ht="3.8525" customHeight="1">
+      <c r="A174" s="16" t="n"/>
+      <c r="B174" s="37" t="n"/>
+      <c r="C174" s="16" t="n"/>
+      <c r="D174" s="16" t="n"/>
+      <c r="E174" s="38" t="n"/>
+      <c r="F174" s="16" t="n"/>
+      <c r="G174" s="25" t="n"/>
+      <c r="H174" s="37" t="n"/>
+      <c r="I174" s="16" t="n"/>
+      <c r="J174" s="16" t="n"/>
+      <c r="K174" s="38" t="n"/>
+      <c r="L174" s="26" t="n"/>
+      <c r="M174" s="37" t="n"/>
+      <c r="N174" s="16" t="n"/>
+      <c r="O174" s="16" t="n"/>
+      <c r="P174" s="38" t="n"/>
+      <c r="Q174" s="27" t="n"/>
+      <c r="R174" s="16" t="n"/>
+    </row>
+    <row r="175" ht="3.8525" customHeight="1">
+      <c r="A175" s="16" t="n"/>
+      <c r="B175" s="37" t="n"/>
+      <c r="C175" s="16" t="n"/>
+      <c r="D175" s="16" t="n"/>
+      <c r="E175" s="38" t="n"/>
+      <c r="F175" s="16" t="n"/>
+      <c r="G175" s="25" t="n"/>
+      <c r="H175" s="37" t="n"/>
+      <c r="I175" s="16" t="n"/>
+      <c r="J175" s="16" t="n"/>
+      <c r="K175" s="38" t="n"/>
+      <c r="L175" s="26" t="n"/>
+      <c r="M175" s="37" t="n"/>
+      <c r="N175" s="16" t="n"/>
+      <c r="O175" s="16" t="n"/>
+      <c r="P175" s="38" t="n"/>
+      <c r="Q175" s="27" t="n"/>
+      <c r="R175" s="16" t="n"/>
+    </row>
+    <row r="176" ht="3.8525" customHeight="1">
+      <c r="A176" s="16" t="n"/>
+      <c r="B176" s="37" t="n"/>
+      <c r="C176" s="16" t="n"/>
+      <c r="D176" s="16" t="n"/>
+      <c r="E176" s="38" t="n"/>
+      <c r="F176" s="16" t="n"/>
+      <c r="G176" s="25" t="n"/>
+      <c r="H176" s="37" t="n"/>
+      <c r="I176" s="16" t="n"/>
+      <c r="J176" s="16" t="n"/>
+      <c r="K176" s="38" t="n"/>
+      <c r="L176" s="26" t="n"/>
+      <c r="M176" s="37" t="n"/>
+      <c r="N176" s="16" t="n"/>
+      <c r="O176" s="16" t="n"/>
+      <c r="P176" s="38" t="n"/>
+      <c r="Q176" s="27" t="n"/>
+      <c r="R176" s="16" t="n"/>
+    </row>
+    <row r="177" ht="3.8525" customHeight="1">
+      <c r="A177" s="16" t="n"/>
+      <c r="B177" s="37" t="n"/>
+      <c r="C177" s="16" t="n"/>
+      <c r="D177" s="16" t="n"/>
+      <c r="E177" s="38" t="n"/>
+      <c r="F177" s="16" t="n"/>
+      <c r="G177" s="25" t="n"/>
+      <c r="H177" s="37" t="n"/>
+      <c r="I177" s="16" t="n"/>
+      <c r="J177" s="16" t="n"/>
+      <c r="K177" s="38" t="n"/>
+      <c r="L177" s="26" t="n"/>
+      <c r="M177" s="37" t="n"/>
+      <c r="N177" s="16" t="n"/>
+      <c r="O177" s="16" t="n"/>
+      <c r="P177" s="38" t="n"/>
+      <c r="Q177" s="27" t="n"/>
+      <c r="R177" s="16" t="n"/>
+    </row>
+    <row r="178" ht="3.8525" customHeight="1">
+      <c r="A178" s="16" t="n"/>
+      <c r="B178" s="37" t="n"/>
+      <c r="C178" s="16" t="n"/>
+      <c r="D178" s="16" t="n"/>
+      <c r="E178" s="38" t="n"/>
+      <c r="F178" s="16" t="n"/>
+      <c r="G178" s="25" t="n"/>
+      <c r="H178" s="37" t="n"/>
+      <c r="I178" s="16" t="n"/>
+      <c r="J178" s="16" t="n"/>
+      <c r="K178" s="38" t="n"/>
+      <c r="L178" s="26" t="n"/>
+      <c r="M178" s="37" t="n"/>
+      <c r="N178" s="16" t="n"/>
+      <c r="O178" s="16" t="n"/>
+      <c r="P178" s="38" t="n"/>
+      <c r="Q178" s="27" t="n"/>
+      <c r="R178" s="16" t="n"/>
+    </row>
+    <row r="179" ht="3.8525" customHeight="1">
+      <c r="A179" s="16" t="n"/>
+      <c r="B179" s="37" t="n"/>
+      <c r="C179" s="16" t="n"/>
+      <c r="D179" s="16" t="n"/>
+      <c r="E179" s="38" t="n"/>
+      <c r="F179" s="16" t="n"/>
+      <c r="G179" s="25" t="n"/>
+      <c r="H179" s="37" t="n"/>
+      <c r="I179" s="16" t="n"/>
+      <c r="J179" s="16" t="n"/>
+      <c r="K179" s="38" t="n"/>
+      <c r="L179" s="26" t="n"/>
+      <c r="M179" s="37" t="n"/>
+      <c r="N179" s="16" t="n"/>
+      <c r="O179" s="16" t="n"/>
+      <c r="P179" s="38" t="n"/>
+      <c r="Q179" s="27" t="n"/>
+      <c r="R179" s="16" t="n"/>
+    </row>
+    <row r="180" ht="3.8525" customHeight="1">
+      <c r="A180" s="16" t="n"/>
+      <c r="B180" s="37" t="n"/>
+      <c r="C180" s="16" t="n"/>
+      <c r="D180" s="16" t="n"/>
+      <c r="E180" s="38" t="n"/>
+      <c r="F180" s="16" t="n"/>
+      <c r="G180" s="25" t="n"/>
+      <c r="H180" s="37" t="n"/>
+      <c r="I180" s="16" t="n"/>
+      <c r="J180" s="16" t="n"/>
+      <c r="K180" s="38" t="n"/>
+      <c r="L180" s="26" t="n"/>
+      <c r="M180" s="37" t="n"/>
+      <c r="N180" s="16" t="n"/>
+      <c r="O180" s="16" t="n"/>
+      <c r="P180" s="38" t="n"/>
+      <c r="Q180" s="27" t="n"/>
+      <c r="R180" s="16" t="n"/>
+    </row>
+    <row r="181" ht="3.8525" customHeight="1">
+      <c r="A181" s="16" t="n"/>
+      <c r="B181" s="37" t="n"/>
+      <c r="C181" s="16" t="n"/>
+      <c r="D181" s="16" t="n"/>
+      <c r="E181" s="38" t="n"/>
+      <c r="F181" s="16" t="n"/>
+      <c r="G181" s="25" t="n"/>
+      <c r="H181" s="37" t="n"/>
+      <c r="I181" s="16" t="n"/>
+      <c r="J181" s="16" t="n"/>
+      <c r="K181" s="38" t="n"/>
+      <c r="L181" s="26" t="n"/>
+      <c r="M181" s="37" t="n"/>
+      <c r="N181" s="16" t="n"/>
+      <c r="O181" s="16" t="n"/>
+      <c r="P181" s="38" t="n"/>
+      <c r="Q181" s="27" t="n"/>
+      <c r="R181" s="16" t="n"/>
+    </row>
+    <row r="182" ht="3.8525" customHeight="1">
+      <c r="A182" s="16" t="n"/>
+      <c r="B182" s="37" t="n"/>
+      <c r="C182" s="16" t="n"/>
+      <c r="D182" s="16" t="n"/>
+      <c r="E182" s="38" t="n"/>
+      <c r="F182" s="16" t="n"/>
+      <c r="G182" s="25" t="n"/>
+      <c r="H182" s="37" t="n"/>
+      <c r="I182" s="16" t="n"/>
+      <c r="J182" s="16" t="n"/>
+      <c r="K182" s="38" t="n"/>
+      <c r="L182" s="26" t="n"/>
+      <c r="M182" s="37" t="n"/>
+      <c r="N182" s="16" t="n"/>
+      <c r="O182" s="16" t="n"/>
+      <c r="P182" s="38" t="n"/>
+      <c r="Q182" s="27" t="n"/>
+      <c r="R182" s="16" t="n"/>
+    </row>
+    <row r="183" ht="3.8525" customHeight="1">
+      <c r="A183" s="16" t="n"/>
+      <c r="B183" s="37" t="n"/>
+      <c r="C183" s="16" t="n"/>
+      <c r="D183" s="16" t="n"/>
+      <c r="E183" s="38" t="n"/>
+      <c r="F183" s="16" t="n"/>
+      <c r="G183" s="25" t="n"/>
+      <c r="H183" s="37" t="n"/>
+      <c r="I183" s="44" t="inlineStr">
+        <is>
+          <t>Exceptions</t>
+        </is>
+      </c>
+      <c r="J183" s="16" t="n"/>
+      <c r="K183" s="38" t="n"/>
+      <c r="L183" s="26" t="n"/>
+      <c r="M183" s="37" t="n"/>
+      <c r="N183" s="16" t="n"/>
+      <c r="O183" s="16" t="n"/>
+      <c r="P183" s="38" t="n"/>
+      <c r="Q183" s="27" t="n"/>
+      <c r="R183" s="16" t="n"/>
+    </row>
+    <row r="184" ht="3.8525" customHeight="1">
+      <c r="A184" s="16" t="n"/>
+      <c r="B184" s="37" t="n"/>
+      <c r="C184" s="16" t="n"/>
+      <c r="D184" s="16" t="n"/>
+      <c r="E184" s="38" t="n"/>
+      <c r="F184" s="16" t="n"/>
+      <c r="G184" s="25" t="n"/>
+      <c r="H184" s="37" t="n"/>
+      <c r="I184" s="16" t="n"/>
+      <c r="J184" s="16" t="n"/>
+      <c r="K184" s="38" t="n"/>
+      <c r="L184" s="26" t="n"/>
+      <c r="M184" s="37" t="n"/>
+      <c r="N184" s="16" t="n"/>
+      <c r="O184" s="16" t="n"/>
+      <c r="P184" s="38" t="n"/>
+      <c r="Q184" s="27" t="n"/>
+      <c r="R184" s="16" t="n"/>
+    </row>
+    <row r="185" ht="3.8525" customHeight="1">
+      <c r="A185" s="16" t="n"/>
+      <c r="B185" s="37" t="n"/>
+      <c r="C185" s="16" t="n"/>
+      <c r="D185" s="16" t="n"/>
+      <c r="E185" s="38" t="n"/>
+      <c r="F185" s="16" t="n"/>
+      <c r="G185" s="25" t="n"/>
+      <c r="H185" s="37" t="n"/>
+      <c r="I185" s="16" t="n"/>
+      <c r="J185" s="16" t="n"/>
+      <c r="K185" s="38" t="n"/>
+      <c r="L185" s="26" t="n"/>
+      <c r="M185" s="37" t="n"/>
+      <c r="N185" s="16" t="n"/>
+      <c r="O185" s="16" t="n"/>
+      <c r="P185" s="38" t="n"/>
+      <c r="Q185" s="27" t="n"/>
+      <c r="R185" s="16" t="n"/>
+    </row>
+    <row r="186" ht="3.8525" customHeight="1">
+      <c r="A186" s="16" t="n"/>
+      <c r="B186" s="37" t="n"/>
+      <c r="C186" s="16" t="n"/>
+      <c r="D186" s="16" t="n"/>
+      <c r="E186" s="38" t="n"/>
+      <c r="F186" s="16" t="n"/>
+      <c r="G186" s="25" t="n"/>
+      <c r="H186" s="37" t="n"/>
+      <c r="I186" s="16" t="n"/>
+      <c r="J186" s="16" t="n"/>
+      <c r="K186" s="38" t="n"/>
+      <c r="L186" s="26" t="n"/>
+      <c r="M186" s="37" t="n"/>
+      <c r="N186" s="16" t="n"/>
+      <c r="O186" s="16" t="n"/>
+      <c r="P186" s="38" t="n"/>
+      <c r="Q186" s="27" t="n"/>
+      <c r="R186" s="16" t="n"/>
+    </row>
+    <row r="187" ht="3.8525" customHeight="1">
+      <c r="A187" s="16" t="n"/>
+      <c r="B187" s="37" t="n"/>
+      <c r="C187" s="16" t="n"/>
+      <c r="D187" s="16" t="n"/>
+      <c r="E187" s="38" t="n"/>
+      <c r="F187" s="16" t="n"/>
+      <c r="G187" s="25" t="n"/>
+      <c r="H187" s="37" t="n"/>
+      <c r="I187" s="16" t="n"/>
+      <c r="J187" s="16" t="n"/>
+      <c r="K187" s="38" t="n"/>
+      <c r="L187" s="26" t="n"/>
+      <c r="M187" s="37" t="n"/>
+      <c r="N187" s="16" t="n"/>
+      <c r="O187" s="16" t="n"/>
+      <c r="P187" s="38" t="n"/>
+      <c r="Q187" s="27" t="n"/>
+      <c r="R187" s="16" t="n"/>
+    </row>
+    <row r="188" ht="3.8525" customHeight="1">
+      <c r="A188" s="16" t="n"/>
+      <c r="B188" s="37" t="n"/>
+      <c r="C188" s="16" t="n"/>
+      <c r="D188" s="16" t="n"/>
+      <c r="E188" s="38" t="n"/>
+      <c r="F188" s="16" t="n"/>
+      <c r="G188" s="25" t="n"/>
+      <c r="H188" s="37" t="n"/>
+      <c r="I188" s="16" t="n"/>
+      <c r="J188" s="16" t="n"/>
+      <c r="K188" s="38" t="n"/>
+      <c r="L188" s="26" t="n"/>
+      <c r="M188" s="37" t="n"/>
+      <c r="N188" s="16" t="n"/>
+      <c r="O188" s="16" t="n"/>
+      <c r="P188" s="38" t="n"/>
+      <c r="Q188" s="27" t="n"/>
+      <c r="R188" s="16" t="n"/>
+    </row>
+    <row r="189" ht="3.8525" customHeight="1">
+      <c r="A189" s="16" t="n"/>
+      <c r="B189" s="37" t="n"/>
+      <c r="C189" s="16" t="n"/>
+      <c r="D189" s="16" t="n"/>
+      <c r="E189" s="38" t="n"/>
+      <c r="F189" s="16" t="n"/>
+      <c r="G189" s="25" t="n"/>
+      <c r="H189" s="37" t="n"/>
+      <c r="I189" s="45" t="inlineStr">
+        <is>
+          <t>What happens when the plan breaks.</t>
+        </is>
+      </c>
+      <c r="J189" s="16" t="n"/>
+      <c r="K189" s="38" t="n"/>
+      <c r="L189" s="26" t="n"/>
+      <c r="M189" s="37" t="n"/>
+      <c r="N189" s="16" t="n"/>
+      <c r="O189" s="16" t="n"/>
+      <c r="P189" s="38" t="n"/>
+      <c r="Q189" s="27" t="n"/>
+      <c r="R189" s="16" t="n"/>
+    </row>
+    <row r="190" ht="3.8525" customHeight="1">
+      <c r="A190" s="16" t="n"/>
+      <c r="B190" s="37" t="n"/>
+      <c r="C190" s="16" t="n"/>
+      <c r="D190" s="16" t="n"/>
+      <c r="E190" s="38" t="n"/>
+      <c r="F190" s="16" t="n"/>
+      <c r="G190" s="25" t="n"/>
+      <c r="H190" s="37" t="n"/>
+      <c r="I190" s="16" t="n"/>
+      <c r="J190" s="16" t="n"/>
+      <c r="K190" s="38" t="n"/>
+      <c r="L190" s="26" t="n"/>
+      <c r="M190" s="37" t="n"/>
+      <c r="N190" s="16" t="n"/>
+      <c r="O190" s="16" t="n"/>
+      <c r="P190" s="38" t="n"/>
+      <c r="Q190" s="27" t="n"/>
+      <c r="R190" s="16" t="n"/>
+    </row>
+    <row r="191" ht="3.8525" customHeight="1">
+      <c r="A191" s="16" t="n"/>
+      <c r="B191" s="37" t="n"/>
+      <c r="C191" s="16" t="n"/>
+      <c r="D191" s="16" t="n"/>
+      <c r="E191" s="38" t="n"/>
+      <c r="F191" s="16" t="n"/>
+      <c r="G191" s="25" t="n"/>
+      <c r="H191" s="37" t="n"/>
+      <c r="I191" s="16" t="n"/>
+      <c r="J191" s="16" t="n"/>
+      <c r="K191" s="38" t="n"/>
+      <c r="L191" s="26" t="n"/>
+      <c r="M191" s="37" t="n"/>
+      <c r="N191" s="16" t="n"/>
+      <c r="O191" s="16" t="n"/>
+      <c r="P191" s="38" t="n"/>
+      <c r="Q191" s="27" t="n"/>
+      <c r="R191" s="16" t="n"/>
+    </row>
+    <row r="192" ht="3.8525" customHeight="1">
+      <c r="A192" s="16" t="n"/>
+      <c r="B192" s="37" t="n"/>
+      <c r="C192" s="16" t="n"/>
+      <c r="D192" s="16" t="n"/>
+      <c r="E192" s="38" t="n"/>
+      <c r="F192" s="16" t="n"/>
+      <c r="G192" s="25" t="n"/>
+      <c r="H192" s="37" t="n"/>
+      <c r="I192" s="16" t="n"/>
+      <c r="J192" s="16" t="n"/>
+      <c r="K192" s="38" t="n"/>
+      <c r="L192" s="26" t="n"/>
+      <c r="M192" s="37" t="n"/>
+      <c r="N192" s="16" t="n"/>
+      <c r="O192" s="16" t="n"/>
+      <c r="P192" s="38" t="n"/>
+      <c r="Q192" s="27" t="n"/>
+      <c r="R192" s="16" t="n"/>
+    </row>
+    <row r="193" ht="3.8525" customHeight="1">
+      <c r="A193" s="16" t="n"/>
+      <c r="B193" s="37" t="n"/>
+      <c r="C193" s="16" t="n"/>
+      <c r="D193" s="16" t="n"/>
+      <c r="E193" s="38" t="n"/>
+      <c r="F193" s="16" t="n"/>
+      <c r="G193" s="25" t="n"/>
+      <c r="H193" s="37" t="n"/>
+      <c r="I193" s="16" t="n"/>
+      <c r="J193" s="16" t="n"/>
+      <c r="K193" s="38" t="n"/>
+      <c r="L193" s="26" t="n"/>
+      <c r="M193" s="37" t="n"/>
+      <c r="N193" s="16" t="n"/>
+      <c r="O193" s="16" t="n"/>
+      <c r="P193" s="38" t="n"/>
+      <c r="Q193" s="27" t="n"/>
+      <c r="R193" s="16" t="n"/>
+    </row>
+    <row r="194" ht="3.8525" customHeight="1">
+      <c r="A194" s="16" t="n"/>
+      <c r="B194" s="37" t="n"/>
+      <c r="C194" s="16" t="n"/>
+      <c r="D194" s="16" t="n"/>
+      <c r="E194" s="38" t="n"/>
+      <c r="F194" s="16" t="n"/>
+      <c r="G194" s="25" t="n"/>
+      <c r="H194" s="37" t="n"/>
+      <c r="I194" s="16" t="n"/>
+      <c r="J194" s="16" t="n"/>
+      <c r="K194" s="38" t="n"/>
+      <c r="L194" s="26" t="n"/>
+      <c r="M194" s="37" t="n"/>
+      <c r="N194" s="16" t="n"/>
+      <c r="O194" s="16" t="n"/>
+      <c r="P194" s="38" t="n"/>
+      <c r="Q194" s="27" t="n"/>
+      <c r="R194" s="16" t="n"/>
+    </row>
+    <row r="195" ht="3.8525" customHeight="1">
+      <c r="A195" s="16" t="n"/>
+      <c r="B195" s="37" t="n"/>
+      <c r="C195" s="16" t="n"/>
+      <c r="D195" s="16" t="n"/>
+      <c r="E195" s="38" t="n"/>
+      <c r="F195" s="16" t="n"/>
+      <c r="G195" s="25" t="n"/>
+      <c r="H195" s="37" t="n"/>
+      <c r="I195" s="46" t="inlineStr">
+        <is>
+          <t>•</t>
+        </is>
+      </c>
+      <c r="J195" s="43" t="inlineStr">
+        <is>
+          <t>Missed-visit management and tracking — and reducing the occurrence</t>
+        </is>
+      </c>
+      <c r="K195" s="38" t="n"/>
+      <c r="L195" s="26" t="n"/>
+      <c r="M195" s="37" t="n"/>
+      <c r="N195" s="16" t="n"/>
+      <c r="O195" s="16" t="n"/>
+      <c r="P195" s="38" t="n"/>
+      <c r="Q195" s="27" t="n"/>
+      <c r="R195" s="16" t="n"/>
+    </row>
+    <row r="196" ht="3.8525" customHeight="1">
+      <c r="A196" s="16" t="n"/>
+      <c r="B196" s="37" t="n"/>
+      <c r="C196" s="16" t="n"/>
+      <c r="D196" s="16" t="n"/>
+      <c r="E196" s="38" t="n"/>
+      <c r="F196" s="16" t="n"/>
+      <c r="G196" s="25" t="n"/>
+      <c r="H196" s="37" t="n"/>
+      <c r="I196" s="16" t="n"/>
+      <c r="J196" s="16" t="n"/>
+      <c r="K196" s="38" t="n"/>
+      <c r="L196" s="26" t="n"/>
+      <c r="M196" s="37" t="n"/>
+      <c r="N196" s="16" t="n"/>
+      <c r="O196" s="16" t="n"/>
+      <c r="P196" s="38" t="n"/>
+      <c r="Q196" s="27" t="n"/>
+      <c r="R196" s="16" t="n"/>
+    </row>
+    <row r="197" ht="3.8525" customHeight="1">
+      <c r="A197" s="16" t="n"/>
+      <c r="B197" s="37" t="n"/>
+      <c r="C197" s="16" t="n"/>
+      <c r="D197" s="16" t="n"/>
+      <c r="E197" s="38" t="n"/>
+      <c r="F197" s="16" t="n"/>
+      <c r="G197" s="25" t="n"/>
+      <c r="H197" s="37" t="n"/>
+      <c r="I197" s="16" t="n"/>
+      <c r="J197" s="16" t="n"/>
+      <c r="K197" s="38" t="n"/>
+      <c r="L197" s="26" t="n"/>
+      <c r="M197" s="37" t="n"/>
+      <c r="N197" s="16" t="n"/>
+      <c r="O197" s="16" t="n"/>
+      <c r="P197" s="38" t="n"/>
+      <c r="Q197" s="27" t="n"/>
+      <c r="R197" s="16" t="n"/>
+    </row>
+    <row r="198" ht="3.8525" customHeight="1">
+      <c r="A198" s="16" t="n"/>
+      <c r="B198" s="37" t="n"/>
+      <c r="C198" s="16" t="n"/>
+      <c r="D198" s="16" t="n"/>
+      <c r="E198" s="38" t="n"/>
+      <c r="F198" s="16" t="n"/>
+      <c r="G198" s="25" t="n"/>
+      <c r="H198" s="37" t="n"/>
+      <c r="I198" s="16" t="n"/>
+      <c r="J198" s="16" t="n"/>
+      <c r="K198" s="38" t="n"/>
+      <c r="L198" s="26" t="n"/>
+      <c r="M198" s="37" t="n"/>
+      <c r="N198" s="16" t="n"/>
+      <c r="O198" s="16" t="n"/>
+      <c r="P198" s="38" t="n"/>
+      <c r="Q198" s="27" t="n"/>
+      <c r="R198" s="16" t="n"/>
+    </row>
+    <row r="199" ht="3.8525" customHeight="1">
+      <c r="A199" s="16" t="n"/>
+      <c r="B199" s="37" t="n"/>
+      <c r="C199" s="16" t="n"/>
+      <c r="D199" s="16" t="n"/>
+      <c r="E199" s="38" t="n"/>
+      <c r="F199" s="16" t="n"/>
+      <c r="G199" s="25" t="n"/>
+      <c r="H199" s="37" t="n"/>
+      <c r="I199" s="16" t="n"/>
+      <c r="J199" s="16" t="n"/>
+      <c r="K199" s="38" t="n"/>
+      <c r="L199" s="26" t="n"/>
+      <c r="M199" s="37" t="n"/>
+      <c r="N199" s="16" t="n"/>
+      <c r="O199" s="16" t="n"/>
+      <c r="P199" s="38" t="n"/>
+      <c r="Q199" s="27" t="n"/>
+      <c r="R199" s="16" t="n"/>
+    </row>
+    <row r="200" ht="3.8525" customHeight="1">
+      <c r="A200" s="16" t="n"/>
+      <c r="B200" s="37" t="n"/>
+      <c r="C200" s="16" t="n"/>
+      <c r="D200" s="16" t="n"/>
+      <c r="E200" s="38" t="n"/>
+      <c r="F200" s="16" t="n"/>
+      <c r="G200" s="25" t="n"/>
+      <c r="H200" s="37" t="n"/>
+      <c r="I200" s="16" t="n"/>
+      <c r="J200" s="16" t="n"/>
+      <c r="K200" s="38" t="n"/>
+      <c r="L200" s="26" t="n"/>
+      <c r="M200" s="37" t="n"/>
+      <c r="N200" s="16" t="n"/>
+      <c r="O200" s="16" t="n"/>
+      <c r="P200" s="38" t="n"/>
+      <c r="Q200" s="27" t="n"/>
+      <c r="R200" s="16" t="n"/>
+    </row>
+    <row r="201" ht="3.8525" customHeight="1">
+      <c r="A201" s="16" t="n"/>
+      <c r="B201" s="37" t="n"/>
+      <c r="C201" s="16" t="n"/>
+      <c r="D201" s="16" t="n"/>
+      <c r="E201" s="38" t="n"/>
+      <c r="F201" s="16" t="n"/>
+      <c r="G201" s="25" t="n"/>
+      <c r="H201" s="37" t="n"/>
+      <c r="I201" s="16" t="n"/>
+      <c r="J201" s="16" t="n"/>
+      <c r="K201" s="38" t="n"/>
+      <c r="L201" s="26" t="n"/>
+      <c r="M201" s="37" t="n"/>
+      <c r="N201" s="16" t="n"/>
+      <c r="O201" s="16" t="n"/>
+      <c r="P201" s="38" t="n"/>
+      <c r="Q201" s="27" t="n"/>
+      <c r="R201" s="16" t="n"/>
+    </row>
+    <row r="202" ht="3.8525" customHeight="1">
+      <c r="A202" s="16" t="n"/>
+      <c r="B202" s="37" t="n"/>
+      <c r="C202" s="16" t="n"/>
+      <c r="D202" s="16" t="n"/>
+      <c r="E202" s="38" t="n"/>
+      <c r="F202" s="16" t="n"/>
+      <c r="G202" s="25" t="n"/>
+      <c r="H202" s="37" t="n"/>
+      <c r="I202" s="16" t="n"/>
+      <c r="J202" s="16" t="n"/>
+      <c r="K202" s="38" t="n"/>
+      <c r="L202" s="26" t="n"/>
+      <c r="M202" s="37" t="n"/>
+      <c r="N202" s="16" t="n"/>
+      <c r="O202" s="16" t="n"/>
+      <c r="P202" s="38" t="n"/>
+      <c r="Q202" s="27" t="n"/>
+      <c r="R202" s="16" t="n"/>
+    </row>
+    <row r="203" ht="3.8525" customHeight="1">
+      <c r="A203" s="16" t="n"/>
+      <c r="B203" s="37" t="n"/>
+      <c r="C203" s="16" t="n"/>
+      <c r="D203" s="16" t="n"/>
+      <c r="E203" s="38" t="n"/>
+      <c r="F203" s="16" t="n"/>
+      <c r="G203" s="25" t="n"/>
+      <c r="H203" s="37" t="n"/>
+      <c r="I203" s="16" t="n"/>
+      <c r="J203" s="16" t="n"/>
+      <c r="K203" s="38" t="n"/>
+      <c r="L203" s="26" t="n"/>
+      <c r="M203" s="37" t="n"/>
+      <c r="N203" s="16" t="n"/>
+      <c r="O203" s="16" t="n"/>
+      <c r="P203" s="38" t="n"/>
+      <c r="Q203" s="27" t="n"/>
+      <c r="R203" s="16" t="n"/>
+    </row>
+    <row r="204" ht="3.8525" customHeight="1">
+      <c r="A204" s="16" t="n"/>
+      <c r="B204" s="37" t="n"/>
+      <c r="C204" s="16" t="n"/>
+      <c r="D204" s="16" t="n"/>
+      <c r="E204" s="38" t="n"/>
+      <c r="F204" s="16" t="n"/>
+      <c r="G204" s="25" t="n"/>
+      <c r="H204" s="37" t="n"/>
+      <c r="I204" s="46" t="inlineStr">
+        <is>
+          <t>•</t>
+        </is>
+      </c>
+      <c r="J204" s="43" t="inlineStr">
+        <is>
+          <t>Reassignment, coverage, and rebooking inside the window</t>
+        </is>
+      </c>
+      <c r="K204" s="38" t="n"/>
+      <c r="L204" s="26" t="n"/>
+      <c r="M204" s="37" t="n"/>
+      <c r="N204" s="16" t="n"/>
+      <c r="O204" s="16" t="n"/>
+      <c r="P204" s="38" t="n"/>
+      <c r="Q204" s="27" t="n"/>
+      <c r="R204" s="16" t="n"/>
+    </row>
+    <row r="205" ht="3.8525" customHeight="1">
+      <c r="A205" s="16" t="n"/>
+      <c r="B205" s="37" t="n"/>
+      <c r="C205" s="16" t="n"/>
+      <c r="D205" s="16" t="n"/>
+      <c r="E205" s="38" t="n"/>
+      <c r="F205" s="16" t="n"/>
+      <c r="G205" s="25" t="n"/>
+      <c r="H205" s="37" t="n"/>
+      <c r="I205" s="16" t="n"/>
+      <c r="J205" s="16" t="n"/>
+      <c r="K205" s="38" t="n"/>
+      <c r="L205" s="26" t="n"/>
+      <c r="M205" s="37" t="n"/>
+      <c r="N205" s="16" t="n"/>
+      <c r="O205" s="16" t="n"/>
+      <c r="P205" s="38" t="n"/>
+      <c r="Q205" s="27" t="n"/>
+      <c r="R205" s="16" t="n"/>
+    </row>
+    <row r="206" ht="3.8525" customHeight="1">
+      <c r="A206" s="16" t="n"/>
+      <c r="B206" s="37" t="n"/>
+      <c r="C206" s="16" t="n"/>
+      <c r="D206" s="16" t="n"/>
+      <c r="E206" s="38" t="n"/>
+      <c r="F206" s="16" t="n"/>
+      <c r="G206" s="25" t="n"/>
+      <c r="H206" s="37" t="n"/>
+      <c r="I206" s="16" t="n"/>
+      <c r="J206" s="16" t="n"/>
+      <c r="K206" s="38" t="n"/>
+      <c r="L206" s="26" t="n"/>
+      <c r="M206" s="37" t="n"/>
+      <c r="N206" s="16" t="n"/>
+      <c r="O206" s="16" t="n"/>
+      <c r="P206" s="38" t="n"/>
+      <c r="Q206" s="27" t="n"/>
+      <c r="R206" s="16" t="n"/>
+    </row>
+    <row r="207" ht="3.8525" customHeight="1">
+      <c r="A207" s="16" t="n"/>
+      <c r="B207" s="37" t="n"/>
+      <c r="C207" s="16" t="n"/>
+      <c r="D207" s="16" t="n"/>
+      <c r="E207" s="38" t="n"/>
+      <c r="F207" s="16" t="n"/>
+      <c r="G207" s="25" t="n"/>
+      <c r="H207" s="37" t="n"/>
+      <c r="I207" s="16" t="n"/>
+      <c r="J207" s="16" t="n"/>
+      <c r="K207" s="38" t="n"/>
+      <c r="L207" s="26" t="n"/>
+      <c r="M207" s="37" t="n"/>
+      <c r="N207" s="16" t="n"/>
+      <c r="O207" s="16" t="n"/>
+      <c r="P207" s="38" t="n"/>
+      <c r="Q207" s="27" t="n"/>
+      <c r="R207" s="16" t="n"/>
+    </row>
+    <row r="208" ht="3.8525" customHeight="1">
+      <c r="A208" s="16" t="n"/>
+      <c r="B208" s="37" t="n"/>
+      <c r="C208" s="16" t="n"/>
+      <c r="D208" s="16" t="n"/>
+      <c r="E208" s="38" t="n"/>
+      <c r="F208" s="16" t="n"/>
+      <c r="G208" s="25" t="n"/>
+      <c r="H208" s="37" t="n"/>
+      <c r="I208" s="16" t="n"/>
+      <c r="J208" s="16" t="n"/>
+      <c r="K208" s="38" t="n"/>
+      <c r="L208" s="26" t="n"/>
+      <c r="M208" s="37" t="n"/>
+      <c r="N208" s="16" t="n"/>
+      <c r="O208" s="16" t="n"/>
+      <c r="P208" s="38" t="n"/>
+      <c r="Q208" s="27" t="n"/>
+      <c r="R208" s="16" t="n"/>
+    </row>
+    <row r="209" ht="3.8525" customHeight="1">
+      <c r="A209" s="16" t="n"/>
+      <c r="B209" s="37" t="n"/>
+      <c r="C209" s="16" t="n"/>
+      <c r="D209" s="16" t="n"/>
+      <c r="E209" s="38" t="n"/>
+      <c r="F209" s="16" t="n"/>
+      <c r="G209" s="25" t="n"/>
+      <c r="H209" s="37" t="n"/>
+      <c r="I209" s="16" t="n"/>
+      <c r="J209" s="16" t="n"/>
+      <c r="K209" s="38" t="n"/>
+      <c r="L209" s="26" t="n"/>
+      <c r="M209" s="37" t="n"/>
+      <c r="N209" s="16" t="n"/>
+      <c r="O209" s="16" t="n"/>
+      <c r="P209" s="38" t="n"/>
+      <c r="Q209" s="27" t="n"/>
+      <c r="R209" s="16" t="n"/>
+    </row>
+    <row r="210" ht="3.8525" customHeight="1">
+      <c r="A210" s="16" t="n"/>
+      <c r="B210" s="37" t="n"/>
+      <c r="C210" s="16" t="n"/>
+      <c r="D210" s="16" t="n"/>
+      <c r="E210" s="38" t="n"/>
+      <c r="F210" s="16" t="n"/>
+      <c r="G210" s="25" t="n"/>
+      <c r="H210" s="37" t="n"/>
+      <c r="I210" s="16" t="n"/>
+      <c r="J210" s="16" t="n"/>
+      <c r="K210" s="38" t="n"/>
+      <c r="L210" s="26" t="n"/>
+      <c r="M210" s="37" t="n"/>
+      <c r="N210" s="16" t="n"/>
+      <c r="O210" s="16" t="n"/>
+      <c r="P210" s="38" t="n"/>
+      <c r="Q210" s="27" t="n"/>
+      <c r="R210" s="16" t="n"/>
+    </row>
+    <row r="211" ht="3.8525" customHeight="1">
+      <c r="A211" s="16" t="n"/>
+      <c r="B211" s="37" t="n"/>
+      <c r="C211" s="16" t="n"/>
+      <c r="D211" s="16" t="n"/>
+      <c r="E211" s="38" t="n"/>
+      <c r="F211" s="16" t="n"/>
+      <c r="G211" s="25" t="n"/>
+      <c r="H211" s="37" t="n"/>
+      <c r="I211" s="16" t="n"/>
+      <c r="J211" s="16" t="n"/>
+      <c r="K211" s="38" t="n"/>
+      <c r="L211" s="26" t="n"/>
+      <c r="M211" s="37" t="n"/>
+      <c r="N211" s="16" t="n"/>
+      <c r="O211" s="16" t="n"/>
+      <c r="P211" s="38" t="n"/>
+      <c r="Q211" s="27" t="n"/>
+      <c r="R211" s="16" t="n"/>
+    </row>
+    <row r="212" ht="3.8525" customHeight="1">
+      <c r="A212" s="16" t="n"/>
+      <c r="B212" s="37" t="n"/>
+      <c r="C212" s="16" t="n"/>
+      <c r="D212" s="16" t="n"/>
+      <c r="E212" s="38" t="n"/>
+      <c r="F212" s="16" t="n"/>
+      <c r="G212" s="25" t="n"/>
+      <c r="H212" s="37" t="n"/>
+      <c r="I212" s="16" t="n"/>
+      <c r="J212" s="16" t="n"/>
+      <c r="K212" s="38" t="n"/>
+      <c r="L212" s="26" t="n"/>
+      <c r="M212" s="37" t="n"/>
+      <c r="N212" s="16" t="n"/>
+      <c r="O212" s="16" t="n"/>
+      <c r="P212" s="38" t="n"/>
+      <c r="Q212" s="27" t="n"/>
+      <c r="R212" s="16" t="n"/>
+    </row>
+    <row r="213" ht="3.8525" customHeight="1">
+      <c r="A213" s="16" t="n"/>
+      <c r="B213" s="37" t="n"/>
+      <c r="C213" s="16" t="n"/>
+      <c r="D213" s="16" t="n"/>
+      <c r="E213" s="38" t="n"/>
+      <c r="F213" s="16" t="n"/>
+      <c r="G213" s="25" t="n"/>
+      <c r="H213" s="37" t="n"/>
+      <c r="I213" s="16" t="n"/>
+      <c r="J213" s="16" t="n"/>
+      <c r="K213" s="38" t="n"/>
+      <c r="L213" s="26" t="n"/>
+      <c r="M213" s="37" t="n"/>
+      <c r="N213" s="16" t="n"/>
+      <c r="O213" s="16" t="n"/>
+      <c r="P213" s="38" t="n"/>
+      <c r="Q213" s="27" t="n"/>
+      <c r="R213" s="16" t="n"/>
+    </row>
+    <row r="214" ht="3.8525" customHeight="1">
+      <c r="A214" s="16" t="n"/>
+      <c r="B214" s="37" t="n"/>
+      <c r="C214" s="16" t="n"/>
+      <c r="D214" s="16" t="n"/>
+      <c r="E214" s="38" t="n"/>
+      <c r="F214" s="16" t="n"/>
+      <c r="G214" s="25" t="n"/>
+      <c r="H214" s="37" t="n"/>
+      <c r="I214" s="16" t="n"/>
+      <c r="J214" s="16" t="n"/>
+      <c r="K214" s="38" t="n"/>
+      <c r="L214" s="26" t="n"/>
+      <c r="M214" s="37" t="n"/>
+      <c r="N214" s="16" t="n"/>
+      <c r="O214" s="16" t="n"/>
+      <c r="P214" s="38" t="n"/>
+      <c r="Q214" s="27" t="n"/>
+      <c r="R214" s="16" t="n"/>
+    </row>
+    <row r="215" ht="3.8525" customHeight="1">
+      <c r="A215" s="16" t="n"/>
+      <c r="B215" s="37" t="n"/>
+      <c r="C215" s="16" t="n"/>
+      <c r="D215" s="16" t="n"/>
+      <c r="E215" s="38" t="n"/>
+      <c r="F215" s="16" t="n"/>
+      <c r="G215" s="25" t="n"/>
+      <c r="H215" s="37" t="n"/>
+      <c r="I215" s="16" t="n"/>
+      <c r="J215" s="16" t="n"/>
+      <c r="K215" s="38" t="n"/>
+      <c r="L215" s="26" t="n"/>
+      <c r="M215" s="37" t="n"/>
+      <c r="N215" s="16" t="n"/>
+      <c r="O215" s="16" t="n"/>
+      <c r="P215" s="38" t="n"/>
+      <c r="Q215" s="27" t="n"/>
+      <c r="R215" s="16" t="n"/>
+    </row>
+    <row r="216" ht="3.8525" customHeight="1">
+      <c r="A216" s="16" t="n"/>
+      <c r="B216" s="49" t="n"/>
+      <c r="C216" s="20" t="n"/>
+      <c r="D216" s="20" t="n"/>
+      <c r="E216" s="50" t="n"/>
+      <c r="F216" s="16" t="n"/>
+      <c r="G216" s="25" t="n"/>
+      <c r="H216" s="49" t="n"/>
+      <c r="I216" s="20" t="n"/>
+      <c r="J216" s="20" t="n"/>
+      <c r="K216" s="50" t="n"/>
+      <c r="L216" s="26" t="n"/>
+      <c r="M216" s="49" t="n"/>
+      <c r="N216" s="20" t="n"/>
+      <c r="O216" s="20" t="n"/>
+      <c r="P216" s="50" t="n"/>
+      <c r="Q216" s="27" t="n"/>
+      <c r="R216" s="16" t="n"/>
+    </row>
+    <row r="217" ht="3.8525" customHeight="1">
+      <c r="A217" s="16" t="n"/>
+      <c r="B217" s="16" t="n"/>
+      <c r="C217" s="16" t="n"/>
+      <c r="D217" s="16" t="n"/>
+      <c r="E217" s="16" t="n"/>
+      <c r="F217" s="16" t="n"/>
+      <c r="G217" s="25" t="n"/>
+      <c r="H217" s="26" t="n"/>
+      <c r="I217" s="26" t="n"/>
+      <c r="J217" s="26" t="n"/>
+      <c r="K217" s="26" t="n"/>
+      <c r="L217" s="26" t="n"/>
+      <c r="M217" s="26" t="n"/>
+      <c r="N217" s="26" t="n"/>
+      <c r="O217" s="26" t="n"/>
+      <c r="P217" s="26" t="n"/>
+      <c r="Q217" s="27" t="n"/>
+      <c r="R217" s="16" t="n"/>
+    </row>
+    <row r="218" ht="3.8525" customHeight="1">
+      <c r="A218" s="16" t="n"/>
+      <c r="B218" s="16" t="n"/>
+      <c r="C218" s="16" t="n"/>
+      <c r="D218" s="16" t="n"/>
+      <c r="E218" s="16" t="n"/>
+      <c r="F218" s="16" t="n"/>
+      <c r="G218" s="51" t="n"/>
+      <c r="H218" s="52" t="n"/>
+      <c r="I218" s="52" t="n"/>
+      <c r="J218" s="52" t="n"/>
+      <c r="K218" s="52" t="n"/>
+      <c r="L218" s="52" t="n"/>
+      <c r="M218" s="52" t="n"/>
+      <c r="N218" s="52" t="n"/>
+      <c r="O218" s="52" t="n"/>
+      <c r="P218" s="52" t="n"/>
+      <c r="Q218" s="53" t="n"/>
+      <c r="R218" s="16" t="n"/>
+    </row>
+    <row r="219" ht="3.8525" customHeight="1">
+      <c r="A219" s="16" t="n"/>
+      <c r="B219" s="16" t="n"/>
+      <c r="C219" s="16" t="n"/>
+      <c r="D219" s="16" t="n"/>
+      <c r="E219" s="16" t="n"/>
+      <c r="F219" s="16" t="n"/>
+      <c r="G219" s="16" t="n"/>
+      <c r="H219" s="16" t="n"/>
+      <c r="I219" s="16" t="n"/>
+      <c r="J219" s="16" t="n"/>
+      <c r="K219" s="16" t="n"/>
+      <c r="L219" s="16" t="n"/>
+      <c r="M219" s="16" t="n"/>
+      <c r="N219" s="16" t="n"/>
+      <c r="O219" s="16" t="n"/>
+      <c r="P219" s="16" t="n"/>
+      <c r="Q219" s="16" t="n"/>
+      <c r="R219" s="16" t="n"/>
+    </row>
+    <row r="220" ht="3.8525" customHeight="1">
+      <c r="A220" s="16" t="n"/>
+      <c r="B220" s="20" t="n"/>
+      <c r="C220" s="20" t="n"/>
+      <c r="D220" s="20" t="n"/>
+      <c r="E220" s="20" t="n"/>
+      <c r="F220" s="20" t="n"/>
+      <c r="G220" s="20" t="n"/>
+      <c r="H220" s="20" t="n"/>
+      <c r="I220" s="20" t="n"/>
+      <c r="J220" s="20" t="n"/>
+      <c r="K220" s="20" t="n"/>
+      <c r="L220" s="20" t="n"/>
+      <c r="M220" s="20" t="n"/>
+      <c r="N220" s="20" t="n"/>
+      <c r="O220" s="20" t="n"/>
+      <c r="P220" s="20" t="n"/>
+      <c r="Q220" s="20" t="n"/>
+      <c r="R220" s="16" t="n"/>
+    </row>
+    <row r="221" ht="3.8525" customHeight="1">
+      <c r="A221" s="16" t="n"/>
+      <c r="B221" s="54" t="inlineStr">
+        <is>
+          <t>Capacity sets the envelope. Scheduling and engagement are both performed against it — which is why we are looking for a platform that treats all three as one system.</t>
+        </is>
+      </c>
+      <c r="R221" s="16" t="n"/>
+    </row>
+    <row r="222" ht="3.8525" customHeight="1">
+      <c r="A222" s="16" t="n"/>
+      <c r="R222" s="16" t="n"/>
+    </row>
+    <row r="223" ht="3.8525" customHeight="1">
+      <c r="A223" s="16" t="n"/>
+      <c r="R223" s="16" t="n"/>
+    </row>
+    <row r="224" ht="3.8525" customHeight="1">
+      <c r="A224" s="16" t="n"/>
+      <c r="R224" s="16" t="n"/>
+    </row>
+    <row r="225" ht="3.8525" customHeight="1">
+      <c r="A225" s="16" t="n"/>
+      <c r="R225" s="16" t="n"/>
+    </row>
+    <row r="226" ht="3.8525" customHeight="1">
+      <c r="A226" s="16" t="n"/>
+      <c r="R226" s="16" t="n"/>
+    </row>
+    <row r="227" ht="3.8525" customHeight="1"/>
+    <row r="228" ht="3.8525" customHeight="1"/>
+  </sheetData>
+  <mergeCells count="108">
+    <mergeCell ref="I156:J159"/>
+    <mergeCell ref="D153:D160"/>
+    <mergeCell ref="J111:J118"/>
+    <mergeCell ref="O120:O123"/>
+    <mergeCell ref="C92:C95"/>
+    <mergeCell ref="I120:I123"/>
+    <mergeCell ref="J167:J170"/>
+    <mergeCell ref="C37:D43"/>
+    <mergeCell ref="C32:D35"/>
+    <mergeCell ref="I162:I165"/>
+    <mergeCell ref="N143:N146"/>
+    <mergeCell ref="J195:J202"/>
+    <mergeCell ref="O125:O132"/>
+    <mergeCell ref="D116:D119"/>
+    <mergeCell ref="C121:C128"/>
+    <mergeCell ref="C104:D108"/>
+    <mergeCell ref="J83:J90"/>
+    <mergeCell ref="J162:J165"/>
+    <mergeCell ref="J65:J76"/>
+    <mergeCell ref="I105:J108"/>
+    <mergeCell ref="D87:D90"/>
+    <mergeCell ref="I134:I141"/>
+    <mergeCell ref="I7:P19"/>
+    <mergeCell ref="J120:J123"/>
+    <mergeCell ref="B221:Q226"/>
+    <mergeCell ref="C97:C100"/>
+    <mergeCell ref="N97:N100"/>
+    <mergeCell ref="H24:J27"/>
+    <mergeCell ref="N79:N86"/>
+    <mergeCell ref="N104:O108"/>
+    <mergeCell ref="I183:J187"/>
+    <mergeCell ref="I204:I211"/>
+    <mergeCell ref="N134:N141"/>
+    <mergeCell ref="O162:O165"/>
+    <mergeCell ref="O97:O100"/>
+    <mergeCell ref="J172:J179"/>
+    <mergeCell ref="B2:D5"/>
+    <mergeCell ref="O74:O77"/>
+    <mergeCell ref="I150:J154"/>
+    <mergeCell ref="I125:I132"/>
+    <mergeCell ref="N69:N72"/>
+    <mergeCell ref="D92:D95"/>
+    <mergeCell ref="I37:J43"/>
+    <mergeCell ref="D121:D128"/>
+    <mergeCell ref="C153:C160"/>
+    <mergeCell ref="J92:J95"/>
+    <mergeCell ref="I111:I118"/>
+    <mergeCell ref="D130:D137"/>
+    <mergeCell ref="O79:O86"/>
+    <mergeCell ref="C63:D66"/>
+    <mergeCell ref="C45:D52"/>
+    <mergeCell ref="N110:O117"/>
+    <mergeCell ref="C57:D61"/>
+    <mergeCell ref="J78:J81"/>
+    <mergeCell ref="C116:C119"/>
+    <mergeCell ref="C141:D145"/>
+    <mergeCell ref="O172:O175"/>
+    <mergeCell ref="C171:C174"/>
+    <mergeCell ref="I99:J103"/>
+    <mergeCell ref="I65:I76"/>
+    <mergeCell ref="O69:O72"/>
+    <mergeCell ref="C110:D113"/>
+    <mergeCell ref="O143:O146"/>
+    <mergeCell ref="I195:I202"/>
+    <mergeCell ref="N125:N132"/>
+    <mergeCell ref="N120:N123"/>
+    <mergeCell ref="N150:O154"/>
+    <mergeCell ref="I143:I146"/>
+    <mergeCell ref="I167:I170"/>
+    <mergeCell ref="I59:J62"/>
+    <mergeCell ref="N37:O43"/>
+    <mergeCell ref="I53:J57"/>
+    <mergeCell ref="J143:J146"/>
+    <mergeCell ref="N63:O66"/>
+    <mergeCell ref="N172:N175"/>
+    <mergeCell ref="O167:O170"/>
+    <mergeCell ref="D171:D174"/>
+    <mergeCell ref="N162:N165"/>
+    <mergeCell ref="C130:C137"/>
+    <mergeCell ref="D162:D169"/>
+    <mergeCell ref="N88:N95"/>
+    <mergeCell ref="C147:D150"/>
+    <mergeCell ref="C87:C90"/>
+    <mergeCell ref="J134:J141"/>
+    <mergeCell ref="I45:J48"/>
+    <mergeCell ref="I32:J35"/>
+    <mergeCell ref="N156:O159"/>
+    <mergeCell ref="C69:C76"/>
+    <mergeCell ref="C78:C85"/>
+    <mergeCell ref="J204:J211"/>
+    <mergeCell ref="D69:D76"/>
+    <mergeCell ref="N167:N170"/>
+    <mergeCell ref="C162:C169"/>
+    <mergeCell ref="O88:O95"/>
+    <mergeCell ref="I92:I95"/>
+    <mergeCell ref="D97:D100"/>
+    <mergeCell ref="O134:O141"/>
+    <mergeCell ref="N32:O35"/>
+    <mergeCell ref="I189:J192"/>
+    <mergeCell ref="N45:O52"/>
+    <mergeCell ref="N57:O61"/>
+    <mergeCell ref="D78:D85"/>
+    <mergeCell ref="I83:I90"/>
+    <mergeCell ref="I78:I81"/>
+    <mergeCell ref="N74:N77"/>
+    <mergeCell ref="J125:J132"/>
+    <mergeCell ref="B7:H19"/>
+    <mergeCell ref="I172:I179"/>
+  </mergeCells>
+  <pageMargins left="0.3" right="0.3" top="0.3" bottom="0.3" header="0" footer="0"/>
+  <pageSetup orientation="landscape" paperSize="1" fitToHeight="1" fitToWidth="1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
@@ -1315,7 +6910,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <tabColor rgb="FF6B7C93"/>
@@ -1340,46 +6935,44 @@
       </c>
     </row>
     <row r="3" ht="32" customHeight="1">
-      <c r="B3" s="15" t="inlineStr">
+      <c r="B3" s="13" t="inlineStr">
         <is>
           <t>An optional deeper version of the Part B grid, rolled up from the variable inventory's own subcategories. Use this instead of the 10-row grid if we want more granularity from vendors. It does not expose the numbered inventory itself.</t>
         </is>
       </c>
     </row>
     <row r="5" ht="22" customHeight="1">
-      <c r="B5" s="10" t="inlineStr">
+      <c r="B5" s="9" t="inlineStr">
         <is>
           <t>COVERAGE — EXPANDED</t>
         </is>
       </c>
-      <c r="C5" s="11" t="n"/>
-      <c r="D5" s="11" t="n"/>
     </row>
     <row r="6">
-      <c r="B6" s="12" t="inlineStr">
+      <c r="B6" s="10" t="inlineStr">
         <is>
           <t>#</t>
         </is>
       </c>
-      <c r="C6" s="12" t="inlineStr">
+      <c r="C6" s="10" t="inlineStr">
         <is>
           <t>AREA</t>
         </is>
       </c>
-      <c r="D6" s="12" t="inlineStr">
+      <c r="D6" s="10" t="inlineStr">
         <is>
           <t>STATUS  →  then notes</t>
         </is>
       </c>
     </row>
     <row r="7" ht="18" customHeight="1">
-      <c r="B7" s="16" t="inlineStr">
+      <c r="B7" s="14" t="inlineStr">
         <is>
           <t>Capacity Management</t>
         </is>
       </c>
-      <c r="C7" s="17" t="n"/>
-      <c r="D7" s="17" t="n"/>
+      <c r="C7" s="15" t="n"/>
+      <c r="D7" s="15" t="n"/>
     </row>
     <row r="8" ht="28" customHeight="1">
       <c r="B8" s="1" t="n">
@@ -1390,7 +6983,7 @@
           <t>Roster — Headcount by discipline, role (assessing vs. assistant), FTE and employment type</t>
         </is>
       </c>
-      <c r="D8" s="18" t="n"/>
+      <c r="D8" s="55" t="n"/>
     </row>
     <row r="9" ht="28" customHeight="1">
       <c r="B9" s="1" t="n">
@@ -1401,7 +6994,7 @@
           <t>Availability — Approved time off and working availability</t>
         </is>
       </c>
-      <c r="D9" s="18" t="n"/>
+      <c r="D9" s="55" t="n"/>
     </row>
     <row r="10" ht="28" customHeight="1">
       <c r="B10" s="1" t="n">
@@ -1412,7 +7005,7 @@
           <t>Territory &amp; geography — Branch coverage area, clinician territory assignment by zip</t>
         </is>
       </c>
-      <c r="D10" s="18" t="n"/>
+      <c r="D10" s="55" t="n"/>
     </row>
     <row r="11" ht="28" customHeight="1">
       <c r="B11" s="1" t="n">
@@ -1423,7 +7016,7 @@
           <t>Reachability — Distance and drive time from the clinician's home base</t>
         </is>
       </c>
-      <c r="D11" s="18" t="n"/>
+      <c r="D11" s="55" t="n"/>
     </row>
     <row r="12" ht="28" customHeight="1">
       <c r="B12" s="1" t="n">
@@ -1434,7 +7027,7 @@
           <t>Visit weighting — Point value per visit type — the shared currency of capacity</t>
         </is>
       </c>
-      <c r="D12" s="18" t="n"/>
+      <c r="D12" s="55" t="n"/>
     </row>
     <row r="13" ht="28" customHeight="1">
       <c r="B13" s="1" t="n">
@@ -1445,7 +7038,7 @@
           <t>Targets &amp; ceilings — Productivity target and the ceiling it is measured against</t>
         </is>
       </c>
-      <c r="D13" s="18" t="n"/>
+      <c r="D13" s="55" t="n"/>
     </row>
     <row r="14" ht="28" customHeight="1">
       <c r="B14" s="1" t="n">
@@ -1456,7 +7049,7 @@
           <t>Committed load — Points already scheduled, by clinician, day and week</t>
         </is>
       </c>
-      <c r="D14" s="18" t="n"/>
+      <c r="D14" s="55" t="n"/>
     </row>
     <row r="15" ht="28" customHeight="1">
       <c r="B15" s="1" t="n">
@@ -1467,7 +7060,7 @@
           <t>Open room — Remaining capacity by day, week, discipline and territory</t>
         </is>
       </c>
-      <c r="D15" s="18" t="n"/>
+      <c r="D15" s="55" t="n"/>
     </row>
     <row r="16" ht="28" customHeight="1">
       <c r="B16" s="1" t="n">
@@ -1478,7 +7071,7 @@
           <t>Start-of-care capacity — SOC-capable clinicians measured as a distinct number</t>
         </is>
       </c>
-      <c r="D16" s="18" t="n"/>
+      <c r="D16" s="55" t="n"/>
     </row>
     <row r="17" ht="28" customHeight="1">
       <c r="B17" s="1" t="n">
@@ -1489,7 +7082,7 @@
           <t>Specialty competency supply — Wound, IV, catheter and other competencies available</t>
         </is>
       </c>
-      <c r="D17" s="18" t="n"/>
+      <c r="D17" s="55" t="n"/>
     </row>
     <row r="18" ht="28" customHeight="1">
       <c r="B18" s="1" t="n">
@@ -1500,7 +7093,7 @@
           <t>Orientation &amp; ramp — Clinicians not yet at full load, and their trajectory</t>
         </is>
       </c>
-      <c r="D18" s="18" t="n"/>
+      <c r="D18" s="55" t="n"/>
     </row>
     <row r="19" ht="28" customHeight="1">
       <c r="B19" s="1" t="n">
@@ -1511,7 +7104,7 @@
           <t>Per-diem &amp; float buffer — Flex capacity available to the branch</t>
         </is>
       </c>
-      <c r="D19" s="18" t="n"/>
+      <c r="D19" s="55" t="n"/>
     </row>
     <row r="20" ht="28" customHeight="1">
       <c r="B20" s="1" t="n">
@@ -1522,7 +7115,7 @@
           <t>On-call &amp; weekend rotation — Rotation load carried alongside the weekday schedule</t>
         </is>
       </c>
-      <c r="D20" s="18" t="n"/>
+      <c r="D20" s="55" t="n"/>
     </row>
     <row r="21" ht="28" customHeight="1">
       <c r="B21" s="1" t="n">
@@ -1533,16 +7126,16 @@
           <t>Demand inflow — Referral volume in, discharge volume out, against the envelope</t>
         </is>
       </c>
-      <c r="D21" s="18" t="n"/>
+      <c r="D21" s="55" t="n"/>
     </row>
     <row r="22" ht="18" customHeight="1">
-      <c r="B22" s="16" t="inlineStr">
+      <c r="B22" s="14" t="inlineStr">
         <is>
           <t>Scheduling Engine</t>
         </is>
       </c>
-      <c r="C22" s="17" t="n"/>
-      <c r="D22" s="17" t="n"/>
+      <c r="C22" s="15" t="n"/>
+      <c r="D22" s="15" t="n"/>
     </row>
     <row r="23" ht="28" customHeight="1">
       <c r="B23" s="1" t="n">
@@ -1553,7 +7146,7 @@
           <t>Plan-of-care orders — Ordered frequency and visit types per discipline</t>
         </is>
       </c>
-      <c r="D23" s="18" t="n"/>
+      <c r="D23" s="55" t="n"/>
     </row>
     <row r="24" ht="28" customHeight="1">
       <c r="B24" s="1" t="n">
@@ -1564,7 +7157,7 @@
           <t>Compliance windows — SOC timing, recertification and face-to-face windows, ordered-frequency windows</t>
         </is>
       </c>
-      <c r="D24" s="18" t="n"/>
+      <c r="D24" s="55" t="n"/>
     </row>
     <row r="25" ht="28" customHeight="1">
       <c r="B25" s="1" t="n">
@@ -1575,7 +7168,7 @@
           <t>Authorization — Authorized visit counts, payer rules, pending-auth state</t>
         </is>
       </c>
-      <c r="D25" s="18" t="n"/>
+      <c r="D25" s="55" t="n"/>
     </row>
     <row r="26" ht="28" customHeight="1">
       <c r="B26" s="1" t="n">
@@ -1586,7 +7179,7 @@
           <t>Order &amp; consent readiness — Signed orders, consent, power-of-attorney signature status</t>
         </is>
       </c>
-      <c r="D26" s="18" t="n"/>
+      <c r="D26" s="55" t="n"/>
     </row>
     <row r="27" ht="28" customHeight="1">
       <c r="B27" s="1" t="n">
@@ -1597,7 +7190,7 @@
           <t>Discipline &amp; role match — Right discipline, and assessing vs. assistant</t>
         </is>
       </c>
-      <c r="D27" s="18" t="n"/>
+      <c r="D27" s="55" t="n"/>
     </row>
     <row r="28" ht="28" customHeight="1">
       <c r="B28" s="1" t="n">
@@ -1608,7 +7201,7 @@
           <t>Specialty &amp; acuity match — Competency and skill level against patient acuity</t>
         </is>
       </c>
-      <c r="D28" s="18" t="n"/>
+      <c r="D28" s="55" t="n"/>
     </row>
     <row r="29" ht="28" customHeight="1">
       <c r="B29" s="1" t="n">
@@ -1619,7 +7212,7 @@
           <t>Clinician working pattern — Preferred days, start and end times, documentation blocks, daily volume</t>
         </is>
       </c>
-      <c r="D29" s="18" t="n"/>
+      <c r="D29" s="55" t="n"/>
     </row>
     <row r="30" ht="28" customHeight="1">
       <c r="B30" s="1" t="n">
@@ -1630,7 +7223,7 @@
           <t>Clinician restrictions — Self-imposed restrictions and individual needs</t>
         </is>
       </c>
-      <c r="D30" s="18" t="n"/>
+      <c r="D30" s="55" t="n"/>
     </row>
     <row r="31" ht="28" customHeight="1">
       <c r="B31" s="1" t="n">
@@ -1641,7 +7234,7 @@
           <t>Patient availability &amp; preference — Preferred windows, day-of-week constraints, time-of-day refusals</t>
         </is>
       </c>
-      <c r="D31" s="18" t="n"/>
+      <c r="D31" s="55" t="n"/>
     </row>
     <row r="32" ht="28" customHeight="1">
       <c r="B32" s="1" t="n">
@@ -1652,7 +7245,7 @@
           <t>Caregiver constraints — Caregiver-present requirements and caregiver availability</t>
         </is>
       </c>
-      <c r="D32" s="18" t="n"/>
+      <c r="D32" s="55" t="n"/>
     </row>
     <row r="33" ht="28" customHeight="1">
       <c r="B33" s="1" t="n">
@@ -1663,7 +7256,7 @@
           <t>Clinical timing — Diagnosis-driven cadence, competing appointments, infection-control sequencing</t>
         </is>
       </c>
-      <c r="D33" s="18" t="n"/>
+      <c r="D33" s="55" t="n"/>
     </row>
     <row r="34" ht="28" customHeight="1">
       <c r="B34" s="1" t="n">
@@ -1674,7 +7267,7 @@
           <t>Continuity &amp; dependency — Continuity of care, supervisory visit dependencies</t>
         </is>
       </c>
-      <c r="D34" s="18" t="n"/>
+      <c r="D34" s="55" t="n"/>
     </row>
     <row r="35" ht="28" customHeight="1">
       <c r="B35" s="1" t="n">
@@ -1685,7 +7278,7 @@
           <t>Routing — Home base start and end, route proximity, mileage, intra-day sequencing</t>
         </is>
       </c>
-      <c r="D35" s="18" t="n"/>
+      <c r="D35" s="55" t="n"/>
     </row>
     <row r="36" ht="28" customHeight="1">
       <c r="B36" s="1" t="n">
@@ -1696,7 +7289,7 @@
           <t>Week distribution — Front-loading, pace against the plan of care, day-by-day balancing</t>
         </is>
       </c>
-      <c r="D36" s="18" t="n"/>
+      <c r="D36" s="55" t="n"/>
     </row>
     <row r="37" ht="28" customHeight="1">
       <c r="B37" s="1" t="n">
@@ -1707,16 +7300,16 @@
           <t>Missed-visit handling — Documentation, notification chain, and rescheduling</t>
         </is>
       </c>
-      <c r="D37" s="18" t="n"/>
+      <c r="D37" s="55" t="n"/>
     </row>
     <row r="38" ht="18" customHeight="1">
-      <c r="B38" s="16" t="inlineStr">
+      <c r="B38" s="14" t="inlineStr">
         <is>
           <t>Engagement</t>
         </is>
       </c>
-      <c r="C38" s="17" t="n"/>
-      <c r="D38" s="17" t="n"/>
+      <c r="C38" s="15" t="n"/>
+      <c r="D38" s="15" t="n"/>
     </row>
     <row r="39" ht="28" customHeight="1">
       <c r="B39" s="1" t="n">
@@ -1727,7 +7320,7 @@
           <t>Welcome call — New-patient introduction and expectation setting</t>
         </is>
       </c>
-      <c r="D39" s="18" t="n"/>
+      <c r="D39" s="55" t="n"/>
     </row>
     <row r="40" ht="28" customHeight="1">
       <c r="B40" s="1" t="n">
@@ -1738,7 +7331,7 @@
           <t>Availability capture — Asking the patient when they can be seen, before booking</t>
         </is>
       </c>
-      <c r="D40" s="18" t="n"/>
+      <c r="D40" s="55" t="n"/>
     </row>
     <row r="41" ht="28" customHeight="1">
       <c r="B41" s="1" t="n">
@@ -1749,7 +7342,7 @@
           <t>Reminders &amp; confirmation — Automated reminders and day-before confirmation</t>
         </is>
       </c>
-      <c r="D41" s="18" t="n"/>
+      <c r="D41" s="55" t="n"/>
     </row>
     <row r="42" ht="28" customHeight="1">
       <c r="B42" s="1" t="n">
@@ -1760,7 +7353,7 @@
           <t>En-route notification — On-my-way messaging to the patient</t>
         </is>
       </c>
-      <c r="D42" s="18" t="n"/>
+      <c r="D42" s="55" t="n"/>
     </row>
     <row r="43" ht="28" customHeight="1">
       <c r="B43" s="1" t="n">
@@ -1771,7 +7364,7 @@
           <t>Channel &amp; preference management — Text, voice, email, language, consent and opt-out</t>
         </is>
       </c>
-      <c r="D43" s="18" t="n"/>
+      <c r="D43" s="55" t="n"/>
     </row>
     <row r="44" ht="28" customHeight="1">
       <c r="B44" s="1" t="n">
@@ -1782,7 +7375,7 @@
           <t>Reschedule coordination — Patient-initiated and clinician-initiated changes</t>
         </is>
       </c>
-      <c r="D44" s="18" t="n"/>
+      <c r="D44" s="55" t="n"/>
     </row>
     <row r="45" ht="28" customHeight="1">
       <c r="B45" s="1" t="n">
@@ -1793,7 +7386,7 @@
           <t>Coverage coordination — Matching potential clinicians to an open need and reaching them</t>
         </is>
       </c>
-      <c r="D45" s="18" t="n"/>
+      <c r="D45" s="55" t="n"/>
     </row>
     <row r="46" ht="28" customHeight="1">
       <c r="B46" s="1" t="n">
@@ -1804,7 +7397,7 @@
           <t>Urgent same-day needs — Call-outs and priority needs surfacing during the day</t>
         </is>
       </c>
-      <c r="D46" s="18" t="n"/>
+      <c r="D46" s="55" t="n"/>
     </row>
     <row r="47" ht="28" customHeight="1">
       <c r="B47" s="1" t="n">
@@ -1815,7 +7408,7 @@
           <t>No-show follow-up — Failed-visit follow-up and rebooking</t>
         </is>
       </c>
-      <c r="D47" s="18" t="n"/>
+      <c r="D47" s="55" t="n"/>
     </row>
     <row r="48" ht="28" customHeight="1">
       <c r="B48" s="1" t="n">
@@ -1826,7 +7419,7 @@
           <t>Multi-discipline coordination — Sequencing visits across disciplines on one case</t>
         </is>
       </c>
-      <c r="D48" s="18" t="n"/>
+      <c r="D48" s="55" t="n"/>
     </row>
     <row r="49" ht="28" customHeight="1">
       <c r="B49" s="1" t="n">
@@ -1837,7 +7430,7 @@
           <t>Care-team &amp; office updates — Keeping clinicians and the office on the same schedule</t>
         </is>
       </c>
-      <c r="D49" s="18" t="n"/>
+      <c r="D49" s="55" t="n"/>
     </row>
     <row r="50" ht="28" customHeight="1">
       <c r="B50" s="1" t="n">
@@ -1848,9 +7441,12 @@
           <t>Coordination time load — How much staff time coordination consumes</t>
         </is>
       </c>
-      <c r="D50" s="18" t="n"/>
+      <c r="D50" s="55" t="n"/>
     </row>
   </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="B5:D5"/>
+  </mergeCells>
   <dataValidations count="1">
     <dataValidation sqref="D8 D9 D10 D11 D12 D13 D14 D15 D16 D17 D18 D19 D20 D21 D23 D24 D25 D26 D27 D28 D29 D30 D31 D32 D33 D34 D35 D36 D37 D39 D40 D41 D42 D43 D44 D45 D46 D47 D48 D49 D50" showDropDown="0" showInputMessage="1" showErrorMessage="0" allowBlank="1" promptTitle="Select status" prompt="Production · In development · Roadmap · Not offered. Add a note after your choice." type="list">
       <formula1>StatusList</formula1>
@@ -1870,7 +7466,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <tabColor rgb="FF8C7A5B"/>
@@ -1894,22 +7490,21 @@
       </c>
     </row>
     <row r="3" ht="32" customHeight="1">
-      <c r="B3" s="15" t="inlineStr">
+      <c r="B3" s="13" t="inlineStr">
         <is>
           <t>Internal. Drafted, judged valuable, and deliberately kept out of round one so the questionnaire stays answerable. Most need a screen, a follow-up or a tone of voice to be worth anything — which is what the virtual calls are for.</t>
         </is>
       </c>
     </row>
     <row r="5" ht="22" customHeight="1">
-      <c r="B5" s="10" t="inlineStr">
+      <c r="B5" s="9" t="inlineStr">
         <is>
           <t>CAPACITY</t>
         </is>
       </c>
-      <c r="C5" s="11" t="n"/>
     </row>
     <row r="6" ht="35" customHeight="1">
-      <c r="B6" s="13" t="n">
+      <c r="B6" s="11" t="n">
         <v>1</v>
       </c>
       <c r="C6" s="4" t="inlineStr">
@@ -1919,7 +7514,7 @@
       </c>
     </row>
     <row r="7" ht="35" customHeight="1">
-      <c r="B7" s="13" t="n">
+      <c r="B7" s="11" t="n">
         <v>2</v>
       </c>
       <c r="C7" s="4" t="inlineStr">
@@ -1929,7 +7524,7 @@
       </c>
     </row>
     <row r="8" ht="21" customHeight="1">
-      <c r="B8" s="13" t="n">
+      <c r="B8" s="11" t="n">
         <v>3</v>
       </c>
       <c r="C8" s="4" t="inlineStr">
@@ -1939,7 +7534,7 @@
       </c>
     </row>
     <row r="9" ht="35" customHeight="1">
-      <c r="B9" s="13" t="n">
+      <c r="B9" s="11" t="n">
         <v>4</v>
       </c>
       <c r="C9" s="4" t="inlineStr">
@@ -1949,15 +7544,14 @@
       </c>
     </row>
     <row r="11" ht="22" customHeight="1">
-      <c r="B11" s="10" t="inlineStr">
+      <c r="B11" s="9" t="inlineStr">
         <is>
           <t>SCHEDULING</t>
         </is>
       </c>
-      <c r="C11" s="11" t="n"/>
     </row>
     <row r="12" ht="35" customHeight="1">
-      <c r="B12" s="13" t="n">
+      <c r="B12" s="11" t="n">
         <v>1</v>
       </c>
       <c r="C12" s="4" t="inlineStr">
@@ -1967,7 +7561,7 @@
       </c>
     </row>
     <row r="13" ht="35" customHeight="1">
-      <c r="B13" s="13" t="n">
+      <c r="B13" s="11" t="n">
         <v>2</v>
       </c>
       <c r="C13" s="4" t="inlineStr">
@@ -1977,7 +7571,7 @@
       </c>
     </row>
     <row r="14" ht="35" customHeight="1">
-      <c r="B14" s="13" t="n">
+      <c r="B14" s="11" t="n">
         <v>3</v>
       </c>
       <c r="C14" s="4" t="inlineStr">
@@ -1987,7 +7581,7 @@
       </c>
     </row>
     <row r="15" ht="21" customHeight="1">
-      <c r="B15" s="13" t="n">
+      <c r="B15" s="11" t="n">
         <v>4</v>
       </c>
       <c r="C15" s="4" t="inlineStr">
@@ -1997,15 +7591,14 @@
       </c>
     </row>
     <row r="17" ht="22" customHeight="1">
-      <c r="B17" s="10" t="inlineStr">
+      <c r="B17" s="9" t="inlineStr">
         <is>
           <t>ENGAGEMENT</t>
         </is>
       </c>
-      <c r="C17" s="11" t="n"/>
     </row>
     <row r="18" ht="35" customHeight="1">
-      <c r="B18" s="13" t="n">
+      <c r="B18" s="11" t="n">
         <v>1</v>
       </c>
       <c r="C18" s="4" t="inlineStr">
@@ -2015,7 +7608,7 @@
       </c>
     </row>
     <row r="19" ht="21" customHeight="1">
-      <c r="B19" s="13" t="n">
+      <c r="B19" s="11" t="n">
         <v>2</v>
       </c>
       <c r="C19" s="4" t="inlineStr">
@@ -2025,7 +7618,7 @@
       </c>
     </row>
     <row r="20" ht="21" customHeight="1">
-      <c r="B20" s="13" t="n">
+      <c r="B20" s="11" t="n">
         <v>3</v>
       </c>
       <c r="C20" s="4" t="inlineStr">
@@ -2035,15 +7628,14 @@
       </c>
     </row>
     <row r="22" ht="22" customHeight="1">
-      <c r="B22" s="10" t="inlineStr">
+      <c r="B22" s="9" t="inlineStr">
         <is>
           <t>THE CLINICIAN</t>
         </is>
       </c>
-      <c r="C22" s="11" t="n"/>
     </row>
     <row r="23" ht="35" customHeight="1">
-      <c r="B23" s="13" t="n">
+      <c r="B23" s="11" t="n">
         <v>1</v>
       </c>
       <c r="C23" s="4" t="inlineStr">
@@ -2053,7 +7645,7 @@
       </c>
     </row>
     <row r="24" ht="35" customHeight="1">
-      <c r="B24" s="13" t="n">
+      <c r="B24" s="11" t="n">
         <v>2</v>
       </c>
       <c r="C24" s="4" t="inlineStr">
@@ -2063,7 +7655,7 @@
       </c>
     </row>
     <row r="25" ht="21" customHeight="1">
-      <c r="B25" s="13" t="n">
+      <c r="B25" s="11" t="n">
         <v>3</v>
       </c>
       <c r="C25" s="4" t="inlineStr">
@@ -2073,15 +7665,14 @@
       </c>
     </row>
     <row r="27" ht="22" customHeight="1">
-      <c r="B27" s="10" t="inlineStr">
+      <c r="B27" s="9" t="inlineStr">
         <is>
           <t>FIT</t>
         </is>
       </c>
-      <c r="C27" s="11" t="n"/>
     </row>
     <row r="28" ht="21" customHeight="1">
-      <c r="B28" s="13" t="n">
+      <c r="B28" s="11" t="n">
         <v>1</v>
       </c>
       <c r="C28" s="4" t="inlineStr">
@@ -2091,15 +7682,14 @@
       </c>
     </row>
     <row r="30" ht="22" customHeight="1">
-      <c r="B30" s="10" t="inlineStr">
+      <c r="B30" s="9" t="inlineStr">
         <is>
           <t>COMMERCIAL</t>
         </is>
       </c>
-      <c r="C30" s="11" t="n"/>
     </row>
     <row r="31" ht="35" customHeight="1">
-      <c r="B31" s="13" t="n">
+      <c r="B31" s="11" t="n">
         <v>1</v>
       </c>
       <c r="C31" s="4" t="inlineStr">
@@ -2109,7 +7699,7 @@
       </c>
     </row>
     <row r="32" ht="21" customHeight="1">
-      <c r="B32" s="13" t="n">
+      <c r="B32" s="11" t="n">
         <v>2</v>
       </c>
       <c r="C32" s="4" t="inlineStr">
@@ -2119,7 +7709,7 @@
       </c>
     </row>
     <row r="33" ht="21" customHeight="1">
-      <c r="B33" s="13" t="n">
+      <c r="B33" s="11" t="n">
         <v>3</v>
       </c>
       <c r="C33" s="4" t="inlineStr">
@@ -2129,15 +7719,14 @@
       </c>
     </row>
     <row r="35" ht="22" customHeight="1">
-      <c r="B35" s="10" t="inlineStr">
+      <c r="B35" s="9" t="inlineStr">
         <is>
           <t>NASHVILLE — DEEP DIVE</t>
         </is>
       </c>
-      <c r="C35" s="11" t="n"/>
     </row>
     <row r="36" ht="21" customHeight="1">
-      <c r="B36" s="13" t="n">
+      <c r="B36" s="11" t="n">
         <v>1</v>
       </c>
       <c r="C36" s="4" t="inlineStr">
@@ -2147,7 +7736,7 @@
       </c>
     </row>
     <row r="37" ht="35" customHeight="1">
-      <c r="B37" s="13" t="n">
+      <c r="B37" s="11" t="n">
         <v>2</v>
       </c>
       <c r="C37" s="4" t="inlineStr">
@@ -2157,7 +7746,7 @@
       </c>
     </row>
     <row r="38" ht="35" customHeight="1">
-      <c r="B38" s="13" t="n">
+      <c r="B38" s="11" t="n">
         <v>3</v>
       </c>
       <c r="C38" s="4" t="inlineStr">
@@ -2167,7 +7756,7 @@
       </c>
     </row>
     <row r="39" ht="21" customHeight="1">
-      <c r="B39" s="13" t="n">
+      <c r="B39" s="11" t="n">
         <v>4</v>
       </c>
       <c r="C39" s="4" t="inlineStr">
@@ -2177,7 +7766,7 @@
       </c>
     </row>
     <row r="40" ht="35" customHeight="1">
-      <c r="B40" s="13" t="n">
+      <c r="B40" s="11" t="n">
         <v>5</v>
       </c>
       <c r="C40" s="4" t="inlineStr">
@@ -2187,7 +7776,7 @@
       </c>
     </row>
     <row r="41" ht="35" customHeight="1">
-      <c r="B41" s="13" t="n">
+      <c r="B41" s="11" t="n">
         <v>6</v>
       </c>
       <c r="C41" s="4" t="inlineStr">
@@ -2197,7 +7786,7 @@
       </c>
     </row>
     <row r="42" ht="21" customHeight="1">
-      <c r="B42" s="13" t="n">
+      <c r="B42" s="11" t="n">
         <v>7</v>
       </c>
       <c r="C42" s="4" t="inlineStr">
@@ -2207,6 +7796,15 @@
       </c>
     </row>
   </sheetData>
+  <mergeCells count="7">
+    <mergeCell ref="B30:C30"/>
+    <mergeCell ref="B11:C11"/>
+    <mergeCell ref="B5:C5"/>
+    <mergeCell ref="B22:C22"/>
+    <mergeCell ref="B17:C17"/>
+    <mergeCell ref="B27:C27"/>
+    <mergeCell ref="B35:C35"/>
+  </mergeCells>
   <printOptions horizontalCentered="1"/>
   <pageMargins left="0.5" right="0.5" top="0.6" bottom="0.6" header="0.5" footer="0.5"/>
   <pageSetup orientation="portrait" paperSize="9" fitToHeight="0" fitToWidth="1"/>
@@ -2221,7 +7819,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <tabColor rgb="FF7A4E4E"/>
@@ -2246,40 +7844,38 @@
       </c>
     </row>
     <row r="3" ht="44" customHeight="1">
-      <c r="B3" s="15" t="inlineStr">
+      <c r="B3" s="13" t="inlineStr">
         <is>
           <t>Set aside from the round-one questionnaire for review with leadership. The working assumption is that the companies on our list have already been vetted for maturity, security posture and contracting readiness — so asking these up front spends goodwill on answers we may already have. They remain here so the decision to include or exclude them is deliberate.</t>
         </is>
       </c>
     </row>
     <row r="5" ht="22" customHeight="1">
-      <c r="B5" s="10" t="inlineStr">
+      <c r="B5" s="9" t="inlineStr">
         <is>
           <t>SET ASIDE FROM ROUND ONE</t>
         </is>
       </c>
-      <c r="C5" s="11" t="n"/>
-      <c r="D5" s="11" t="n"/>
     </row>
     <row r="6">
-      <c r="B6" s="12" t="inlineStr">
+      <c r="B6" s="10" t="inlineStr">
         <is>
           <t>TOPIC</t>
         </is>
       </c>
-      <c r="C6" s="12" t="inlineStr">
+      <c r="C6" s="10" t="inlineStr">
         <is>
           <t>QUESTION AS DRAFTED</t>
         </is>
       </c>
-      <c r="D6" s="12" t="inlineStr">
+      <c r="D6" s="10" t="inlineStr">
         <is>
           <t>WHY IT IS SET ASIDE</t>
         </is>
       </c>
     </row>
     <row r="7" ht="79" customHeight="1">
-      <c r="B7" s="19" t="inlineStr">
+      <c r="B7" s="56" t="inlineStr">
         <is>
           <t>Company maturity</t>
         </is>
@@ -2289,14 +7885,14 @@
           <t>Year founded, current headcount, and where you are in your funding cycle (bootstrapped, seed, Series A/B/C, PE-backed, profitable), including your most recent raise and date. Not asking for cap-table detail — we are trying to understand the durability of a multi-year partnership.</t>
         </is>
       </c>
-      <c r="D7" s="15" t="inlineStr">
+      <c r="D7" s="13" t="inlineStr">
         <is>
           <t>Was A4. Likely already known for most of the list.</t>
         </is>
       </c>
     </row>
     <row r="8" ht="35" customHeight="1">
-      <c r="B8" s="19" t="inlineStr">
+      <c r="B8" s="56" t="inlineStr">
         <is>
           <t>Security and compliance</t>
         </is>
@@ -2306,14 +7902,14 @@
           <t>Hosting model, SOC 2 and/or HITRUST status, willingness to sign a BAA, and how PHI is handled.</t>
         </is>
       </c>
-      <c r="D8" s="15" t="inlineStr">
+      <c r="D8" s="13" t="inlineStr">
         <is>
           <t>Was A6. Near-certain to be satisfied by anyone we are talking to; verifiable afterwards.</t>
         </is>
       </c>
     </row>
     <row r="9" ht="50" customHeight="1">
-      <c r="B9" s="19" t="inlineStr">
+      <c r="B9" s="56" t="inlineStr">
         <is>
           <t>Implementation shape</t>
         </is>
@@ -2323,14 +7919,14 @@
           <t>Roughly what does implementation look like for an organization of our size — duration, phases, and what you need from us?</t>
         </is>
       </c>
-      <c r="D9" s="15" t="inlineStr">
+      <c r="D9" s="13" t="inlineStr">
         <is>
           <t>Was part of A6. More useful on a call, where follow-up is possible.</t>
         </is>
       </c>
     </row>
     <row r="10" ht="35" customHeight="1">
-      <c r="B10" s="19" t="inlineStr">
+      <c r="B10" s="56" t="inlineStr">
         <is>
           <t>Insurance and contracting</t>
         </is>
@@ -2340,14 +7936,14 @@
           <t>Cyber liability and professional liability coverage; standard contracting vehicle; any terms you will not negotiate.</t>
         </is>
       </c>
-      <c r="D10" s="15" t="inlineStr">
+      <c r="D10" s="13" t="inlineStr">
         <is>
           <t>Not previously asked. Procurement territory — likely belongs after selection, not before.</t>
         </is>
       </c>
     </row>
     <row r="11" ht="35" customHeight="1">
-      <c r="B11" s="19" t="inlineStr">
+      <c r="B11" s="56" t="inlineStr">
         <is>
           <t>Product and engineering scale</t>
         </is>
@@ -2357,13 +7953,16 @@
           <t>Size of the product and engineering team, release cadence, and how customers influence the roadmap.</t>
         </is>
       </c>
-      <c r="D11" s="15" t="inlineStr">
+      <c r="D11" s="13" t="inlineStr">
         <is>
           <t>Not previously asked. Relevant if we pursue a design-partner arrangement (see E2).</t>
         </is>
       </c>
     </row>
   </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="B5:D5"/>
+  </mergeCells>
   <printOptions horizontalCentered="1"/>
   <pageMargins left="0.5" right="0.5" top="0.6" bottom="0.6" header="0.5" footer="0.5"/>
   <pageSetup orientation="portrait" paperSize="9" fitToHeight="0" fitToWidth="1"/>
@@ -2378,7 +7977,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>

--- a/agents/compassus-capacity-pm/rfp/Compassus-Vendor-Questionnaire-MASTER.xlsx
+++ b/agents/compassus-capacity-pm/rfp/Compassus-Vendor-Questionnaire-MASTER.xlsx
@@ -862,7 +862,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="B2:E22"/>
+  <dimension ref="B2:E19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="2.5" customWidth="1" min="1" max="1"/>
@@ -904,95 +904,79 @@
     <row r="8">
       <c r="B8" s="3" t="inlineStr">
         <is>
-          <t>Answering</t>
+          <t>Practical notes</t>
         </is>
       </c>
     </row>
     <row r="9" ht="35" customHeight="1">
       <c r="B9" s="4" t="inlineStr">
         <is>
-          <t>Answer in your own words. Most answers run a short paragraph. There is no advantage in volume, and where something does not apply to your product, saying so plainly is a genuinely useful answer.</t>
+          <t>Press Alt+Enter to start a new paragraph inside a cell. Press Ctrl+Shift+U to expand the formula bar if you would rather write there. You can drag any row taller if you need more room.</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="B11" s="3" t="inlineStr">
         <is>
-          <t>Practical notes</t>
-        </is>
-      </c>
-    </row>
-    <row r="12" ht="35" customHeight="1">
+          <t>Working as a team</t>
+        </is>
+      </c>
+    </row>
+    <row r="12" ht="21" customHeight="1">
       <c r="B12" s="4" t="inlineStr">
         <is>
-          <t>Press Alt+Enter to start a new paragraph inside a cell. Press Ctrl+Shift+U to expand the formula bar if you would rather write there. You can drag any row taller if you need more room — the height we set is only a suggestion of length.</t>
+          <t>If several people need to contribute, put the file in your own SharePoint or Drive to co-author it, then send the completed workbook back.</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="B14" s="3" t="inlineStr">
         <is>
-          <t>Working as a team</t>
+          <t>The Overview tab</t>
         </is>
       </c>
     </row>
     <row r="15" ht="21" customHeight="1">
       <c r="B15" s="4" t="inlineStr">
         <is>
-          <t>If several people need to contribute, put the file in your own SharePoint or Drive to co-author it, then send the completed workbook back.</t>
+          <t>The Overview tab reproduces the one-page summary of what we are looking for. It is there for reference while you answer.</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="B17" s="3" t="inlineStr">
         <is>
-          <t>The Overview tab</t>
-        </is>
-      </c>
-    </row>
-    <row r="18" ht="21" customHeight="1">
-      <c r="B18" s="4" t="inlineStr">
-        <is>
-          <t>The Overview tab reproduces the one-page summary of what we are looking for. It is there for reference while you answer.</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="B20" s="3" t="inlineStr">
-        <is>
           <t>Progress</t>
         </is>
       </c>
     </row>
-    <row r="21" ht="20" customHeight="1">
-      <c r="B21" s="5">
+    <row r="18" ht="20" customHeight="1">
+      <c r="B18" s="5">
         <f>COUNTA(Questionnaire!E9,Questionnaire!E11,Questionnaire!E13,Questionnaire!E15,Questionnaire!E37,Questionnaire!E39,Questionnaire!E41,Questionnaire!E43,Questionnaire!E45,Questionnaire!E47,Questionnaire!E53,Questionnaire!E55,Questionnaire!E57,Questionnaire!E59,Questionnaire!E64,Questionnaire!E66,Questionnaire!E68) &amp; " of 17 questions answered"</f>
         <v/>
       </c>
     </row>
-    <row r="22" ht="20" customHeight="1">
-      <c r="B22" s="6" t="inlineStr">
+    <row r="19" ht="20" customHeight="1">
+      <c r="B19" s="6" t="inlineStr">
         <is>
           <t>Updates as you type. Counts the answer cells only, not the coverage grid.</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="15">
-    <mergeCell ref="B20:E20"/>
+  <mergeCells count="13">
     <mergeCell ref="B17:E17"/>
     <mergeCell ref="B9:E9"/>
     <mergeCell ref="B18:E18"/>
     <mergeCell ref="B8:E8"/>
     <mergeCell ref="B12:E12"/>
     <mergeCell ref="B6:E6"/>
-    <mergeCell ref="B21:E21"/>
     <mergeCell ref="B15:E15"/>
     <mergeCell ref="B11:E11"/>
     <mergeCell ref="B3:E3"/>
     <mergeCell ref="B5:E5"/>
     <mergeCell ref="B2:E2"/>
-    <mergeCell ref="B22:E22"/>
+    <mergeCell ref="B19:E19"/>
     <mergeCell ref="B14:E14"/>
   </mergeCells>
   <printOptions horizontalCentered="1"/>

--- a/agents/compassus-capacity-pm/rfp/Compassus-Vendor-Questionnaire-MASTER.xlsx
+++ b/agents/compassus-capacity-pm/rfp/Compassus-Vendor-Questionnaire-MASTER.xlsx
@@ -2374,7 +2374,6 @@
     </row>
     <row r="78" ht="5" customHeight="1"/>
   </sheetData>
-  <sheetProtection selectLockedCells="0" selectUnlockedCells="0" sheet="1" objects="1" insertRows="1" insertHyperlinks="1" autoFilter="1" scenarios="1" formatColumns="1" deleteColumns="1" insertColumns="1" pivotTables="1" deleteRows="1" formatCells="0" formatRows="0" sort="1" password="DB7D"/>
   <mergeCells count="35">
     <mergeCell ref="B2:G2"/>
     <mergeCell ref="D56:G56"/>

--- a/agents/compassus-capacity-pm/rfp/Compassus-Vendor-Questionnaire-MASTER.xlsx
+++ b/agents/compassus-capacity-pm/rfp/Compassus-Vendor-Questionnaire-MASTER.xlsx
@@ -17,9 +17,10 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Meta" sheetId="8" state="hidden" r:id="rId8"/>
   </sheets>
   <definedNames>
-    <definedName name="InScopeList">Lists!$A$1:$A$3</definedName>
-    <definedName name="StatusList">Lists!$B$1:$B$4</definedName>
-    <definedName name="DeliveryList">Lists!$C$1:$C$4</definedName>
+    <definedName name="InScopeList">Lists!$A$1:$A$4</definedName>
+    <definedName name="StatusList">Lists!$B$1:$B$5</definedName>
+    <definedName name="DeliveryList">Lists!$C$1:$C$5</definedName>
+    <definedName name="CapacityInputList">Lists!$D$1:$D$6</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="1">'Questionnaire'!$1:$2</definedName>
     <definedName name="_xlnm.Print_Area" localSheetId="2">'Overview'!$A$1:$R$259</definedName>
   </definedNames>
@@ -30,7 +31,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="25">
+  <fonts count="24">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -90,11 +91,6 @@
       <b val="1"/>
       <color rgb="FF1F3B57"/>
       <sz val="10.5"/>
-    </font>
-    <font>
-      <name val="Calibri"/>
-      <color rgb="FF5B6572"/>
-      <sz val="10"/>
     </font>
     <font>
       <name val="Arial"/>
@@ -176,7 +172,7 @@
       <sz val="12.2"/>
     </font>
   </fonts>
-  <fills count="13">
+  <fills count="12">
     <fill>
       <patternFill/>
     </fill>
@@ -200,17 +196,12 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFF3B0"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor rgb="FFEEF2F6"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFF1F2F4"/>
+        <fgColor rgb="FFFFF3B0"/>
       </patternFill>
     </fill>
     <fill>
@@ -239,13 +230,48 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="19">
+  <borders count="22">
     <border>
       <left/>
       <right/>
       <top/>
       <bottom/>
       <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FFC7B37A"/>
+      </left>
+      <top style="thin">
+        <color rgb="FFC7B37A"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FFC7B37A"/>
+      </bottom>
+    </border>
+    <border>
+      <top style="thin">
+        <color rgb="FFC7B37A"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FFC7B37A"/>
+      </bottom>
+    </border>
+    <border>
+      <right style="thin">
+        <color rgb="FFC7B37A"/>
+      </right>
+      <top style="thin">
+        <color rgb="FFC7B37A"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FFC7B37A"/>
+      </bottom>
+    </border>
+    <border>
+      <bottom style="thin">
+        <color rgb="FFD8DEE6"/>
+      </bottom>
     </border>
     <border>
       <left style="thin">
@@ -259,11 +285,6 @@
       </top>
       <bottom style="thin">
         <color rgb="FFC7B37A"/>
-      </bottom>
-    </border>
-    <border>
-      <bottom style="thin">
-        <color rgb="FFD8DEE6"/>
       </bottom>
     </border>
     <border>
@@ -414,7 +435,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="67">
+  <cellXfs count="61">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -433,13 +454,16 @@
       <alignment vertical="top" wrapText="1" indent="1"/>
       <protection locked="0" hidden="0"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="2" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <protection locked="0" hidden="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="3" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
       <protection locked="0" hidden="0"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center" indent="1"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="2" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="4" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top"/>
     </xf>
@@ -452,100 +476,86 @@
     <xf numFmtId="0" fontId="0" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="5" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="9" fillId="5" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="5" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1" indent="1"/>
+      <protection locked="0" hidden="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="6" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="5" borderId="2" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="9" fillId="6" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="center" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="8" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="11" fillId="8" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="10" fillId="7" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="8" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="11" fillId="7" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="8" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="12" fillId="7" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="8" borderId="3" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="9" borderId="6" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="11" fillId="9" borderId="4" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="6" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="8" borderId="9" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="10" fillId="8" borderId="7" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="9" borderId="4" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="9" borderId="7" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="9" borderId="8" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="9" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="9" borderId="9" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="10" borderId="13" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="10" borderId="12" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="10" borderId="14" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="11" borderId="13" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="11" borderId="12" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="11" borderId="14" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="12" borderId="13" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="12" borderId="12" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="12" borderId="14" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="8" borderId="15" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="8" borderId="16" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="14" fillId="8" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="0" fillId="8" borderId="7" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="8" borderId="10" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="8" borderId="11" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="8" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="8" borderId="12" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="9" borderId="16" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="9" borderId="15" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="9" borderId="17" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="10" borderId="16" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="10" borderId="15" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="10" borderId="17" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="11" borderId="16" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="11" borderId="15" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="11" borderId="17" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="18" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="19" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="13" fillId="7" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="8" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="19" fillId="7" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="8" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="21" fillId="7" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="8" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="14" fillId="7" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="8" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="15" fillId="7" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="8" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="16" fillId="7" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="8" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="17" fillId="7" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="8" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="20" fillId="7" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="8" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="18" fillId="7" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="23" fillId="5" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="22" fillId="7" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="5" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="23" fillId="8" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="8" borderId="17" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="8" borderId="18" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="9" borderId="10" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="9" borderId="5" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="9" borderId="11" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="24" fillId="8" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="20" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="21" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="8" borderId="13" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="8" borderId="8" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="8" borderId="14" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="23" fillId="7" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -1007,10 +1017,10 @@
         </is>
       </c>
     </row>
-    <row r="18" ht="35" customHeight="1">
+    <row r="18" ht="50" customHeight="1">
       <c r="B18" s="4" t="inlineStr">
         <is>
-          <t>Part B marks each area three ways. IN SCOPE is whether your product does this at all. STATUS is how far along it is. HOW IT RUNS is whether a person still does the work. All three are dropdowns; the notes column beside them is free text.</t>
+          <t>Part B marks each area three ways. IN SCOPE is whether your product does this at all. STATUS is how far along it is. HOW IT'S DONE asks where the data comes from on the capacity rows, and how much of the work is automated on the rest. All three are dropdowns, each carrying an Other option, and the notes column beside them is free text — use it whenever a dropdown does not fit your answer.</t>
         </is>
       </c>
     </row>
@@ -1023,7 +1033,7 @@
     </row>
     <row r="21" ht="20" customHeight="1">
       <c r="B21" s="5">
-        <f>COUNTA(Questionnaire!D9,Questionnaire!D11,Questionnaire!D13,Questionnaire!D36,Questionnaire!D38,Questionnaire!D40,Questionnaire!D42,Questionnaire!D44,Questionnaire!D46,Questionnaire!D48,Questionnaire!D50,Questionnaire!D56,Questionnaire!D58,Questionnaire!D60,Questionnaire!D62,Questionnaire!D64,Questionnaire!D69,Questionnaire!D71,Questionnaire!D73,Questionnaire!D75,Questionnaire!D77) &amp; " of 21 questions answered"</f>
+        <f>COUNTA(Questionnaire!D9,Questionnaire!D11,Questionnaire!D13,Questionnaire!D36,Questionnaire!D38,Questionnaire!D40,Questionnaire!D42,Questionnaire!D44,Questionnaire!D46,Questionnaire!D48,Questionnaire!D54,Questionnaire!D56,Questionnaire!D58,Questionnaire!D63,Questionnaire!D65,Questionnaire!D67,Questionnaire!D69) &amp; " of 17 questions answered"</f>
         <v/>
       </c>
     </row>
@@ -1073,7 +1083,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="B1:G77"/>
+  <dimension ref="B1:G69"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="2.5" customWidth="1" min="1" max="1"/>
@@ -1110,7 +1120,7 @@
       <c r="D4" s="8" t="n"/>
       <c r="E4" s="9" t="n"/>
       <c r="F4" s="9" t="n"/>
-      <c r="G4" s="9" t="n"/>
+      <c r="G4" s="10" t="n"/>
     </row>
     <row r="5" ht="20" customHeight="1">
       <c r="C5" s="7" t="inlineStr">
@@ -1121,43 +1131,43 @@
       <c r="D5" s="8" t="n"/>
       <c r="E5" s="9" t="n"/>
       <c r="F5" s="9" t="n"/>
-      <c r="G5" s="9" t="n"/>
+      <c r="G5" s="10" t="n"/>
     </row>
     <row r="6" ht="8" customHeight="1"/>
     <row r="7" ht="22" customHeight="1">
-      <c r="B7" s="10" t="inlineStr">
+      <c r="B7" s="11" t="inlineStr">
         <is>
           <t>A.   COMPANY AND PRODUCT</t>
         </is>
       </c>
     </row>
     <row r="8" ht="15" customHeight="1">
-      <c r="B8" s="11" t="inlineStr">
+      <c r="B8" s="12" t="inlineStr">
         <is>
           <t>#</t>
         </is>
       </c>
-      <c r="C8" s="11" t="inlineStr">
+      <c r="C8" s="12" t="inlineStr">
         <is>
           <t>QUESTION</t>
         </is>
       </c>
-      <c r="D8" s="11" t="inlineStr">
+      <c r="D8" s="12" t="inlineStr">
         <is>
           <t>YOUR ANSWER</t>
         </is>
       </c>
-      <c r="E8" s="11" t="n"/>
-      <c r="F8" s="11" t="n"/>
-      <c r="G8" s="11" t="n"/>
+      <c r="E8" s="12" t="n"/>
+      <c r="F8" s="12" t="n"/>
+      <c r="G8" s="12" t="n"/>
     </row>
     <row r="9" ht="200" customHeight="1">
-      <c r="B9" s="12" t="inlineStr">
+      <c r="B9" s="13" t="inlineStr">
         <is>
           <t>A1</t>
         </is>
       </c>
-      <c r="C9" s="13" t="inlineStr">
+      <c r="C9" s="14" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -1182,16 +1192,16 @@
       <c r="D9" s="8" t="n"/>
       <c r="E9" s="9" t="n"/>
       <c r="F9" s="9" t="n"/>
-      <c r="G9" s="9" t="n"/>
+      <c r="G9" s="10" t="n"/>
     </row>
     <row r="10" ht="5" customHeight="1"/>
-    <row r="11" ht="214" customHeight="1">
-      <c r="B11" s="14" t="inlineStr">
+    <row r="11" ht="155" customHeight="1">
+      <c r="B11" s="15" t="inlineStr">
         <is>
           <t>A2</t>
         </is>
       </c>
-      <c r="C11" s="15" t="inlineStr">
+      <c r="C11" s="16" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -1209,23 +1219,23 @@
               <color rgb="001F2A37"/>
               <sz val="11"/>
             </rPr>
-            <t>How many organizations run your product in production today, and how many of those are Medicare-certified home health? Give us the census of your three largest deployments, along with branch and clinician counts. What share of your business is Medicare-certified home health, versus hospice, private duty or home care? References will be a significant part of our process. You do not need to supply the detail now, but please tell us whether you expect to be able to provide them.</t>
+            <t>How many organizations run your product in production today? Give us the census of your three largest deployments. What is the split of your business across home health, hospice and private duty? References will be a significant part of our process. You do not need to supply the detail now, but please tell us whether you expect to be able to provide them.</t>
           </r>
         </is>
       </c>
       <c r="D11" s="8" t="n"/>
       <c r="E11" s="9" t="n"/>
       <c r="F11" s="9" t="n"/>
-      <c r="G11" s="9" t="n"/>
+      <c r="G11" s="10" t="n"/>
     </row>
     <row r="12" ht="5" customHeight="1"/>
     <row r="13" ht="141" customHeight="1">
-      <c r="B13" s="16" t="inlineStr">
+      <c r="B13" s="13" t="inlineStr">
         <is>
           <t>A3</t>
         </is>
       </c>
-      <c r="C13" s="17" t="inlineStr">
+      <c r="C13" s="14" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -1250,11 +1260,11 @@
       <c r="D13" s="8" t="n"/>
       <c r="E13" s="9" t="n"/>
       <c r="F13" s="9" t="n"/>
-      <c r="G13" s="9" t="n"/>
+      <c r="G13" s="10" t="n"/>
     </row>
     <row r="14" ht="5" customHeight="1"/>
     <row r="16" ht="22" customHeight="1">
-      <c r="B16" s="10" t="inlineStr">
+      <c r="B16" s="11" t="inlineStr">
         <is>
           <t>B.   COVERAGE SELF-ASSESSMENT</t>
         </is>
@@ -1268,49 +1278,49 @@
       </c>
     </row>
     <row r="18" ht="15" customHeight="1">
-      <c r="B18" s="11" t="inlineStr">
+      <c r="B18" s="12" t="inlineStr">
         <is>
           <t>#</t>
         </is>
       </c>
-      <c r="C18" s="11" t="inlineStr">
+      <c r="C18" s="12" t="inlineStr">
         <is>
           <t>AREA</t>
         </is>
       </c>
-      <c r="D18" s="18" t="inlineStr">
+      <c r="D18" s="12" t="inlineStr">
         <is>
           <t>IN SCOPE</t>
         </is>
       </c>
-      <c r="E18" s="11" t="inlineStr">
+      <c r="E18" s="12" t="inlineStr">
         <is>
           <t>STATUS</t>
         </is>
       </c>
-      <c r="F18" s="18" t="inlineStr">
-        <is>
-          <t>HOW IT RUNS</t>
-        </is>
-      </c>
-      <c r="G18" s="11" t="inlineStr">
+      <c r="F18" s="12" t="inlineStr">
+        <is>
+          <t>HOW IT'S DONE</t>
+        </is>
+      </c>
+      <c r="G18" s="12" t="inlineStr">
         <is>
           <t>NOTES</t>
         </is>
       </c>
     </row>
     <row r="19" ht="18" customHeight="1">
-      <c r="B19" s="19" t="inlineStr">
+      <c r="B19" s="17" t="inlineStr">
         <is>
           <t>Capacity Management</t>
         </is>
       </c>
     </row>
     <row r="20" ht="54" customHeight="1">
-      <c r="B20" s="12" t="n">
+      <c r="B20" s="13" t="n">
         <v>1</v>
       </c>
-      <c r="C20" s="13" t="inlineStr">
+      <c r="C20" s="14" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -1332,20 +1342,16 @@
           </r>
         </is>
       </c>
-      <c r="D20" s="8" t="n"/>
-      <c r="E20" s="8" t="n"/>
-      <c r="F20" s="20" t="inlineStr">
-        <is>
-          <t>n/a</t>
-        </is>
-      </c>
-      <c r="G20" s="8" t="n"/>
+      <c r="D20" s="18" t="n"/>
+      <c r="E20" s="18" t="n"/>
+      <c r="F20" s="18" t="n"/>
+      <c r="G20" s="18" t="n"/>
     </row>
     <row r="21" ht="54" customHeight="1">
-      <c r="B21" s="12" t="n">
+      <c r="B21" s="13" t="n">
         <v>2</v>
       </c>
-      <c r="C21" s="13" t="inlineStr">
+      <c r="C21" s="14" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -1367,20 +1373,16 @@
           </r>
         </is>
       </c>
-      <c r="D21" s="8" t="n"/>
-      <c r="E21" s="8" t="n"/>
-      <c r="F21" s="20" t="inlineStr">
-        <is>
-          <t>n/a</t>
-        </is>
-      </c>
-      <c r="G21" s="8" t="n"/>
+      <c r="D21" s="18" t="n"/>
+      <c r="E21" s="18" t="n"/>
+      <c r="F21" s="18" t="n"/>
+      <c r="G21" s="18" t="n"/>
     </row>
     <row r="22" ht="54" customHeight="1">
-      <c r="B22" s="12" t="n">
+      <c r="B22" s="13" t="n">
         <v>3</v>
       </c>
-      <c r="C22" s="13" t="inlineStr">
+      <c r="C22" s="14" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -1402,27 +1404,23 @@
           </r>
         </is>
       </c>
-      <c r="D22" s="8" t="n"/>
-      <c r="E22" s="8" t="n"/>
-      <c r="F22" s="20" t="inlineStr">
-        <is>
-          <t>n/a</t>
-        </is>
-      </c>
-      <c r="G22" s="8" t="n"/>
+      <c r="D22" s="18" t="n"/>
+      <c r="E22" s="18" t="n"/>
+      <c r="F22" s="18" t="n"/>
+      <c r="G22" s="18" t="n"/>
     </row>
     <row r="23" ht="18" customHeight="1">
-      <c r="B23" s="19" t="inlineStr">
+      <c r="B23" s="17" t="inlineStr">
         <is>
           <t>Scheduling Engine</t>
         </is>
       </c>
     </row>
     <row r="24" ht="54" customHeight="1">
-      <c r="B24" s="12" t="n">
+      <c r="B24" s="13" t="n">
         <v>4</v>
       </c>
-      <c r="C24" s="13" t="inlineStr">
+      <c r="C24" s="14" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -1444,16 +1442,16 @@
           </r>
         </is>
       </c>
-      <c r="D24" s="8" t="n"/>
-      <c r="E24" s="8" t="n"/>
-      <c r="F24" s="8" t="n"/>
-      <c r="G24" s="8" t="n"/>
+      <c r="D24" s="18" t="n"/>
+      <c r="E24" s="18" t="n"/>
+      <c r="F24" s="18" t="n"/>
+      <c r="G24" s="18" t="n"/>
     </row>
     <row r="25" ht="54" customHeight="1">
-      <c r="B25" s="12" t="n">
+      <c r="B25" s="13" t="n">
         <v>5</v>
       </c>
-      <c r="C25" s="13" t="inlineStr">
+      <c r="C25" s="14" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -1475,16 +1473,16 @@
           </r>
         </is>
       </c>
-      <c r="D25" s="8" t="n"/>
-      <c r="E25" s="8" t="n"/>
-      <c r="F25" s="8" t="n"/>
-      <c r="G25" s="8" t="n"/>
+      <c r="D25" s="18" t="n"/>
+      <c r="E25" s="18" t="n"/>
+      <c r="F25" s="18" t="n"/>
+      <c r="G25" s="18" t="n"/>
     </row>
     <row r="26" ht="54" customHeight="1">
-      <c r="B26" s="12" t="n">
+      <c r="B26" s="13" t="n">
         <v>6</v>
       </c>
-      <c r="C26" s="13" t="inlineStr">
+      <c r="C26" s="14" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -1506,16 +1504,16 @@
           </r>
         </is>
       </c>
-      <c r="D26" s="8" t="n"/>
-      <c r="E26" s="8" t="n"/>
-      <c r="F26" s="8" t="n"/>
-      <c r="G26" s="8" t="n"/>
+      <c r="D26" s="18" t="n"/>
+      <c r="E26" s="18" t="n"/>
+      <c r="F26" s="18" t="n"/>
+      <c r="G26" s="18" t="n"/>
     </row>
     <row r="27" ht="54" customHeight="1">
-      <c r="B27" s="14" t="n">
+      <c r="B27" s="13" t="n">
         <v>7</v>
       </c>
-      <c r="C27" s="15" t="inlineStr">
+      <c r="C27" s="14" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -1537,23 +1535,23 @@
           </r>
         </is>
       </c>
-      <c r="D27" s="8" t="n"/>
-      <c r="E27" s="8" t="n"/>
-      <c r="F27" s="8" t="n"/>
-      <c r="G27" s="8" t="n"/>
+      <c r="D27" s="18" t="n"/>
+      <c r="E27" s="18" t="n"/>
+      <c r="F27" s="18" t="n"/>
+      <c r="G27" s="18" t="n"/>
     </row>
     <row r="28" ht="18" customHeight="1">
-      <c r="B28" s="19" t="inlineStr">
+      <c r="B28" s="17" t="inlineStr">
         <is>
           <t>Engagement</t>
         </is>
       </c>
     </row>
     <row r="29" ht="54" customHeight="1">
-      <c r="B29" s="12" t="n">
+      <c r="B29" s="13" t="n">
         <v>8</v>
       </c>
-      <c r="C29" s="13" t="inlineStr">
+      <c r="C29" s="14" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -1575,16 +1573,16 @@
           </r>
         </is>
       </c>
-      <c r="D29" s="8" t="n"/>
-      <c r="E29" s="8" t="n"/>
-      <c r="F29" s="8" t="n"/>
-      <c r="G29" s="8" t="n"/>
+      <c r="D29" s="18" t="n"/>
+      <c r="E29" s="18" t="n"/>
+      <c r="F29" s="18" t="n"/>
+      <c r="G29" s="18" t="n"/>
     </row>
     <row r="30" ht="54" customHeight="1">
-      <c r="B30" s="12" t="n">
+      <c r="B30" s="13" t="n">
         <v>9</v>
       </c>
-      <c r="C30" s="13" t="inlineStr">
+      <c r="C30" s="14" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -1606,16 +1604,16 @@
           </r>
         </is>
       </c>
-      <c r="D30" s="8" t="n"/>
-      <c r="E30" s="8" t="n"/>
-      <c r="F30" s="8" t="n"/>
-      <c r="G30" s="8" t="n"/>
+      <c r="D30" s="18" t="n"/>
+      <c r="E30" s="18" t="n"/>
+      <c r="F30" s="18" t="n"/>
+      <c r="G30" s="18" t="n"/>
     </row>
     <row r="31" ht="54" customHeight="1">
-      <c r="B31" s="16" t="n">
+      <c r="B31" s="13" t="n">
         <v>10</v>
       </c>
-      <c r="C31" s="17" t="inlineStr">
+      <c r="C31" s="14" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -1637,16 +1635,16 @@
           </r>
         </is>
       </c>
-      <c r="D31" s="8" t="n"/>
-      <c r="E31" s="8" t="n"/>
-      <c r="F31" s="8" t="n"/>
-      <c r="G31" s="8" t="n"/>
+      <c r="D31" s="18" t="n"/>
+      <c r="E31" s="18" t="n"/>
+      <c r="F31" s="18" t="n"/>
+      <c r="G31" s="18" t="n"/>
     </row>
     <row r="32" ht="54" customHeight="1">
-      <c r="B32" s="12" t="n">
+      <c r="B32" s="13" t="n">
         <v>11</v>
       </c>
-      <c r="C32" s="13" t="inlineStr">
+      <c r="C32" s="14" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -1668,45 +1666,45 @@
           </r>
         </is>
       </c>
-      <c r="D32" s="8" t="n"/>
-      <c r="E32" s="8" t="n"/>
-      <c r="F32" s="8" t="n"/>
-      <c r="G32" s="8" t="n"/>
+      <c r="D32" s="18" t="n"/>
+      <c r="E32" s="18" t="n"/>
+      <c r="F32" s="18" t="n"/>
+      <c r="G32" s="18" t="n"/>
     </row>
     <row r="34" ht="22" customHeight="1">
-      <c r="B34" s="10" t="inlineStr">
+      <c r="B34" s="11" t="inlineStr">
         <is>
           <t>C.   HOW YOUR PRODUCT WORKS</t>
         </is>
       </c>
     </row>
     <row r="35" ht="15" customHeight="1">
-      <c r="B35" s="11" t="inlineStr">
+      <c r="B35" s="12" t="inlineStr">
         <is>
           <t>#</t>
         </is>
       </c>
-      <c r="C35" s="11" t="inlineStr">
+      <c r="C35" s="12" t="inlineStr">
         <is>
           <t>QUESTION</t>
         </is>
       </c>
-      <c r="D35" s="11" t="inlineStr">
+      <c r="D35" s="12" t="inlineStr">
         <is>
           <t>YOUR ANSWER</t>
         </is>
       </c>
-      <c r="E35" s="11" t="n"/>
-      <c r="F35" s="11" t="n"/>
-      <c r="G35" s="11" t="n"/>
-    </row>
-    <row r="36" ht="124" customHeight="1">
-      <c r="B36" s="12" t="inlineStr">
+      <c r="E35" s="12" t="n"/>
+      <c r="F35" s="12" t="n"/>
+      <c r="G35" s="12" t="n"/>
+    </row>
+    <row r="36" ht="155" customHeight="1">
+      <c r="B36" s="15" t="inlineStr">
         <is>
           <t>C1</t>
         </is>
       </c>
-      <c r="C36" s="13" t="inlineStr">
+      <c r="C36" s="16" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -1724,23 +1722,23 @@
               <color rgb="001F2A37"/>
               <sz val="11"/>
             </rPr>
-            <t>How does your product determine how much capacity a branch has and how much is left? Cover the unit you measure in and where the inputs come from. Add anything else you think we should understand about how you approach this.</t>
+            <t>How does your product determine how much capacity a branch has and how much is left? Cover the unit you measure in and where the inputs come from. Then make it concrete: a branch leader is deciding whether to accept a referral today — what can your product tell them? Add anything else you think we should understand about how you approach this.</t>
           </r>
         </is>
       </c>
       <c r="D36" s="8" t="n"/>
       <c r="E36" s="9" t="n"/>
       <c r="F36" s="9" t="n"/>
-      <c r="G36" s="9" t="n"/>
+      <c r="G36" s="10" t="n"/>
     </row>
     <row r="37" ht="5" customHeight="1"/>
-    <row r="38" ht="80" customHeight="1">
-      <c r="B38" s="12" t="inlineStr">
+    <row r="38" ht="124" customHeight="1">
+      <c r="B38" s="13" t="inlineStr">
         <is>
           <t>C2</t>
         </is>
       </c>
-      <c r="C38" s="13" t="inlineStr">
+      <c r="C38" s="14" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -1749,7 +1747,7 @@
               <color rgb="001F2A37"/>
               <sz val="11"/>
             </rPr>
-            <t xml:space="preserve">Capacity in use
+            <t xml:space="preserve">Assignment
 </t>
           </r>
           <r>
@@ -1758,23 +1756,23 @@
               <color rgb="001F2A37"/>
               <sz val="11"/>
             </rPr>
-            <t>A branch leader is deciding whether to accept a referral today. What can your product tell them?</t>
+            <t>Walk us through how your product decides which clinician should take a given visit — what it considers, how it weighs those factors, and what a customer can configure.</t>
           </r>
         </is>
       </c>
       <c r="D38" s="8" t="n"/>
       <c r="E38" s="9" t="n"/>
       <c r="F38" s="9" t="n"/>
-      <c r="G38" s="9" t="n"/>
+      <c r="G38" s="10" t="n"/>
     </row>
     <row r="39" ht="5" customHeight="1"/>
-    <row r="40" ht="124" customHeight="1">
-      <c r="B40" s="12" t="inlineStr">
+    <row r="40" ht="126" customHeight="1">
+      <c r="B40" s="13" t="inlineStr">
         <is>
           <t>C3</t>
         </is>
       </c>
-      <c r="C40" s="13" t="inlineStr">
+      <c r="C40" s="14" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -1783,7 +1781,7 @@
               <color rgb="001F2A37"/>
               <sz val="11"/>
             </rPr>
-            <t xml:space="preserve">Assignment
+            <t xml:space="preserve">Readiness
 </t>
           </r>
           <r>
@@ -1792,23 +1790,23 @@
               <color rgb="001F2A37"/>
               <sz val="11"/>
             </rPr>
-            <t>Walk us through how your product decides which clinician should take a given visit — what it considers, how it weighs those factors, and what a customer can configure.</t>
+            <t>What does your product do with a visit that has been ordered but is not yet schedulable — for example because authorization is still pending, consent from a power of attorney is outstanding, or the clinician it will be assigned to has not yet been determined?</t>
           </r>
         </is>
       </c>
       <c r="D40" s="8" t="n"/>
       <c r="E40" s="9" t="n"/>
       <c r="F40" s="9" t="n"/>
-      <c r="G40" s="9" t="n"/>
+      <c r="G40" s="10" t="n"/>
     </row>
     <row r="41" ht="5" customHeight="1"/>
-    <row r="42" ht="126" customHeight="1">
-      <c r="B42" s="12" t="inlineStr">
+    <row r="42" ht="94" customHeight="1">
+      <c r="B42" s="13" t="inlineStr">
         <is>
           <t>C4</t>
         </is>
       </c>
-      <c r="C42" s="13" t="inlineStr">
+      <c r="C42" s="14" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -1817,7 +1815,7 @@
               <color rgb="001F2A37"/>
               <sz val="11"/>
             </rPr>
-            <t xml:space="preserve">Readiness
+            <t xml:space="preserve">The week
 </t>
           </r>
           <r>
@@ -1826,23 +1824,23 @@
               <color rgb="001F2A37"/>
               <sz val="11"/>
             </rPr>
-            <t>What does your product do with a visit that has been ordered but is not yet schedulable — for example because authorization is still pending, consent from a power of attorney is outstanding, or the clinician it will be assigned to has not yet been determined?</t>
+            <t>How does your product plan across a week or an episode rather than a single day?</t>
           </r>
         </is>
       </c>
       <c r="D42" s="8" t="n"/>
       <c r="E42" s="9" t="n"/>
       <c r="F42" s="9" t="n"/>
-      <c r="G42" s="9" t="n"/>
+      <c r="G42" s="10" t="n"/>
     </row>
     <row r="43" ht="5" customHeight="1"/>
-    <row r="44" ht="94" customHeight="1">
-      <c r="B44" s="14" t="inlineStr">
+    <row r="44" ht="126" customHeight="1">
+      <c r="B44" s="13" t="inlineStr">
         <is>
           <t>C5</t>
         </is>
       </c>
-      <c r="C44" s="15" t="inlineStr">
+      <c r="C44" s="14" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -1851,7 +1849,7 @@
               <color rgb="001F2A37"/>
               <sz val="11"/>
             </rPr>
-            <t xml:space="preserve">The week
+            <t xml:space="preserve">When the plan breaks
 </t>
           </r>
           <r>
@@ -1860,23 +1858,23 @@
               <color rgb="001F2A37"/>
               <sz val="11"/>
             </rPr>
-            <t>How does your product plan across a week or an episode rather than a single day?</t>
+            <t>Walk us through what your product does when a clinician calls out, a visit is missed, or a patient reschedules. Cover how the open need is identified, how coverage is found and offered, how quickly that happens, and what your product does when nobody takes it.</t>
           </r>
         </is>
       </c>
       <c r="D44" s="8" t="n"/>
       <c r="E44" s="9" t="n"/>
       <c r="F44" s="9" t="n"/>
-      <c r="G44" s="9" t="n"/>
+      <c r="G44" s="10" t="n"/>
     </row>
     <row r="45" ht="5" customHeight="1"/>
-    <row r="46" ht="126" customHeight="1">
-      <c r="B46" s="16" t="inlineStr">
+    <row r="46" ht="170" customHeight="1">
+      <c r="B46" s="19" t="inlineStr">
         <is>
           <t>C6</t>
         </is>
       </c>
-      <c r="C46" s="17" t="inlineStr">
+      <c r="C46" s="20" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -1885,7 +1883,7 @@
               <color rgb="001F2A37"/>
               <sz val="11"/>
             </rPr>
-            <t xml:space="preserve">When the plan breaks
+            <t xml:space="preserve">When your product is down
 </t>
           </r>
           <r>
@@ -1894,23 +1892,23 @@
               <color rgb="001F2A37"/>
               <sz val="11"/>
             </rPr>
-            <t>Walk us through what your product does when a clinician calls out, a visit is missed, or a patient reschedules. Cover how the open need is identified, how coverage is found and offered, how quickly that happens, and what your product does when nobody takes it.</t>
+            <t>This product would carry work that hundreds of schedulers do today, so an outage does not slow us down — it stops nurses being deployed. How do you think about business continuity? Cover your uptime over the last twelve months, what a customer experiences during an outage, what they are able to do while it lasts, and what you commit to contractually.</t>
           </r>
         </is>
       </c>
       <c r="D46" s="8" t="n"/>
       <c r="E46" s="9" t="n"/>
       <c r="F46" s="9" t="n"/>
-      <c r="G46" s="9" t="n"/>
+      <c r="G46" s="10" t="n"/>
     </row>
     <row r="47" ht="5" customHeight="1"/>
-    <row r="48" ht="124" customHeight="1">
-      <c r="B48" s="14" t="inlineStr">
+    <row r="48" ht="155" customHeight="1">
+      <c r="B48" s="15" t="inlineStr">
         <is>
           <t>C7</t>
         </is>
       </c>
-      <c r="C48" s="15" t="inlineStr">
+      <c r="C48" s="16" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -1919,7 +1917,7 @@
               <color rgb="001F2A37"/>
               <sz val="11"/>
             </rPr>
-            <t xml:space="preserve">Automated outreach
+            <t xml:space="preserve">Talking to the patient
 </t>
           </r>
           <r>
@@ -1928,23 +1926,57 @@
               <color rgb="001F2A37"/>
               <sz val="11"/>
             </rPr>
-            <t>Where automated outreach exists in your product, how far does it go? Describe the channels, whether the conversation is scripted or agentic, what it can resolve on its own, what it hands to a person, and what controls a customer has over all of it.</t>
+            <t>How and when do you capture a patient's availability, and what does your product do when that availability conflicts with clinical need? Where your outreach to patients is automated, how far does it go — the channels, whether the conversation is scripted or agentic, what it resolves on its own, and what it hands to a person.</t>
           </r>
         </is>
       </c>
       <c r="D48" s="8" t="n"/>
       <c r="E48" s="9" t="n"/>
       <c r="F48" s="9" t="n"/>
-      <c r="G48" s="9" t="n"/>
+      <c r="G48" s="10" t="n"/>
     </row>
     <row r="49" ht="5" customHeight="1"/>
-    <row r="50" ht="82" customHeight="1">
-      <c r="B50" s="16" t="inlineStr">
-        <is>
-          <t>C8</t>
-        </is>
-      </c>
-      <c r="C50" s="17" t="inlineStr">
+    <row r="51" ht="22" customHeight="1">
+      <c r="B51" s="11" t="inlineStr">
+        <is>
+          <t>D.   THE CLINICIAN'S PLACE IN THE MODEL</t>
+        </is>
+      </c>
+    </row>
+    <row r="52" ht="48" customHeight="1">
+      <c r="B52" s="6" t="inlineStr">
+        <is>
+          <t>Scheduling in home health is operationally critical and personally consequential. Many clinicians come to home health for the control it gives them over their own day and week, and any change to how visits get assigned lands on people who feel strongly about it. In our experience adoption, more than algorithm quality, decides whether tools like this succeed. These questions are about how your product treats the clinician.</t>
+        </is>
+      </c>
+    </row>
+    <row r="53" ht="15" customHeight="1">
+      <c r="B53" s="12" t="inlineStr">
+        <is>
+          <t>#</t>
+        </is>
+      </c>
+      <c r="C53" s="12" t="inlineStr">
+        <is>
+          <t>QUESTION</t>
+        </is>
+      </c>
+      <c r="D53" s="12" t="inlineStr">
+        <is>
+          <t>YOUR ANSWER</t>
+        </is>
+      </c>
+      <c r="E53" s="12" t="n"/>
+      <c r="F53" s="12" t="n"/>
+      <c r="G53" s="12" t="n"/>
+    </row>
+    <row r="54" ht="170" customHeight="1">
+      <c r="B54" s="15" t="inlineStr">
+        <is>
+          <t>D1</t>
+        </is>
+      </c>
+      <c r="C54" s="16" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -1953,7 +1985,7 @@
               <color rgb="001F2A37"/>
               <sz val="11"/>
             </rPr>
-            <t xml:space="preserve">Patient availability
+            <t xml:space="preserve">What the clinician decides
 </t>
           </r>
           <r>
@@ -1962,57 +1994,23 @@
               <color rgb="001F2A37"/>
               <sz val="11"/>
             </rPr>
-            <t>How and when do you capture a patient's availability, and what does your product do when that availability conflicts with clinical need?</t>
-          </r>
-        </is>
-      </c>
-      <c r="D50" s="8" t="n"/>
-      <c r="E50" s="9" t="n"/>
-      <c r="F50" s="9" t="n"/>
-      <c r="G50" s="9" t="n"/>
-    </row>
-    <row r="51" ht="5" customHeight="1"/>
-    <row r="53" ht="22" customHeight="1">
-      <c r="B53" s="10" t="inlineStr">
-        <is>
-          <t>D.   THE CLINICIAN'S PLACE IN THE MODEL</t>
-        </is>
-      </c>
-    </row>
-    <row r="54" ht="48" customHeight="1">
-      <c r="B54" s="6" t="inlineStr">
-        <is>
-          <t>Scheduling in home health is operationally critical and personally consequential. Many clinicians come to home health for the control it gives them over their own day and week, and any change to how visits get assigned lands on people who feel strongly about it. In our experience adoption, more than algorithm quality, decides whether tools like this succeed. These questions are about how your product treats the clinician.</t>
-        </is>
-      </c>
-    </row>
-    <row r="55" ht="15" customHeight="1">
-      <c r="B55" s="11" t="inlineStr">
-        <is>
-          <t>#</t>
-        </is>
-      </c>
-      <c r="C55" s="11" t="inlineStr">
-        <is>
-          <t>QUESTION</t>
-        </is>
-      </c>
-      <c r="D55" s="11" t="inlineStr">
-        <is>
-          <t>YOUR ANSWER</t>
-        </is>
-      </c>
-      <c r="E55" s="11" t="n"/>
-      <c r="F55" s="11" t="n"/>
-      <c r="G55" s="11" t="n"/>
-    </row>
-    <row r="56" ht="124" customHeight="1">
-      <c r="B56" s="12" t="inlineStr">
-        <is>
-          <t>D1</t>
-        </is>
-      </c>
-      <c r="C56" s="13" t="inlineStr">
+            <t>Which scheduling decisions does the clinician make in your product, and which are made for them? Be specific about what they can change, what requires approval, and what they cannot change at all. And when your product proposes an assignment the clinician disagrees with, what happens — does anything change as a result, for that clinician or in the model?</t>
+          </r>
+        </is>
+      </c>
+      <c r="D54" s="8" t="n"/>
+      <c r="E54" s="9" t="n"/>
+      <c r="F54" s="9" t="n"/>
+      <c r="G54" s="10" t="n"/>
+    </row>
+    <row r="55" ht="5" customHeight="1"/>
+    <row r="56" ht="96" customHeight="1">
+      <c r="B56" s="13" t="inlineStr">
+        <is>
+          <t>D2</t>
+        </is>
+      </c>
+      <c r="C56" s="14" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -2021,7 +2019,7 @@
               <color rgb="001F2A37"/>
               <sz val="11"/>
             </rPr>
-            <t xml:space="preserve">What the clinician decides
+            <t xml:space="preserve">Decide or advise
 </t>
           </r>
           <r>
@@ -2030,23 +2028,23 @@
               <color rgb="001F2A37"/>
               <sz val="11"/>
             </rPr>
-            <t>Which scheduling decisions does the clinician make in your product, and which are made for them? Be specific about what they can change, what requires approval, and what they cannot change at all.</t>
+            <t>Some organizations want the system to decide; others want it to advise. Where was your product designed to sit on that spectrum, and how much of that can a customer change?</t>
           </r>
         </is>
       </c>
       <c r="D56" s="8" t="n"/>
       <c r="E56" s="9" t="n"/>
       <c r="F56" s="9" t="n"/>
-      <c r="G56" s="9" t="n"/>
+      <c r="G56" s="10" t="n"/>
     </row>
     <row r="57" ht="5" customHeight="1"/>
-    <row r="58" ht="96" customHeight="1">
-      <c r="B58" s="12" t="inlineStr">
-        <is>
-          <t>D2</t>
-        </is>
-      </c>
-      <c r="C58" s="13" t="inlineStr">
+    <row r="58" ht="111" customHeight="1">
+      <c r="B58" s="13" t="inlineStr">
+        <is>
+          <t>D3</t>
+        </is>
+      </c>
+      <c r="C58" s="14" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -2055,7 +2053,7 @@
               <color rgb="001F2A37"/>
               <sz val="11"/>
             </rPr>
-            <t xml:space="preserve">Disagreement
+            <t xml:space="preserve">Adoption
 </t>
           </r>
           <r>
@@ -2064,23 +2062,50 @@
               <color rgb="001F2A37"/>
               <sz val="11"/>
             </rPr>
-            <t>When your product proposes an assignment and the clinician disagrees, what happens? Does anything change as a result — for that clinician, or in the model?</t>
+            <t>How do you measure clinician adoption, what do you consider healthy, and what does your data show across the first six months? Separately — what can a clinician see in your product about their own results?</t>
           </r>
         </is>
       </c>
       <c r="D58" s="8" t="n"/>
       <c r="E58" s="9" t="n"/>
       <c r="F58" s="9" t="n"/>
-      <c r="G58" s="9" t="n"/>
+      <c r="G58" s="10" t="n"/>
     </row>
     <row r="59" ht="5" customHeight="1"/>
-    <row r="60" ht="124" customHeight="1">
-      <c r="B60" s="12" t="inlineStr">
-        <is>
-          <t>D3</t>
-        </is>
-      </c>
-      <c r="C60" s="13" t="inlineStr">
+    <row r="61" ht="22" customHeight="1">
+      <c r="B61" s="11" t="inlineStr">
+        <is>
+          <t>E.   FIT AND PARTNERSHIP</t>
+        </is>
+      </c>
+    </row>
+    <row r="62" ht="15" customHeight="1">
+      <c r="B62" s="12" t="inlineStr">
+        <is>
+          <t>#</t>
+        </is>
+      </c>
+      <c r="C62" s="12" t="inlineStr">
+        <is>
+          <t>QUESTION</t>
+        </is>
+      </c>
+      <c r="D62" s="12" t="inlineStr">
+        <is>
+          <t>YOUR ANSWER</t>
+        </is>
+      </c>
+      <c r="E62" s="12" t="n"/>
+      <c r="F62" s="12" t="n"/>
+      <c r="G62" s="12" t="n"/>
+    </row>
+    <row r="63" ht="109" customHeight="1">
+      <c r="B63" s="13" t="inlineStr">
+        <is>
+          <t>E1</t>
+        </is>
+      </c>
+      <c r="C63" s="14" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -2089,7 +2114,7 @@
               <color rgb="001F2A37"/>
               <sz val="11"/>
             </rPr>
-            <t xml:space="preserve">Resistance
+            <t xml:space="preserve">What we did not ask
 </t>
           </r>
           <r>
@@ -2098,23 +2123,23 @@
               <color rgb="001F2A37"/>
               <sz val="11"/>
             </rPr>
-            <t>Describe a deployment where clinicians resisted your product. What did you learn, and what did you change — in the product, or in how you rolled it out?</t>
-          </r>
-        </is>
-      </c>
-      <c r="D60" s="8" t="n"/>
-      <c r="E60" s="9" t="n"/>
-      <c r="F60" s="9" t="n"/>
-      <c r="G60" s="9" t="n"/>
-    </row>
-    <row r="61" ht="5" customHeight="1"/>
-    <row r="62" ht="96" customHeight="1">
-      <c r="B62" s="12" t="inlineStr">
-        <is>
-          <t>D4</t>
-        </is>
-      </c>
-      <c r="C62" s="13" t="inlineStr">
+            <t>What do you do that we have not asked about, and that you believe would matter to an organization like ours?</t>
+          </r>
+        </is>
+      </c>
+      <c r="D63" s="8" t="n"/>
+      <c r="E63" s="9" t="n"/>
+      <c r="F63" s="9" t="n"/>
+      <c r="G63" s="10" t="n"/>
+    </row>
+    <row r="64" ht="5" customHeight="1"/>
+    <row r="65" ht="229" customHeight="1">
+      <c r="B65" s="15" t="inlineStr">
+        <is>
+          <t>E2</t>
+        </is>
+      </c>
+      <c r="C65" s="16" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -2123,7 +2148,7 @@
               <color rgb="001F2A37"/>
               <sz val="11"/>
             </rPr>
-            <t xml:space="preserve">Decide or advise
+            <t xml:space="preserve">Sharing in the value
 </t>
           </r>
           <r>
@@ -2132,23 +2157,23 @@
               <color rgb="001F2A37"/>
               <sz val="11"/>
             </rPr>
-            <t>Some organizations want the system to decide; others want it to advise. Where was your product designed to sit on that spectrum, and how much of that can a customer change?</t>
-          </r>
-        </is>
-      </c>
-      <c r="D62" s="8" t="n"/>
-      <c r="E62" s="9" t="n"/>
-      <c r="F62" s="9" t="n"/>
-      <c r="G62" s="9" t="n"/>
-    </row>
-    <row r="63" ht="5" customHeight="1"/>
-    <row r="64" ht="111" customHeight="1">
-      <c r="B64" s="16" t="inlineStr">
-        <is>
-          <t>D5</t>
-        </is>
-      </c>
-      <c r="C64" s="17" t="inlineStr">
+            <t>Compassus will be putting a significant investment into the success of this work, including a dedicated scheduling optimization team, SME support, design partnership, a deep people-centric enterprise deployment, and ongoing enhancement tracking.  We are also willing to be a co-marketing partner; presenting at conferences, interviews, white papers, etc.  Given this material investment, we are looking to share in the value we'll be helping to create.  Please share some detail on your proposed / preferred ways of partnering.</t>
+          </r>
+        </is>
+      </c>
+      <c r="D65" s="8" t="n"/>
+      <c r="E65" s="9" t="n"/>
+      <c r="F65" s="9" t="n"/>
+      <c r="G65" s="10" t="n"/>
+    </row>
+    <row r="66" ht="5" customHeight="1"/>
+    <row r="67" ht="155" customHeight="1">
+      <c r="B67" s="15" t="inlineStr">
+        <is>
+          <t>E3</t>
+        </is>
+      </c>
+      <c r="C67" s="16" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -2157,7 +2182,7 @@
               <color rgb="001F2A37"/>
               <sz val="11"/>
             </rPr>
-            <t xml:space="preserve">Adoption
+            <t xml:space="preserve">Deployment and change management
 </t>
           </r>
           <r>
@@ -2166,50 +2191,23 @@
               <color rgb="001F2A37"/>
               <sz val="11"/>
             </rPr>
-            <t>How do you measure clinician adoption, what do you consider healthy, and what does your data show across the first six months? Separately — what can a clinician see in your product about their own results?</t>
-          </r>
-        </is>
-      </c>
-      <c r="D64" s="8" t="n"/>
-      <c r="E64" s="9" t="n"/>
-      <c r="F64" s="9" t="n"/>
-      <c r="G64" s="9" t="n"/>
-    </row>
-    <row r="65" ht="5" customHeight="1"/>
-    <row r="67" ht="22" customHeight="1">
-      <c r="B67" s="10" t="inlineStr">
-        <is>
-          <t>E.   FIT AND PARTNERSHIP</t>
-        </is>
-      </c>
-    </row>
-    <row r="68" ht="15" customHeight="1">
-      <c r="B68" s="11" t="inlineStr">
-        <is>
-          <t>#</t>
-        </is>
-      </c>
-      <c r="C68" s="11" t="inlineStr">
-        <is>
-          <t>QUESTION</t>
-        </is>
-      </c>
-      <c r="D68" s="11" t="inlineStr">
-        <is>
-          <t>YOUR ANSWER</t>
-        </is>
-      </c>
-      <c r="E68" s="11" t="n"/>
-      <c r="F68" s="11" t="n"/>
-      <c r="G68" s="11" t="n"/>
-    </row>
-    <row r="69" ht="109" customHeight="1">
-      <c r="B69" s="12" t="inlineStr">
-        <is>
-          <t>E1</t>
-        </is>
-      </c>
-      <c r="C69" s="13" t="inlineStr">
+            <t>Changing how clinician schedules get made is sensitive work. What approaches to deployment and change management have you used with other customers? How do you support a customer through it, what have you learned, and what is critical to get right? Include a deployment where clinicians resisted the product, and what you changed as a result.</t>
+          </r>
+        </is>
+      </c>
+      <c r="D67" s="8" t="n"/>
+      <c r="E67" s="9" t="n"/>
+      <c r="F67" s="9" t="n"/>
+      <c r="G67" s="10" t="n"/>
+    </row>
+    <row r="68" ht="5" customHeight="1"/>
+    <row r="69" ht="80" customHeight="1">
+      <c r="B69" s="13" t="inlineStr">
+        <is>
+          <t>E4</t>
+        </is>
+      </c>
+      <c r="C69" s="14" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -2218,7 +2216,7 @@
               <color rgb="001F2A37"/>
               <sz val="11"/>
             </rPr>
-            <t xml:space="preserve">What we did not ask
+            <t xml:space="preserve">What you chose not to build
 </t>
           </r>
           <r>
@@ -2227,198 +2225,61 @@
               <color rgb="001F2A37"/>
               <sz val="11"/>
             </rPr>
-            <t>What do you do that we have not asked about, and that you believe would matter to an organization like ours?</t>
+            <t>What have you deliberately chosen not to build, and why?</t>
           </r>
         </is>
       </c>
       <c r="D69" s="8" t="n"/>
       <c r="E69" s="9" t="n"/>
       <c r="F69" s="9" t="n"/>
-      <c r="G69" s="9" t="n"/>
+      <c r="G69" s="10" t="n"/>
     </row>
     <row r="70" ht="5" customHeight="1"/>
-    <row r="71" ht="111" customHeight="1">
-      <c r="B71" s="12" t="inlineStr">
-        <is>
-          <t>E2</t>
-        </is>
-      </c>
-      <c r="C71" s="13" t="inlineStr">
-        <is>
-          <r>
-            <rPr>
-              <rFont val="Calibri"/>
-              <b val="1"/>
-              <color rgb="001F2A37"/>
-              <sz val="11"/>
-            </rPr>
-            <t xml:space="preserve">Where a design partner helps
-</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Calibri"/>
-              <color rgb="001F2A37"/>
-              <sz val="11"/>
-            </rPr>
-            <t>We are open to partnering with a product that is strong today and still building. Which parts of what we have described are you actively building, and where would a committed design partner be genuinely useful to you?</t>
-          </r>
-        </is>
-      </c>
-      <c r="D71" s="8" t="n"/>
-      <c r="E71" s="9" t="n"/>
-      <c r="F71" s="9" t="n"/>
-      <c r="G71" s="9" t="n"/>
-    </row>
-    <row r="72" ht="5" customHeight="1"/>
-    <row r="73" ht="170" customHeight="1">
-      <c r="B73" s="16" t="inlineStr">
-        <is>
-          <t>E3</t>
-        </is>
-      </c>
-      <c r="C73" s="17" t="inlineStr">
-        <is>
-          <r>
-            <rPr>
-              <rFont val="Calibri"/>
-              <b val="1"/>
-              <color rgb="001F2A37"/>
-              <sz val="11"/>
-            </rPr>
-            <t xml:space="preserve">Sharing in the value
-</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Calibri"/>
-              <color rgb="001F2A37"/>
-              <sz val="11"/>
-            </rPr>
-            <t>We expect to put real weight behind whichever product we choose — subject-matter guidance from people who run this work every day, deployment effort across our branches, and a willingness to act as a reference and co-marketing partner in a market where our competitors are your prospects. That creates value well beyond our subscription. In what ways would you be open to sharing in it?</t>
-          </r>
-        </is>
-      </c>
-      <c r="D73" s="8" t="n"/>
-      <c r="E73" s="9" t="n"/>
-      <c r="F73" s="9" t="n"/>
-      <c r="G73" s="9" t="n"/>
-    </row>
-    <row r="74" ht="5" customHeight="1"/>
-    <row r="75" ht="126" customHeight="1">
-      <c r="B75" s="16" t="inlineStr">
-        <is>
-          <t>E4</t>
-        </is>
-      </c>
-      <c r="C75" s="17" t="inlineStr">
-        <is>
-          <r>
-            <rPr>
-              <rFont val="Calibri"/>
-              <b val="1"/>
-              <color rgb="001F2A37"/>
-              <sz val="11"/>
-            </rPr>
-            <t xml:space="preserve">Deployment and change management
-</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Calibri"/>
-              <color rgb="001F2A37"/>
-              <sz val="11"/>
-            </rPr>
-            <t>Changing how clinician schedules get made is sensitive work. What approaches to deployment and change management have you used with other customers? How do you support a customer through it, what have you learned, and what is critical to get right?</t>
-          </r>
-        </is>
-      </c>
-      <c r="D75" s="8" t="n"/>
-      <c r="E75" s="9" t="n"/>
-      <c r="F75" s="9" t="n"/>
-      <c r="G75" s="9" t="n"/>
-    </row>
-    <row r="76" ht="5" customHeight="1"/>
-    <row r="77" ht="80" customHeight="1">
-      <c r="B77" s="12" t="inlineStr">
-        <is>
-          <t>E5</t>
-        </is>
-      </c>
-      <c r="C77" s="13" t="inlineStr">
-        <is>
-          <r>
-            <rPr>
-              <rFont val="Calibri"/>
-              <b val="1"/>
-              <color rgb="001F2A37"/>
-              <sz val="11"/>
-            </rPr>
-            <t xml:space="preserve">What you chose not to build
-</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Calibri"/>
-              <color rgb="001F2A37"/>
-              <sz val="11"/>
-            </rPr>
-            <t>What have you deliberately chosen not to build, and why?</t>
-          </r>
-        </is>
-      </c>
-      <c r="D77" s="8" t="n"/>
-      <c r="E77" s="9" t="n"/>
-      <c r="F77" s="9" t="n"/>
-      <c r="G77" s="9" t="n"/>
-    </row>
-    <row r="78" ht="5" customHeight="1"/>
   </sheetData>
-  <mergeCells count="35">
+  <mergeCells count="31">
     <mergeCell ref="B2:G2"/>
     <mergeCell ref="D56:G56"/>
-    <mergeCell ref="D71:G71"/>
     <mergeCell ref="D9:G9"/>
     <mergeCell ref="D58:G58"/>
-    <mergeCell ref="B67:G67"/>
     <mergeCell ref="B17:G17"/>
     <mergeCell ref="B23:G23"/>
     <mergeCell ref="B1:G1"/>
-    <mergeCell ref="D64:G64"/>
-    <mergeCell ref="D73:G73"/>
+    <mergeCell ref="B61:G61"/>
+    <mergeCell ref="D67:G67"/>
     <mergeCell ref="D42:G42"/>
     <mergeCell ref="D5:G5"/>
     <mergeCell ref="D38:G38"/>
-    <mergeCell ref="B53:G53"/>
     <mergeCell ref="B19:G19"/>
     <mergeCell ref="B34:G34"/>
+    <mergeCell ref="D54:G54"/>
     <mergeCell ref="B28:G28"/>
-    <mergeCell ref="D50:G50"/>
     <mergeCell ref="D69:G69"/>
     <mergeCell ref="D44:G44"/>
-    <mergeCell ref="D60:G60"/>
+    <mergeCell ref="D63:G63"/>
     <mergeCell ref="D46:G46"/>
     <mergeCell ref="D40:G40"/>
+    <mergeCell ref="B51:G51"/>
+    <mergeCell ref="D65:G65"/>
     <mergeCell ref="D36:G36"/>
-    <mergeCell ref="D77:G77"/>
     <mergeCell ref="D11:G11"/>
     <mergeCell ref="D13:G13"/>
     <mergeCell ref="B7:G7"/>
     <mergeCell ref="B16:G16"/>
-    <mergeCell ref="B54:G54"/>
     <mergeCell ref="D48:G48"/>
-    <mergeCell ref="D75:G75"/>
-    <mergeCell ref="D62:G62"/>
+    <mergeCell ref="B52:G52"/>
     <mergeCell ref="D4:G4"/>
   </mergeCells>
-  <dataValidations count="3">
-    <dataValidation sqref="D20 D21 D22 D24 D25 D26 D27 D29 D30 D31 D32" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" errorTitle="Pick from the list" error="Yes  ·  Through a partner  ·  No" promptTitle="Do you do this at all?" prompt="Yes  ·  Through a partner  ·  No" type="list">
+  <dataValidations count="4">
+    <dataValidation sqref="D20 D21 D22 D24 D25 D26 D27 D29 D30 D31 D32" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" errorTitle="Pick from the list" error="Yes  ·  Through a partner  ·  No  ·  Other" promptTitle="Do you do this at all?" prompt="Yes  ·  Through a partner  ·  No  ·  Other" type="list">
       <formula1>InScopeList</formula1>
     </dataValidation>
-    <dataValidation sqref="E20 E21 E22 E24 E25 E26 E27 E29 E30 E31 E32" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" errorTitle="Pick from the list" error="Production (multiple / one customer)  ·  In development  ·  Roadmap" promptTitle="How far along is it?" prompt="Production (multiple / one customer)  ·  In development  ·  Roadmap" type="list">
+    <dataValidation sqref="E20 E21 E22 E24 E25 E26 E27 E29 E30 E31 E32" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" errorTitle="Pick from the list" error="Production (multiple / one customer)  ·  In development  ·  Roadmap  ·  Other" promptTitle="How far along is it?" prompt="Production (multiple / one customer)  ·  In development  ·  Roadmap  ·  Other" type="list">
       <formula1>StatusList</formula1>
     </dataValidation>
-    <dataValidation sqref="F24 F25 F26 F27 F29 F30 F31 F32" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" errorTitle="Pick from the list" error="Automated end to end  ·  Automated, person approves  ·  System prepares it  ·  Person does it" promptTitle="Does a person still do the work?" prompt="Automated end to end  ·  Automated, person approves  ·  System prepares it  ·  Person does it" type="list">
+    <dataValidation sqref="F20 F21 F22" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" errorTitle="Pick from the list" error="Live feed  ·  Imported on a schedule  ·  Maintained by staff  ·  Entered by the clinician  ·  Derived from FT/PT  ·  Other" promptTitle="Where does this come from?" prompt="Live feed  ·  Imported on a schedule  ·  Maintained by staff  ·  Entered by the clinician  ·  Derived from FT/PT  ·  Other" type="list">
+      <formula1>CapacityInputList</formula1>
+    </dataValidation>
+    <dataValidation sqref="F24 F25 F26 F27 F29 F30 F31 F32" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" errorTitle="Pick from the list" error="Automated end to end  ·  Automated, person approves  ·  System prepares it  ·  Person does it  ·  Other" promptTitle="Does a person still do the work?" prompt="Automated end to end  ·  Automated, person approves  ·  System prepares it  ·  Person does it  ·  Other" type="list">
       <formula1>DeliveryList</formula1>
     </dataValidation>
   </dataValidations>
@@ -3937,7 +3798,7 @@
           <t>•</t>
         </is>
       </c>
-      <c r="O69" s="54" t="inlineStr">
+      <c r="O69" s="48" t="inlineStr">
         <is>
           <t>Outreach carried by the platform itself — agentic voice, text and email — rather than queued up for a coordinator to work</t>
         </is>
@@ -3960,8 +3821,8 @@
       <c r="K70" s="43" t="n"/>
       <c r="L70" s="31" t="n"/>
       <c r="M70" s="42" t="n"/>
-      <c r="N70" s="55" t="n"/>
-      <c r="O70" s="55" t="n"/>
+      <c r="N70" s="21" t="n"/>
+      <c r="O70" s="21" t="n"/>
       <c r="P70" s="43" t="n"/>
       <c r="Q70" s="32" t="n"/>
       <c r="R70" s="21" t="n"/>
@@ -3980,8 +3841,8 @@
       <c r="K71" s="43" t="n"/>
       <c r="L71" s="31" t="n"/>
       <c r="M71" s="42" t="n"/>
-      <c r="N71" s="55" t="n"/>
-      <c r="O71" s="55" t="n"/>
+      <c r="N71" s="21" t="n"/>
+      <c r="O71" s="21" t="n"/>
       <c r="P71" s="43" t="n"/>
       <c r="Q71" s="32" t="n"/>
       <c r="R71" s="21" t="n"/>
@@ -4000,8 +3861,8 @@
       <c r="K72" s="43" t="n"/>
       <c r="L72" s="31" t="n"/>
       <c r="M72" s="42" t="n"/>
-      <c r="N72" s="55" t="n"/>
-      <c r="O72" s="55" t="n"/>
+      <c r="N72" s="21" t="n"/>
+      <c r="O72" s="21" t="n"/>
       <c r="P72" s="43" t="n"/>
       <c r="Q72" s="32" t="n"/>
       <c r="R72" s="21" t="n"/>
@@ -4020,8 +3881,8 @@
       <c r="K73" s="43" t="n"/>
       <c r="L73" s="31" t="n"/>
       <c r="M73" s="42" t="n"/>
-      <c r="N73" s="55" t="n"/>
-      <c r="O73" s="55" t="n"/>
+      <c r="N73" s="21" t="n"/>
+      <c r="O73" s="21" t="n"/>
       <c r="P73" s="43" t="n"/>
       <c r="Q73" s="32" t="n"/>
       <c r="R73" s="21" t="n"/>
@@ -4040,8 +3901,8 @@
       <c r="K74" s="43" t="n"/>
       <c r="L74" s="31" t="n"/>
       <c r="M74" s="42" t="n"/>
-      <c r="N74" s="55" t="n"/>
-      <c r="O74" s="55" t="n"/>
+      <c r="N74" s="21" t="n"/>
+      <c r="O74" s="21" t="n"/>
       <c r="P74" s="43" t="n"/>
       <c r="Q74" s="32" t="n"/>
       <c r="R74" s="21" t="n"/>
@@ -4060,8 +3921,8 @@
       <c r="K75" s="43" t="n"/>
       <c r="L75" s="31" t="n"/>
       <c r="M75" s="42" t="n"/>
-      <c r="N75" s="55" t="n"/>
-      <c r="O75" s="55" t="n"/>
+      <c r="N75" s="21" t="n"/>
+      <c r="O75" s="21" t="n"/>
       <c r="P75" s="43" t="n"/>
       <c r="Q75" s="32" t="n"/>
       <c r="R75" s="21" t="n"/>
@@ -4080,8 +3941,8 @@
       <c r="K76" s="43" t="n"/>
       <c r="L76" s="31" t="n"/>
       <c r="M76" s="42" t="n"/>
-      <c r="N76" s="55" t="n"/>
-      <c r="O76" s="55" t="n"/>
+      <c r="N76" s="21" t="n"/>
+      <c r="O76" s="21" t="n"/>
       <c r="P76" s="43" t="n"/>
       <c r="Q76" s="32" t="n"/>
       <c r="R76" s="21" t="n"/>
@@ -4100,8 +3961,8 @@
       <c r="K77" s="43" t="n"/>
       <c r="L77" s="31" t="n"/>
       <c r="M77" s="42" t="n"/>
-      <c r="N77" s="55" t="n"/>
-      <c r="O77" s="55" t="n"/>
+      <c r="N77" s="21" t="n"/>
+      <c r="O77" s="21" t="n"/>
       <c r="P77" s="43" t="n"/>
       <c r="Q77" s="32" t="n"/>
       <c r="R77" s="21" t="n"/>
@@ -4136,8 +3997,8 @@
       <c r="K78" s="43" t="n"/>
       <c r="L78" s="31" t="n"/>
       <c r="M78" s="42" t="n"/>
-      <c r="N78" s="55" t="n"/>
-      <c r="O78" s="55" t="n"/>
+      <c r="N78" s="21" t="n"/>
+      <c r="O78" s="21" t="n"/>
       <c r="P78" s="43" t="n"/>
       <c r="Q78" s="32" t="n"/>
       <c r="R78" s="21" t="n"/>
@@ -4156,8 +4017,8 @@
       <c r="K79" s="43" t="n"/>
       <c r="L79" s="31" t="n"/>
       <c r="M79" s="42" t="n"/>
-      <c r="N79" s="55" t="n"/>
-      <c r="O79" s="55" t="n"/>
+      <c r="N79" s="21" t="n"/>
+      <c r="O79" s="21" t="n"/>
       <c r="P79" s="43" t="n"/>
       <c r="Q79" s="32" t="n"/>
       <c r="R79" s="21" t="n"/>
@@ -4176,8 +4037,8 @@
       <c r="K80" s="43" t="n"/>
       <c r="L80" s="31" t="n"/>
       <c r="M80" s="42" t="n"/>
-      <c r="N80" s="55" t="n"/>
-      <c r="O80" s="55" t="n"/>
+      <c r="N80" s="21" t="n"/>
+      <c r="O80" s="21" t="n"/>
       <c r="P80" s="43" t="n"/>
       <c r="Q80" s="32" t="n"/>
       <c r="R80" s="21" t="n"/>
@@ -4221,7 +4082,7 @@
           <t>•</t>
         </is>
       </c>
-      <c r="O82" s="54" t="inlineStr">
+      <c r="O82" s="48" t="inlineStr">
         <is>
           <t>Staff able to see it, intervene, override, and take any conversation back</t>
         </is>
@@ -4252,8 +4113,8 @@
       <c r="K83" s="43" t="n"/>
       <c r="L83" s="31" t="n"/>
       <c r="M83" s="42" t="n"/>
-      <c r="N83" s="55" t="n"/>
-      <c r="O83" s="55" t="n"/>
+      <c r="N83" s="21" t="n"/>
+      <c r="O83" s="21" t="n"/>
       <c r="P83" s="43" t="n"/>
       <c r="Q83" s="32" t="n"/>
       <c r="R83" s="21" t="n"/>
@@ -4272,8 +4133,8 @@
       <c r="K84" s="43" t="n"/>
       <c r="L84" s="31" t="n"/>
       <c r="M84" s="42" t="n"/>
-      <c r="N84" s="55" t="n"/>
-      <c r="O84" s="55" t="n"/>
+      <c r="N84" s="21" t="n"/>
+      <c r="O84" s="21" t="n"/>
       <c r="P84" s="43" t="n"/>
       <c r="Q84" s="32" t="n"/>
       <c r="R84" s="21" t="n"/>
@@ -4292,8 +4153,8 @@
       <c r="K85" s="43" t="n"/>
       <c r="L85" s="31" t="n"/>
       <c r="M85" s="42" t="n"/>
-      <c r="N85" s="55" t="n"/>
-      <c r="O85" s="55" t="n"/>
+      <c r="N85" s="21" t="n"/>
+      <c r="O85" s="21" t="n"/>
       <c r="P85" s="43" t="n"/>
       <c r="Q85" s="32" t="n"/>
       <c r="R85" s="21" t="n"/>
@@ -4312,8 +4173,8 @@
       <c r="K86" s="43" t="n"/>
       <c r="L86" s="31" t="n"/>
       <c r="M86" s="42" t="n"/>
-      <c r="N86" s="55" t="n"/>
-      <c r="O86" s="55" t="n"/>
+      <c r="N86" s="21" t="n"/>
+      <c r="O86" s="21" t="n"/>
       <c r="P86" s="43" t="n"/>
       <c r="Q86" s="32" t="n"/>
       <c r="R86" s="21" t="n"/>
@@ -4340,8 +4201,8 @@
       <c r="K87" s="43" t="n"/>
       <c r="L87" s="31" t="n"/>
       <c r="M87" s="42" t="n"/>
-      <c r="N87" s="55" t="n"/>
-      <c r="O87" s="55" t="n"/>
+      <c r="N87" s="21" t="n"/>
+      <c r="O87" s="21" t="n"/>
       <c r="P87" s="43" t="n"/>
       <c r="Q87" s="32" t="n"/>
       <c r="R87" s="21" t="n"/>
@@ -4360,8 +4221,8 @@
       <c r="K88" s="43" t="n"/>
       <c r="L88" s="31" t="n"/>
       <c r="M88" s="42" t="n"/>
-      <c r="N88" s="55" t="n"/>
-      <c r="O88" s="55" t="n"/>
+      <c r="N88" s="21" t="n"/>
+      <c r="O88" s="21" t="n"/>
       <c r="P88" s="43" t="n"/>
       <c r="Q88" s="32" t="n"/>
       <c r="R88" s="21" t="n"/>
@@ -4380,8 +4241,8 @@
       <c r="K89" s="43" t="n"/>
       <c r="L89" s="31" t="n"/>
       <c r="M89" s="42" t="n"/>
-      <c r="N89" s="55" t="n"/>
-      <c r="O89" s="55" t="n"/>
+      <c r="N89" s="21" t="n"/>
+      <c r="O89" s="21" t="n"/>
       <c r="P89" s="43" t="n"/>
       <c r="Q89" s="32" t="n"/>
       <c r="R89" s="21" t="n"/>
@@ -4744,7 +4605,7 @@
       <c r="K105" s="43" t="n"/>
       <c r="L105" s="31" t="n"/>
       <c r="M105" s="42" t="n"/>
-      <c r="N105" s="56" t="inlineStr">
+      <c r="N105" s="53" t="inlineStr">
         <is>
           <t>•</t>
         </is>
@@ -4856,7 +4717,7 @@
       <c r="K110" s="43" t="n"/>
       <c r="L110" s="31" t="n"/>
       <c r="M110" s="42" t="n"/>
-      <c r="N110" s="56" t="inlineStr">
+      <c r="N110" s="53" t="inlineStr">
         <is>
           <t>•</t>
         </is>
@@ -4972,7 +4833,7 @@
       <c r="K115" s="43" t="n"/>
       <c r="L115" s="31" t="n"/>
       <c r="M115" s="42" t="n"/>
-      <c r="N115" s="56" t="inlineStr">
+      <c r="N115" s="53" t="inlineStr">
         <is>
           <t>•</t>
         </is>
@@ -5096,12 +4957,12 @@
       <c r="K120" s="43" t="n"/>
       <c r="L120" s="31" t="n"/>
       <c r="M120" s="42" t="n"/>
-      <c r="N120" s="57" t="inlineStr">
+      <c r="N120" s="53" t="inlineStr">
         <is>
           <t>•</t>
         </is>
       </c>
-      <c r="O120" s="58" t="inlineStr">
+      <c r="O120" s="48" t="inlineStr">
         <is>
           <t>The day-before confirmation round automated for every patient, every day</t>
         </is>
@@ -5132,8 +4993,8 @@
       <c r="K121" s="43" t="n"/>
       <c r="L121" s="31" t="n"/>
       <c r="M121" s="42" t="n"/>
-      <c r="N121" s="59" t="n"/>
-      <c r="O121" s="59" t="n"/>
+      <c r="N121" s="21" t="n"/>
+      <c r="O121" s="21" t="n"/>
       <c r="P121" s="43" t="n"/>
       <c r="Q121" s="32" t="n"/>
       <c r="R121" s="21" t="n"/>
@@ -5152,8 +5013,8 @@
       <c r="K122" s="43" t="n"/>
       <c r="L122" s="31" t="n"/>
       <c r="M122" s="42" t="n"/>
-      <c r="N122" s="59" t="n"/>
-      <c r="O122" s="59" t="n"/>
+      <c r="N122" s="21" t="n"/>
+      <c r="O122" s="21" t="n"/>
       <c r="P122" s="43" t="n"/>
       <c r="Q122" s="32" t="n"/>
       <c r="R122" s="21" t="n"/>
@@ -5172,8 +5033,8 @@
       <c r="K123" s="43" t="n"/>
       <c r="L123" s="31" t="n"/>
       <c r="M123" s="42" t="n"/>
-      <c r="N123" s="59" t="n"/>
-      <c r="O123" s="59" t="n"/>
+      <c r="N123" s="21" t="n"/>
+      <c r="O123" s="21" t="n"/>
       <c r="P123" s="43" t="n"/>
       <c r="Q123" s="32" t="n"/>
       <c r="R123" s="21" t="n"/>
@@ -5192,8 +5053,8 @@
       <c r="K124" s="43" t="n"/>
       <c r="L124" s="31" t="n"/>
       <c r="M124" s="42" t="n"/>
-      <c r="N124" s="59" t="n"/>
-      <c r="O124" s="59" t="n"/>
+      <c r="N124" s="21" t="n"/>
+      <c r="O124" s="21" t="n"/>
       <c r="P124" s="43" t="n"/>
       <c r="Q124" s="32" t="n"/>
       <c r="R124" s="21" t="n"/>
@@ -5220,8 +5081,8 @@
       <c r="K125" s="43" t="n"/>
       <c r="L125" s="31" t="n"/>
       <c r="M125" s="42" t="n"/>
-      <c r="N125" s="59" t="n"/>
-      <c r="O125" s="59" t="n"/>
+      <c r="N125" s="21" t="n"/>
+      <c r="O125" s="21" t="n"/>
       <c r="P125" s="43" t="n"/>
       <c r="Q125" s="32" t="n"/>
       <c r="R125" s="21" t="n"/>
@@ -5240,8 +5101,8 @@
       <c r="K126" s="43" t="n"/>
       <c r="L126" s="31" t="n"/>
       <c r="M126" s="42" t="n"/>
-      <c r="N126" s="59" t="n"/>
-      <c r="O126" s="59" t="n"/>
+      <c r="N126" s="21" t="n"/>
+      <c r="O126" s="21" t="n"/>
       <c r="P126" s="43" t="n"/>
       <c r="Q126" s="32" t="n"/>
       <c r="R126" s="21" t="n"/>
@@ -5260,8 +5121,8 @@
       <c r="K127" s="43" t="n"/>
       <c r="L127" s="31" t="n"/>
       <c r="M127" s="42" t="n"/>
-      <c r="N127" s="59" t="n"/>
-      <c r="O127" s="59" t="n"/>
+      <c r="N127" s="21" t="n"/>
+      <c r="O127" s="21" t="n"/>
       <c r="P127" s="43" t="n"/>
       <c r="Q127" s="32" t="n"/>
       <c r="R127" s="21" t="n"/>
@@ -5305,7 +5166,7 @@
           <t>•</t>
         </is>
       </c>
-      <c r="O129" s="54" t="inlineStr">
+      <c r="O129" s="48" t="inlineStr">
         <is>
           <t>The schedule staying pliable until that confirmation, so clinician and capacity changes can land before the patient is told</t>
         </is>
@@ -5336,8 +5197,8 @@
       <c r="K130" s="43" t="n"/>
       <c r="L130" s="31" t="n"/>
       <c r="M130" s="42" t="n"/>
-      <c r="N130" s="55" t="n"/>
-      <c r="O130" s="55" t="n"/>
+      <c r="N130" s="21" t="n"/>
+      <c r="O130" s="21" t="n"/>
       <c r="P130" s="43" t="n"/>
       <c r="Q130" s="32" t="n"/>
       <c r="R130" s="21" t="n"/>
@@ -5356,8 +5217,8 @@
       <c r="K131" s="43" t="n"/>
       <c r="L131" s="31" t="n"/>
       <c r="M131" s="42" t="n"/>
-      <c r="N131" s="55" t="n"/>
-      <c r="O131" s="55" t="n"/>
+      <c r="N131" s="21" t="n"/>
+      <c r="O131" s="21" t="n"/>
       <c r="P131" s="43" t="n"/>
       <c r="Q131" s="32" t="n"/>
       <c r="R131" s="21" t="n"/>
@@ -5376,8 +5237,8 @@
       <c r="K132" s="43" t="n"/>
       <c r="L132" s="31" t="n"/>
       <c r="M132" s="42" t="n"/>
-      <c r="N132" s="55" t="n"/>
-      <c r="O132" s="55" t="n"/>
+      <c r="N132" s="21" t="n"/>
+      <c r="O132" s="21" t="n"/>
       <c r="P132" s="43" t="n"/>
       <c r="Q132" s="32" t="n"/>
       <c r="R132" s="21" t="n"/>
@@ -5396,8 +5257,8 @@
       <c r="K133" s="43" t="n"/>
       <c r="L133" s="31" t="n"/>
       <c r="M133" s="42" t="n"/>
-      <c r="N133" s="55" t="n"/>
-      <c r="O133" s="55" t="n"/>
+      <c r="N133" s="21" t="n"/>
+      <c r="O133" s="21" t="n"/>
       <c r="P133" s="43" t="n"/>
       <c r="Q133" s="32" t="n"/>
       <c r="R133" s="21" t="n"/>
@@ -5424,8 +5285,8 @@
       <c r="K134" s="43" t="n"/>
       <c r="L134" s="31" t="n"/>
       <c r="M134" s="42" t="n"/>
-      <c r="N134" s="55" t="n"/>
-      <c r="O134" s="55" t="n"/>
+      <c r="N134" s="21" t="n"/>
+      <c r="O134" s="21" t="n"/>
       <c r="P134" s="43" t="n"/>
       <c r="Q134" s="32" t="n"/>
       <c r="R134" s="21" t="n"/>
@@ -5444,8 +5305,8 @@
       <c r="K135" s="43" t="n"/>
       <c r="L135" s="31" t="n"/>
       <c r="M135" s="42" t="n"/>
-      <c r="N135" s="55" t="n"/>
-      <c r="O135" s="55" t="n"/>
+      <c r="N135" s="21" t="n"/>
+      <c r="O135" s="21" t="n"/>
       <c r="P135" s="43" t="n"/>
       <c r="Q135" s="32" t="n"/>
       <c r="R135" s="21" t="n"/>
@@ -5464,8 +5325,8 @@
       <c r="K136" s="43" t="n"/>
       <c r="L136" s="31" t="n"/>
       <c r="M136" s="42" t="n"/>
-      <c r="N136" s="55" t="n"/>
-      <c r="O136" s="55" t="n"/>
+      <c r="N136" s="21" t="n"/>
+      <c r="O136" s="21" t="n"/>
       <c r="P136" s="43" t="n"/>
       <c r="Q136" s="32" t="n"/>
       <c r="R136" s="21" t="n"/>
@@ -5484,8 +5345,8 @@
       <c r="K137" s="43" t="n"/>
       <c r="L137" s="31" t="n"/>
       <c r="M137" s="42" t="n"/>
-      <c r="N137" s="55" t="n"/>
-      <c r="O137" s="55" t="n"/>
+      <c r="N137" s="21" t="n"/>
+      <c r="O137" s="21" t="n"/>
       <c r="P137" s="43" t="n"/>
       <c r="Q137" s="32" t="n"/>
       <c r="R137" s="21" t="n"/>
@@ -5504,8 +5365,8 @@
       <c r="K138" s="43" t="n"/>
       <c r="L138" s="31" t="n"/>
       <c r="M138" s="42" t="n"/>
-      <c r="N138" s="55" t="n"/>
-      <c r="O138" s="55" t="n"/>
+      <c r="N138" s="21" t="n"/>
+      <c r="O138" s="21" t="n"/>
       <c r="P138" s="43" t="n"/>
       <c r="Q138" s="32" t="n"/>
       <c r="R138" s="21" t="n"/>
@@ -5524,8 +5385,8 @@
       <c r="K139" s="43" t="n"/>
       <c r="L139" s="31" t="n"/>
       <c r="M139" s="42" t="n"/>
-      <c r="N139" s="55" t="n"/>
-      <c r="O139" s="55" t="n"/>
+      <c r="N139" s="21" t="n"/>
+      <c r="O139" s="21" t="n"/>
       <c r="P139" s="43" t="n"/>
       <c r="Q139" s="32" t="n"/>
       <c r="R139" s="21" t="n"/>
@@ -5544,8 +5405,8 @@
       <c r="K140" s="43" t="n"/>
       <c r="L140" s="31" t="n"/>
       <c r="M140" s="42" t="n"/>
-      <c r="N140" s="55" t="n"/>
-      <c r="O140" s="55" t="n"/>
+      <c r="N140" s="21" t="n"/>
+      <c r="O140" s="21" t="n"/>
       <c r="P140" s="43" t="n"/>
       <c r="Q140" s="32" t="n"/>
       <c r="R140" s="21" t="n"/>
@@ -5588,7 +5449,7 @@
       <c r="K142" s="43" t="n"/>
       <c r="L142" s="31" t="n"/>
       <c r="M142" s="42" t="n"/>
-      <c r="N142" s="56" t="inlineStr">
+      <c r="N142" s="53" t="inlineStr">
         <is>
           <t>•</t>
         </is>
@@ -6108,7 +5969,7 @@
       <c r="K165" s="43" t="n"/>
       <c r="L165" s="31" t="n"/>
       <c r="M165" s="42" t="n"/>
-      <c r="N165" s="56" t="inlineStr">
+      <c r="N165" s="53" t="inlineStr">
         <is>
           <t>•</t>
         </is>
@@ -6224,7 +6085,7 @@
       <c r="K170" s="43" t="n"/>
       <c r="L170" s="31" t="n"/>
       <c r="M170" s="42" t="n"/>
-      <c r="N170" s="56" t="inlineStr">
+      <c r="N170" s="53" t="inlineStr">
         <is>
           <t>•</t>
         </is>
@@ -6428,7 +6289,7 @@
       <c r="K179" s="43" t="n"/>
       <c r="L179" s="31" t="n"/>
       <c r="M179" s="42" t="n"/>
-      <c r="N179" s="56" t="inlineStr">
+      <c r="N179" s="53" t="inlineStr">
         <is>
           <t>•</t>
         </is>
@@ -6625,7 +6486,7 @@
           <t>•</t>
         </is>
       </c>
-      <c r="O188" s="54" t="inlineStr">
+      <c r="O188" s="48" t="inlineStr">
         <is>
           <t>Incentives or differentials attached to hard-to-fill visits, and offered to the clinicians who can take them</t>
         </is>
@@ -6652,8 +6513,8 @@
       <c r="K189" s="43" t="n"/>
       <c r="L189" s="31" t="n"/>
       <c r="M189" s="42" t="n"/>
-      <c r="N189" s="55" t="n"/>
-      <c r="O189" s="55" t="n"/>
+      <c r="N189" s="21" t="n"/>
+      <c r="O189" s="21" t="n"/>
       <c r="P189" s="43" t="n"/>
       <c r="Q189" s="32" t="n"/>
       <c r="R189" s="21" t="n"/>
@@ -6672,8 +6533,8 @@
       <c r="K190" s="43" t="n"/>
       <c r="L190" s="31" t="n"/>
       <c r="M190" s="42" t="n"/>
-      <c r="N190" s="55" t="n"/>
-      <c r="O190" s="55" t="n"/>
+      <c r="N190" s="21" t="n"/>
+      <c r="O190" s="21" t="n"/>
       <c r="P190" s="43" t="n"/>
       <c r="Q190" s="32" t="n"/>
       <c r="R190" s="21" t="n"/>
@@ -6692,8 +6553,8 @@
       <c r="K191" s="43" t="n"/>
       <c r="L191" s="31" t="n"/>
       <c r="M191" s="42" t="n"/>
-      <c r="N191" s="55" t="n"/>
-      <c r="O191" s="55" t="n"/>
+      <c r="N191" s="21" t="n"/>
+      <c r="O191" s="21" t="n"/>
       <c r="P191" s="43" t="n"/>
       <c r="Q191" s="32" t="n"/>
       <c r="R191" s="21" t="n"/>
@@ -6712,8 +6573,8 @@
       <c r="K192" s="43" t="n"/>
       <c r="L192" s="31" t="n"/>
       <c r="M192" s="42" t="n"/>
-      <c r="N192" s="55" t="n"/>
-      <c r="O192" s="55" t="n"/>
+      <c r="N192" s="21" t="n"/>
+      <c r="O192" s="21" t="n"/>
       <c r="P192" s="43" t="n"/>
       <c r="Q192" s="32" t="n"/>
       <c r="R192" s="21" t="n"/>
@@ -6732,8 +6593,8 @@
       <c r="K193" s="43" t="n"/>
       <c r="L193" s="31" t="n"/>
       <c r="M193" s="42" t="n"/>
-      <c r="N193" s="55" t="n"/>
-      <c r="O193" s="55" t="n"/>
+      <c r="N193" s="21" t="n"/>
+      <c r="O193" s="21" t="n"/>
       <c r="P193" s="43" t="n"/>
       <c r="Q193" s="32" t="n"/>
       <c r="R193" s="21" t="n"/>
@@ -6752,8 +6613,8 @@
       <c r="K194" s="43" t="n"/>
       <c r="L194" s="31" t="n"/>
       <c r="M194" s="42" t="n"/>
-      <c r="N194" s="55" t="n"/>
-      <c r="O194" s="55" t="n"/>
+      <c r="N194" s="21" t="n"/>
+      <c r="O194" s="21" t="n"/>
       <c r="P194" s="43" t="n"/>
       <c r="Q194" s="32" t="n"/>
       <c r="R194" s="21" t="n"/>
@@ -6780,8 +6641,8 @@
       <c r="K195" s="43" t="n"/>
       <c r="L195" s="31" t="n"/>
       <c r="M195" s="42" t="n"/>
-      <c r="N195" s="55" t="n"/>
-      <c r="O195" s="55" t="n"/>
+      <c r="N195" s="21" t="n"/>
+      <c r="O195" s="21" t="n"/>
       <c r="P195" s="43" t="n"/>
       <c r="Q195" s="32" t="n"/>
       <c r="R195" s="21" t="n"/>
@@ -6820,7 +6681,7 @@
       <c r="K197" s="43" t="n"/>
       <c r="L197" s="31" t="n"/>
       <c r="M197" s="42" t="n"/>
-      <c r="N197" s="56" t="inlineStr">
+      <c r="N197" s="53" t="inlineStr">
         <is>
           <t>•</t>
         </is>
@@ -7224,7 +7085,7 @@
       <c r="K216" s="43" t="n"/>
       <c r="L216" s="31" t="n"/>
       <c r="M216" s="42" t="n"/>
-      <c r="N216" s="56" t="inlineStr">
+      <c r="N216" s="53" t="inlineStr">
         <is>
           <t>•</t>
         </is>
@@ -7332,7 +7193,7 @@
       <c r="K221" s="43" t="n"/>
       <c r="L221" s="31" t="n"/>
       <c r="M221" s="42" t="n"/>
-      <c r="N221" s="56" t="inlineStr">
+      <c r="N221" s="53" t="inlineStr">
         <is>
           <t>•</t>
         </is>
@@ -7445,7 +7306,7 @@
           <t>•</t>
         </is>
       </c>
-      <c r="O226" s="54" t="inlineStr">
+      <c r="O226" s="48" t="inlineStr">
         <is>
           <t>A clinician view of their own schedule and their own results — the case for the change, made to the person it lands on</t>
         </is>
@@ -7468,8 +7329,8 @@
       <c r="K227" s="43" t="n"/>
       <c r="L227" s="31" t="n"/>
       <c r="M227" s="42" t="n"/>
-      <c r="N227" s="55" t="n"/>
-      <c r="O227" s="55" t="n"/>
+      <c r="N227" s="21" t="n"/>
+      <c r="O227" s="21" t="n"/>
       <c r="P227" s="43" t="n"/>
       <c r="Q227" s="32" t="n"/>
       <c r="R227" s="21" t="n"/>
@@ -7488,8 +7349,8 @@
       <c r="K228" s="43" t="n"/>
       <c r="L228" s="31" t="n"/>
       <c r="M228" s="42" t="n"/>
-      <c r="N228" s="55" t="n"/>
-      <c r="O228" s="55" t="n"/>
+      <c r="N228" s="21" t="n"/>
+      <c r="O228" s="21" t="n"/>
       <c r="P228" s="43" t="n"/>
       <c r="Q228" s="32" t="n"/>
       <c r="R228" s="21" t="n"/>
@@ -7508,8 +7369,8 @@
       <c r="K229" s="43" t="n"/>
       <c r="L229" s="31" t="n"/>
       <c r="M229" s="42" t="n"/>
-      <c r="N229" s="55" t="n"/>
-      <c r="O229" s="55" t="n"/>
+      <c r="N229" s="21" t="n"/>
+      <c r="O229" s="21" t="n"/>
       <c r="P229" s="43" t="n"/>
       <c r="Q229" s="32" t="n"/>
       <c r="R229" s="21" t="n"/>
@@ -7528,8 +7389,8 @@
       <c r="K230" s="43" t="n"/>
       <c r="L230" s="31" t="n"/>
       <c r="M230" s="42" t="n"/>
-      <c r="N230" s="55" t="n"/>
-      <c r="O230" s="55" t="n"/>
+      <c r="N230" s="21" t="n"/>
+      <c r="O230" s="21" t="n"/>
       <c r="P230" s="43" t="n"/>
       <c r="Q230" s="32" t="n"/>
       <c r="R230" s="21" t="n"/>
@@ -7548,8 +7409,8 @@
       <c r="K231" s="43" t="n"/>
       <c r="L231" s="31" t="n"/>
       <c r="M231" s="42" t="n"/>
-      <c r="N231" s="55" t="n"/>
-      <c r="O231" s="55" t="n"/>
+      <c r="N231" s="21" t="n"/>
+      <c r="O231" s="21" t="n"/>
       <c r="P231" s="43" t="n"/>
       <c r="Q231" s="32" t="n"/>
       <c r="R231" s="21" t="n"/>
@@ -7568,8 +7429,8 @@
       <c r="K232" s="43" t="n"/>
       <c r="L232" s="31" t="n"/>
       <c r="M232" s="42" t="n"/>
-      <c r="N232" s="55" t="n"/>
-      <c r="O232" s="55" t="n"/>
+      <c r="N232" s="21" t="n"/>
+      <c r="O232" s="21" t="n"/>
       <c r="P232" s="43" t="n"/>
       <c r="Q232" s="32" t="n"/>
       <c r="R232" s="21" t="n"/>
@@ -7588,8 +7449,8 @@
       <c r="K233" s="43" t="n"/>
       <c r="L233" s="31" t="n"/>
       <c r="M233" s="42" t="n"/>
-      <c r="N233" s="55" t="n"/>
-      <c r="O233" s="55" t="n"/>
+      <c r="N233" s="21" t="n"/>
+      <c r="O233" s="21" t="n"/>
       <c r="P233" s="43" t="n"/>
       <c r="Q233" s="32" t="n"/>
       <c r="R233" s="21" t="n"/>
@@ -7608,8 +7469,8 @@
       <c r="K234" s="43" t="n"/>
       <c r="L234" s="31" t="n"/>
       <c r="M234" s="42" t="n"/>
-      <c r="N234" s="55" t="n"/>
-      <c r="O234" s="55" t="n"/>
+      <c r="N234" s="21" t="n"/>
+      <c r="O234" s="21" t="n"/>
       <c r="P234" s="43" t="n"/>
       <c r="Q234" s="32" t="n"/>
       <c r="R234" s="21" t="n"/>
@@ -7628,8 +7489,8 @@
       <c r="K235" s="43" t="n"/>
       <c r="L235" s="31" t="n"/>
       <c r="M235" s="42" t="n"/>
-      <c r="N235" s="55" t="n"/>
-      <c r="O235" s="55" t="n"/>
+      <c r="N235" s="21" t="n"/>
+      <c r="O235" s="21" t="n"/>
       <c r="P235" s="43" t="n"/>
       <c r="Q235" s="32" t="n"/>
       <c r="R235" s="21" t="n"/>
@@ -7648,8 +7509,8 @@
       <c r="K236" s="43" t="n"/>
       <c r="L236" s="31" t="n"/>
       <c r="M236" s="42" t="n"/>
-      <c r="N236" s="55" t="n"/>
-      <c r="O236" s="55" t="n"/>
+      <c r="N236" s="21" t="n"/>
+      <c r="O236" s="21" t="n"/>
       <c r="P236" s="43" t="n"/>
       <c r="Q236" s="32" t="n"/>
       <c r="R236" s="21" t="n"/>
@@ -7668,8 +7529,8 @@
       <c r="K237" s="43" t="n"/>
       <c r="L237" s="31" t="n"/>
       <c r="M237" s="42" t="n"/>
-      <c r="N237" s="55" t="n"/>
-      <c r="O237" s="55" t="n"/>
+      <c r="N237" s="21" t="n"/>
+      <c r="O237" s="21" t="n"/>
       <c r="P237" s="43" t="n"/>
       <c r="Q237" s="32" t="n"/>
       <c r="R237" s="21" t="n"/>
@@ -7708,7 +7569,7 @@
       <c r="K239" s="43" t="n"/>
       <c r="L239" s="31" t="n"/>
       <c r="M239" s="42" t="n"/>
-      <c r="N239" s="56" t="inlineStr">
+      <c r="N239" s="53" t="inlineStr">
         <is>
           <t>•</t>
         </is>
@@ -7864,21 +7725,21 @@
     </row>
     <row r="247" ht="3.8525" customHeight="1">
       <c r="A247" s="21" t="n"/>
-      <c r="B247" s="60" t="n"/>
+      <c r="B247" s="54" t="n"/>
       <c r="C247" s="25" t="n"/>
       <c r="D247" s="25" t="n"/>
-      <c r="E247" s="61" t="n"/>
+      <c r="E247" s="55" t="n"/>
       <c r="F247" s="21" t="n"/>
       <c r="G247" s="30" t="n"/>
-      <c r="H247" s="60" t="n"/>
+      <c r="H247" s="54" t="n"/>
       <c r="I247" s="25" t="n"/>
       <c r="J247" s="25" t="n"/>
-      <c r="K247" s="61" t="n"/>
+      <c r="K247" s="55" t="n"/>
       <c r="L247" s="31" t="n"/>
-      <c r="M247" s="60" t="n"/>
+      <c r="M247" s="54" t="n"/>
       <c r="N247" s="25" t="n"/>
       <c r="O247" s="25" t="n"/>
-      <c r="P247" s="61" t="n"/>
+      <c r="P247" s="55" t="n"/>
       <c r="Q247" s="32" t="n"/>
       <c r="R247" s="21" t="n"/>
     </row>
@@ -7909,17 +7770,17 @@
       <c r="D249" s="21" t="n"/>
       <c r="E249" s="21" t="n"/>
       <c r="F249" s="21" t="n"/>
-      <c r="G249" s="62" t="n"/>
-      <c r="H249" s="63" t="n"/>
-      <c r="I249" s="63" t="n"/>
-      <c r="J249" s="63" t="n"/>
-      <c r="K249" s="63" t="n"/>
-      <c r="L249" s="63" t="n"/>
-      <c r="M249" s="63" t="n"/>
-      <c r="N249" s="63" t="n"/>
-      <c r="O249" s="63" t="n"/>
-      <c r="P249" s="63" t="n"/>
-      <c r="Q249" s="64" t="n"/>
+      <c r="G249" s="56" t="n"/>
+      <c r="H249" s="57" t="n"/>
+      <c r="I249" s="57" t="n"/>
+      <c r="J249" s="57" t="n"/>
+      <c r="K249" s="57" t="n"/>
+      <c r="L249" s="57" t="n"/>
+      <c r="M249" s="57" t="n"/>
+      <c r="N249" s="57" t="n"/>
+      <c r="O249" s="57" t="n"/>
+      <c r="P249" s="57" t="n"/>
+      <c r="Q249" s="58" t="n"/>
       <c r="R249" s="21" t="n"/>
     </row>
     <row r="250" ht="3.8525" customHeight="1">
@@ -7964,7 +7825,7 @@
     </row>
     <row r="252" ht="3.8525" customHeight="1">
       <c r="A252" s="21" t="n"/>
-      <c r="B252" s="65" t="inlineStr">
+      <c r="B252" s="59" t="inlineStr">
         <is>
           <t>Capacity sets the envelope. Scheduling and engagement are both performed against it — which is why we are looking for a platform that treats all three as one system.</t>
         </is>
@@ -8127,7 +7988,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C4"/>
+  <dimension ref="A1:D6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -8146,6 +8007,11 @@
           <t>Automated end to end</t>
         </is>
       </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>Live feed from a source system</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -8163,6 +8029,11 @@
           <t>Automated, person approves</t>
         </is>
       </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>Imported on a schedule</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -8180,8 +8051,18 @@
           <t>System prepares it, person does it</t>
         </is>
       </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>Maintained by staff in your product</t>
+        </is>
+      </c>
     </row>
     <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>Other — see notes</t>
+        </is>
+      </c>
       <c r="B4" t="inlineStr">
         <is>
           <t>Roadmap — no date yet</t>
@@ -8190,6 +8071,35 @@
       <c r="C4" t="inlineStr">
         <is>
           <t>Person does it</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>Entered by the clinician</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>Other — see notes</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>Other — see notes</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>Derived from FT/PT allocation</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>Other — see notes</t>
         </is>
       </c>
     </row>
@@ -8233,7 +8143,7 @@
       </c>
     </row>
     <row r="5" ht="22" customHeight="1">
-      <c r="B5" s="10" t="inlineStr">
+      <c r="B5" s="11" t="inlineStr">
         <is>
           <t>COVERAGE — EXPANDED</t>
         </is>
@@ -8247,49 +8157,49 @@
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">
-      <c r="B7" s="11" t="inlineStr">
+      <c r="B7" s="12" t="inlineStr">
         <is>
           <t>#</t>
         </is>
       </c>
-      <c r="C7" s="11" t="inlineStr">
+      <c r="C7" s="12" t="inlineStr">
         <is>
           <t>AREA</t>
         </is>
       </c>
-      <c r="D7" s="18" t="inlineStr">
+      <c r="D7" s="12" t="inlineStr">
         <is>
           <t>IN SCOPE</t>
         </is>
       </c>
-      <c r="E7" s="11" t="inlineStr">
+      <c r="E7" s="12" t="inlineStr">
         <is>
           <t>STATUS</t>
         </is>
       </c>
-      <c r="F7" s="18" t="inlineStr">
-        <is>
-          <t>HOW IT RUNS</t>
-        </is>
-      </c>
-      <c r="G7" s="11" t="inlineStr">
+      <c r="F7" s="12" t="inlineStr">
+        <is>
+          <t>HOW IT'S DONE</t>
+        </is>
+      </c>
+      <c r="G7" s="12" t="inlineStr">
         <is>
           <t>NOTES</t>
         </is>
       </c>
     </row>
     <row r="8" ht="18" customHeight="1">
-      <c r="B8" s="19" t="inlineStr">
+      <c r="B8" s="17" t="inlineStr">
         <is>
           <t>Capacity Management</t>
         </is>
       </c>
     </row>
     <row r="9" ht="54" customHeight="1">
-      <c r="B9" s="12" t="n">
+      <c r="B9" s="13" t="n">
         <v>1</v>
       </c>
-      <c r="C9" s="13" t="inlineStr">
+      <c r="C9" s="14" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -8311,20 +8221,16 @@
           </r>
         </is>
       </c>
-      <c r="D9" s="8" t="n"/>
-      <c r="E9" s="8" t="n"/>
-      <c r="F9" s="20" t="inlineStr">
-        <is>
-          <t>n/a</t>
-        </is>
-      </c>
-      <c r="G9" s="8" t="n"/>
+      <c r="D9" s="18" t="n"/>
+      <c r="E9" s="18" t="n"/>
+      <c r="F9" s="18" t="n"/>
+      <c r="G9" s="18" t="n"/>
     </row>
     <row r="10" ht="39" customHeight="1">
-      <c r="B10" s="12" t="n">
+      <c r="B10" s="13" t="n">
         <v>2</v>
       </c>
-      <c r="C10" s="13" t="inlineStr">
+      <c r="C10" s="14" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -8346,20 +8252,16 @@
           </r>
         </is>
       </c>
-      <c r="D10" s="8" t="n"/>
-      <c r="E10" s="8" t="n"/>
-      <c r="F10" s="20" t="inlineStr">
-        <is>
-          <t>n/a</t>
-        </is>
-      </c>
-      <c r="G10" s="8" t="n"/>
+      <c r="D10" s="18" t="n"/>
+      <c r="E10" s="18" t="n"/>
+      <c r="F10" s="18" t="n"/>
+      <c r="G10" s="18" t="n"/>
     </row>
     <row r="11" ht="54" customHeight="1">
-      <c r="B11" s="12" t="n">
+      <c r="B11" s="13" t="n">
         <v>3</v>
       </c>
-      <c r="C11" s="13" t="inlineStr">
+      <c r="C11" s="14" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -8381,20 +8283,16 @@
           </r>
         </is>
       </c>
-      <c r="D11" s="8" t="n"/>
-      <c r="E11" s="8" t="n"/>
-      <c r="F11" s="20" t="inlineStr">
-        <is>
-          <t>n/a</t>
-        </is>
-      </c>
-      <c r="G11" s="8" t="n"/>
+      <c r="D11" s="18" t="n"/>
+      <c r="E11" s="18" t="n"/>
+      <c r="F11" s="18" t="n"/>
+      <c r="G11" s="18" t="n"/>
     </row>
     <row r="12" ht="54" customHeight="1">
-      <c r="B12" s="12" t="n">
+      <c r="B12" s="13" t="n">
         <v>4</v>
       </c>
-      <c r="C12" s="13" t="inlineStr">
+      <c r="C12" s="14" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -8416,20 +8314,16 @@
           </r>
         </is>
       </c>
-      <c r="D12" s="8" t="n"/>
-      <c r="E12" s="8" t="n"/>
-      <c r="F12" s="20" t="inlineStr">
-        <is>
-          <t>n/a</t>
-        </is>
-      </c>
-      <c r="G12" s="8" t="n"/>
+      <c r="D12" s="18" t="n"/>
+      <c r="E12" s="18" t="n"/>
+      <c r="F12" s="18" t="n"/>
+      <c r="G12" s="18" t="n"/>
     </row>
     <row r="13" ht="54" customHeight="1">
-      <c r="B13" s="12" t="n">
+      <c r="B13" s="13" t="n">
         <v>5</v>
       </c>
-      <c r="C13" s="13" t="inlineStr">
+      <c r="C13" s="14" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -8451,20 +8345,16 @@
           </r>
         </is>
       </c>
-      <c r="D13" s="8" t="n"/>
-      <c r="E13" s="8" t="n"/>
-      <c r="F13" s="20" t="inlineStr">
-        <is>
-          <t>n/a</t>
-        </is>
-      </c>
-      <c r="G13" s="8" t="n"/>
+      <c r="D13" s="18" t="n"/>
+      <c r="E13" s="18" t="n"/>
+      <c r="F13" s="18" t="n"/>
+      <c r="G13" s="18" t="n"/>
     </row>
     <row r="14" ht="54" customHeight="1">
-      <c r="B14" s="12" t="n">
+      <c r="B14" s="13" t="n">
         <v>6</v>
       </c>
-      <c r="C14" s="13" t="inlineStr">
+      <c r="C14" s="14" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -8486,20 +8376,16 @@
           </r>
         </is>
       </c>
-      <c r="D14" s="8" t="n"/>
-      <c r="E14" s="8" t="n"/>
-      <c r="F14" s="20" t="inlineStr">
-        <is>
-          <t>n/a</t>
-        </is>
-      </c>
-      <c r="G14" s="8" t="n"/>
+      <c r="D14" s="18" t="n"/>
+      <c r="E14" s="18" t="n"/>
+      <c r="F14" s="18" t="n"/>
+      <c r="G14" s="18" t="n"/>
     </row>
     <row r="15" ht="54" customHeight="1">
-      <c r="B15" s="12" t="n">
+      <c r="B15" s="13" t="n">
         <v>7</v>
       </c>
-      <c r="C15" s="13" t="inlineStr">
+      <c r="C15" s="14" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -8521,20 +8407,16 @@
           </r>
         </is>
       </c>
-      <c r="D15" s="8" t="n"/>
-      <c r="E15" s="8" t="n"/>
-      <c r="F15" s="20" t="inlineStr">
-        <is>
-          <t>n/a</t>
-        </is>
-      </c>
-      <c r="G15" s="8" t="n"/>
+      <c r="D15" s="18" t="n"/>
+      <c r="E15" s="18" t="n"/>
+      <c r="F15" s="18" t="n"/>
+      <c r="G15" s="18" t="n"/>
     </row>
     <row r="16" ht="54" customHeight="1">
-      <c r="B16" s="12" t="n">
+      <c r="B16" s="13" t="n">
         <v>8</v>
       </c>
-      <c r="C16" s="13" t="inlineStr">
+      <c r="C16" s="14" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -8556,20 +8438,16 @@
           </r>
         </is>
       </c>
-      <c r="D16" s="8" t="n"/>
-      <c r="E16" s="8" t="n"/>
-      <c r="F16" s="20" t="inlineStr">
-        <is>
-          <t>n/a</t>
-        </is>
-      </c>
-      <c r="G16" s="8" t="n"/>
+      <c r="D16" s="18" t="n"/>
+      <c r="E16" s="18" t="n"/>
+      <c r="F16" s="18" t="n"/>
+      <c r="G16" s="18" t="n"/>
     </row>
     <row r="17" ht="54" customHeight="1">
-      <c r="B17" s="12" t="n">
+      <c r="B17" s="13" t="n">
         <v>9</v>
       </c>
-      <c r="C17" s="13" t="inlineStr">
+      <c r="C17" s="14" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -8591,20 +8469,16 @@
           </r>
         </is>
       </c>
-      <c r="D17" s="8" t="n"/>
-      <c r="E17" s="8" t="n"/>
-      <c r="F17" s="20" t="inlineStr">
-        <is>
-          <t>n/a</t>
-        </is>
-      </c>
-      <c r="G17" s="8" t="n"/>
+      <c r="D17" s="18" t="n"/>
+      <c r="E17" s="18" t="n"/>
+      <c r="F17" s="18" t="n"/>
+      <c r="G17" s="18" t="n"/>
     </row>
     <row r="18" ht="54" customHeight="1">
-      <c r="B18" s="12" t="n">
+      <c r="B18" s="13" t="n">
         <v>10</v>
       </c>
-      <c r="C18" s="13" t="inlineStr">
+      <c r="C18" s="14" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -8626,20 +8500,16 @@
           </r>
         </is>
       </c>
-      <c r="D18" s="8" t="n"/>
-      <c r="E18" s="8" t="n"/>
-      <c r="F18" s="20" t="inlineStr">
-        <is>
-          <t>n/a</t>
-        </is>
-      </c>
-      <c r="G18" s="8" t="n"/>
+      <c r="D18" s="18" t="n"/>
+      <c r="E18" s="18" t="n"/>
+      <c r="F18" s="18" t="n"/>
+      <c r="G18" s="18" t="n"/>
     </row>
     <row r="19" ht="54" customHeight="1">
-      <c r="B19" s="12" t="n">
+      <c r="B19" s="13" t="n">
         <v>11</v>
       </c>
-      <c r="C19" s="13" t="inlineStr">
+      <c r="C19" s="14" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -8661,20 +8531,16 @@
           </r>
         </is>
       </c>
-      <c r="D19" s="8" t="n"/>
-      <c r="E19" s="8" t="n"/>
-      <c r="F19" s="20" t="inlineStr">
-        <is>
-          <t>n/a</t>
-        </is>
-      </c>
-      <c r="G19" s="8" t="n"/>
+      <c r="D19" s="18" t="n"/>
+      <c r="E19" s="18" t="n"/>
+      <c r="F19" s="18" t="n"/>
+      <c r="G19" s="18" t="n"/>
     </row>
     <row r="20" ht="39" customHeight="1">
-      <c r="B20" s="12" t="n">
+      <c r="B20" s="13" t="n">
         <v>12</v>
       </c>
-      <c r="C20" s="13" t="inlineStr">
+      <c r="C20" s="14" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -8696,20 +8562,16 @@
           </r>
         </is>
       </c>
-      <c r="D20" s="8" t="n"/>
-      <c r="E20" s="8" t="n"/>
-      <c r="F20" s="20" t="inlineStr">
-        <is>
-          <t>n/a</t>
-        </is>
-      </c>
-      <c r="G20" s="8" t="n"/>
+      <c r="D20" s="18" t="n"/>
+      <c r="E20" s="18" t="n"/>
+      <c r="F20" s="18" t="n"/>
+      <c r="G20" s="18" t="n"/>
     </row>
     <row r="21" ht="54" customHeight="1">
-      <c r="B21" s="12" t="n">
+      <c r="B21" s="13" t="n">
         <v>13</v>
       </c>
-      <c r="C21" s="13" t="inlineStr">
+      <c r="C21" s="14" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -8731,20 +8593,16 @@
           </r>
         </is>
       </c>
-      <c r="D21" s="8" t="n"/>
-      <c r="E21" s="8" t="n"/>
-      <c r="F21" s="20" t="inlineStr">
-        <is>
-          <t>n/a</t>
-        </is>
-      </c>
-      <c r="G21" s="8" t="n"/>
+      <c r="D21" s="18" t="n"/>
+      <c r="E21" s="18" t="n"/>
+      <c r="F21" s="18" t="n"/>
+      <c r="G21" s="18" t="n"/>
     </row>
     <row r="22" ht="54" customHeight="1">
-      <c r="B22" s="12" t="n">
+      <c r="B22" s="13" t="n">
         <v>14</v>
       </c>
-      <c r="C22" s="13" t="inlineStr">
+      <c r="C22" s="14" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -8766,27 +8624,23 @@
           </r>
         </is>
       </c>
-      <c r="D22" s="8" t="n"/>
-      <c r="E22" s="8" t="n"/>
-      <c r="F22" s="20" t="inlineStr">
-        <is>
-          <t>n/a</t>
-        </is>
-      </c>
-      <c r="G22" s="8" t="n"/>
+      <c r="D22" s="18" t="n"/>
+      <c r="E22" s="18" t="n"/>
+      <c r="F22" s="18" t="n"/>
+      <c r="G22" s="18" t="n"/>
     </row>
     <row r="23" ht="18" customHeight="1">
-      <c r="B23" s="19" t="inlineStr">
+      <c r="B23" s="17" t="inlineStr">
         <is>
           <t>Scheduling Engine</t>
         </is>
       </c>
     </row>
     <row r="24" ht="54" customHeight="1">
-      <c r="B24" s="12" t="n">
+      <c r="B24" s="13" t="n">
         <v>15</v>
       </c>
-      <c r="C24" s="13" t="inlineStr">
+      <c r="C24" s="14" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -8808,16 +8662,16 @@
           </r>
         </is>
       </c>
-      <c r="D24" s="8" t="n"/>
-      <c r="E24" s="8" t="n"/>
-      <c r="F24" s="8" t="n"/>
-      <c r="G24" s="8" t="n"/>
+      <c r="D24" s="18" t="n"/>
+      <c r="E24" s="18" t="n"/>
+      <c r="F24" s="18" t="n"/>
+      <c r="G24" s="18" t="n"/>
     </row>
     <row r="25" ht="54" customHeight="1">
-      <c r="B25" s="12" t="n">
+      <c r="B25" s="13" t="n">
         <v>16</v>
       </c>
-      <c r="C25" s="13" t="inlineStr">
+      <c r="C25" s="14" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -8839,16 +8693,16 @@
           </r>
         </is>
       </c>
-      <c r="D25" s="8" t="n"/>
-      <c r="E25" s="8" t="n"/>
-      <c r="F25" s="8" t="n"/>
-      <c r="G25" s="8" t="n"/>
+      <c r="D25" s="18" t="n"/>
+      <c r="E25" s="18" t="n"/>
+      <c r="F25" s="18" t="n"/>
+      <c r="G25" s="18" t="n"/>
     </row>
     <row r="26" ht="54" customHeight="1">
-      <c r="B26" s="12" t="n">
+      <c r="B26" s="13" t="n">
         <v>17</v>
       </c>
-      <c r="C26" s="13" t="inlineStr">
+      <c r="C26" s="14" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -8870,16 +8724,16 @@
           </r>
         </is>
       </c>
-      <c r="D26" s="8" t="n"/>
-      <c r="E26" s="8" t="n"/>
-      <c r="F26" s="8" t="n"/>
-      <c r="G26" s="8" t="n"/>
+      <c r="D26" s="18" t="n"/>
+      <c r="E26" s="18" t="n"/>
+      <c r="F26" s="18" t="n"/>
+      <c r="G26" s="18" t="n"/>
     </row>
     <row r="27" ht="54" customHeight="1">
-      <c r="B27" s="12" t="n">
+      <c r="B27" s="13" t="n">
         <v>18</v>
       </c>
-      <c r="C27" s="13" t="inlineStr">
+      <c r="C27" s="14" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -8901,16 +8755,16 @@
           </r>
         </is>
       </c>
-      <c r="D27" s="8" t="n"/>
-      <c r="E27" s="8" t="n"/>
-      <c r="F27" s="8" t="n"/>
-      <c r="G27" s="8" t="n"/>
+      <c r="D27" s="18" t="n"/>
+      <c r="E27" s="18" t="n"/>
+      <c r="F27" s="18" t="n"/>
+      <c r="G27" s="18" t="n"/>
     </row>
     <row r="28" ht="39" customHeight="1">
-      <c r="B28" s="12" t="n">
+      <c r="B28" s="13" t="n">
         <v>19</v>
       </c>
-      <c r="C28" s="13" t="inlineStr">
+      <c r="C28" s="14" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -8932,16 +8786,16 @@
           </r>
         </is>
       </c>
-      <c r="D28" s="8" t="n"/>
-      <c r="E28" s="8" t="n"/>
-      <c r="F28" s="8" t="n"/>
-      <c r="G28" s="8" t="n"/>
+      <c r="D28" s="18" t="n"/>
+      <c r="E28" s="18" t="n"/>
+      <c r="F28" s="18" t="n"/>
+      <c r="G28" s="18" t="n"/>
     </row>
     <row r="29" ht="54" customHeight="1">
-      <c r="B29" s="12" t="n">
+      <c r="B29" s="13" t="n">
         <v>20</v>
       </c>
-      <c r="C29" s="13" t="inlineStr">
+      <c r="C29" s="14" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -8963,16 +8817,16 @@
           </r>
         </is>
       </c>
-      <c r="D29" s="8" t="n"/>
-      <c r="E29" s="8" t="n"/>
-      <c r="F29" s="8" t="n"/>
-      <c r="G29" s="8" t="n"/>
+      <c r="D29" s="18" t="n"/>
+      <c r="E29" s="18" t="n"/>
+      <c r="F29" s="18" t="n"/>
+      <c r="G29" s="18" t="n"/>
     </row>
     <row r="30" ht="54" customHeight="1">
-      <c r="B30" s="12" t="n">
+      <c r="B30" s="13" t="n">
         <v>21</v>
       </c>
-      <c r="C30" s="13" t="inlineStr">
+      <c r="C30" s="14" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -8994,16 +8848,16 @@
           </r>
         </is>
       </c>
-      <c r="D30" s="8" t="n"/>
-      <c r="E30" s="8" t="n"/>
-      <c r="F30" s="8" t="n"/>
-      <c r="G30" s="8" t="n"/>
+      <c r="D30" s="18" t="n"/>
+      <c r="E30" s="18" t="n"/>
+      <c r="F30" s="18" t="n"/>
+      <c r="G30" s="18" t="n"/>
     </row>
     <row r="31" ht="39" customHeight="1">
-      <c r="B31" s="12" t="n">
+      <c r="B31" s="13" t="n">
         <v>22</v>
       </c>
-      <c r="C31" s="13" t="inlineStr">
+      <c r="C31" s="14" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -9025,16 +8879,16 @@
           </r>
         </is>
       </c>
-      <c r="D31" s="8" t="n"/>
-      <c r="E31" s="8" t="n"/>
-      <c r="F31" s="8" t="n"/>
-      <c r="G31" s="8" t="n"/>
+      <c r="D31" s="18" t="n"/>
+      <c r="E31" s="18" t="n"/>
+      <c r="F31" s="18" t="n"/>
+      <c r="G31" s="18" t="n"/>
     </row>
     <row r="32" ht="54" customHeight="1">
-      <c r="B32" s="12" t="n">
+      <c r="B32" s="13" t="n">
         <v>23</v>
       </c>
-      <c r="C32" s="13" t="inlineStr">
+      <c r="C32" s="14" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -9056,16 +8910,16 @@
           </r>
         </is>
       </c>
-      <c r="D32" s="8" t="n"/>
-      <c r="E32" s="8" t="n"/>
-      <c r="F32" s="8" t="n"/>
-      <c r="G32" s="8" t="n"/>
+      <c r="D32" s="18" t="n"/>
+      <c r="E32" s="18" t="n"/>
+      <c r="F32" s="18" t="n"/>
+      <c r="G32" s="18" t="n"/>
     </row>
     <row r="33" ht="54" customHeight="1">
-      <c r="B33" s="12" t="n">
+      <c r="B33" s="13" t="n">
         <v>24</v>
       </c>
-      <c r="C33" s="13" t="inlineStr">
+      <c r="C33" s="14" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -9087,16 +8941,16 @@
           </r>
         </is>
       </c>
-      <c r="D33" s="8" t="n"/>
-      <c r="E33" s="8" t="n"/>
-      <c r="F33" s="8" t="n"/>
-      <c r="G33" s="8" t="n"/>
+      <c r="D33" s="18" t="n"/>
+      <c r="E33" s="18" t="n"/>
+      <c r="F33" s="18" t="n"/>
+      <c r="G33" s="18" t="n"/>
     </row>
     <row r="34" ht="54" customHeight="1">
-      <c r="B34" s="12" t="n">
+      <c r="B34" s="13" t="n">
         <v>25</v>
       </c>
-      <c r="C34" s="13" t="inlineStr">
+      <c r="C34" s="14" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -9118,16 +8972,16 @@
           </r>
         </is>
       </c>
-      <c r="D34" s="8" t="n"/>
-      <c r="E34" s="8" t="n"/>
-      <c r="F34" s="8" t="n"/>
-      <c r="G34" s="8" t="n"/>
+      <c r="D34" s="18" t="n"/>
+      <c r="E34" s="18" t="n"/>
+      <c r="F34" s="18" t="n"/>
+      <c r="G34" s="18" t="n"/>
     </row>
     <row r="35" ht="54" customHeight="1">
-      <c r="B35" s="12" t="n">
+      <c r="B35" s="13" t="n">
         <v>26</v>
       </c>
-      <c r="C35" s="13" t="inlineStr">
+      <c r="C35" s="14" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -9149,16 +9003,16 @@
           </r>
         </is>
       </c>
-      <c r="D35" s="8" t="n"/>
-      <c r="E35" s="8" t="n"/>
-      <c r="F35" s="8" t="n"/>
-      <c r="G35" s="8" t="n"/>
+      <c r="D35" s="18" t="n"/>
+      <c r="E35" s="18" t="n"/>
+      <c r="F35" s="18" t="n"/>
+      <c r="G35" s="18" t="n"/>
     </row>
     <row r="36" ht="54" customHeight="1">
-      <c r="B36" s="12" t="n">
+      <c r="B36" s="13" t="n">
         <v>27</v>
       </c>
-      <c r="C36" s="13" t="inlineStr">
+      <c r="C36" s="14" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -9180,16 +9034,16 @@
           </r>
         </is>
       </c>
-      <c r="D36" s="8" t="n"/>
-      <c r="E36" s="8" t="n"/>
-      <c r="F36" s="8" t="n"/>
-      <c r="G36" s="8" t="n"/>
+      <c r="D36" s="18" t="n"/>
+      <c r="E36" s="18" t="n"/>
+      <c r="F36" s="18" t="n"/>
+      <c r="G36" s="18" t="n"/>
     </row>
     <row r="37" ht="54" customHeight="1">
-      <c r="B37" s="12" t="n">
+      <c r="B37" s="13" t="n">
         <v>28</v>
       </c>
-      <c r="C37" s="13" t="inlineStr">
+      <c r="C37" s="14" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -9211,16 +9065,16 @@
           </r>
         </is>
       </c>
-      <c r="D37" s="8" t="n"/>
-      <c r="E37" s="8" t="n"/>
-      <c r="F37" s="8" t="n"/>
-      <c r="G37" s="8" t="n"/>
+      <c r="D37" s="18" t="n"/>
+      <c r="E37" s="18" t="n"/>
+      <c r="F37" s="18" t="n"/>
+      <c r="G37" s="18" t="n"/>
     </row>
     <row r="38" ht="54" customHeight="1">
-      <c r="B38" s="12" t="n">
+      <c r="B38" s="13" t="n">
         <v>29</v>
       </c>
-      <c r="C38" s="13" t="inlineStr">
+      <c r="C38" s="14" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -9242,23 +9096,23 @@
           </r>
         </is>
       </c>
-      <c r="D38" s="8" t="n"/>
-      <c r="E38" s="8" t="n"/>
-      <c r="F38" s="8" t="n"/>
-      <c r="G38" s="8" t="n"/>
+      <c r="D38" s="18" t="n"/>
+      <c r="E38" s="18" t="n"/>
+      <c r="F38" s="18" t="n"/>
+      <c r="G38" s="18" t="n"/>
     </row>
     <row r="39" ht="18" customHeight="1">
-      <c r="B39" s="19" t="inlineStr">
+      <c r="B39" s="17" t="inlineStr">
         <is>
           <t>Engagement</t>
         </is>
       </c>
     </row>
     <row r="40" ht="54" customHeight="1">
-      <c r="B40" s="12" t="n">
+      <c r="B40" s="13" t="n">
         <v>30</v>
       </c>
-      <c r="C40" s="13" t="inlineStr">
+      <c r="C40" s="14" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -9280,16 +9134,16 @@
           </r>
         </is>
       </c>
-      <c r="D40" s="8" t="n"/>
-      <c r="E40" s="8" t="n"/>
-      <c r="F40" s="8" t="n"/>
-      <c r="G40" s="8" t="n"/>
+      <c r="D40" s="18" t="n"/>
+      <c r="E40" s="18" t="n"/>
+      <c r="F40" s="18" t="n"/>
+      <c r="G40" s="18" t="n"/>
     </row>
     <row r="41" ht="54" customHeight="1">
-      <c r="B41" s="12" t="n">
+      <c r="B41" s="13" t="n">
         <v>31</v>
       </c>
-      <c r="C41" s="13" t="inlineStr">
+      <c r="C41" s="14" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -9311,16 +9165,16 @@
           </r>
         </is>
       </c>
-      <c r="D41" s="8" t="n"/>
-      <c r="E41" s="8" t="n"/>
-      <c r="F41" s="8" t="n"/>
-      <c r="G41" s="8" t="n"/>
+      <c r="D41" s="18" t="n"/>
+      <c r="E41" s="18" t="n"/>
+      <c r="F41" s="18" t="n"/>
+      <c r="G41" s="18" t="n"/>
     </row>
     <row r="42" ht="54" customHeight="1">
-      <c r="B42" s="12" t="n">
+      <c r="B42" s="13" t="n">
         <v>32</v>
       </c>
-      <c r="C42" s="13" t="inlineStr">
+      <c r="C42" s="14" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -9342,16 +9196,16 @@
           </r>
         </is>
       </c>
-      <c r="D42" s="8" t="n"/>
-      <c r="E42" s="8" t="n"/>
-      <c r="F42" s="8" t="n"/>
-      <c r="G42" s="8" t="n"/>
+      <c r="D42" s="18" t="n"/>
+      <c r="E42" s="18" t="n"/>
+      <c r="F42" s="18" t="n"/>
+      <c r="G42" s="18" t="n"/>
     </row>
     <row r="43" ht="39" customHeight="1">
-      <c r="B43" s="12" t="n">
+      <c r="B43" s="13" t="n">
         <v>33</v>
       </c>
-      <c r="C43" s="13" t="inlineStr">
+      <c r="C43" s="14" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -9373,16 +9227,16 @@
           </r>
         </is>
       </c>
-      <c r="D43" s="8" t="n"/>
-      <c r="E43" s="8" t="n"/>
-      <c r="F43" s="8" t="n"/>
-      <c r="G43" s="8" t="n"/>
+      <c r="D43" s="18" t="n"/>
+      <c r="E43" s="18" t="n"/>
+      <c r="F43" s="18" t="n"/>
+      <c r="G43" s="18" t="n"/>
     </row>
     <row r="44" ht="54" customHeight="1">
-      <c r="B44" s="12" t="n">
+      <c r="B44" s="13" t="n">
         <v>34</v>
       </c>
-      <c r="C44" s="13" t="inlineStr">
+      <c r="C44" s="14" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -9404,16 +9258,16 @@
           </r>
         </is>
       </c>
-      <c r="D44" s="8" t="n"/>
-      <c r="E44" s="8" t="n"/>
-      <c r="F44" s="8" t="n"/>
-      <c r="G44" s="8" t="n"/>
+      <c r="D44" s="18" t="n"/>
+      <c r="E44" s="18" t="n"/>
+      <c r="F44" s="18" t="n"/>
+      <c r="G44" s="18" t="n"/>
     </row>
     <row r="45" ht="39" customHeight="1">
-      <c r="B45" s="12" t="n">
+      <c r="B45" s="13" t="n">
         <v>35</v>
       </c>
-      <c r="C45" s="13" t="inlineStr">
+      <c r="C45" s="14" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -9435,16 +9289,16 @@
           </r>
         </is>
       </c>
-      <c r="D45" s="8" t="n"/>
-      <c r="E45" s="8" t="n"/>
-      <c r="F45" s="8" t="n"/>
-      <c r="G45" s="8" t="n"/>
+      <c r="D45" s="18" t="n"/>
+      <c r="E45" s="18" t="n"/>
+      <c r="F45" s="18" t="n"/>
+      <c r="G45" s="18" t="n"/>
     </row>
     <row r="46" ht="54" customHeight="1">
-      <c r="B46" s="12" t="n">
+      <c r="B46" s="13" t="n">
         <v>36</v>
       </c>
-      <c r="C46" s="13" t="inlineStr">
+      <c r="C46" s="14" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -9466,16 +9320,16 @@
           </r>
         </is>
       </c>
-      <c r="D46" s="8" t="n"/>
-      <c r="E46" s="8" t="n"/>
-      <c r="F46" s="8" t="n"/>
-      <c r="G46" s="8" t="n"/>
+      <c r="D46" s="18" t="n"/>
+      <c r="E46" s="18" t="n"/>
+      <c r="F46" s="18" t="n"/>
+      <c r="G46" s="18" t="n"/>
     </row>
     <row r="47" ht="54" customHeight="1">
-      <c r="B47" s="12" t="n">
+      <c r="B47" s="13" t="n">
         <v>37</v>
       </c>
-      <c r="C47" s="13" t="inlineStr">
+      <c r="C47" s="14" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -9497,16 +9351,16 @@
           </r>
         </is>
       </c>
-      <c r="D47" s="8" t="n"/>
-      <c r="E47" s="8" t="n"/>
-      <c r="F47" s="8" t="n"/>
-      <c r="G47" s="8" t="n"/>
+      <c r="D47" s="18" t="n"/>
+      <c r="E47" s="18" t="n"/>
+      <c r="F47" s="18" t="n"/>
+      <c r="G47" s="18" t="n"/>
     </row>
     <row r="48" ht="39" customHeight="1">
-      <c r="B48" s="12" t="n">
+      <c r="B48" s="13" t="n">
         <v>38</v>
       </c>
-      <c r="C48" s="13" t="inlineStr">
+      <c r="C48" s="14" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -9528,16 +9382,16 @@
           </r>
         </is>
       </c>
-      <c r="D48" s="8" t="n"/>
-      <c r="E48" s="8" t="n"/>
-      <c r="F48" s="8" t="n"/>
-      <c r="G48" s="8" t="n"/>
+      <c r="D48" s="18" t="n"/>
+      <c r="E48" s="18" t="n"/>
+      <c r="F48" s="18" t="n"/>
+      <c r="G48" s="18" t="n"/>
     </row>
     <row r="49" ht="54" customHeight="1">
-      <c r="B49" s="12" t="n">
+      <c r="B49" s="13" t="n">
         <v>39</v>
       </c>
-      <c r="C49" s="13" t="inlineStr">
+      <c r="C49" s="14" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -9559,16 +9413,16 @@
           </r>
         </is>
       </c>
-      <c r="D49" s="8" t="n"/>
-      <c r="E49" s="8" t="n"/>
-      <c r="F49" s="8" t="n"/>
-      <c r="G49" s="8" t="n"/>
+      <c r="D49" s="18" t="n"/>
+      <c r="E49" s="18" t="n"/>
+      <c r="F49" s="18" t="n"/>
+      <c r="G49" s="18" t="n"/>
     </row>
     <row r="50" ht="54" customHeight="1">
-      <c r="B50" s="12" t="n">
+      <c r="B50" s="13" t="n">
         <v>40</v>
       </c>
-      <c r="C50" s="13" t="inlineStr">
+      <c r="C50" s="14" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -9590,16 +9444,16 @@
           </r>
         </is>
       </c>
-      <c r="D50" s="8" t="n"/>
-      <c r="E50" s="8" t="n"/>
-      <c r="F50" s="8" t="n"/>
-      <c r="G50" s="8" t="n"/>
+      <c r="D50" s="18" t="n"/>
+      <c r="E50" s="18" t="n"/>
+      <c r="F50" s="18" t="n"/>
+      <c r="G50" s="18" t="n"/>
     </row>
     <row r="51" ht="39" customHeight="1">
-      <c r="B51" s="12" t="n">
+      <c r="B51" s="13" t="n">
         <v>41</v>
       </c>
-      <c r="C51" s="13" t="inlineStr">
+      <c r="C51" s="14" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -9621,10 +9475,10 @@
           </r>
         </is>
       </c>
-      <c r="D51" s="8" t="n"/>
-      <c r="E51" s="8" t="n"/>
-      <c r="F51" s="8" t="n"/>
-      <c r="G51" s="8" t="n"/>
+      <c r="D51" s="18" t="n"/>
+      <c r="E51" s="18" t="n"/>
+      <c r="F51" s="18" t="n"/>
+      <c r="G51" s="18" t="n"/>
     </row>
   </sheetData>
   <mergeCells count="7">
@@ -9636,14 +9490,17 @@
     <mergeCell ref="B39:G39"/>
     <mergeCell ref="B6:G6"/>
   </mergeCells>
-  <dataValidations count="3">
-    <dataValidation sqref="D9 D10 D11 D12 D13 D14 D15 D16 D17 D18 D19 D20 D21 D22 D24 D25 D26 D27 D28 D29 D30 D31 D32 D33 D34 D35 D36 D37 D38 D40 D41 D42 D43 D44 D45 D46 D47 D48 D49 D50 D51" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" errorTitle="Pick from the list" error="Yes  ·  Through a partner  ·  No" promptTitle="Do you do this at all?" prompt="Yes  ·  Through a partner  ·  No" type="list">
+  <dataValidations count="4">
+    <dataValidation sqref="D9 D10 D11 D12 D13 D14 D15 D16 D17 D18 D19 D20 D21 D22 D24 D25 D26 D27 D28 D29 D30 D31 D32 D33 D34 D35 D36 D37 D38 D40 D41 D42 D43 D44 D45 D46 D47 D48 D49 D50 D51" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" errorTitle="Pick from the list" error="Yes  ·  Through a partner  ·  No  ·  Other" promptTitle="Do you do this at all?" prompt="Yes  ·  Through a partner  ·  No  ·  Other" type="list">
       <formula1>InScopeList</formula1>
     </dataValidation>
-    <dataValidation sqref="E9 E10 E11 E12 E13 E14 E15 E16 E17 E18 E19 E20 E21 E22 E24 E25 E26 E27 E28 E29 E30 E31 E32 E33 E34 E35 E36 E37 E38 E40 E41 E42 E43 E44 E45 E46 E47 E48 E49 E50 E51" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" errorTitle="Pick from the list" error="Production (multiple / one customer)  ·  In development  ·  Roadmap" promptTitle="How far along is it?" prompt="Production (multiple / one customer)  ·  In development  ·  Roadmap" type="list">
+    <dataValidation sqref="E9 E10 E11 E12 E13 E14 E15 E16 E17 E18 E19 E20 E21 E22 E24 E25 E26 E27 E28 E29 E30 E31 E32 E33 E34 E35 E36 E37 E38 E40 E41 E42 E43 E44 E45 E46 E47 E48 E49 E50 E51" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" errorTitle="Pick from the list" error="Production (multiple / one customer)  ·  In development  ·  Roadmap  ·  Other" promptTitle="How far along is it?" prompt="Production (multiple / one customer)  ·  In development  ·  Roadmap  ·  Other" type="list">
       <formula1>StatusList</formula1>
     </dataValidation>
-    <dataValidation sqref="F24 F25 F26 F27 F28 F29 F30 F31 F32 F33 F34 F35 F36 F37 F38 F40 F41 F42 F43 F44 F45 F46 F47 F48 F49 F50 F51" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" errorTitle="Pick from the list" error="Automated end to end  ·  Automated, person approves  ·  System prepares it  ·  Person does it" promptTitle="Does a person still do the work?" prompt="Automated end to end  ·  Automated, person approves  ·  System prepares it  ·  Person does it" type="list">
+    <dataValidation sqref="F9 F10 F11 F12 F13 F14 F15 F16 F17 F18 F19 F20 F21 F22" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" errorTitle="Pick from the list" error="Live feed  ·  Imported on a schedule  ·  Maintained by staff  ·  Entered by the clinician  ·  Derived from FT/PT  ·  Other" promptTitle="Where does this come from?" prompt="Live feed  ·  Imported on a schedule  ·  Maintained by staff  ·  Entered by the clinician  ·  Derived from FT/PT  ·  Other" type="list">
+      <formula1>CapacityInputList</formula1>
+    </dataValidation>
+    <dataValidation sqref="F24 F25 F26 F27 F28 F29 F30 F31 F32 F33 F34 F35 F36 F37 F38 F40 F41 F42 F43 F44 F45 F46 F47 F48 F49 F50 F51" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" errorTitle="Pick from the list" error="Automated end to end  ·  Automated, person approves  ·  System prepares it  ·  Person does it  ·  Other" promptTitle="Does a person still do the work?" prompt="Automated end to end  ·  Automated, person approves  ·  System prepares it  ·  Person does it  ·  Other" type="list">
       <formula1>DeliveryList</formula1>
     </dataValidation>
   </dataValidations>
@@ -9696,14 +9553,14 @@
       </c>
     </row>
     <row r="5" ht="22" customHeight="1">
-      <c r="B5" s="10" t="inlineStr">
+      <c r="B5" s="11" t="inlineStr">
         <is>
           <t>CAPACITY</t>
         </is>
       </c>
     </row>
     <row r="6" ht="23" customHeight="1">
-      <c r="B6" s="12" t="n">
+      <c r="B6" s="13" t="n">
         <v>1</v>
       </c>
       <c r="C6" s="4" t="inlineStr">
@@ -9713,7 +9570,7 @@
       </c>
     </row>
     <row r="7" ht="23" customHeight="1">
-      <c r="B7" s="12" t="n">
+      <c r="B7" s="13" t="n">
         <v>2</v>
       </c>
       <c r="C7" s="4" t="inlineStr">
@@ -9723,7 +9580,7 @@
       </c>
     </row>
     <row r="8" ht="23" customHeight="1">
-      <c r="B8" s="12" t="n">
+      <c r="B8" s="13" t="n">
         <v>3</v>
       </c>
       <c r="C8" s="4" t="inlineStr">
@@ -9733,7 +9590,7 @@
       </c>
     </row>
     <row r="9" ht="23" customHeight="1">
-      <c r="B9" s="12" t="n">
+      <c r="B9" s="13" t="n">
         <v>4</v>
       </c>
       <c r="C9" s="4" t="inlineStr">
@@ -9743,14 +9600,14 @@
       </c>
     </row>
     <row r="11" ht="22" customHeight="1">
-      <c r="B11" s="10" t="inlineStr">
+      <c r="B11" s="11" t="inlineStr">
         <is>
           <t>SCHEDULING</t>
         </is>
       </c>
     </row>
     <row r="12" ht="23" customHeight="1">
-      <c r="B12" s="12" t="n">
+      <c r="B12" s="13" t="n">
         <v>1</v>
       </c>
       <c r="C12" s="4" t="inlineStr">
@@ -9760,7 +9617,7 @@
       </c>
     </row>
     <row r="13" ht="23" customHeight="1">
-      <c r="B13" s="12" t="n">
+      <c r="B13" s="13" t="n">
         <v>2</v>
       </c>
       <c r="C13" s="4" t="inlineStr">
@@ -9770,7 +9627,7 @@
       </c>
     </row>
     <row r="14" ht="23" customHeight="1">
-      <c r="B14" s="12" t="n">
+      <c r="B14" s="13" t="n">
         <v>3</v>
       </c>
       <c r="C14" s="4" t="inlineStr">
@@ -9780,7 +9637,7 @@
       </c>
     </row>
     <row r="15" ht="23" customHeight="1">
-      <c r="B15" s="12" t="n">
+      <c r="B15" s="13" t="n">
         <v>4</v>
       </c>
       <c r="C15" s="4" t="inlineStr">
@@ -9790,14 +9647,14 @@
       </c>
     </row>
     <row r="17" ht="22" customHeight="1">
-      <c r="B17" s="10" t="inlineStr">
+      <c r="B17" s="11" t="inlineStr">
         <is>
           <t>ENGAGEMENT</t>
         </is>
       </c>
     </row>
     <row r="18" ht="23" customHeight="1">
-      <c r="B18" s="12" t="n">
+      <c r="B18" s="13" t="n">
         <v>1</v>
       </c>
       <c r="C18" s="4" t="inlineStr">
@@ -9807,7 +9664,7 @@
       </c>
     </row>
     <row r="19" ht="23" customHeight="1">
-      <c r="B19" s="12" t="n">
+      <c r="B19" s="13" t="n">
         <v>2</v>
       </c>
       <c r="C19" s="4" t="inlineStr">
@@ -9817,7 +9674,7 @@
       </c>
     </row>
     <row r="20" ht="23" customHeight="1">
-      <c r="B20" s="12" t="n">
+      <c r="B20" s="13" t="n">
         <v>3</v>
       </c>
       <c r="C20" s="4" t="inlineStr">
@@ -9827,14 +9684,14 @@
       </c>
     </row>
     <row r="22" ht="22" customHeight="1">
-      <c r="B22" s="10" t="inlineStr">
+      <c r="B22" s="11" t="inlineStr">
         <is>
           <t>THE CLINICIAN</t>
         </is>
       </c>
     </row>
     <row r="23" ht="23" customHeight="1">
-      <c r="B23" s="12" t="n">
+      <c r="B23" s="13" t="n">
         <v>1</v>
       </c>
       <c r="C23" s="4" t="inlineStr">
@@ -9844,7 +9701,7 @@
       </c>
     </row>
     <row r="24" ht="23" customHeight="1">
-      <c r="B24" s="12" t="n">
+      <c r="B24" s="13" t="n">
         <v>2</v>
       </c>
       <c r="C24" s="4" t="inlineStr">
@@ -9854,7 +9711,7 @@
       </c>
     </row>
     <row r="25" ht="23" customHeight="1">
-      <c r="B25" s="12" t="n">
+      <c r="B25" s="13" t="n">
         <v>3</v>
       </c>
       <c r="C25" s="4" t="inlineStr">
@@ -9864,14 +9721,14 @@
       </c>
     </row>
     <row r="27" ht="22" customHeight="1">
-      <c r="B27" s="10" t="inlineStr">
+      <c r="B27" s="11" t="inlineStr">
         <is>
           <t>FIT</t>
         </is>
       </c>
     </row>
     <row r="28" ht="23" customHeight="1">
-      <c r="B28" s="12" t="n">
+      <c r="B28" s="13" t="n">
         <v>1</v>
       </c>
       <c r="C28" s="4" t="inlineStr">
@@ -9881,14 +9738,14 @@
       </c>
     </row>
     <row r="30" ht="22" customHeight="1">
-      <c r="B30" s="10" t="inlineStr">
+      <c r="B30" s="11" t="inlineStr">
         <is>
           <t>COMMERCIAL</t>
         </is>
       </c>
     </row>
     <row r="31" ht="37" customHeight="1">
-      <c r="B31" s="12" t="n">
+      <c r="B31" s="13" t="n">
         <v>1</v>
       </c>
       <c r="C31" s="4" t="inlineStr">
@@ -9898,7 +9755,7 @@
       </c>
     </row>
     <row r="32" ht="23" customHeight="1">
-      <c r="B32" s="12" t="n">
+      <c r="B32" s="13" t="n">
         <v>2</v>
       </c>
       <c r="C32" s="4" t="inlineStr">
@@ -9908,7 +9765,7 @@
       </c>
     </row>
     <row r="33" ht="23" customHeight="1">
-      <c r="B33" s="12" t="n">
+      <c r="B33" s="13" t="n">
         <v>3</v>
       </c>
       <c r="C33" s="4" t="inlineStr">
@@ -9918,14 +9775,14 @@
       </c>
     </row>
     <row r="35" ht="22" customHeight="1">
-      <c r="B35" s="10" t="inlineStr">
+      <c r="B35" s="11" t="inlineStr">
         <is>
           <t>NASHVILLE — DEEP DIVE</t>
         </is>
       </c>
     </row>
     <row r="36" ht="23" customHeight="1">
-      <c r="B36" s="12" t="n">
+      <c r="B36" s="13" t="n">
         <v>1</v>
       </c>
       <c r="C36" s="4" t="inlineStr">
@@ -9935,7 +9792,7 @@
       </c>
     </row>
     <row r="37" ht="37" customHeight="1">
-      <c r="B37" s="12" t="n">
+      <c r="B37" s="13" t="n">
         <v>2</v>
       </c>
       <c r="C37" s="4" t="inlineStr">
@@ -9945,7 +9802,7 @@
       </c>
     </row>
     <row r="38" ht="23" customHeight="1">
-      <c r="B38" s="12" t="n">
+      <c r="B38" s="13" t="n">
         <v>3</v>
       </c>
       <c r="C38" s="4" t="inlineStr">
@@ -9955,7 +9812,7 @@
       </c>
     </row>
     <row r="39" ht="23" customHeight="1">
-      <c r="B39" s="12" t="n">
+      <c r="B39" s="13" t="n">
         <v>4</v>
       </c>
       <c r="C39" s="4" t="inlineStr">
@@ -9965,7 +9822,7 @@
       </c>
     </row>
     <row r="40" ht="23" customHeight="1">
-      <c r="B40" s="12" t="n">
+      <c r="B40" s="13" t="n">
         <v>5</v>
       </c>
       <c r="C40" s="4" t="inlineStr">
@@ -9975,7 +9832,7 @@
       </c>
     </row>
     <row r="41" ht="23" customHeight="1">
-      <c r="B41" s="12" t="n">
+      <c r="B41" s="13" t="n">
         <v>6</v>
       </c>
       <c r="C41" s="4" t="inlineStr">
@@ -9985,7 +9842,7 @@
       </c>
     </row>
     <row r="42" ht="23" customHeight="1">
-      <c r="B42" s="12" t="n">
+      <c r="B42" s="13" t="n">
         <v>7</v>
       </c>
       <c r="C42" s="4" t="inlineStr">
@@ -10077,31 +9934,31 @@
       </c>
     </row>
     <row r="5" ht="22" customHeight="1">
-      <c r="B5" s="10" t="inlineStr">
+      <c r="B5" s="11" t="inlineStr">
         <is>
           <t>SET ASIDE FROM ROUND ONE</t>
         </is>
       </c>
     </row>
     <row r="6" ht="15" customHeight="1">
-      <c r="B6" s="11" t="inlineStr">
+      <c r="B6" s="12" t="inlineStr">
         <is>
           <t>TOPIC</t>
         </is>
       </c>
-      <c r="C6" s="11" t="inlineStr">
+      <c r="C6" s="12" t="inlineStr">
         <is>
           <t>QUESTION AS DRAFTED</t>
         </is>
       </c>
-      <c r="D6" s="11" t="inlineStr">
+      <c r="D6" s="12" t="inlineStr">
         <is>
           <t>WHY IT IS SET ASIDE</t>
         </is>
       </c>
     </row>
     <row r="7" ht="84" customHeight="1">
-      <c r="B7" s="66" t="inlineStr">
+      <c r="B7" s="60" t="inlineStr">
         <is>
           <t>Company maturity</t>
         </is>
@@ -10118,7 +9975,7 @@
       </c>
     </row>
     <row r="8" ht="39" customHeight="1">
-      <c r="B8" s="66" t="inlineStr">
+      <c r="B8" s="60" t="inlineStr">
         <is>
           <t>Security and compliance</t>
         </is>
@@ -10135,7 +9992,7 @@
       </c>
     </row>
     <row r="9" ht="39" customHeight="1">
-      <c r="B9" s="66" t="inlineStr">
+      <c r="B9" s="60" t="inlineStr">
         <is>
           <t>Implementation shape</t>
         </is>
@@ -10152,7 +10009,7 @@
       </c>
     </row>
     <row r="10" ht="39" customHeight="1">
-      <c r="B10" s="66" t="inlineStr">
+      <c r="B10" s="60" t="inlineStr">
         <is>
           <t>Insurance and contracting</t>
         </is>
@@ -10169,7 +10026,7 @@
       </c>
     </row>
     <row r="11" ht="39" customHeight="1">
-      <c r="B11" s="66" t="inlineStr">
+      <c r="B11" s="60" t="inlineStr">
         <is>
           <t>Product and engineering scale</t>
         </is>
@@ -10258,7 +10115,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>A1,A2,A3,C1,C2,C3,C4,C5,C6,C7,C8,D1,D2,D3,D4,D5,E1,E2,E3,E4,E5</t>
+          <t>A1,A2,A3,C1,C2,C3,C4,C5,C6,C7,D1,D2,D3,E1,E2,E3,E4</t>
         </is>
       </c>
     </row>
